--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="1526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="1525">
   <si>
     <t>图标</t>
   </si>
@@ -4399,9 +4399,6 @@
   </si>
   <si>
     <t>彩池图标4</t>
-  </si>
-  <si>
-    <t>透明图标</t>
   </si>
   <si>
     <t>图标1</t>
@@ -4924,12 +4921,12 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -6046,7 +6043,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N1191"/>
+  <dimension ref="A1:N1190"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -29532,57 +29529,55 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="938" s="2" customFormat="1" spans="1:9">
-      <c r="A938" s="57">
-        <v>10510024</v>
-      </c>
-      <c r="B938" s="57">
-        <v>105100</v>
-      </c>
-      <c r="C938" s="57">
-        <v>24</v>
-      </c>
-      <c r="D938" s="57">
-        <v>2</v>
-      </c>
-      <c r="E938" s="57"/>
-      <c r="F938" s="57"/>
-      <c r="G938" s="57"/>
-      <c r="H938" s="57"/>
-      <c r="I938" s="59" t="s">
-        <v>1428</v>
+    <row r="938" spans="1:9">
+      <c r="A938" s="60">
+        <v>10540001</v>
+      </c>
+      <c r="B938" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C938" s="60">
+        <v>1</v>
+      </c>
+      <c r="D938" s="60">
+        <v>0</v>
+      </c>
+      <c r="E938" s="60"/>
+      <c r="F938" s="60"/>
+      <c r="G938" s="60"/>
+      <c r="H938" s="60"/>
+      <c r="I938" s="61">
+        <v>10</v>
       </c>
     </row>
     <row r="939" spans="1:9">
       <c r="A939" s="60">
-        <v>10540001</v>
+        <v>10540002</v>
       </c>
       <c r="B939" s="60">
         <v>105400</v>
       </c>
       <c r="C939" s="60">
-        <v>1</v>
-      </c>
-      <c r="D939" s="60">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D939" s="60"/>
       <c r="E939" s="60"/>
       <c r="F939" s="60"/>
       <c r="G939" s="60"/>
       <c r="H939" s="60"/>
-      <c r="I939" s="61">
-        <v>10</v>
+      <c r="I939" s="60" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="940" spans="1:9">
       <c r="A940" s="60">
-        <v>10540002</v>
+        <v>10540003</v>
       </c>
       <c r="B940" s="60">
         <v>105400</v>
       </c>
       <c r="C940" s="60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D940" s="60"/>
       <c r="E940" s="60"/>
@@ -29590,18 +29585,18 @@
       <c r="G940" s="60"/>
       <c r="H940" s="60"/>
       <c r="I940" s="60" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="941" spans="1:9">
       <c r="A941" s="60">
-        <v>10540003</v>
+        <v>10540004</v>
       </c>
       <c r="B941" s="60">
         <v>105400</v>
       </c>
       <c r="C941" s="60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D941" s="60"/>
       <c r="E941" s="60"/>
@@ -29609,18 +29604,18 @@
       <c r="G941" s="60"/>
       <c r="H941" s="60"/>
       <c r="I941" s="60" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="942" spans="1:9">
       <c r="A942" s="60">
-        <v>10540004</v>
+        <v>10540005</v>
       </c>
       <c r="B942" s="60">
         <v>105400</v>
       </c>
       <c r="C942" s="60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D942" s="60"/>
       <c r="E942" s="60"/>
@@ -29628,18 +29623,18 @@
       <c r="G942" s="60"/>
       <c r="H942" s="60"/>
       <c r="I942" s="60" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="943" spans="1:9">
       <c r="A943" s="60">
-        <v>10540005</v>
+        <v>10540006</v>
       </c>
       <c r="B943" s="60">
         <v>105400</v>
       </c>
       <c r="C943" s="60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D943" s="60"/>
       <c r="E943" s="60"/>
@@ -29647,18 +29642,18 @@
       <c r="G943" s="60"/>
       <c r="H943" s="60"/>
       <c r="I943" s="60" t="s">
-        <v>27</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="944" spans="1:9">
       <c r="A944" s="60">
-        <v>10540006</v>
+        <v>10540007</v>
       </c>
       <c r="B944" s="60">
         <v>105400</v>
       </c>
       <c r="C944" s="60">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D944" s="60"/>
       <c r="E944" s="60"/>
@@ -29671,13 +29666,13 @@
     </row>
     <row r="945" spans="1:9">
       <c r="A945" s="60">
-        <v>10540007</v>
+        <v>10540008</v>
       </c>
       <c r="B945" s="60">
         <v>105400</v>
       </c>
       <c r="C945" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D945" s="60"/>
       <c r="E945" s="60"/>
@@ -29690,13 +29685,13 @@
     </row>
     <row r="946" spans="1:9">
       <c r="A946" s="60">
-        <v>10540008</v>
+        <v>10540009</v>
       </c>
       <c r="B946" s="60">
         <v>105400</v>
       </c>
       <c r="C946" s="60">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D946" s="60"/>
       <c r="E946" s="60"/>
@@ -29709,13 +29704,13 @@
     </row>
     <row r="947" spans="1:9">
       <c r="A947" s="60">
-        <v>10540009</v>
+        <v>10540010</v>
       </c>
       <c r="B947" s="60">
         <v>105400</v>
       </c>
       <c r="C947" s="60">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D947" s="60"/>
       <c r="E947" s="60"/>
@@ -29728,13 +29723,13 @@
     </row>
     <row r="948" spans="1:9">
       <c r="A948" s="60">
-        <v>10540010</v>
+        <v>10540011</v>
       </c>
       <c r="B948" s="60">
         <v>105400</v>
       </c>
       <c r="C948" s="60">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D948" s="60"/>
       <c r="E948" s="60"/>
@@ -29742,18 +29737,18 @@
       <c r="G948" s="60"/>
       <c r="H948" s="60"/>
       <c r="I948" s="60" t="s">
-        <v>1433</v>
+        <v>117</v>
       </c>
     </row>
     <row r="949" spans="1:9">
       <c r="A949" s="60">
-        <v>10540011</v>
+        <v>10540012</v>
       </c>
       <c r="B949" s="60">
         <v>105400</v>
       </c>
       <c r="C949" s="60">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D949" s="60"/>
       <c r="E949" s="60"/>
@@ -29761,18 +29756,18 @@
       <c r="G949" s="60"/>
       <c r="H949" s="60"/>
       <c r="I949" s="60" t="s">
-        <v>117</v>
+        <v>208</v>
       </c>
     </row>
     <row r="950" spans="1:9">
       <c r="A950" s="60">
-        <v>10540012</v>
+        <v>10540013</v>
       </c>
       <c r="B950" s="60">
         <v>105400</v>
       </c>
       <c r="C950" s="60">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D950" s="60"/>
       <c r="E950" s="60"/>
@@ -29780,18 +29775,18 @@
       <c r="G950" s="60"/>
       <c r="H950" s="60"/>
       <c r="I950" s="60" t="s">
-        <v>208</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="951" spans="1:9">
       <c r="A951" s="60">
-        <v>10540013</v>
+        <v>10540014</v>
       </c>
       <c r="B951" s="60">
         <v>105400</v>
       </c>
       <c r="C951" s="60">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D951" s="60"/>
       <c r="E951" s="60"/>
@@ -29799,18 +29794,18 @@
       <c r="G951" s="60"/>
       <c r="H951" s="60"/>
       <c r="I951" s="60" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="952" spans="1:9">
       <c r="A952" s="60">
-        <v>10540014</v>
+        <v>10540015</v>
       </c>
       <c r="B952" s="60">
         <v>105400</v>
       </c>
       <c r="C952" s="60">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D952" s="60"/>
       <c r="E952" s="60"/>
@@ -29818,18 +29813,18 @@
       <c r="G952" s="60"/>
       <c r="H952" s="60"/>
       <c r="I952" s="60" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="953" spans="1:9">
       <c r="A953" s="60">
-        <v>10540015</v>
+        <v>10540016</v>
       </c>
       <c r="B953" s="60">
         <v>105400</v>
       </c>
       <c r="C953" s="60">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D953" s="60"/>
       <c r="E953" s="60"/>
@@ -29837,37 +29832,39 @@
       <c r="G953" s="60"/>
       <c r="H953" s="60"/>
       <c r="I953" s="60" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="954" spans="1:9">
       <c r="A954" s="60">
-        <v>10540016</v>
+        <v>10540017</v>
       </c>
       <c r="B954" s="60">
         <v>105400</v>
       </c>
       <c r="C954" s="60">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D954" s="60"/>
       <c r="E954" s="60"/>
       <c r="F954" s="60"/>
       <c r="G954" s="60"/>
-      <c r="H954" s="60"/>
-      <c r="I954" s="60" t="s">
-        <v>1427</v>
+      <c r="H954" s="60">
+        <v>2</v>
+      </c>
+      <c r="I954" s="61" t="s">
+        <v>1291</v>
       </c>
     </row>
     <row r="955" spans="1:9">
       <c r="A955" s="60">
-        <v>10540017</v>
+        <v>10540018</v>
       </c>
       <c r="B955" s="60">
         <v>105400</v>
       </c>
       <c r="C955" s="60">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D955" s="60"/>
       <c r="E955" s="60"/>
@@ -29876,19 +29873,19 @@
       <c r="H955" s="60">
         <v>2</v>
       </c>
-      <c r="I955" s="61" t="s">
-        <v>1291</v>
+      <c r="I955" s="60" t="s">
+        <v>1292</v>
       </c>
     </row>
     <row r="956" spans="1:9">
       <c r="A956" s="60">
-        <v>10540018</v>
+        <v>10540019</v>
       </c>
       <c r="B956" s="60">
         <v>105400</v>
       </c>
       <c r="C956" s="60">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D956" s="60"/>
       <c r="E956" s="60"/>
@@ -29898,18 +29895,18 @@
         <v>2</v>
       </c>
       <c r="I956" s="60" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="957" spans="1:9">
       <c r="A957" s="60">
-        <v>10540019</v>
+        <v>10540020</v>
       </c>
       <c r="B957" s="60">
         <v>105400</v>
       </c>
       <c r="C957" s="60">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D957" s="60"/>
       <c r="E957" s="60"/>
@@ -29919,18 +29916,18 @@
         <v>2</v>
       </c>
       <c r="I957" s="60" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="958" spans="1:9">
       <c r="A958" s="60">
-        <v>10540020</v>
+        <v>10540021</v>
       </c>
       <c r="B958" s="60">
         <v>105400</v>
       </c>
       <c r="C958" s="60">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D958" s="60"/>
       <c r="E958" s="60"/>
@@ -29940,18 +29937,18 @@
         <v>2</v>
       </c>
       <c r="I958" s="60" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="959" spans="1:9">
       <c r="A959" s="60">
-        <v>10540021</v>
+        <v>10540022</v>
       </c>
       <c r="B959" s="60">
         <v>105400</v>
       </c>
       <c r="C959" s="60">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D959" s="60"/>
       <c r="E959" s="60"/>
@@ -29961,18 +29958,18 @@
         <v>2</v>
       </c>
       <c r="I959" s="60" t="s">
-        <v>1295</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="960" spans="1:9">
       <c r="A960" s="60">
-        <v>10540022</v>
+        <v>10540023</v>
       </c>
       <c r="B960" s="60">
         <v>105400</v>
       </c>
       <c r="C960" s="60">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D960" s="60"/>
       <c r="E960" s="60"/>
@@ -29987,13 +29984,13 @@
     </row>
     <row r="961" spans="1:9">
       <c r="A961" s="60">
-        <v>10540023</v>
+        <v>10540024</v>
       </c>
       <c r="B961" s="60">
         <v>105400</v>
       </c>
       <c r="C961" s="60">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D961" s="60"/>
       <c r="E961" s="60"/>
@@ -30008,13 +30005,13 @@
     </row>
     <row r="962" spans="1:9">
       <c r="A962" s="60">
-        <v>10540024</v>
+        <v>10540025</v>
       </c>
       <c r="B962" s="60">
         <v>105400</v>
       </c>
       <c r="C962" s="60">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D962" s="60"/>
       <c r="E962" s="60"/>
@@ -30029,13 +30026,13 @@
     </row>
     <row r="963" spans="1:9">
       <c r="A963" s="60">
-        <v>10540025</v>
+        <v>10540026</v>
       </c>
       <c r="B963" s="60">
         <v>105400</v>
       </c>
       <c r="C963" s="60">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D963" s="60"/>
       <c r="E963" s="60"/>
@@ -30050,13 +30047,13 @@
     </row>
     <row r="964" spans="1:9">
       <c r="A964" s="60">
-        <v>10540026</v>
+        <v>10540027</v>
       </c>
       <c r="B964" s="60">
         <v>105400</v>
       </c>
       <c r="C964" s="60">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D964" s="60"/>
       <c r="E964" s="60"/>
@@ -30071,34 +30068,34 @@
     </row>
     <row r="965" spans="1:9">
       <c r="A965" s="60">
-        <v>10540027</v>
+        <v>10540028</v>
       </c>
       <c r="B965" s="60">
         <v>105400</v>
       </c>
       <c r="C965" s="60">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D965" s="60"/>
       <c r="E965" s="60"/>
       <c r="F965" s="60"/>
       <c r="G965" s="60"/>
       <c r="H965" s="60">
-        <v>2</v>
-      </c>
-      <c r="I965" s="60" t="s">
-        <v>1439</v>
+        <v>3</v>
+      </c>
+      <c r="I965" s="61" t="s">
+        <v>1305</v>
       </c>
     </row>
     <row r="966" spans="1:9">
       <c r="A966" s="60">
-        <v>10540028</v>
+        <v>10540029</v>
       </c>
       <c r="B966" s="60">
         <v>105400</v>
       </c>
       <c r="C966" s="60">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D966" s="60"/>
       <c r="E966" s="60"/>
@@ -30107,19 +30104,19 @@
       <c r="H966" s="60">
         <v>3</v>
       </c>
-      <c r="I966" s="61" t="s">
-        <v>1305</v>
+      <c r="I966" s="60" t="s">
+        <v>1306</v>
       </c>
     </row>
     <row r="967" spans="1:9">
       <c r="A967" s="60">
-        <v>10540029</v>
+        <v>10540030</v>
       </c>
       <c r="B967" s="60">
         <v>105400</v>
       </c>
       <c r="C967" s="60">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D967" s="60"/>
       <c r="E967" s="60"/>
@@ -30129,18 +30126,18 @@
         <v>3</v>
       </c>
       <c r="I967" s="60" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="968" spans="1:9">
       <c r="A968" s="60">
-        <v>10540030</v>
+        <v>10540031</v>
       </c>
       <c r="B968" s="60">
         <v>105400</v>
       </c>
       <c r="C968" s="60">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D968" s="60"/>
       <c r="E968" s="60"/>
@@ -30150,18 +30147,18 @@
         <v>3</v>
       </c>
       <c r="I968" s="60" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="969" spans="1:9">
       <c r="A969" s="60">
-        <v>10540031</v>
+        <v>10540032</v>
       </c>
       <c r="B969" s="60">
         <v>105400</v>
       </c>
       <c r="C969" s="60">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D969" s="60"/>
       <c r="E969" s="60"/>
@@ -30171,18 +30168,18 @@
         <v>3</v>
       </c>
       <c r="I969" s="60" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="970" spans="1:9">
       <c r="A970" s="60">
-        <v>10540032</v>
+        <v>10540033</v>
       </c>
       <c r="B970" s="60">
         <v>105400</v>
       </c>
       <c r="C970" s="60">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D970" s="60"/>
       <c r="E970" s="60"/>
@@ -30192,18 +30189,18 @@
         <v>3</v>
       </c>
       <c r="I970" s="60" t="s">
-        <v>1309</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="971" spans="1:9">
       <c r="A971" s="60">
-        <v>10540033</v>
+        <v>10540034</v>
       </c>
       <c r="B971" s="60">
         <v>105400</v>
       </c>
       <c r="C971" s="60">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D971" s="60"/>
       <c r="E971" s="60"/>
@@ -30218,13 +30215,13 @@
     </row>
     <row r="972" spans="1:9">
       <c r="A972" s="60">
-        <v>10540034</v>
+        <v>10540035</v>
       </c>
       <c r="B972" s="60">
         <v>105400</v>
       </c>
       <c r="C972" s="60">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D972" s="60"/>
       <c r="E972" s="60"/>
@@ -30239,13 +30236,13 @@
     </row>
     <row r="973" spans="1:9">
       <c r="A973" s="60">
-        <v>10540035</v>
+        <v>10540036</v>
       </c>
       <c r="B973" s="60">
         <v>105400</v>
       </c>
       <c r="C973" s="60">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D973" s="60"/>
       <c r="E973" s="60"/>
@@ -30260,13 +30257,13 @@
     </row>
     <row r="974" spans="1:9">
       <c r="A974" s="60">
-        <v>10540036</v>
+        <v>10540037</v>
       </c>
       <c r="B974" s="60">
         <v>105400</v>
       </c>
       <c r="C974" s="60">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D974" s="60"/>
       <c r="E974" s="60"/>
@@ -30281,13 +30278,13 @@
     </row>
     <row r="975" spans="1:9">
       <c r="A975" s="60">
-        <v>10540037</v>
+        <v>10540038</v>
       </c>
       <c r="B975" s="60">
         <v>105400</v>
       </c>
       <c r="C975" s="60">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D975" s="60"/>
       <c r="E975" s="60"/>
@@ -30302,34 +30299,34 @@
     </row>
     <row r="976" spans="1:9">
       <c r="A976" s="60">
-        <v>10540038</v>
+        <v>10540039</v>
       </c>
       <c r="B976" s="60">
         <v>105400</v>
       </c>
       <c r="C976" s="60">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D976" s="60"/>
       <c r="E976" s="60"/>
       <c r="F976" s="60"/>
       <c r="G976" s="60"/>
       <c r="H976" s="60">
-        <v>3</v>
-      </c>
-      <c r="I976" s="60" t="s">
-        <v>1445</v>
+        <v>4</v>
+      </c>
+      <c r="I976" s="61" t="s">
+        <v>1319</v>
       </c>
     </row>
     <row r="977" spans="1:9">
       <c r="A977" s="60">
-        <v>10540039</v>
+        <v>10540040</v>
       </c>
       <c r="B977" s="60">
         <v>105400</v>
       </c>
       <c r="C977" s="60">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D977" s="60"/>
       <c r="E977" s="60"/>
@@ -30338,19 +30335,19 @@
       <c r="H977" s="60">
         <v>4</v>
       </c>
-      <c r="I977" s="61" t="s">
-        <v>1319</v>
+      <c r="I977" s="60" t="s">
+        <v>1320</v>
       </c>
     </row>
     <row r="978" spans="1:9">
       <c r="A978" s="60">
-        <v>10540040</v>
+        <v>10540041</v>
       </c>
       <c r="B978" s="60">
         <v>105400</v>
       </c>
       <c r="C978" s="60">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D978" s="60"/>
       <c r="E978" s="60"/>
@@ -30360,18 +30357,18 @@
         <v>4</v>
       </c>
       <c r="I978" s="60" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="979" spans="1:9">
       <c r="A979" s="60">
-        <v>10540041</v>
+        <v>10540042</v>
       </c>
       <c r="B979" s="60">
         <v>105400</v>
       </c>
       <c r="C979" s="60">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D979" s="60"/>
       <c r="E979" s="60"/>
@@ -30381,18 +30378,18 @@
         <v>4</v>
       </c>
       <c r="I979" s="60" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="980" spans="1:9">
       <c r="A980" s="60">
-        <v>10540042</v>
+        <v>10540043</v>
       </c>
       <c r="B980" s="60">
         <v>105400</v>
       </c>
       <c r="C980" s="60">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D980" s="60"/>
       <c r="E980" s="60"/>
@@ -30402,18 +30399,18 @@
         <v>4</v>
       </c>
       <c r="I980" s="60" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="981" spans="1:9">
       <c r="A981" s="60">
-        <v>10540043</v>
+        <v>10540044</v>
       </c>
       <c r="B981" s="60">
         <v>105400</v>
       </c>
       <c r="C981" s="60">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D981" s="60"/>
       <c r="E981" s="60"/>
@@ -30423,18 +30420,18 @@
         <v>4</v>
       </c>
       <c r="I981" s="60" t="s">
-        <v>1323</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="982" spans="1:9">
       <c r="A982" s="60">
-        <v>10540044</v>
+        <v>10540045</v>
       </c>
       <c r="B982" s="60">
         <v>105400</v>
       </c>
       <c r="C982" s="60">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D982" s="60"/>
       <c r="E982" s="60"/>
@@ -30449,13 +30446,13 @@
     </row>
     <row r="983" spans="1:9">
       <c r="A983" s="60">
-        <v>10540045</v>
+        <v>10540046</v>
       </c>
       <c r="B983" s="60">
         <v>105400</v>
       </c>
       <c r="C983" s="60">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D983" s="60"/>
       <c r="E983" s="60"/>
@@ -30470,13 +30467,13 @@
     </row>
     <row r="984" spans="1:9">
       <c r="A984" s="60">
-        <v>10540046</v>
+        <v>10540047</v>
       </c>
       <c r="B984" s="60">
         <v>105400</v>
       </c>
       <c r="C984" s="60">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D984" s="60"/>
       <c r="E984" s="60"/>
@@ -30491,13 +30488,13 @@
     </row>
     <row r="985" spans="1:9">
       <c r="A985" s="60">
-        <v>10540047</v>
+        <v>10540048</v>
       </c>
       <c r="B985" s="60">
         <v>105400</v>
       </c>
       <c r="C985" s="60">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D985" s="60"/>
       <c r="E985" s="60"/>
@@ -30512,13 +30509,13 @@
     </row>
     <row r="986" spans="1:9">
       <c r="A986" s="60">
-        <v>10540048</v>
+        <v>10540049</v>
       </c>
       <c r="B986" s="60">
         <v>105400</v>
       </c>
       <c r="C986" s="60">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D986" s="60"/>
       <c r="E986" s="60"/>
@@ -30533,39 +30530,39 @@
     </row>
     <row r="987" spans="1:9">
       <c r="A987" s="60">
-        <v>10540049</v>
+        <v>10540050</v>
       </c>
       <c r="B987" s="60">
         <v>105400</v>
       </c>
       <c r="C987" s="60">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D987" s="60"/>
       <c r="E987" s="60"/>
-      <c r="F987" s="60"/>
+      <c r="F987" s="60" t="s">
+        <v>1451</v>
+      </c>
       <c r="G987" s="60"/>
-      <c r="H987" s="60">
-        <v>4</v>
-      </c>
+      <c r="H987" s="60"/>
       <c r="I987" s="60" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="988" spans="1:9">
       <c r="A988" s="60">
-        <v>10540050</v>
+        <v>10540051</v>
       </c>
       <c r="B988" s="60">
         <v>105400</v>
       </c>
       <c r="C988" s="60">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D988" s="60"/>
       <c r="E988" s="60"/>
       <c r="F988" s="60" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G988" s="60"/>
       <c r="H988" s="60"/>
@@ -30575,18 +30572,18 @@
     </row>
     <row r="989" spans="1:9">
       <c r="A989" s="60">
-        <v>10540051</v>
+        <v>10540052</v>
       </c>
       <c r="B989" s="60">
         <v>105400</v>
       </c>
       <c r="C989" s="60">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D989" s="60"/>
       <c r="E989" s="60"/>
       <c r="F989" s="60" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G989" s="60"/>
       <c r="H989" s="60"/>
@@ -30596,18 +30593,18 @@
     </row>
     <row r="990" spans="1:9">
       <c r="A990" s="60">
-        <v>10540052</v>
+        <v>10540053</v>
       </c>
       <c r="B990" s="60">
         <v>105400</v>
       </c>
       <c r="C990" s="60">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D990" s="60"/>
       <c r="E990" s="60"/>
       <c r="F990" s="60" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G990" s="60"/>
       <c r="H990" s="60"/>
@@ -30617,18 +30614,18 @@
     </row>
     <row r="991" spans="1:9">
       <c r="A991" s="60">
-        <v>10540053</v>
+        <v>10540054</v>
       </c>
       <c r="B991" s="60">
         <v>105400</v>
       </c>
       <c r="C991" s="60">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D991" s="60"/>
       <c r="E991" s="60"/>
       <c r="F991" s="60" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G991" s="60"/>
       <c r="H991" s="60"/>
@@ -30638,18 +30635,18 @@
     </row>
     <row r="992" spans="1:9">
       <c r="A992" s="60">
-        <v>10540054</v>
+        <v>10540055</v>
       </c>
       <c r="B992" s="60">
         <v>105400</v>
       </c>
       <c r="C992" s="60">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D992" s="60"/>
       <c r="E992" s="60"/>
       <c r="F992" s="60" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G992" s="60"/>
       <c r="H992" s="60"/>
@@ -30659,18 +30656,18 @@
     </row>
     <row r="993" spans="1:9">
       <c r="A993" s="60">
-        <v>10540055</v>
+        <v>10540056</v>
       </c>
       <c r="B993" s="60">
         <v>105400</v>
       </c>
       <c r="C993" s="60">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D993" s="60"/>
       <c r="E993" s="60"/>
       <c r="F993" s="60" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G993" s="60"/>
       <c r="H993" s="60"/>
@@ -30680,18 +30677,18 @@
     </row>
     <row r="994" spans="1:9">
       <c r="A994" s="60">
-        <v>10540056</v>
+        <v>10540057</v>
       </c>
       <c r="B994" s="60">
         <v>105400</v>
       </c>
       <c r="C994" s="60">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D994" s="60"/>
       <c r="E994" s="60"/>
       <c r="F994" s="60" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G994" s="60"/>
       <c r="H994" s="60"/>
@@ -30701,18 +30698,18 @@
     </row>
     <row r="995" spans="1:9">
       <c r="A995" s="60">
-        <v>10540057</v>
+        <v>10540058</v>
       </c>
       <c r="B995" s="60">
         <v>105400</v>
       </c>
       <c r="C995" s="60">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D995" s="60"/>
       <c r="E995" s="60"/>
       <c r="F995" s="60" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G995" s="60"/>
       <c r="H995" s="60"/>
@@ -30722,18 +30719,18 @@
     </row>
     <row r="996" spans="1:9">
       <c r="A996" s="60">
-        <v>10540058</v>
+        <v>10540059</v>
       </c>
       <c r="B996" s="60">
         <v>105400</v>
       </c>
       <c r="C996" s="60">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D996" s="60"/>
       <c r="E996" s="60"/>
       <c r="F996" s="60" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="G996" s="60"/>
       <c r="H996" s="60"/>
@@ -30743,39 +30740,41 @@
     </row>
     <row r="997" spans="1:9">
       <c r="A997" s="60">
-        <v>10540059</v>
+        <v>10540060</v>
       </c>
       <c r="B997" s="60">
         <v>105400</v>
       </c>
       <c r="C997" s="60">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D997" s="60"/>
       <c r="E997" s="60"/>
       <c r="F997" s="60" t="s">
-        <v>1452</v>
+        <v>1462</v>
       </c>
       <c r="G997" s="60"/>
-      <c r="H997" s="60"/>
+      <c r="H997" s="60">
+        <v>2</v>
+      </c>
       <c r="I997" s="60" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="998" spans="1:9">
       <c r="A998" s="60">
-        <v>10540060</v>
+        <v>10540061</v>
       </c>
       <c r="B998" s="60">
         <v>105400</v>
       </c>
       <c r="C998" s="60">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D998" s="60"/>
       <c r="E998" s="60"/>
       <c r="F998" s="60" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G998" s="60"/>
       <c r="H998" s="60">
@@ -30787,18 +30786,18 @@
     </row>
     <row r="999" spans="1:9">
       <c r="A999" s="60">
-        <v>10540061</v>
+        <v>10540062</v>
       </c>
       <c r="B999" s="60">
         <v>105400</v>
       </c>
       <c r="C999" s="60">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D999" s="60"/>
       <c r="E999" s="60"/>
       <c r="F999" s="60" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G999" s="60"/>
       <c r="H999" s="60">
@@ -30810,18 +30809,18 @@
     </row>
     <row r="1000" spans="1:9">
       <c r="A1000" s="60">
-        <v>10540062</v>
+        <v>10540063</v>
       </c>
       <c r="B1000" s="60">
         <v>105400</v>
       </c>
       <c r="C1000" s="60">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1000" s="60"/>
       <c r="E1000" s="60"/>
       <c r="F1000" s="60" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G1000" s="60"/>
       <c r="H1000" s="60">
@@ -30833,18 +30832,18 @@
     </row>
     <row r="1001" spans="1:9">
       <c r="A1001" s="60">
-        <v>10540063</v>
+        <v>10540064</v>
       </c>
       <c r="B1001" s="60">
         <v>105400</v>
       </c>
       <c r="C1001" s="60">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D1001" s="60"/>
       <c r="E1001" s="60"/>
       <c r="F1001" s="60" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G1001" s="60"/>
       <c r="H1001" s="60">
@@ -30856,18 +30855,18 @@
     </row>
     <row r="1002" spans="1:9">
       <c r="A1002" s="60">
-        <v>10540064</v>
+        <v>10540065</v>
       </c>
       <c r="B1002" s="60">
         <v>105400</v>
       </c>
       <c r="C1002" s="60">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D1002" s="60"/>
       <c r="E1002" s="60"/>
       <c r="F1002" s="60" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G1002" s="60"/>
       <c r="H1002" s="60">
@@ -30879,18 +30878,18 @@
     </row>
     <row r="1003" spans="1:9">
       <c r="A1003" s="60">
-        <v>10540065</v>
+        <v>10540066</v>
       </c>
       <c r="B1003" s="60">
         <v>105400</v>
       </c>
       <c r="C1003" s="60">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D1003" s="60"/>
       <c r="E1003" s="60"/>
       <c r="F1003" s="60" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G1003" s="60"/>
       <c r="H1003" s="60">
@@ -30902,18 +30901,18 @@
     </row>
     <row r="1004" spans="1:9">
       <c r="A1004" s="60">
-        <v>10540066</v>
+        <v>10540067</v>
       </c>
       <c r="B1004" s="60">
         <v>105400</v>
       </c>
       <c r="C1004" s="60">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1004" s="60"/>
       <c r="E1004" s="60"/>
       <c r="F1004" s="60" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G1004" s="60"/>
       <c r="H1004" s="60">
@@ -30925,18 +30924,18 @@
     </row>
     <row r="1005" spans="1:9">
       <c r="A1005" s="60">
-        <v>10540067</v>
+        <v>10540068</v>
       </c>
       <c r="B1005" s="60">
         <v>105400</v>
       </c>
       <c r="C1005" s="60">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1005" s="60"/>
       <c r="E1005" s="60"/>
       <c r="F1005" s="60" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G1005" s="60"/>
       <c r="H1005" s="60">
@@ -30948,18 +30947,18 @@
     </row>
     <row r="1006" spans="1:9">
       <c r="A1006" s="60">
-        <v>10540068</v>
+        <v>10540069</v>
       </c>
       <c r="B1006" s="60">
         <v>105400</v>
       </c>
       <c r="C1006" s="60">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1006" s="60"/>
       <c r="E1006" s="60"/>
       <c r="F1006" s="60" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G1006" s="60"/>
       <c r="H1006" s="60">
@@ -30971,41 +30970,41 @@
     </row>
     <row r="1007" spans="1:9">
       <c r="A1007" s="60">
-        <v>10540069</v>
+        <v>10540070</v>
       </c>
       <c r="B1007" s="60">
         <v>105400</v>
       </c>
       <c r="C1007" s="60">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1007" s="60"/>
       <c r="E1007" s="60"/>
       <c r="F1007" s="60" t="s">
-        <v>1463</v>
+        <v>1473</v>
       </c>
       <c r="G1007" s="60"/>
       <c r="H1007" s="60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1007" s="60" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="1008" spans="1:9">
       <c r="A1008" s="60">
-        <v>10540070</v>
+        <v>10540071</v>
       </c>
       <c r="B1008" s="60">
         <v>105400</v>
       </c>
       <c r="C1008" s="60">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D1008" s="60"/>
       <c r="E1008" s="60"/>
       <c r="F1008" s="60" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G1008" s="60"/>
       <c r="H1008" s="60">
@@ -31017,18 +31016,18 @@
     </row>
     <row r="1009" spans="1:9">
       <c r="A1009" s="60">
-        <v>10540071</v>
+        <v>10540072</v>
       </c>
       <c r="B1009" s="60">
         <v>105400</v>
       </c>
       <c r="C1009" s="60">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D1009" s="60"/>
       <c r="E1009" s="60"/>
       <c r="F1009" s="60" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G1009" s="60"/>
       <c r="H1009" s="60">
@@ -31040,18 +31039,18 @@
     </row>
     <row r="1010" spans="1:9">
       <c r="A1010" s="60">
-        <v>10540072</v>
+        <v>10540073</v>
       </c>
       <c r="B1010" s="60">
         <v>105400</v>
       </c>
       <c r="C1010" s="60">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1010" s="60"/>
       <c r="E1010" s="60"/>
       <c r="F1010" s="60" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G1010" s="60"/>
       <c r="H1010" s="60">
@@ -31063,18 +31062,18 @@
     </row>
     <row r="1011" spans="1:9">
       <c r="A1011" s="60">
-        <v>10540073</v>
+        <v>10540074</v>
       </c>
       <c r="B1011" s="60">
         <v>105400</v>
       </c>
       <c r="C1011" s="60">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1011" s="60"/>
       <c r="E1011" s="60"/>
       <c r="F1011" s="60" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G1011" s="60"/>
       <c r="H1011" s="60">
@@ -31086,18 +31085,18 @@
     </row>
     <row r="1012" spans="1:9">
       <c r="A1012" s="60">
-        <v>10540074</v>
+        <v>10540075</v>
       </c>
       <c r="B1012" s="60">
         <v>105400</v>
       </c>
       <c r="C1012" s="60">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1012" s="60"/>
       <c r="E1012" s="60"/>
       <c r="F1012" s="60" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G1012" s="60"/>
       <c r="H1012" s="60">
@@ -31109,18 +31108,18 @@
     </row>
     <row r="1013" spans="1:9">
       <c r="A1013" s="60">
-        <v>10540075</v>
+        <v>10540076</v>
       </c>
       <c r="B1013" s="60">
         <v>105400</v>
       </c>
       <c r="C1013" s="60">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1013" s="60"/>
       <c r="E1013" s="60"/>
       <c r="F1013" s="60" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G1013" s="60"/>
       <c r="H1013" s="60">
@@ -31132,18 +31131,18 @@
     </row>
     <row r="1014" spans="1:9">
       <c r="A1014" s="60">
-        <v>10540076</v>
+        <v>10540077</v>
       </c>
       <c r="B1014" s="60">
         <v>105400</v>
       </c>
       <c r="C1014" s="60">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1014" s="60"/>
       <c r="E1014" s="60"/>
       <c r="F1014" s="60" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G1014" s="60"/>
       <c r="H1014" s="60">
@@ -31155,18 +31154,18 @@
     </row>
     <row r="1015" spans="1:9">
       <c r="A1015" s="60">
-        <v>10540077</v>
+        <v>10540078</v>
       </c>
       <c r="B1015" s="60">
         <v>105400</v>
       </c>
       <c r="C1015" s="60">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D1015" s="60"/>
       <c r="E1015" s="60"/>
       <c r="F1015" s="60" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G1015" s="60"/>
       <c r="H1015" s="60">
@@ -31178,18 +31177,18 @@
     </row>
     <row r="1016" spans="1:9">
       <c r="A1016" s="60">
-        <v>10540078</v>
+        <v>10540079</v>
       </c>
       <c r="B1016" s="60">
         <v>105400</v>
       </c>
       <c r="C1016" s="60">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D1016" s="60"/>
       <c r="E1016" s="60"/>
       <c r="F1016" s="60" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G1016" s="60"/>
       <c r="H1016" s="60">
@@ -31201,41 +31200,41 @@
     </row>
     <row r="1017" spans="1:9">
       <c r="A1017" s="60">
-        <v>10540079</v>
+        <v>10540080</v>
       </c>
       <c r="B1017" s="60">
         <v>105400</v>
       </c>
       <c r="C1017" s="60">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D1017" s="60"/>
       <c r="E1017" s="60"/>
       <c r="F1017" s="60" t="s">
-        <v>1474</v>
+        <v>1484</v>
       </c>
       <c r="G1017" s="60"/>
       <c r="H1017" s="60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1017" s="60" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="1018" spans="1:9">
       <c r="A1018" s="60">
-        <v>10540080</v>
+        <v>10540081</v>
       </c>
       <c r="B1018" s="60">
         <v>105400</v>
       </c>
       <c r="C1018" s="60">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D1018" s="60"/>
       <c r="E1018" s="60"/>
       <c r="F1018" s="60" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="G1018" s="60"/>
       <c r="H1018" s="60">
@@ -31247,18 +31246,18 @@
     </row>
     <row r="1019" spans="1:9">
       <c r="A1019" s="60">
-        <v>10540081</v>
+        <v>10540082</v>
       </c>
       <c r="B1019" s="60">
         <v>105400</v>
       </c>
       <c r="C1019" s="60">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D1019" s="60"/>
       <c r="E1019" s="60"/>
       <c r="F1019" s="60" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="G1019" s="60"/>
       <c r="H1019" s="60">
@@ -31270,18 +31269,18 @@
     </row>
     <row r="1020" spans="1:9">
       <c r="A1020" s="60">
-        <v>10540082</v>
+        <v>10540083</v>
       </c>
       <c r="B1020" s="60">
         <v>105400</v>
       </c>
       <c r="C1020" s="60">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D1020" s="60"/>
       <c r="E1020" s="60"/>
       <c r="F1020" s="60" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="G1020" s="60"/>
       <c r="H1020" s="60">
@@ -31293,18 +31292,18 @@
     </row>
     <row r="1021" spans="1:9">
       <c r="A1021" s="60">
-        <v>10540083</v>
+        <v>10540084</v>
       </c>
       <c r="B1021" s="60">
         <v>105400</v>
       </c>
       <c r="C1021" s="60">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D1021" s="60"/>
       <c r="E1021" s="60"/>
       <c r="F1021" s="60" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="G1021" s="60"/>
       <c r="H1021" s="60">
@@ -31316,18 +31315,18 @@
     </row>
     <row r="1022" spans="1:9">
       <c r="A1022" s="60">
-        <v>10540084</v>
+        <v>10540085</v>
       </c>
       <c r="B1022" s="60">
         <v>105400</v>
       </c>
       <c r="C1022" s="60">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D1022" s="60"/>
       <c r="E1022" s="60"/>
       <c r="F1022" s="60" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="G1022" s="60"/>
       <c r="H1022" s="60">
@@ -31339,18 +31338,18 @@
     </row>
     <row r="1023" spans="1:9">
       <c r="A1023" s="60">
-        <v>10540085</v>
+        <v>10540086</v>
       </c>
       <c r="B1023" s="60">
         <v>105400</v>
       </c>
       <c r="C1023" s="60">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D1023" s="60"/>
       <c r="E1023" s="60"/>
       <c r="F1023" s="60" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="G1023" s="60"/>
       <c r="H1023" s="60">
@@ -31362,18 +31361,18 @@
     </row>
     <row r="1024" spans="1:9">
       <c r="A1024" s="60">
-        <v>10540086</v>
+        <v>10540087</v>
       </c>
       <c r="B1024" s="60">
         <v>105400</v>
       </c>
       <c r="C1024" s="60">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D1024" s="60"/>
       <c r="E1024" s="60"/>
       <c r="F1024" s="60" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="G1024" s="60"/>
       <c r="H1024" s="60">
@@ -31385,18 +31384,18 @@
     </row>
     <row r="1025" spans="1:9">
       <c r="A1025" s="60">
-        <v>10540087</v>
+        <v>10540088</v>
       </c>
       <c r="B1025" s="60">
         <v>105400</v>
       </c>
       <c r="C1025" s="60">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1025" s="60"/>
       <c r="E1025" s="60"/>
       <c r="F1025" s="60" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="G1025" s="60"/>
       <c r="H1025" s="60">
@@ -31408,18 +31407,18 @@
     </row>
     <row r="1026" spans="1:9">
       <c r="A1026" s="60">
-        <v>10540088</v>
+        <v>10540089</v>
       </c>
       <c r="B1026" s="60">
         <v>105400</v>
       </c>
       <c r="C1026" s="60">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D1026" s="60"/>
       <c r="E1026" s="60"/>
       <c r="F1026" s="60" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="G1026" s="60"/>
       <c r="H1026" s="60">
@@ -31430,37 +31429,35 @@
       </c>
     </row>
     <row r="1027" spans="1:9">
-      <c r="A1027" s="60">
-        <v>10540089</v>
-      </c>
-      <c r="B1027" s="60">
-        <v>105400</v>
-      </c>
-      <c r="C1027" s="60">
-        <v>89</v>
-      </c>
-      <c r="D1027" s="60"/>
-      <c r="E1027" s="60"/>
-      <c r="F1027" s="60" t="s">
-        <v>1485</v>
-      </c>
-      <c r="G1027" s="60"/>
-      <c r="H1027" s="60">
-        <v>4</v>
-      </c>
-      <c r="I1027" s="60" t="s">
-        <v>1495</v>
+      <c r="A1027" s="28">
+        <v>10080001</v>
+      </c>
+      <c r="B1027" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1027" s="28">
+        <v>1</v>
+      </c>
+      <c r="D1027" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1027" s="28"/>
+      <c r="F1027" s="28"/>
+      <c r="G1027" s="28"/>
+      <c r="H1027" s="28"/>
+      <c r="I1027" s="62">
+        <v>10</v>
       </c>
     </row>
     <row r="1028" spans="1:9">
       <c r="A1028" s="28">
-        <v>10080001</v>
+        <v>10080002</v>
       </c>
       <c r="B1028" s="28">
         <v>100800</v>
       </c>
       <c r="C1028" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1028" s="28">
         <v>0</v>
@@ -31469,19 +31466,19 @@
       <c r="F1028" s="28"/>
       <c r="G1028" s="28"/>
       <c r="H1028" s="28"/>
-      <c r="I1028" s="62">
-        <v>10</v>
+      <c r="I1028" s="28" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="1029" spans="1:9">
       <c r="A1029" s="28">
-        <v>10080002</v>
+        <v>10080003</v>
       </c>
       <c r="B1029" s="28">
         <v>100800</v>
       </c>
       <c r="C1029" s="28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1029" s="28">
         <v>0</v>
@@ -31491,18 +31488,18 @@
       <c r="G1029" s="28"/>
       <c r="H1029" s="28"/>
       <c r="I1029" s="28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1030" spans="1:9">
       <c r="A1030" s="28">
-        <v>10080003</v>
+        <v>10080004</v>
       </c>
       <c r="B1030" s="28">
         <v>100800</v>
       </c>
       <c r="C1030" s="28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1030" s="28">
         <v>0</v>
@@ -31512,18 +31509,18 @@
       <c r="G1030" s="28"/>
       <c r="H1030" s="28"/>
       <c r="I1030" s="28" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1031" spans="1:9">
       <c r="A1031" s="28">
-        <v>10080004</v>
+        <v>10080005</v>
       </c>
       <c r="B1031" s="28">
         <v>100800</v>
       </c>
       <c r="C1031" s="28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1031" s="28">
         <v>0</v>
@@ -31533,18 +31530,18 @@
       <c r="G1031" s="28"/>
       <c r="H1031" s="28"/>
       <c r="I1031" s="28" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1032" spans="1:9">
       <c r="A1032" s="28">
-        <v>10080005</v>
+        <v>10080006</v>
       </c>
       <c r="B1032" s="28">
         <v>100800</v>
       </c>
       <c r="C1032" s="28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1032" s="28">
         <v>0</v>
@@ -31554,18 +31551,18 @@
       <c r="G1032" s="28"/>
       <c r="H1032" s="28"/>
       <c r="I1032" s="28" t="s">
-        <v>27</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="1033" spans="1:9">
       <c r="A1033" s="28">
-        <v>10080006</v>
+        <v>10080007</v>
       </c>
       <c r="B1033" s="28">
         <v>100800</v>
       </c>
       <c r="C1033" s="28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D1033" s="28">
         <v>0</v>
@@ -31575,18 +31572,18 @@
       <c r="G1033" s="28"/>
       <c r="H1033" s="28"/>
       <c r="I1033" s="28" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="1034" spans="1:9">
       <c r="A1034" s="28">
-        <v>10080007</v>
+        <v>10080008</v>
       </c>
       <c r="B1034" s="28">
         <v>100800</v>
       </c>
       <c r="C1034" s="28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1034" s="28">
         <v>0</v>
@@ -31596,18 +31593,18 @@
       <c r="G1034" s="28"/>
       <c r="H1034" s="28"/>
       <c r="I1034" s="28" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="1035" spans="1:9">
       <c r="A1035" s="28">
-        <v>10080008</v>
+        <v>10080009</v>
       </c>
       <c r="B1035" s="28">
         <v>100800</v>
       </c>
       <c r="C1035" s="28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1035" s="28">
         <v>0</v>
@@ -31617,18 +31614,18 @@
       <c r="G1035" s="28"/>
       <c r="H1035" s="28"/>
       <c r="I1035" s="28" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="1036" spans="1:9">
       <c r="A1036" s="28">
-        <v>10080009</v>
+        <v>10080010</v>
       </c>
       <c r="B1036" s="28">
         <v>100800</v>
       </c>
       <c r="C1036" s="28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D1036" s="28">
         <v>0</v>
@@ -31638,18 +31635,18 @@
       <c r="G1036" s="28"/>
       <c r="H1036" s="28"/>
       <c r="I1036" s="28" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="1037" spans="1:9">
       <c r="A1037" s="28">
-        <v>10080010</v>
+        <v>10080011</v>
       </c>
       <c r="B1037" s="28">
         <v>100800</v>
       </c>
       <c r="C1037" s="28">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D1037" s="28">
         <v>0</v>
@@ -31659,60 +31656,60 @@
       <c r="G1037" s="28"/>
       <c r="H1037" s="28"/>
       <c r="I1037" s="28" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="1038" spans="1:9">
       <c r="A1038" s="28">
-        <v>10080011</v>
+        <v>10080012</v>
       </c>
       <c r="B1038" s="28">
         <v>100800</v>
       </c>
       <c r="C1038" s="28">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1038" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1038" s="28"/>
       <c r="F1038" s="28"/>
       <c r="G1038" s="28"/>
       <c r="H1038" s="28"/>
       <c r="I1038" s="28" t="s">
-        <v>1090</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1039" spans="1:9">
       <c r="A1039" s="28">
-        <v>10080012</v>
+        <v>10080013</v>
       </c>
       <c r="B1039" s="28">
         <v>100800</v>
       </c>
       <c r="C1039" s="28">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1039" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1039" s="28"/>
       <c r="F1039" s="28"/>
       <c r="G1039" s="28"/>
       <c r="H1039" s="28"/>
       <c r="I1039" s="28" t="s">
-        <v>117</v>
+        <v>190</v>
       </c>
     </row>
     <row r="1040" spans="1:9">
       <c r="A1040" s="28">
-        <v>10080013</v>
+        <v>10080014</v>
       </c>
       <c r="B1040" s="28">
         <v>100800</v>
       </c>
       <c r="C1040" s="28">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1040" s="28">
         <v>2</v>
@@ -31721,19 +31718,19 @@
       <c r="F1040" s="28"/>
       <c r="G1040" s="28"/>
       <c r="H1040" s="28"/>
-      <c r="I1040" s="28" t="s">
-        <v>190</v>
+      <c r="I1040" s="63" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="1041" spans="1:9">
       <c r="A1041" s="28">
-        <v>10080014</v>
+        <v>10080015</v>
       </c>
       <c r="B1041" s="28">
         <v>100800</v>
       </c>
       <c r="C1041" s="28">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1041" s="28">
         <v>2</v>
@@ -31743,18 +31740,18 @@
       <c r="G1041" s="28"/>
       <c r="H1041" s="28"/>
       <c r="I1041" s="63" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1042" spans="1:9">
       <c r="A1042" s="28">
-        <v>10080015</v>
+        <v>10080016</v>
       </c>
       <c r="B1042" s="28">
         <v>100800</v>
       </c>
       <c r="C1042" s="28">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1042" s="28">
         <v>2</v>
@@ -31764,18 +31761,18 @@
       <c r="G1042" s="28"/>
       <c r="H1042" s="28"/>
       <c r="I1042" s="63" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1043" spans="1:9">
       <c r="A1043" s="28">
-        <v>10080016</v>
+        <v>10080017</v>
       </c>
       <c r="B1043" s="28">
         <v>100800</v>
       </c>
       <c r="C1043" s="28">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1043" s="28">
         <v>2</v>
@@ -31785,39 +31782,41 @@
       <c r="G1043" s="28"/>
       <c r="H1043" s="28"/>
       <c r="I1043" s="63" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="1044" spans="1:9">
       <c r="A1044" s="28">
-        <v>10080017</v>
+        <v>10080018</v>
       </c>
       <c r="B1044" s="28">
         <v>100800</v>
       </c>
       <c r="C1044" s="28">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1044" s="28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1044" s="28"/>
       <c r="F1044" s="28"/>
       <c r="G1044" s="28"/>
-      <c r="H1044" s="28"/>
-      <c r="I1044" s="63" t="s">
-        <v>232</v>
+      <c r="H1044" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1044" s="45" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="1045" spans="1:9">
       <c r="A1045" s="28">
-        <v>10080018</v>
+        <v>10080019</v>
       </c>
       <c r="B1045" s="28">
         <v>100800</v>
       </c>
       <c r="C1045" s="28">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1045" s="28">
         <v>0</v>
@@ -31829,18 +31828,18 @@
         <v>2</v>
       </c>
       <c r="I1045" s="45" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="1046" spans="1:9">
       <c r="A1046" s="28">
-        <v>10080019</v>
+        <v>10080020</v>
       </c>
       <c r="B1046" s="28">
         <v>100800</v>
       </c>
       <c r="C1046" s="28">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1046" s="28">
         <v>0</v>
@@ -31852,18 +31851,18 @@
         <v>2</v>
       </c>
       <c r="I1046" s="45" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="1047" spans="1:9">
       <c r="A1047" s="28">
-        <v>10080020</v>
+        <v>10080021</v>
       </c>
       <c r="B1047" s="28">
         <v>100800</v>
       </c>
       <c r="C1047" s="28">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1047" s="28">
         <v>0</v>
@@ -31875,18 +31874,18 @@
         <v>2</v>
       </c>
       <c r="I1047" s="45" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="1048" spans="1:9">
       <c r="A1048" s="28">
-        <v>10080021</v>
+        <v>10080022</v>
       </c>
       <c r="B1048" s="28">
         <v>100800</v>
       </c>
       <c r="C1048" s="28">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1048" s="28">
         <v>0</v>
@@ -31898,18 +31897,18 @@
         <v>2</v>
       </c>
       <c r="I1048" s="45" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1049" spans="1:9">
       <c r="A1049" s="28">
-        <v>10080022</v>
+        <v>10080023</v>
       </c>
       <c r="B1049" s="28">
         <v>100800</v>
       </c>
       <c r="C1049" s="28">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1049" s="28">
         <v>0</v>
@@ -31921,18 +31920,18 @@
         <v>2</v>
       </c>
       <c r="I1049" s="45" t="s">
-        <v>449</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="1050" spans="1:9">
       <c r="A1050" s="28">
-        <v>10080023</v>
+        <v>10080024</v>
       </c>
       <c r="B1050" s="28">
         <v>100800</v>
       </c>
       <c r="C1050" s="28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1050" s="28">
         <v>0</v>
@@ -31944,18 +31943,18 @@
         <v>2</v>
       </c>
       <c r="I1050" s="45" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="1051" spans="1:9">
       <c r="A1051" s="28">
-        <v>10080024</v>
+        <v>10080025</v>
       </c>
       <c r="B1051" s="28">
         <v>100800</v>
       </c>
       <c r="C1051" s="28">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1051" s="28">
         <v>0</v>
@@ -31967,18 +31966,18 @@
         <v>2</v>
       </c>
       <c r="I1051" s="45" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="1052" spans="1:9">
       <c r="A1052" s="28">
-        <v>10080025</v>
+        <v>10080026</v>
       </c>
       <c r="B1052" s="28">
         <v>100800</v>
       </c>
       <c r="C1052" s="28">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1052" s="28">
         <v>0</v>
@@ -31990,18 +31989,18 @@
         <v>2</v>
       </c>
       <c r="I1052" s="45" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="1053" spans="1:9">
       <c r="A1053" s="28">
-        <v>10080026</v>
+        <v>10080027</v>
       </c>
       <c r="B1053" s="28">
         <v>100800</v>
       </c>
       <c r="C1053" s="28">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1053" s="28">
         <v>0</v>
@@ -32013,18 +32012,18 @@
         <v>2</v>
       </c>
       <c r="I1053" s="45" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="1054" spans="1:9">
       <c r="A1054" s="28">
-        <v>10080027</v>
+        <v>10080028</v>
       </c>
       <c r="B1054" s="28">
         <v>100800</v>
       </c>
       <c r="C1054" s="28">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1054" s="28">
         <v>0</v>
@@ -32036,21 +32035,21 @@
         <v>2</v>
       </c>
       <c r="I1054" s="45" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="1055" spans="1:9">
       <c r="A1055" s="28">
-        <v>10080028</v>
+        <v>10080029</v>
       </c>
       <c r="B1055" s="28">
         <v>100800</v>
       </c>
       <c r="C1055" s="28">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1055" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1055" s="28"/>
       <c r="F1055" s="28"/>
@@ -32059,41 +32058,41 @@
         <v>2</v>
       </c>
       <c r="I1055" s="45" t="s">
-        <v>1113</v>
+        <v>463</v>
       </c>
     </row>
     <row r="1056" spans="1:9">
       <c r="A1056" s="28">
-        <v>10080029</v>
+        <v>10080030</v>
       </c>
       <c r="B1056" s="28">
         <v>100800</v>
       </c>
       <c r="C1056" s="28">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1056" s="28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1056" s="28"/>
       <c r="F1056" s="28"/>
       <c r="G1056" s="28"/>
       <c r="H1056" s="28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1056" s="45" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="1057" spans="1:9">
       <c r="A1057" s="28">
-        <v>10080030</v>
+        <v>10080031</v>
       </c>
       <c r="B1057" s="28">
         <v>100800</v>
       </c>
       <c r="C1057" s="28">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D1057" s="28">
         <v>0</v>
@@ -32105,18 +32104,18 @@
         <v>3</v>
       </c>
       <c r="I1057" s="45" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1058" spans="1:9">
       <c r="A1058" s="28">
-        <v>10080031</v>
+        <v>10080032</v>
       </c>
       <c r="B1058" s="28">
         <v>100800</v>
       </c>
       <c r="C1058" s="28">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D1058" s="28">
         <v>0</v>
@@ -32128,18 +32127,18 @@
         <v>3</v>
       </c>
       <c r="I1058" s="45" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="1059" spans="1:9">
       <c r="A1059" s="28">
-        <v>10080032</v>
+        <v>10080033</v>
       </c>
       <c r="B1059" s="28">
         <v>100800</v>
       </c>
       <c r="C1059" s="28">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1059" s="28">
         <v>0</v>
@@ -32151,18 +32150,18 @@
         <v>3</v>
       </c>
       <c r="I1059" s="45" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="1060" spans="1:9">
       <c r="A1060" s="28">
-        <v>10080033</v>
+        <v>10080034</v>
       </c>
       <c r="B1060" s="28">
         <v>100800</v>
       </c>
       <c r="C1060" s="28">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1060" s="28">
         <v>0</v>
@@ -32174,18 +32173,18 @@
         <v>3</v>
       </c>
       <c r="I1060" s="45" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1061" spans="1:9">
       <c r="A1061" s="28">
-        <v>10080034</v>
+        <v>10080035</v>
       </c>
       <c r="B1061" s="28">
         <v>100800</v>
       </c>
       <c r="C1061" s="28">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1061" s="28">
         <v>0</v>
@@ -32197,18 +32196,18 @@
         <v>3</v>
       </c>
       <c r="I1061" s="45" t="s">
-        <v>473</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="1062" spans="1:9">
       <c r="A1062" s="28">
-        <v>10080035</v>
+        <v>10080036</v>
       </c>
       <c r="B1062" s="28">
         <v>100800</v>
       </c>
       <c r="C1062" s="28">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1062" s="28">
         <v>0</v>
@@ -32220,18 +32219,18 @@
         <v>3</v>
       </c>
       <c r="I1062" s="45" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="1063" spans="1:9">
       <c r="A1063" s="28">
-        <v>10080036</v>
+        <v>10080037</v>
       </c>
       <c r="B1063" s="28">
         <v>100800</v>
       </c>
       <c r="C1063" s="28">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1063" s="28">
         <v>0</v>
@@ -32243,18 +32242,18 @@
         <v>3</v>
       </c>
       <c r="I1063" s="45" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="1064" spans="1:9">
       <c r="A1064" s="28">
-        <v>10080037</v>
+        <v>10080038</v>
       </c>
       <c r="B1064" s="28">
         <v>100800</v>
       </c>
       <c r="C1064" s="28">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1064" s="28">
         <v>0</v>
@@ -32266,18 +32265,18 @@
         <v>3</v>
       </c>
       <c r="I1064" s="45" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="1065" spans="1:9">
       <c r="A1065" s="28">
-        <v>10080038</v>
+        <v>10080039</v>
       </c>
       <c r="B1065" s="28">
         <v>100800</v>
       </c>
       <c r="C1065" s="28">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1065" s="28">
         <v>0</v>
@@ -32289,18 +32288,18 @@
         <v>3</v>
       </c>
       <c r="I1065" s="45" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="1066" spans="1:9">
       <c r="A1066" s="28">
-        <v>10080039</v>
+        <v>10080040</v>
       </c>
       <c r="B1066" s="28">
         <v>100800</v>
       </c>
       <c r="C1066" s="28">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1066" s="28">
         <v>0</v>
@@ -32312,21 +32311,21 @@
         <v>3</v>
       </c>
       <c r="I1066" s="45" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="1067" spans="1:9">
       <c r="A1067" s="28">
-        <v>10080040</v>
+        <v>10080041</v>
       </c>
       <c r="B1067" s="28">
         <v>100800</v>
       </c>
       <c r="C1067" s="28">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D1067" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1067" s="28"/>
       <c r="F1067" s="28"/>
@@ -32335,41 +32334,41 @@
         <v>3</v>
       </c>
       <c r="I1067" s="45" t="s">
-        <v>1131</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1068" spans="1:9">
       <c r="A1068" s="28">
-        <v>10080041</v>
+        <v>10080042</v>
       </c>
       <c r="B1068" s="28">
         <v>100800</v>
       </c>
       <c r="C1068" s="28">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1068" s="28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1068" s="28"/>
       <c r="F1068" s="28"/>
       <c r="G1068" s="28"/>
       <c r="H1068" s="28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1068" s="45" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1069" spans="1:9">
       <c r="A1069" s="28">
-        <v>10080042</v>
+        <v>10080043</v>
       </c>
       <c r="B1069" s="28">
         <v>100800</v>
       </c>
       <c r="C1069" s="28">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1069" s="28">
         <v>0</v>
@@ -32381,18 +32380,18 @@
         <v>4</v>
       </c>
       <c r="I1069" s="45" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1070" spans="1:9">
       <c r="A1070" s="28">
-        <v>10080043</v>
+        <v>10080044</v>
       </c>
       <c r="B1070" s="28">
         <v>100800</v>
       </c>
       <c r="C1070" s="28">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1070" s="28">
         <v>0</v>
@@ -32404,18 +32403,18 @@
         <v>4</v>
       </c>
       <c r="I1070" s="45" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1071" spans="1:9">
       <c r="A1071" s="28">
-        <v>10080044</v>
+        <v>10080045</v>
       </c>
       <c r="B1071" s="28">
         <v>100800</v>
       </c>
       <c r="C1071" s="28">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1071" s="28">
         <v>0</v>
@@ -32427,18 +32426,18 @@
         <v>4</v>
       </c>
       <c r="I1071" s="45" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1072" spans="1:9">
       <c r="A1072" s="28">
-        <v>10080045</v>
+        <v>10080046</v>
       </c>
       <c r="B1072" s="28">
         <v>100800</v>
       </c>
       <c r="C1072" s="28">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1072" s="28">
         <v>0</v>
@@ -32450,18 +32449,18 @@
         <v>4</v>
       </c>
       <c r="I1072" s="45" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1073" spans="1:9">
       <c r="A1073" s="28">
-        <v>10080046</v>
+        <v>10080047</v>
       </c>
       <c r="B1073" s="28">
         <v>100800</v>
       </c>
       <c r="C1073" s="28">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1073" s="28">
         <v>0</v>
@@ -32473,18 +32472,18 @@
         <v>4</v>
       </c>
       <c r="I1073" s="45" t="s">
-        <v>497</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="1074" spans="1:9">
       <c r="A1074" s="28">
-        <v>10080047</v>
+        <v>10080048</v>
       </c>
       <c r="B1074" s="28">
         <v>100800</v>
       </c>
       <c r="C1074" s="28">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D1074" s="28">
         <v>0</v>
@@ -32496,18 +32495,18 @@
         <v>4</v>
       </c>
       <c r="I1074" s="45" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="1075" spans="1:9">
       <c r="A1075" s="28">
-        <v>10080048</v>
+        <v>10080049</v>
       </c>
       <c r="B1075" s="28">
         <v>100800</v>
       </c>
       <c r="C1075" s="28">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D1075" s="28">
         <v>0</v>
@@ -32519,18 +32518,18 @@
         <v>4</v>
       </c>
       <c r="I1075" s="45" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="1076" spans="1:9">
       <c r="A1076" s="28">
-        <v>10080049</v>
+        <v>10080050</v>
       </c>
       <c r="B1076" s="28">
         <v>100800</v>
       </c>
       <c r="C1076" s="28">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D1076" s="28">
         <v>0</v>
@@ -32542,18 +32541,18 @@
         <v>4</v>
       </c>
       <c r="I1076" s="45" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="1077" spans="1:9">
       <c r="A1077" s="28">
-        <v>10080050</v>
+        <v>10080051</v>
       </c>
       <c r="B1077" s="28">
         <v>100800</v>
       </c>
       <c r="C1077" s="28">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D1077" s="28">
         <v>0</v>
@@ -32565,18 +32564,18 @@
         <v>4</v>
       </c>
       <c r="I1077" s="45" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="1078" spans="1:9">
       <c r="A1078" s="28">
-        <v>10080051</v>
+        <v>10080052</v>
       </c>
       <c r="B1078" s="28">
         <v>100800</v>
       </c>
       <c r="C1078" s="28">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D1078" s="28">
         <v>0</v>
@@ -32588,21 +32587,21 @@
         <v>4</v>
       </c>
       <c r="I1078" s="45" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="1079" spans="1:9">
       <c r="A1079" s="28">
-        <v>10080052</v>
+        <v>10080053</v>
       </c>
       <c r="B1079" s="28">
         <v>100800</v>
       </c>
       <c r="C1079" s="28">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D1079" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1079" s="28"/>
       <c r="F1079" s="28"/>
@@ -32611,41 +32610,43 @@
         <v>4</v>
       </c>
       <c r="I1079" s="45" t="s">
-        <v>1149</v>
+        <v>511</v>
       </c>
     </row>
     <row r="1080" spans="1:9">
       <c r="A1080" s="28">
-        <v>10080053</v>
+        <v>10080054</v>
       </c>
       <c r="B1080" s="28">
         <v>100800</v>
       </c>
       <c r="C1080" s="28">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1080" s="28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1080" s="28"/>
-      <c r="F1080" s="28"/>
+      <c r="F1080" s="28" t="s">
+        <v>1176</v>
+      </c>
       <c r="G1080" s="28"/>
       <c r="H1080" s="28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1080" s="45" t="s">
-        <v>511</v>
+        <v>858</v>
       </c>
     </row>
     <row r="1081" spans="1:9">
       <c r="A1081" s="28">
-        <v>10080054</v>
+        <v>10080055</v>
       </c>
       <c r="B1081" s="28">
         <v>100800</v>
       </c>
       <c r="C1081" s="28">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1081" s="28">
         <v>0</v>
@@ -32659,18 +32660,18 @@
         <v>2</v>
       </c>
       <c r="I1081" s="45" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
     </row>
     <row r="1082" spans="1:9">
       <c r="A1082" s="28">
-        <v>10080055</v>
+        <v>10080056</v>
       </c>
       <c r="B1082" s="28">
         <v>100800</v>
       </c>
       <c r="C1082" s="28">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1082" s="28">
         <v>0</v>
@@ -32684,18 +32685,18 @@
         <v>2</v>
       </c>
       <c r="I1082" s="45" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
     <row r="1083" spans="1:9">
       <c r="A1083" s="28">
-        <v>10080056</v>
+        <v>10080057</v>
       </c>
       <c r="B1083" s="28">
         <v>100800</v>
       </c>
       <c r="C1083" s="28">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1083" s="28">
         <v>0</v>
@@ -32709,18 +32710,18 @@
         <v>2</v>
       </c>
       <c r="I1083" s="45" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
     <row r="1084" spans="1:9">
       <c r="A1084" s="28">
-        <v>10080057</v>
+        <v>10080058</v>
       </c>
       <c r="B1084" s="28">
         <v>100800</v>
       </c>
       <c r="C1084" s="28">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1084" s="28">
         <v>0</v>
@@ -32734,18 +32735,18 @@
         <v>2</v>
       </c>
       <c r="I1084" s="45" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
     </row>
     <row r="1085" spans="1:9">
       <c r="A1085" s="28">
-        <v>10080058</v>
+        <v>10080059</v>
       </c>
       <c r="B1085" s="28">
         <v>100800</v>
       </c>
       <c r="C1085" s="28">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D1085" s="28">
         <v>0</v>
@@ -32759,18 +32760,18 @@
         <v>2</v>
       </c>
       <c r="I1085" s="45" t="s">
-        <v>870</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="1086" spans="1:9">
       <c r="A1086" s="28">
-        <v>10080059</v>
+        <v>10080060</v>
       </c>
       <c r="B1086" s="28">
         <v>100800</v>
       </c>
       <c r="C1086" s="28">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1086" s="28">
         <v>0</v>
@@ -32784,18 +32785,18 @@
         <v>2</v>
       </c>
       <c r="I1086" s="45" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="1087" spans="1:9">
       <c r="A1087" s="28">
-        <v>10080060</v>
+        <v>10080061</v>
       </c>
       <c r="B1087" s="28">
         <v>100800</v>
       </c>
       <c r="C1087" s="28">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1087" s="28">
         <v>0</v>
@@ -32809,18 +32810,18 @@
         <v>2</v>
       </c>
       <c r="I1087" s="45" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="1088" spans="1:9">
       <c r="A1088" s="28">
-        <v>10080061</v>
+        <v>10080062</v>
       </c>
       <c r="B1088" s="28">
         <v>100800</v>
       </c>
       <c r="C1088" s="28">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1088" s="28">
         <v>0</v>
@@ -32834,18 +32835,18 @@
         <v>2</v>
       </c>
       <c r="I1088" s="45" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="1089" spans="1:9">
       <c r="A1089" s="28">
-        <v>10080062</v>
+        <v>10080063</v>
       </c>
       <c r="B1089" s="28">
         <v>100800</v>
       </c>
       <c r="C1089" s="28">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1089" s="28">
         <v>0</v>
@@ -32859,268 +32860,268 @@
         <v>2</v>
       </c>
       <c r="I1089" s="45" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="1090" spans="1:9">
       <c r="A1090" s="28">
-        <v>10080063</v>
+        <v>10080064</v>
       </c>
       <c r="B1090" s="28">
         <v>100800</v>
       </c>
       <c r="C1090" s="28">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D1090" s="28">
         <v>0</v>
       </c>
       <c r="E1090" s="28"/>
       <c r="F1090" s="28" t="s">
-        <v>1176</v>
+        <v>1495</v>
       </c>
       <c r="G1090" s="28"/>
       <c r="H1090" s="28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1090" s="45" t="s">
-        <v>1174</v>
+        <v>891</v>
       </c>
     </row>
     <row r="1091" spans="1:9">
       <c r="A1091" s="28">
-        <v>10080064</v>
+        <v>10080065</v>
       </c>
       <c r="B1091" s="28">
         <v>100800</v>
       </c>
       <c r="C1091" s="28">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D1091" s="28">
         <v>0</v>
       </c>
       <c r="E1091" s="28"/>
       <c r="F1091" s="28" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G1091" s="28"/>
       <c r="H1091" s="28">
         <v>3</v>
       </c>
       <c r="I1091" s="45" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
     </row>
     <row r="1092" spans="1:9">
       <c r="A1092" s="28">
-        <v>10080065</v>
+        <v>10080066</v>
       </c>
       <c r="B1092" s="28">
         <v>100800</v>
       </c>
       <c r="C1092" s="28">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D1092" s="28">
         <v>0</v>
       </c>
       <c r="E1092" s="28"/>
       <c r="F1092" s="28" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G1092" s="28"/>
       <c r="H1092" s="28">
         <v>3</v>
       </c>
       <c r="I1092" s="45" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="1093" spans="1:9">
       <c r="A1093" s="28">
-        <v>10080066</v>
+        <v>10080067</v>
       </c>
       <c r="B1093" s="28">
         <v>100800</v>
       </c>
       <c r="C1093" s="28">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1093" s="28">
         <v>0</v>
       </c>
       <c r="E1093" s="28"/>
       <c r="F1093" s="28" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G1093" s="28"/>
       <c r="H1093" s="28">
         <v>3</v>
       </c>
       <c r="I1093" s="45" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="1094" spans="1:9">
       <c r="A1094" s="28">
-        <v>10080067</v>
+        <v>10080068</v>
       </c>
       <c r="B1094" s="28">
         <v>100800</v>
       </c>
       <c r="C1094" s="28">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1094" s="28">
         <v>0</v>
       </c>
       <c r="E1094" s="28"/>
       <c r="F1094" s="28" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G1094" s="28"/>
       <c r="H1094" s="28">
         <v>3</v>
       </c>
       <c r="I1094" s="45" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
     </row>
     <row r="1095" spans="1:9">
       <c r="A1095" s="28">
-        <v>10080068</v>
+        <v>10080069</v>
       </c>
       <c r="B1095" s="28">
         <v>100800</v>
       </c>
       <c r="C1095" s="28">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1095" s="28">
         <v>0</v>
       </c>
       <c r="E1095" s="28"/>
       <c r="F1095" s="28" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G1095" s="28"/>
       <c r="H1095" s="28">
         <v>3</v>
       </c>
       <c r="I1095" s="45" t="s">
-        <v>903</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="1096" spans="1:9">
       <c r="A1096" s="28">
-        <v>10080069</v>
+        <v>10080070</v>
       </c>
       <c r="B1096" s="28">
         <v>100800</v>
       </c>
       <c r="C1096" s="28">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1096" s="28">
         <v>0</v>
       </c>
       <c r="E1096" s="28"/>
       <c r="F1096" s="28" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G1096" s="28"/>
       <c r="H1096" s="28">
         <v>3</v>
       </c>
       <c r="I1096" s="45" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="1097" spans="1:9">
       <c r="A1097" s="28">
-        <v>10080070</v>
+        <v>10080071</v>
       </c>
       <c r="B1097" s="28">
         <v>100800</v>
       </c>
       <c r="C1097" s="28">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D1097" s="28">
         <v>0</v>
       </c>
       <c r="E1097" s="28"/>
       <c r="F1097" s="28" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G1097" s="28"/>
       <c r="H1097" s="28">
         <v>3</v>
       </c>
       <c r="I1097" s="45" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="1098" spans="1:9">
       <c r="A1098" s="28">
-        <v>10080071</v>
+        <v>10080072</v>
       </c>
       <c r="B1098" s="28">
         <v>100800</v>
       </c>
       <c r="C1098" s="28">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D1098" s="28">
         <v>0</v>
       </c>
       <c r="E1098" s="28"/>
       <c r="F1098" s="28" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G1098" s="28"/>
       <c r="H1098" s="28">
         <v>3</v>
       </c>
       <c r="I1098" s="45" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="1099" spans="1:9">
       <c r="A1099" s="28">
-        <v>10080072</v>
+        <v>10080073</v>
       </c>
       <c r="B1099" s="28">
         <v>100800</v>
       </c>
       <c r="C1099" s="28">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1099" s="28">
         <v>0</v>
       </c>
       <c r="E1099" s="28"/>
       <c r="F1099" s="28" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G1099" s="28"/>
       <c r="H1099" s="28">
         <v>3</v>
       </c>
       <c r="I1099" s="45" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="1100" spans="1:9">
       <c r="A1100" s="28">
-        <v>10080073</v>
+        <v>10080074</v>
       </c>
       <c r="B1100" s="28">
         <v>100800</v>
       </c>
       <c r="C1100" s="28">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1100" s="28">
         <v>0</v>
@@ -33131,271 +33132,271 @@
       </c>
       <c r="G1100" s="28"/>
       <c r="H1100" s="28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1100" s="45" t="s">
-        <v>1201</v>
+        <v>924</v>
       </c>
     </row>
     <row r="1101" spans="1:9">
       <c r="A1101" s="28">
-        <v>10080074</v>
+        <v>10080075</v>
       </c>
       <c r="B1101" s="28">
         <v>100800</v>
       </c>
       <c r="C1101" s="28">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1101" s="28">
         <v>0</v>
       </c>
       <c r="E1101" s="28"/>
       <c r="F1101" s="28" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="G1101" s="28"/>
       <c r="H1101" s="28">
         <v>4</v>
       </c>
       <c r="I1101" s="45" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
     </row>
     <row r="1102" spans="1:9">
       <c r="A1102" s="28">
-        <v>10080075</v>
+        <v>10080076</v>
       </c>
       <c r="B1102" s="28">
         <v>100800</v>
       </c>
       <c r="C1102" s="28">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1102" s="28">
         <v>0</v>
       </c>
       <c r="E1102" s="28"/>
       <c r="F1102" s="28" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="G1102" s="28"/>
       <c r="H1102" s="28">
         <v>4</v>
       </c>
       <c r="I1102" s="45" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
     </row>
     <row r="1103" spans="1:9">
       <c r="A1103" s="28">
-        <v>10080076</v>
+        <v>10080077</v>
       </c>
       <c r="B1103" s="28">
         <v>100800</v>
       </c>
       <c r="C1103" s="28">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1103" s="28">
         <v>0</v>
       </c>
       <c r="E1103" s="28"/>
       <c r="F1103" s="28" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="G1103" s="28"/>
       <c r="H1103" s="28">
         <v>4</v>
       </c>
       <c r="I1103" s="45" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="1104" spans="1:9">
       <c r="A1104" s="28">
-        <v>10080077</v>
+        <v>10080078</v>
       </c>
       <c r="B1104" s="28">
         <v>100800</v>
       </c>
       <c r="C1104" s="28">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D1104" s="28">
         <v>0</v>
       </c>
       <c r="E1104" s="28"/>
       <c r="F1104" s="28" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="G1104" s="28"/>
       <c r="H1104" s="28">
         <v>4</v>
       </c>
       <c r="I1104" s="45" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
     </row>
     <row r="1105" spans="1:9">
       <c r="A1105" s="28">
-        <v>10080078</v>
+        <v>10080079</v>
       </c>
       <c r="B1105" s="28">
         <v>100800</v>
       </c>
       <c r="C1105" s="28">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D1105" s="28">
         <v>0</v>
       </c>
       <c r="E1105" s="28"/>
       <c r="F1105" s="28" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="G1105" s="28"/>
       <c r="H1105" s="28">
         <v>4</v>
       </c>
       <c r="I1105" s="45" t="s">
-        <v>936</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="1106" spans="1:9">
       <c r="A1106" s="28">
-        <v>10080079</v>
+        <v>10080080</v>
       </c>
       <c r="B1106" s="28">
         <v>100800</v>
       </c>
       <c r="C1106" s="28">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D1106" s="28">
         <v>0</v>
       </c>
       <c r="E1106" s="28"/>
       <c r="F1106" s="28" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="G1106" s="28"/>
       <c r="H1106" s="28">
         <v>4</v>
       </c>
       <c r="I1106" s="45" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="1107" spans="1:9">
       <c r="A1107" s="28">
-        <v>10080080</v>
+        <v>10080081</v>
       </c>
       <c r="B1107" s="28">
         <v>100800</v>
       </c>
       <c r="C1107" s="28">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D1107" s="28">
         <v>0</v>
       </c>
       <c r="E1107" s="28"/>
       <c r="F1107" s="28" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="G1107" s="28"/>
       <c r="H1107" s="28">
         <v>4</v>
       </c>
       <c r="I1107" s="45" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="1108" spans="1:9">
       <c r="A1108" s="28">
-        <v>10080081</v>
+        <v>10080082</v>
       </c>
       <c r="B1108" s="28">
         <v>100800</v>
       </c>
       <c r="C1108" s="28">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D1108" s="28">
         <v>0</v>
       </c>
       <c r="E1108" s="28"/>
       <c r="F1108" s="28" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="G1108" s="28"/>
       <c r="H1108" s="28">
         <v>4</v>
       </c>
       <c r="I1108" s="45" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="1109" spans="1:9">
       <c r="A1109" s="28">
-        <v>10080082</v>
+        <v>10080083</v>
       </c>
       <c r="B1109" s="28">
         <v>100800</v>
       </c>
       <c r="C1109" s="28">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D1109" s="28">
         <v>0</v>
       </c>
       <c r="E1109" s="28"/>
       <c r="F1109" s="28" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="G1109" s="28"/>
       <c r="H1109" s="28">
         <v>4</v>
       </c>
       <c r="I1109" s="45" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="1110" spans="1:9">
       <c r="A1110" s="28">
-        <v>10080083</v>
+        <v>10080084</v>
       </c>
       <c r="B1110" s="28">
         <v>100800</v>
       </c>
       <c r="C1110" s="28">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D1110" s="28">
         <v>0</v>
       </c>
       <c r="E1110" s="28"/>
       <c r="F1110" s="28" t="s">
-        <v>1497</v>
+        <v>513</v>
       </c>
       <c r="G1110" s="28"/>
-      <c r="H1110" s="28">
-        <v>4</v>
+      <c r="H1110" s="64">
+        <v>2</v>
       </c>
       <c r="I1110" s="45" t="s">
-        <v>1228</v>
+        <v>957</v>
       </c>
     </row>
     <row r="1111" spans="1:9">
       <c r="A1111" s="28">
-        <v>10080084</v>
+        <v>10080085</v>
       </c>
       <c r="B1111" s="28">
         <v>100800</v>
       </c>
       <c r="C1111" s="28">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D1111" s="28">
         <v>0</v>
@@ -33405,22 +33406,22 @@
         <v>513</v>
       </c>
       <c r="G1111" s="28"/>
-      <c r="H1111" s="64">
+      <c r="H1111" s="28">
         <v>2</v>
       </c>
       <c r="I1111" s="45" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
     </row>
     <row r="1112" spans="1:9">
       <c r="A1112" s="28">
-        <v>10080085</v>
+        <v>10080086</v>
       </c>
       <c r="B1112" s="28">
         <v>100800</v>
       </c>
       <c r="C1112" s="28">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D1112" s="28">
         <v>0</v>
@@ -33430,22 +33431,22 @@
         <v>513</v>
       </c>
       <c r="G1112" s="28"/>
-      <c r="H1112" s="28">
+      <c r="H1112" s="64">
         <v>2</v>
       </c>
       <c r="I1112" s="45" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
     </row>
     <row r="1113" spans="1:9">
       <c r="A1113" s="28">
-        <v>10080086</v>
+        <v>10080087</v>
       </c>
       <c r="B1113" s="28">
         <v>100800</v>
       </c>
       <c r="C1113" s="28">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D1113" s="28">
         <v>0</v>
@@ -33455,22 +33456,22 @@
         <v>513</v>
       </c>
       <c r="G1113" s="28"/>
-      <c r="H1113" s="64">
+      <c r="H1113" s="28">
         <v>2</v>
       </c>
       <c r="I1113" s="45" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
     </row>
     <row r="1114" spans="1:9">
       <c r="A1114" s="28">
-        <v>10080087</v>
+        <v>10080088</v>
       </c>
       <c r="B1114" s="28">
         <v>100800</v>
       </c>
       <c r="C1114" s="28">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1114" s="28">
         <v>0</v>
@@ -33480,22 +33481,22 @@
         <v>513</v>
       </c>
       <c r="G1114" s="28"/>
-      <c r="H1114" s="28">
+      <c r="H1114" s="64">
         <v>2</v>
       </c>
       <c r="I1114" s="45" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
     </row>
     <row r="1115" spans="1:9">
       <c r="A1115" s="28">
-        <v>10080088</v>
+        <v>10080089</v>
       </c>
       <c r="B1115" s="28">
         <v>100800</v>
       </c>
       <c r="C1115" s="28">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D1115" s="28">
         <v>0</v>
@@ -33505,22 +33506,22 @@
         <v>513</v>
       </c>
       <c r="G1115" s="28"/>
-      <c r="H1115" s="64">
+      <c r="H1115" s="28">
         <v>2</v>
       </c>
       <c r="I1115" s="45" t="s">
-        <v>965</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="1116" spans="1:9">
       <c r="A1116" s="28">
-        <v>10080089</v>
+        <v>10080090</v>
       </c>
       <c r="B1116" s="28">
         <v>100800</v>
       </c>
       <c r="C1116" s="28">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D1116" s="28">
         <v>0</v>
@@ -33530,22 +33531,22 @@
         <v>513</v>
       </c>
       <c r="G1116" s="28"/>
-      <c r="H1116" s="28">
+      <c r="H1116" s="64">
         <v>2</v>
       </c>
       <c r="I1116" s="45" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="1117" spans="1:9">
       <c r="A1117" s="28">
-        <v>10080090</v>
+        <v>10080091</v>
       </c>
       <c r="B1117" s="28">
         <v>100800</v>
       </c>
       <c r="C1117" s="28">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D1117" s="28">
         <v>0</v>
@@ -33555,22 +33556,22 @@
         <v>513</v>
       </c>
       <c r="G1117" s="28"/>
-      <c r="H1117" s="64">
+      <c r="H1117" s="28">
         <v>2</v>
       </c>
       <c r="I1117" s="45" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="1118" spans="1:9">
       <c r="A1118" s="28">
-        <v>10080091</v>
+        <v>10080092</v>
       </c>
       <c r="B1118" s="28">
         <v>100800</v>
       </c>
       <c r="C1118" s="28">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D1118" s="28">
         <v>0</v>
@@ -33580,22 +33581,22 @@
         <v>513</v>
       </c>
       <c r="G1118" s="28"/>
-      <c r="H1118" s="28">
+      <c r="H1118" s="64">
         <v>2</v>
       </c>
       <c r="I1118" s="45" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="1119" spans="1:9">
       <c r="A1119" s="28">
-        <v>10080092</v>
+        <v>10080093</v>
       </c>
       <c r="B1119" s="28">
         <v>100800</v>
       </c>
       <c r="C1119" s="28">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D1119" s="28">
         <v>0</v>
@@ -33605,47 +33606,47 @@
         <v>513</v>
       </c>
       <c r="G1119" s="28"/>
-      <c r="H1119" s="64">
+      <c r="H1119" s="28">
         <v>2</v>
       </c>
       <c r="I1119" s="45" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="1120" spans="1:9">
       <c r="A1120" s="28">
-        <v>10080093</v>
+        <v>10080094</v>
       </c>
       <c r="B1120" s="28">
         <v>100800</v>
       </c>
       <c r="C1120" s="28">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D1120" s="28">
         <v>0</v>
       </c>
       <c r="E1120" s="28"/>
       <c r="F1120" s="28" t="s">
-        <v>513</v>
+        <v>979</v>
       </c>
       <c r="G1120" s="28"/>
       <c r="H1120" s="28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1120" s="45" t="s">
-        <v>1246</v>
+        <v>980</v>
       </c>
     </row>
     <row r="1121" spans="1:9">
       <c r="A1121" s="28">
-        <v>10080094</v>
+        <v>10080095</v>
       </c>
       <c r="B1121" s="28">
         <v>100800</v>
       </c>
       <c r="C1121" s="28">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D1121" s="28">
         <v>0</v>
@@ -33659,18 +33660,18 @@
         <v>3</v>
       </c>
       <c r="I1121" s="45" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="1122" spans="1:9">
       <c r="A1122" s="28">
-        <v>10080095</v>
+        <v>10080096</v>
       </c>
       <c r="B1122" s="28">
         <v>100800</v>
       </c>
       <c r="C1122" s="28">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D1122" s="28">
         <v>0</v>
@@ -33684,18 +33685,18 @@
         <v>3</v>
       </c>
       <c r="I1122" s="45" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="1123" spans="1:9">
       <c r="A1123" s="28">
-        <v>10080096</v>
+        <v>10080097</v>
       </c>
       <c r="B1123" s="28">
         <v>100800</v>
       </c>
       <c r="C1123" s="28">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D1123" s="28">
         <v>0</v>
@@ -33709,18 +33710,18 @@
         <v>3</v>
       </c>
       <c r="I1123" s="45" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
     </row>
     <row r="1124" spans="1:9">
       <c r="A1124" s="28">
-        <v>10080097</v>
+        <v>10080098</v>
       </c>
       <c r="B1124" s="28">
         <v>100800</v>
       </c>
       <c r="C1124" s="28">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D1124" s="28">
         <v>0</v>
@@ -33734,18 +33735,18 @@
         <v>3</v>
       </c>
       <c r="I1124" s="45" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
     </row>
     <row r="1125" spans="1:9">
       <c r="A1125" s="28">
-        <v>10080098</v>
+        <v>10080099</v>
       </c>
       <c r="B1125" s="28">
         <v>100800</v>
       </c>
       <c r="C1125" s="28">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D1125" s="28">
         <v>0</v>
@@ -33759,18 +33760,18 @@
         <v>3</v>
       </c>
       <c r="I1125" s="45" t="s">
-        <v>988</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="1126" spans="1:9">
       <c r="A1126" s="28">
-        <v>10080099</v>
+        <v>10080100</v>
       </c>
       <c r="B1126" s="28">
         <v>100800</v>
       </c>
       <c r="C1126" s="28">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D1126" s="28">
         <v>0</v>
@@ -33784,18 +33785,18 @@
         <v>3</v>
       </c>
       <c r="I1126" s="45" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="1127" spans="1:9">
       <c r="A1127" s="28">
-        <v>10080100</v>
+        <v>10080101</v>
       </c>
       <c r="B1127" s="28">
         <v>100800</v>
       </c>
       <c r="C1127" s="28">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D1127" s="28">
         <v>0</v>
@@ -33809,18 +33810,18 @@
         <v>3</v>
       </c>
       <c r="I1127" s="45" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="1128" spans="1:9">
       <c r="A1128" s="28">
-        <v>10080101</v>
+        <v>10080102</v>
       </c>
       <c r="B1128" s="28">
         <v>100800</v>
       </c>
       <c r="C1128" s="28">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D1128" s="28">
         <v>0</v>
@@ -33834,18 +33835,18 @@
         <v>3</v>
       </c>
       <c r="I1128" s="45" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="1129" spans="1:9">
       <c r="A1129" s="28">
-        <v>10080102</v>
+        <v>10080103</v>
       </c>
       <c r="B1129" s="28">
         <v>100800</v>
       </c>
       <c r="C1129" s="28">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D1129" s="28">
         <v>0</v>
@@ -33859,293 +33860,289 @@
         <v>3</v>
       </c>
       <c r="I1129" s="45" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="1130" spans="1:9">
       <c r="A1130" s="28">
-        <v>10080103</v>
+        <v>10080104</v>
       </c>
       <c r="B1130" s="28">
         <v>100800</v>
       </c>
       <c r="C1130" s="28">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D1130" s="28">
         <v>0</v>
       </c>
       <c r="E1130" s="28"/>
       <c r="F1130" s="28" t="s">
-        <v>979</v>
+        <v>1497</v>
       </c>
       <c r="G1130" s="28"/>
       <c r="H1130" s="28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1130" s="45" t="s">
-        <v>1263</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="1131" spans="1:9">
       <c r="A1131" s="28">
-        <v>10080104</v>
+        <v>10080105</v>
       </c>
       <c r="B1131" s="28">
         <v>100800</v>
       </c>
       <c r="C1131" s="28">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D1131" s="28">
         <v>0</v>
       </c>
       <c r="E1131" s="28"/>
       <c r="F1131" s="28" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="G1131" s="28"/>
       <c r="H1131" s="28">
         <v>4</v>
       </c>
       <c r="I1131" s="45" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="1132" spans="1:9">
       <c r="A1132" s="28">
-        <v>10080105</v>
+        <v>10080106</v>
       </c>
       <c r="B1132" s="28">
         <v>100800</v>
       </c>
       <c r="C1132" s="28">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D1132" s="28">
         <v>0</v>
       </c>
       <c r="E1132" s="28"/>
       <c r="F1132" s="28" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="G1132" s="28"/>
       <c r="H1132" s="28">
         <v>4</v>
       </c>
       <c r="I1132" s="45" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="1133" spans="1:9">
       <c r="A1133" s="28">
-        <v>10080106</v>
+        <v>10080107</v>
       </c>
       <c r="B1133" s="28">
         <v>100800</v>
       </c>
       <c r="C1133" s="28">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D1133" s="28">
         <v>0</v>
       </c>
       <c r="E1133" s="28"/>
       <c r="F1133" s="28" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="G1133" s="28"/>
       <c r="H1133" s="28">
         <v>4</v>
       </c>
       <c r="I1133" s="45" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="1134" spans="1:9">
       <c r="A1134" s="28">
-        <v>10080107</v>
+        <v>10080108</v>
       </c>
       <c r="B1134" s="28">
         <v>100800</v>
       </c>
       <c r="C1134" s="28">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D1134" s="28">
         <v>0</v>
       </c>
       <c r="E1134" s="28"/>
       <c r="F1134" s="28" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="G1134" s="28"/>
       <c r="H1134" s="28">
         <v>4</v>
       </c>
       <c r="I1134" s="45" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="1135" spans="1:9">
       <c r="A1135" s="28">
-        <v>10080108</v>
+        <v>10080109</v>
       </c>
       <c r="B1135" s="28">
         <v>100800</v>
       </c>
       <c r="C1135" s="28">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D1135" s="28">
         <v>0</v>
       </c>
       <c r="E1135" s="28"/>
       <c r="F1135" s="28" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="G1135" s="28"/>
       <c r="H1135" s="28">
         <v>4</v>
       </c>
       <c r="I1135" s="45" t="s">
-        <v>1011</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="1136" spans="1:9">
       <c r="A1136" s="28">
-        <v>10080109</v>
+        <v>10080110</v>
       </c>
       <c r="B1136" s="28">
         <v>100800</v>
       </c>
       <c r="C1136" s="28">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D1136" s="28">
         <v>0</v>
       </c>
       <c r="E1136" s="28"/>
       <c r="F1136" s="28" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="G1136" s="28"/>
       <c r="H1136" s="28">
         <v>4</v>
       </c>
       <c r="I1136" s="45" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="1137" spans="1:9">
       <c r="A1137" s="28">
-        <v>10080110</v>
+        <v>10080111</v>
       </c>
       <c r="B1137" s="28">
         <v>100800</v>
       </c>
       <c r="C1137" s="28">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1137" s="28">
         <v>0</v>
       </c>
       <c r="E1137" s="28"/>
       <c r="F1137" s="28" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="G1137" s="28"/>
       <c r="H1137" s="28">
         <v>4</v>
       </c>
       <c r="I1137" s="45" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="1138" spans="1:9">
       <c r="A1138" s="28">
-        <v>10080111</v>
+        <v>10080112</v>
       </c>
       <c r="B1138" s="28">
         <v>100800</v>
       </c>
       <c r="C1138" s="28">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D1138" s="28">
         <v>0</v>
       </c>
       <c r="E1138" s="28"/>
       <c r="F1138" s="28" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="G1138" s="28"/>
       <c r="H1138" s="28">
         <v>4</v>
       </c>
       <c r="I1138" s="45" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1139" spans="1:9">
       <c r="A1139" s="28">
-        <v>10080112</v>
+        <v>10080113</v>
       </c>
       <c r="B1139" s="28">
         <v>100800</v>
       </c>
       <c r="C1139" s="28">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D1139" s="28">
         <v>0</v>
       </c>
       <c r="E1139" s="28"/>
       <c r="F1139" s="28" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="G1139" s="28"/>
       <c r="H1139" s="28">
         <v>4</v>
       </c>
       <c r="I1139" s="45" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="1140" spans="1:9">
-      <c r="A1140" s="28">
-        <v>10080113</v>
-      </c>
-      <c r="B1140" s="28">
-        <v>100800</v>
-      </c>
-      <c r="C1140" s="28">
-        <v>113</v>
-      </c>
-      <c r="D1140" s="28">
-        <v>0</v>
-      </c>
-      <c r="E1140" s="28"/>
-      <c r="F1140" s="28" t="s">
+      <c r="A1140" s="65">
+        <v>10530001</v>
+      </c>
+      <c r="B1140" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1140" s="65">
+        <v>1</v>
+      </c>
+      <c r="D1140" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1140" s="65"/>
+      <c r="F1140" s="65"/>
+      <c r="G1140" s="65"/>
+      <c r="H1140" s="65"/>
+      <c r="I1140" s="65" t="s">
         <v>1498</v>
-      </c>
-      <c r="G1140" s="28"/>
-      <c r="H1140" s="28">
-        <v>4</v>
-      </c>
-      <c r="I1140" s="45" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="1141" spans="1:9">
       <c r="A1141" s="65">
-        <v>10530001</v>
+        <v>10530002</v>
       </c>
       <c r="B1141" s="65">
         <v>105300</v>
       </c>
       <c r="C1141" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1141" s="65">
         <v>0</v>
@@ -34160,13 +34157,13 @@
     </row>
     <row r="1142" spans="1:9">
       <c r="A1142" s="65">
-        <v>10530002</v>
+        <v>10530003</v>
       </c>
       <c r="B1142" s="65">
         <v>105300</v>
       </c>
       <c r="C1142" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1142" s="65">
         <v>0</v>
@@ -34181,13 +34178,13 @@
     </row>
     <row r="1143" spans="1:9">
       <c r="A1143" s="65">
-        <v>10530003</v>
+        <v>10530004</v>
       </c>
       <c r="B1143" s="65">
         <v>105300</v>
       </c>
       <c r="C1143" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1143" s="65">
         <v>0</v>
@@ -34202,13 +34199,13 @@
     </row>
     <row r="1144" spans="1:9">
       <c r="A1144" s="65">
-        <v>10530004</v>
+        <v>10530005</v>
       </c>
       <c r="B1144" s="65">
         <v>105300</v>
       </c>
       <c r="C1144" s="65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1144" s="65">
         <v>0</v>
@@ -34223,13 +34220,13 @@
     </row>
     <row r="1145" spans="1:9">
       <c r="A1145" s="65">
-        <v>10530005</v>
+        <v>10530006</v>
       </c>
       <c r="B1145" s="65">
         <v>105300</v>
       </c>
       <c r="C1145" s="65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1145" s="65">
         <v>0</v>
@@ -34239,18 +34236,18 @@
       <c r="G1145" s="65"/>
       <c r="H1145" s="65"/>
       <c r="I1145" s="65" t="s">
-        <v>1503</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1146" spans="1:9">
       <c r="A1146" s="65">
-        <v>10530006</v>
+        <v>10530007</v>
       </c>
       <c r="B1146" s="65">
         <v>105300</v>
       </c>
       <c r="C1146" s="65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D1146" s="65">
         <v>0</v>
@@ -34260,18 +34257,18 @@
       <c r="G1146" s="65"/>
       <c r="H1146" s="65"/>
       <c r="I1146" s="65" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="1147" spans="1:9">
       <c r="A1147" s="65">
-        <v>10530007</v>
+        <v>10530008</v>
       </c>
       <c r="B1147" s="65">
         <v>105300</v>
       </c>
       <c r="C1147" s="65">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1147" s="65">
         <v>0</v>
@@ -34281,18 +34278,18 @@
       <c r="G1147" s="65"/>
       <c r="H1147" s="65"/>
       <c r="I1147" s="65" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1148" spans="1:9">
       <c r="A1148" s="65">
-        <v>10530008</v>
+        <v>10530009</v>
       </c>
       <c r="B1148" s="65">
         <v>105300</v>
       </c>
       <c r="C1148" s="65">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1148" s="65">
         <v>0</v>
@@ -34302,88 +34299,90 @@
       <c r="G1148" s="65"/>
       <c r="H1148" s="65"/>
       <c r="I1148" s="65" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1149" spans="1:9">
       <c r="A1149" s="65">
-        <v>10530009</v>
+        <v>10530010</v>
       </c>
       <c r="B1149" s="65">
         <v>105300</v>
       </c>
       <c r="C1149" s="65">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D1149" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1149" s="65"/>
       <c r="F1149" s="65"/>
       <c r="G1149" s="65"/>
       <c r="H1149" s="65"/>
       <c r="I1149" s="65" t="s">
-        <v>115</v>
+        <v>249</v>
       </c>
     </row>
     <row r="1150" spans="1:9">
       <c r="A1150" s="65">
-        <v>10530010</v>
+        <v>10530011</v>
       </c>
       <c r="B1150" s="65">
         <v>105300</v>
       </c>
       <c r="C1150" s="65">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D1150" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1150" s="65"/>
       <c r="F1150" s="65"/>
       <c r="G1150" s="65"/>
       <c r="H1150" s="65"/>
       <c r="I1150" s="65" t="s">
-        <v>249</v>
+        <v>119</v>
       </c>
     </row>
     <row r="1151" spans="1:9">
       <c r="A1151" s="65">
-        <v>10530011</v>
+        <v>10530012</v>
       </c>
       <c r="B1151" s="65">
         <v>105300</v>
       </c>
       <c r="C1151" s="65">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1151" s="65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1151" s="65"/>
-      <c r="F1151" s="65"/>
+      <c r="F1151" s="65" t="s">
+        <v>1503</v>
+      </c>
       <c r="G1151" s="65"/>
       <c r="H1151" s="65"/>
       <c r="I1151" s="65" t="s">
-        <v>119</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="1152" spans="1:9">
       <c r="A1152" s="65">
-        <v>10530012</v>
+        <v>10530013</v>
       </c>
       <c r="B1152" s="65">
         <v>105300</v>
       </c>
       <c r="C1152" s="65">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1152" s="65">
         <v>0</v>
       </c>
       <c r="E1152" s="65"/>
       <c r="F1152" s="65" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="G1152" s="65"/>
       <c r="H1152" s="65"/>
@@ -34393,20 +34392,20 @@
     </row>
     <row r="1153" spans="1:9">
       <c r="A1153" s="65">
-        <v>10530013</v>
+        <v>10530014</v>
       </c>
       <c r="B1153" s="65">
         <v>105300</v>
       </c>
       <c r="C1153" s="65">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1153" s="65">
         <v>0</v>
       </c>
       <c r="E1153" s="65"/>
       <c r="F1153" s="65" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="G1153" s="65"/>
       <c r="H1153" s="65"/>
@@ -34416,20 +34415,20 @@
     </row>
     <row r="1154" spans="1:9">
       <c r="A1154" s="65">
-        <v>10530014</v>
+        <v>10530015</v>
       </c>
       <c r="B1154" s="65">
         <v>105300</v>
       </c>
       <c r="C1154" s="65">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1154" s="65">
         <v>0</v>
       </c>
       <c r="E1154" s="65"/>
       <c r="F1154" s="65" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="G1154" s="65"/>
       <c r="H1154" s="65"/>
@@ -34439,20 +34438,20 @@
     </row>
     <row r="1155" spans="1:9">
       <c r="A1155" s="65">
-        <v>10530015</v>
+        <v>10530016</v>
       </c>
       <c r="B1155" s="65">
         <v>105300</v>
       </c>
       <c r="C1155" s="65">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1155" s="65">
         <v>0</v>
       </c>
       <c r="E1155" s="65"/>
       <c r="F1155" s="65" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="G1155" s="65"/>
       <c r="H1155" s="65"/>
@@ -34462,128 +34461,126 @@
     </row>
     <row r="1156" spans="1:9">
       <c r="A1156" s="65">
-        <v>10530016</v>
+        <v>10530017</v>
       </c>
       <c r="B1156" s="65">
         <v>105300</v>
       </c>
       <c r="C1156" s="65">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1156" s="65">
         <v>0</v>
       </c>
       <c r="E1156" s="65"/>
       <c r="F1156" s="65" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="G1156" s="65"/>
       <c r="H1156" s="65"/>
       <c r="I1156" s="65" t="s">
-        <v>1509</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1157" spans="1:9">
       <c r="A1157" s="65">
-        <v>10530017</v>
+        <v>10530018</v>
       </c>
       <c r="B1157" s="65">
         <v>105300</v>
       </c>
       <c r="C1157" s="65">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1157" s="65">
         <v>0</v>
       </c>
       <c r="E1157" s="65"/>
       <c r="F1157" s="65" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="G1157" s="65"/>
       <c r="H1157" s="65"/>
       <c r="I1157" s="65" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="1158" spans="1:9">
       <c r="A1158" s="65">
-        <v>10530018</v>
+        <v>10530019</v>
       </c>
       <c r="B1158" s="65">
         <v>105300</v>
       </c>
       <c r="C1158" s="65">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1158" s="65">
         <v>0</v>
       </c>
       <c r="E1158" s="65"/>
       <c r="F1158" s="65" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="G1158" s="65"/>
       <c r="H1158" s="65"/>
       <c r="I1158" s="65" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1159" spans="1:9">
       <c r="A1159" s="65">
-        <v>10530019</v>
+        <v>10530020</v>
       </c>
       <c r="B1159" s="65">
         <v>105300</v>
       </c>
       <c r="C1159" s="65">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1159" s="65">
         <v>0</v>
       </c>
       <c r="E1159" s="65"/>
       <c r="F1159" s="65" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="G1159" s="65"/>
       <c r="H1159" s="65"/>
       <c r="I1159" s="65" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="1160" spans="1:9">
-      <c r="A1160" s="65">
-        <v>10530020</v>
-      </c>
-      <c r="B1160" s="65">
-        <v>105300</v>
-      </c>
-      <c r="C1160" s="65">
-        <v>20</v>
-      </c>
-      <c r="D1160" s="65">
-        <v>0</v>
-      </c>
-      <c r="E1160" s="65"/>
-      <c r="F1160" s="65" t="s">
-        <v>1504</v>
-      </c>
-      <c r="G1160" s="65"/>
-      <c r="H1160" s="65"/>
-      <c r="I1160" s="65" t="s">
-        <v>136</v>
+      <c r="A1160" s="23">
+        <v>10570001</v>
+      </c>
+      <c r="B1160" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1160" s="23">
+        <v>1</v>
+      </c>
+      <c r="D1160" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1160" s="23"/>
+      <c r="F1160" s="23"/>
+      <c r="G1160" s="23"/>
+      <c r="H1160" s="23"/>
+      <c r="I1160" s="23" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="1161" spans="1:9">
       <c r="A1161" s="23">
-        <v>10570001</v>
+        <v>10570002</v>
       </c>
       <c r="B1161" s="23">
         <v>105700</v>
       </c>
       <c r="C1161" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1161" s="23">
         <v>0</v>
@@ -34593,18 +34590,18 @@
       <c r="G1161" s="23"/>
       <c r="H1161" s="23"/>
       <c r="I1161" s="23" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1162" spans="1:9">
       <c r="A1162" s="23">
-        <v>10570002</v>
+        <v>10570003</v>
       </c>
       <c r="B1162" s="23">
         <v>105700</v>
       </c>
       <c r="C1162" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1162" s="23">
         <v>0</v>
@@ -34614,18 +34611,18 @@
       <c r="G1162" s="23"/>
       <c r="H1162" s="23"/>
       <c r="I1162" s="23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1163" spans="1:9">
       <c r="A1163" s="23">
-        <v>10570003</v>
+        <v>10570004</v>
       </c>
       <c r="B1163" s="23">
         <v>105700</v>
       </c>
       <c r="C1163" s="23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1163" s="23">
         <v>0</v>
@@ -34635,18 +34632,18 @@
       <c r="G1163" s="23"/>
       <c r="H1163" s="23"/>
       <c r="I1163" s="23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1164" spans="1:9">
       <c r="A1164" s="23">
-        <v>10570004</v>
+        <v>10570005</v>
       </c>
       <c r="B1164" s="23">
         <v>105700</v>
       </c>
       <c r="C1164" s="23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1164" s="23">
         <v>0</v>
@@ -34656,18 +34653,18 @@
       <c r="G1164" s="23"/>
       <c r="H1164" s="23"/>
       <c r="I1164" s="23" t="s">
-        <v>27</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="1165" spans="1:9">
       <c r="A1165" s="23">
-        <v>10570005</v>
+        <v>10570006</v>
       </c>
       <c r="B1165" s="23">
         <v>105700</v>
       </c>
       <c r="C1165" s="23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1165" s="23">
         <v>0</v>
@@ -34677,18 +34674,18 @@
       <c r="G1165" s="23"/>
       <c r="H1165" s="23"/>
       <c r="I1165" s="23" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="1166" spans="1:9">
       <c r="A1166" s="23">
-        <v>10570006</v>
+        <v>10570007</v>
       </c>
       <c r="B1166" s="23">
         <v>105700</v>
       </c>
       <c r="C1166" s="23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D1166" s="23">
         <v>0</v>
@@ -34698,18 +34695,18 @@
       <c r="G1166" s="23"/>
       <c r="H1166" s="23"/>
       <c r="I1166" s="23" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="1167" spans="1:9">
       <c r="A1167" s="23">
-        <v>10570007</v>
+        <v>10570008</v>
       </c>
       <c r="B1167" s="23">
         <v>105700</v>
       </c>
       <c r="C1167" s="23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1167" s="23">
         <v>0</v>
@@ -34719,60 +34716,60 @@
       <c r="G1167" s="23"/>
       <c r="H1167" s="23"/>
       <c r="I1167" s="23" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="1168" spans="1:9">
       <c r="A1168" s="23">
-        <v>10570008</v>
+        <v>10570009</v>
       </c>
       <c r="B1168" s="23">
         <v>105700</v>
       </c>
       <c r="C1168" s="23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1168" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1168" s="23"/>
       <c r="F1168" s="23"/>
       <c r="G1168" s="23"/>
       <c r="H1168" s="23"/>
       <c r="I1168" s="23" t="s">
-        <v>1086</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1169" spans="1:9">
       <c r="A1169" s="23">
-        <v>10570009</v>
+        <v>10570010</v>
       </c>
       <c r="B1169" s="23">
         <v>105700</v>
       </c>
       <c r="C1169" s="23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D1169" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1169" s="23"/>
       <c r="F1169" s="23"/>
       <c r="G1169" s="23"/>
       <c r="H1169" s="23"/>
       <c r="I1169" s="23" t="s">
-        <v>39</v>
+        <v>208</v>
       </c>
     </row>
     <row r="1170" spans="1:9">
       <c r="A1170" s="23">
-        <v>10570010</v>
+        <v>10570011</v>
       </c>
       <c r="B1170" s="23">
         <v>105700</v>
       </c>
       <c r="C1170" s="23">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D1170" s="23">
         <v>2</v>
@@ -34782,18 +34779,18 @@
       <c r="G1170" s="23"/>
       <c r="H1170" s="23"/>
       <c r="I1170" s="23" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
     </row>
     <row r="1171" spans="1:9">
       <c r="A1171" s="23">
-        <v>10570011</v>
+        <v>10570012</v>
       </c>
       <c r="B1171" s="23">
         <v>105700</v>
       </c>
       <c r="C1171" s="23">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1171" s="23">
         <v>2</v>
@@ -34803,18 +34800,18 @@
       <c r="G1171" s="23"/>
       <c r="H1171" s="23"/>
       <c r="I1171" s="23" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1172" spans="1:9">
       <c r="A1172" s="23">
-        <v>10570012</v>
+        <v>10570013</v>
       </c>
       <c r="B1172" s="23">
         <v>105700</v>
       </c>
       <c r="C1172" s="23">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1172" s="23">
         <v>2</v>
@@ -34824,18 +34821,18 @@
       <c r="G1172" s="23"/>
       <c r="H1172" s="23"/>
       <c r="I1172" s="23" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1173" spans="1:9">
       <c r="A1173" s="23">
-        <v>10570013</v>
+        <v>10570014</v>
       </c>
       <c r="B1173" s="23">
         <v>105700</v>
       </c>
       <c r="C1173" s="23">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1173" s="23">
         <v>2</v>
@@ -34845,39 +34842,41 @@
       <c r="G1173" s="23"/>
       <c r="H1173" s="23"/>
       <c r="I1173" s="23" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="1174" spans="1:9">
       <c r="A1174" s="23">
-        <v>10570014</v>
+        <v>10570015</v>
       </c>
       <c r="B1174" s="23">
         <v>105700</v>
       </c>
       <c r="C1174" s="23">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1174" s="23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1174" s="23"/>
-      <c r="F1174" s="23"/>
+      <c r="F1174" s="23" t="s">
+        <v>121</v>
+      </c>
       <c r="G1174" s="23"/>
       <c r="H1174" s="23"/>
       <c r="I1174" s="23" t="s">
-        <v>232</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="1175" spans="1:9">
       <c r="A1175" s="23">
-        <v>10570015</v>
+        <v>10570016</v>
       </c>
       <c r="B1175" s="23">
         <v>105700</v>
       </c>
       <c r="C1175" s="23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1175" s="23">
         <v>0</v>
@@ -34894,13 +34893,13 @@
     </row>
     <row r="1176" spans="1:9">
       <c r="A1176" s="23">
-        <v>10570016</v>
+        <v>10570017</v>
       </c>
       <c r="B1176" s="23">
         <v>105700</v>
       </c>
       <c r="C1176" s="23">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1176" s="23">
         <v>0</v>
@@ -34917,13 +34916,13 @@
     </row>
     <row r="1177" spans="1:9">
       <c r="A1177" s="23">
-        <v>10570017</v>
+        <v>10570018</v>
       </c>
       <c r="B1177" s="23">
         <v>105700</v>
       </c>
       <c r="C1177" s="23">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1177" s="23">
         <v>0</v>
@@ -34940,13 +34939,13 @@
     </row>
     <row r="1178" spans="1:9">
       <c r="A1178" s="23">
-        <v>10570018</v>
+        <v>10570019</v>
       </c>
       <c r="B1178" s="23">
         <v>105700</v>
       </c>
       <c r="C1178" s="23">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1178" s="23">
         <v>0</v>
@@ -34963,13 +34962,13 @@
     </row>
     <row r="1179" spans="1:9">
       <c r="A1179" s="23">
-        <v>10570019</v>
+        <v>10570020</v>
       </c>
       <c r="B1179" s="23">
         <v>105700</v>
       </c>
       <c r="C1179" s="23">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1179" s="23">
         <v>0</v>
@@ -34986,13 +34985,13 @@
     </row>
     <row r="1180" spans="1:9">
       <c r="A1180" s="23">
-        <v>10570020</v>
+        <v>10570021</v>
       </c>
       <c r="B1180" s="23">
         <v>105700</v>
       </c>
       <c r="C1180" s="23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1180" s="23">
         <v>0</v>
@@ -35009,13 +35008,13 @@
     </row>
     <row r="1181" spans="1:9">
       <c r="A1181" s="23">
-        <v>10570021</v>
+        <v>10570022</v>
       </c>
       <c r="B1181" s="23">
         <v>105700</v>
       </c>
       <c r="C1181" s="23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1181" s="23">
         <v>0</v>
@@ -35031,37 +35030,35 @@
       </c>
     </row>
     <row r="1182" spans="1:9">
-      <c r="A1182" s="23">
-        <v>10570022</v>
-      </c>
-      <c r="B1182" s="23">
-        <v>105700</v>
-      </c>
-      <c r="C1182" s="23">
-        <v>22</v>
-      </c>
-      <c r="D1182" s="23">
-        <v>0</v>
-      </c>
-      <c r="E1182" s="23"/>
-      <c r="F1182" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="G1182" s="23"/>
-      <c r="H1182" s="23"/>
-      <c r="I1182" s="23" t="s">
+      <c r="A1182" s="43">
+        <v>10580001</v>
+      </c>
+      <c r="B1182" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1182" s="43">
+        <v>1</v>
+      </c>
+      <c r="D1182" s="43">
+        <v>0</v>
+      </c>
+      <c r="E1182" s="43"/>
+      <c r="F1182" s="43"/>
+      <c r="G1182" s="43"/>
+      <c r="H1182" s="43"/>
+      <c r="I1182" s="43" t="s">
         <v>1517</v>
       </c>
     </row>
     <row r="1183" spans="1:9">
       <c r="A1183" s="43">
-        <v>10580001</v>
+        <v>10580002</v>
       </c>
       <c r="B1183" s="43">
         <v>105800</v>
       </c>
       <c r="C1183" s="43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1183" s="43">
         <v>0</v>
@@ -35076,13 +35073,13 @@
     </row>
     <row r="1184" spans="1:9">
       <c r="A1184" s="43">
-        <v>10580002</v>
+        <v>10580003</v>
       </c>
       <c r="B1184" s="43">
         <v>105800</v>
       </c>
       <c r="C1184" s="43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1184" s="43">
         <v>0</v>
@@ -35097,13 +35094,13 @@
     </row>
     <row r="1185" spans="1:9">
       <c r="A1185" s="43">
-        <v>10580003</v>
+        <v>10580004</v>
       </c>
       <c r="B1185" s="43">
         <v>105800</v>
       </c>
       <c r="C1185" s="43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1185" s="43">
         <v>0</v>
@@ -35118,13 +35115,13 @@
     </row>
     <row r="1186" spans="1:9">
       <c r="A1186" s="43">
-        <v>10580004</v>
+        <v>10580005</v>
       </c>
       <c r="B1186" s="43">
         <v>105800</v>
       </c>
       <c r="C1186" s="43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1186" s="43">
         <v>0</v>
@@ -35139,13 +35136,13 @@
     </row>
     <row r="1187" spans="1:9">
       <c r="A1187" s="43">
-        <v>10580005</v>
+        <v>10580006</v>
       </c>
       <c r="B1187" s="43">
         <v>105800</v>
       </c>
       <c r="C1187" s="43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1187" s="43">
         <v>0</v>
@@ -35160,13 +35157,13 @@
     </row>
     <row r="1188" spans="1:9">
       <c r="A1188" s="43">
-        <v>10580006</v>
+        <v>10580007</v>
       </c>
       <c r="B1188" s="43">
         <v>105800</v>
       </c>
       <c r="C1188" s="43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D1188" s="43">
         <v>0</v>
@@ -35181,34 +35178,34 @@
     </row>
     <row r="1189" spans="1:9">
       <c r="A1189" s="43">
-        <v>10580007</v>
+        <v>10580008</v>
       </c>
       <c r="B1189" s="43">
         <v>105800</v>
       </c>
       <c r="C1189" s="43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1189" s="43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1189" s="43"/>
       <c r="F1189" s="43"/>
       <c r="G1189" s="43"/>
       <c r="H1189" s="43"/>
       <c r="I1189" s="43" t="s">
-        <v>1524</v>
-      </c>
-    </row>
-    <row r="1190" spans="1:9">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1190" ht="17.25" spans="1:9">
       <c r="A1190" s="43">
-        <v>10580008</v>
+        <v>10580009</v>
       </c>
       <c r="B1190" s="43">
         <v>105800</v>
       </c>
       <c r="C1190" s="43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1190" s="43">
         <v>2</v>
@@ -35217,29 +35214,8 @@
       <c r="F1190" s="43"/>
       <c r="G1190" s="43"/>
       <c r="H1190" s="43"/>
-      <c r="I1190" s="43" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="1191" ht="17.25" spans="1:9">
-      <c r="A1191" s="43">
-        <v>10580009</v>
-      </c>
-      <c r="B1191" s="43">
-        <v>105800</v>
-      </c>
-      <c r="C1191" s="43">
-        <v>9</v>
-      </c>
-      <c r="D1191" s="43">
-        <v>2</v>
-      </c>
-      <c r="E1191" s="43"/>
-      <c r="F1191" s="43"/>
-      <c r="G1191" s="43"/>
-      <c r="H1191" s="43"/>
-      <c r="I1191" s="66" t="s">
-        <v>1525</v>
+      <c r="I1190" s="66" t="s">
+        <v>1524</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="1429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="1525">
   <si>
     <t>图标</t>
   </si>
@@ -4401,7 +4401,295 @@
     <t>彩池图标4</t>
   </si>
   <si>
-    <t>透明图标</t>
+    <t>图标1</t>
+  </si>
+  <si>
+    <t>图标2</t>
+  </si>
+  <si>
+    <t>图标3</t>
+  </si>
+  <si>
+    <t>图标4</t>
+  </si>
+  <si>
+    <t>图标5</t>
+  </si>
+  <si>
+    <t>图标1*2</t>
+  </si>
+  <si>
+    <t>图标2*2</t>
+  </si>
+  <si>
+    <t>图标3*2</t>
+  </si>
+  <si>
+    <t>图标4*2</t>
+  </si>
+  <si>
+    <t>图标5*2</t>
+  </si>
+  <si>
+    <t>Wild*2</t>
+  </si>
+  <si>
+    <t>图标1*3</t>
+  </si>
+  <si>
+    <t>图标2*3</t>
+  </si>
+  <si>
+    <t>图标3*3</t>
+  </si>
+  <si>
+    <t>图标4*3</t>
+  </si>
+  <si>
+    <t>图标5*3</t>
+  </si>
+  <si>
+    <t>Wild*3</t>
+  </si>
+  <si>
+    <t>图标1*4</t>
+  </si>
+  <si>
+    <t>图标2*4</t>
+  </si>
+  <si>
+    <t>图标3*4</t>
+  </si>
+  <si>
+    <t>图标4*4</t>
+  </si>
+  <si>
+    <t>图标5*4</t>
+  </si>
+  <si>
+    <t>Wild*4</t>
+  </si>
+  <si>
+    <t>11_1</t>
+  </si>
+  <si>
+    <t>金框10*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框J*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框Q*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框K*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框A*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框图标1*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框图标2*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框图标3*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框图标4*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框图标5*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>27_1</t>
+  </si>
+  <si>
+    <t>金框10*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框J*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框Q*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框K*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框A*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框图标1*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框图标2*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框图标3*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框图标4*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框图标5*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>38_1</t>
+  </si>
+  <si>
+    <t>金框10*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框J*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框Q*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框K*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框A*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框图标1*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框图标2*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框图标3*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框图标4*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框图标5*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>49_1</t>
+  </si>
+  <si>
+    <t>金框10*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框J*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框Q*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框K*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框A*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框图标1*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框图标2*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框图标3*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框图标4*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框图标5*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>97_100|98_80|99_60|100_40|101_20|102_10|103_8|104_6|105_3|106_1</t>
+  </si>
+  <si>
+    <t>107_100|108_80|109_60|110_40|111_20|112_10|113_8|114_6|115_3|116_1</t>
+  </si>
+  <si>
+    <t>55_1</t>
+  </si>
+  <si>
+    <t>二条</t>
+  </si>
+  <si>
+    <t>二筒</t>
+  </si>
+  <si>
+    <t>三筒</t>
+  </si>
+  <si>
+    <t>五条</t>
+  </si>
+  <si>
+    <t>五筒</t>
+  </si>
+  <si>
+    <t>10_1</t>
+  </si>
+  <si>
+    <t>黄金_二条|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>黄金_二筒|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>黄金_三筒|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>黄金_五条|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>黄金_五筒|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>金框_J|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>金框_Q|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>金框_K|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>金框_A|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>金框_图案1|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>金框_图案2|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>金框_图案3|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>金框_图案4|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>橙色小熊</t>
+  </si>
+  <si>
+    <t>紫色小熊</t>
+  </si>
+  <si>
+    <t>红色小熊</t>
+  </si>
+  <si>
+    <t>绿色星星</t>
+  </si>
+  <si>
+    <t>紫色软糖</t>
+  </si>
+  <si>
+    <t>橙色爱心</t>
+  </si>
+  <si>
+    <t>粉色糖果</t>
+  </si>
+  <si>
+    <t>奖池图标</t>
   </si>
 </sst>
 </file>
@@ -4414,7 +4702,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4467,6 +4755,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -4615,6 +4909,12 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4622,12 +4922,6 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -5092,16 +5386,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5110,120 +5401,123 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5403,6 +5697,27 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -5728,7 +6043,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N938"/>
+  <dimension ref="A1:N1190"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -11326,7 +11641,7 @@
       <c r="F211" s="31"/>
       <c r="G211" s="32"/>
       <c r="H211" s="34"/>
-      <c r="I211" s="60" t="s">
+      <c r="I211" s="67" t="s">
         <v>302</v>
       </c>
     </row>
@@ -29214,25 +29529,5693 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="938" s="2" customFormat="1" spans="1:9">
-      <c r="A938" s="57">
-        <v>10510024</v>
-      </c>
-      <c r="B938" s="57">
-        <v>105100</v>
-      </c>
-      <c r="C938" s="57">
+    <row r="938" spans="1:9">
+      <c r="A938" s="60">
+        <v>10540001</v>
+      </c>
+      <c r="B938" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C938" s="60">
+        <v>1</v>
+      </c>
+      <c r="D938" s="60">
+        <v>0</v>
+      </c>
+      <c r="E938" s="60"/>
+      <c r="F938" s="60"/>
+      <c r="G938" s="60"/>
+      <c r="H938" s="60"/>
+      <c r="I938" s="61">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="939" spans="1:9">
+      <c r="A939" s="60">
+        <v>10540002</v>
+      </c>
+      <c r="B939" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C939" s="60">
+        <v>2</v>
+      </c>
+      <c r="D939" s="60"/>
+      <c r="E939" s="60"/>
+      <c r="F939" s="60"/>
+      <c r="G939" s="60"/>
+      <c r="H939" s="60"/>
+      <c r="I939" s="60" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="940" spans="1:9">
+      <c r="A940" s="60">
+        <v>10540003</v>
+      </c>
+      <c r="B940" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C940" s="60">
+        <v>3</v>
+      </c>
+      <c r="D940" s="60"/>
+      <c r="E940" s="60"/>
+      <c r="F940" s="60"/>
+      <c r="G940" s="60"/>
+      <c r="H940" s="60"/>
+      <c r="I940" s="60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="941" spans="1:9">
+      <c r="A941" s="60">
+        <v>10540004</v>
+      </c>
+      <c r="B941" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C941" s="60">
+        <v>4</v>
+      </c>
+      <c r="D941" s="60"/>
+      <c r="E941" s="60"/>
+      <c r="F941" s="60"/>
+      <c r="G941" s="60"/>
+      <c r="H941" s="60"/>
+      <c r="I941" s="60" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="942" spans="1:9">
+      <c r="A942" s="60">
+        <v>10540005</v>
+      </c>
+      <c r="B942" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C942" s="60">
+        <v>5</v>
+      </c>
+      <c r="D942" s="60"/>
+      <c r="E942" s="60"/>
+      <c r="F942" s="60"/>
+      <c r="G942" s="60"/>
+      <c r="H942" s="60"/>
+      <c r="I942" s="60" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="943" spans="1:9">
+      <c r="A943" s="60">
+        <v>10540006</v>
+      </c>
+      <c r="B943" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C943" s="60">
+        <v>6</v>
+      </c>
+      <c r="D943" s="60"/>
+      <c r="E943" s="60"/>
+      <c r="F943" s="60"/>
+      <c r="G943" s="60"/>
+      <c r="H943" s="60"/>
+      <c r="I943" s="60" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="944" spans="1:9">
+      <c r="A944" s="60">
+        <v>10540007</v>
+      </c>
+      <c r="B944" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C944" s="60">
+        <v>7</v>
+      </c>
+      <c r="D944" s="60"/>
+      <c r="E944" s="60"/>
+      <c r="F944" s="60"/>
+      <c r="G944" s="60"/>
+      <c r="H944" s="60"/>
+      <c r="I944" s="60" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="945" spans="1:9">
+      <c r="A945" s="60">
+        <v>10540008</v>
+      </c>
+      <c r="B945" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C945" s="60">
+        <v>8</v>
+      </c>
+      <c r="D945" s="60"/>
+      <c r="E945" s="60"/>
+      <c r="F945" s="60"/>
+      <c r="G945" s="60"/>
+      <c r="H945" s="60"/>
+      <c r="I945" s="60" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="946" spans="1:9">
+      <c r="A946" s="60">
+        <v>10540009</v>
+      </c>
+      <c r="B946" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C946" s="60">
+        <v>9</v>
+      </c>
+      <c r="D946" s="60"/>
+      <c r="E946" s="60"/>
+      <c r="F946" s="60"/>
+      <c r="G946" s="60"/>
+      <c r="H946" s="60"/>
+      <c r="I946" s="60" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="947" spans="1:9">
+      <c r="A947" s="60">
+        <v>10540010</v>
+      </c>
+      <c r="B947" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C947" s="60">
+        <v>10</v>
+      </c>
+      <c r="D947" s="60"/>
+      <c r="E947" s="60"/>
+      <c r="F947" s="60"/>
+      <c r="G947" s="60"/>
+      <c r="H947" s="60"/>
+      <c r="I947" s="60" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="948" spans="1:9">
+      <c r="A948" s="60">
+        <v>10540011</v>
+      </c>
+      <c r="B948" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C948" s="60">
+        <v>11</v>
+      </c>
+      <c r="D948" s="60"/>
+      <c r="E948" s="60"/>
+      <c r="F948" s="60"/>
+      <c r="G948" s="60"/>
+      <c r="H948" s="60"/>
+      <c r="I948" s="60" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="949" spans="1:9">
+      <c r="A949" s="60">
+        <v>10540012</v>
+      </c>
+      <c r="B949" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C949" s="60">
+        <v>12</v>
+      </c>
+      <c r="D949" s="60"/>
+      <c r="E949" s="60"/>
+      <c r="F949" s="60"/>
+      <c r="G949" s="60"/>
+      <c r="H949" s="60"/>
+      <c r="I949" s="60" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="950" spans="1:9">
+      <c r="A950" s="60">
+        <v>10540013</v>
+      </c>
+      <c r="B950" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C950" s="60">
+        <v>13</v>
+      </c>
+      <c r="D950" s="60"/>
+      <c r="E950" s="60"/>
+      <c r="F950" s="60"/>
+      <c r="G950" s="60"/>
+      <c r="H950" s="60"/>
+      <c r="I950" s="60" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="951" spans="1:9">
+      <c r="A951" s="60">
+        <v>10540014</v>
+      </c>
+      <c r="B951" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C951" s="60">
+        <v>14</v>
+      </c>
+      <c r="D951" s="60"/>
+      <c r="E951" s="60"/>
+      <c r="F951" s="60"/>
+      <c r="G951" s="60"/>
+      <c r="H951" s="60"/>
+      <c r="I951" s="60" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="952" spans="1:9">
+      <c r="A952" s="60">
+        <v>10540015</v>
+      </c>
+      <c r="B952" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C952" s="60">
+        <v>15</v>
+      </c>
+      <c r="D952" s="60"/>
+      <c r="E952" s="60"/>
+      <c r="F952" s="60"/>
+      <c r="G952" s="60"/>
+      <c r="H952" s="60"/>
+      <c r="I952" s="60" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="953" spans="1:9">
+      <c r="A953" s="60">
+        <v>10540016</v>
+      </c>
+      <c r="B953" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C953" s="60">
+        <v>16</v>
+      </c>
+      <c r="D953" s="60"/>
+      <c r="E953" s="60"/>
+      <c r="F953" s="60"/>
+      <c r="G953" s="60"/>
+      <c r="H953" s="60"/>
+      <c r="I953" s="60" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="954" spans="1:9">
+      <c r="A954" s="60">
+        <v>10540017</v>
+      </c>
+      <c r="B954" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C954" s="60">
+        <v>17</v>
+      </c>
+      <c r="D954" s="60"/>
+      <c r="E954" s="60"/>
+      <c r="F954" s="60"/>
+      <c r="G954" s="60"/>
+      <c r="H954" s="60">
+        <v>2</v>
+      </c>
+      <c r="I954" s="61" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="955" spans="1:9">
+      <c r="A955" s="60">
+        <v>10540018</v>
+      </c>
+      <c r="B955" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C955" s="60">
+        <v>18</v>
+      </c>
+      <c r="D955" s="60"/>
+      <c r="E955" s="60"/>
+      <c r="F955" s="60"/>
+      <c r="G955" s="60"/>
+      <c r="H955" s="60">
+        <v>2</v>
+      </c>
+      <c r="I955" s="60" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="956" spans="1:9">
+      <c r="A956" s="60">
+        <v>10540019</v>
+      </c>
+      <c r="B956" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C956" s="60">
+        <v>19</v>
+      </c>
+      <c r="D956" s="60"/>
+      <c r="E956" s="60"/>
+      <c r="F956" s="60"/>
+      <c r="G956" s="60"/>
+      <c r="H956" s="60">
+        <v>2</v>
+      </c>
+      <c r="I956" s="60" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="957" spans="1:9">
+      <c r="A957" s="60">
+        <v>10540020</v>
+      </c>
+      <c r="B957" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C957" s="60">
+        <v>20</v>
+      </c>
+      <c r="D957" s="60"/>
+      <c r="E957" s="60"/>
+      <c r="F957" s="60"/>
+      <c r="G957" s="60"/>
+      <c r="H957" s="60">
+        <v>2</v>
+      </c>
+      <c r="I957" s="60" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="958" spans="1:9">
+      <c r="A958" s="60">
+        <v>10540021</v>
+      </c>
+      <c r="B958" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C958" s="60">
+        <v>21</v>
+      </c>
+      <c r="D958" s="60"/>
+      <c r="E958" s="60"/>
+      <c r="F958" s="60"/>
+      <c r="G958" s="60"/>
+      <c r="H958" s="60">
+        <v>2</v>
+      </c>
+      <c r="I958" s="60" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="959" spans="1:9">
+      <c r="A959" s="60">
+        <v>10540022</v>
+      </c>
+      <c r="B959" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C959" s="60">
+        <v>22</v>
+      </c>
+      <c r="D959" s="60"/>
+      <c r="E959" s="60"/>
+      <c r="F959" s="60"/>
+      <c r="G959" s="60"/>
+      <c r="H959" s="60">
+        <v>2</v>
+      </c>
+      <c r="I959" s="60" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="960" spans="1:9">
+      <c r="A960" s="60">
+        <v>10540023</v>
+      </c>
+      <c r="B960" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C960" s="60">
+        <v>23</v>
+      </c>
+      <c r="D960" s="60"/>
+      <c r="E960" s="60"/>
+      <c r="F960" s="60"/>
+      <c r="G960" s="60"/>
+      <c r="H960" s="60">
+        <v>2</v>
+      </c>
+      <c r="I960" s="60" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="961" spans="1:9">
+      <c r="A961" s="60">
+        <v>10540024</v>
+      </c>
+      <c r="B961" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C961" s="60">
         <v>24</v>
       </c>
-      <c r="D938" s="57">
+      <c r="D961" s="60"/>
+      <c r="E961" s="60"/>
+      <c r="F961" s="60"/>
+      <c r="G961" s="60"/>
+      <c r="H961" s="60">
         <v>2</v>
       </c>
-      <c r="E938" s="57"/>
-      <c r="F938" s="57"/>
-      <c r="G938" s="57"/>
-      <c r="H938" s="57"/>
-      <c r="I938" s="59" t="s">
-        <v>1428</v>
+      <c r="I961" s="60" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="962" spans="1:9">
+      <c r="A962" s="60">
+        <v>10540025</v>
+      </c>
+      <c r="B962" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C962" s="60">
+        <v>25</v>
+      </c>
+      <c r="D962" s="60"/>
+      <c r="E962" s="60"/>
+      <c r="F962" s="60"/>
+      <c r="G962" s="60"/>
+      <c r="H962" s="60">
+        <v>2</v>
+      </c>
+      <c r="I962" s="60" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="963" spans="1:9">
+      <c r="A963" s="60">
+        <v>10540026</v>
+      </c>
+      <c r="B963" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C963" s="60">
+        <v>26</v>
+      </c>
+      <c r="D963" s="60"/>
+      <c r="E963" s="60"/>
+      <c r="F963" s="60"/>
+      <c r="G963" s="60"/>
+      <c r="H963" s="60">
+        <v>2</v>
+      </c>
+      <c r="I963" s="60" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="964" spans="1:9">
+      <c r="A964" s="60">
+        <v>10540027</v>
+      </c>
+      <c r="B964" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C964" s="60">
+        <v>27</v>
+      </c>
+      <c r="D964" s="60"/>
+      <c r="E964" s="60"/>
+      <c r="F964" s="60"/>
+      <c r="G964" s="60"/>
+      <c r="H964" s="60">
+        <v>2</v>
+      </c>
+      <c r="I964" s="60" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="965" spans="1:9">
+      <c r="A965" s="60">
+        <v>10540028</v>
+      </c>
+      <c r="B965" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C965" s="60">
+        <v>28</v>
+      </c>
+      <c r="D965" s="60"/>
+      <c r="E965" s="60"/>
+      <c r="F965" s="60"/>
+      <c r="G965" s="60"/>
+      <c r="H965" s="60">
+        <v>3</v>
+      </c>
+      <c r="I965" s="61" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="966" spans="1:9">
+      <c r="A966" s="60">
+        <v>10540029</v>
+      </c>
+      <c r="B966" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C966" s="60">
+        <v>29</v>
+      </c>
+      <c r="D966" s="60"/>
+      <c r="E966" s="60"/>
+      <c r="F966" s="60"/>
+      <c r="G966" s="60"/>
+      <c r="H966" s="60">
+        <v>3</v>
+      </c>
+      <c r="I966" s="60" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="967" spans="1:9">
+      <c r="A967" s="60">
+        <v>10540030</v>
+      </c>
+      <c r="B967" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C967" s="60">
+        <v>30</v>
+      </c>
+      <c r="D967" s="60"/>
+      <c r="E967" s="60"/>
+      <c r="F967" s="60"/>
+      <c r="G967" s="60"/>
+      <c r="H967" s="60">
+        <v>3</v>
+      </c>
+      <c r="I967" s="60" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="968" spans="1:9">
+      <c r="A968" s="60">
+        <v>10540031</v>
+      </c>
+      <c r="B968" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C968" s="60">
+        <v>31</v>
+      </c>
+      <c r="D968" s="60"/>
+      <c r="E968" s="60"/>
+      <c r="F968" s="60"/>
+      <c r="G968" s="60"/>
+      <c r="H968" s="60">
+        <v>3</v>
+      </c>
+      <c r="I968" s="60" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="969" spans="1:9">
+      <c r="A969" s="60">
+        <v>10540032</v>
+      </c>
+      <c r="B969" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C969" s="60">
+        <v>32</v>
+      </c>
+      <c r="D969" s="60"/>
+      <c r="E969" s="60"/>
+      <c r="F969" s="60"/>
+      <c r="G969" s="60"/>
+      <c r="H969" s="60">
+        <v>3</v>
+      </c>
+      <c r="I969" s="60" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="970" spans="1:9">
+      <c r="A970" s="60">
+        <v>10540033</v>
+      </c>
+      <c r="B970" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C970" s="60">
+        <v>33</v>
+      </c>
+      <c r="D970" s="60"/>
+      <c r="E970" s="60"/>
+      <c r="F970" s="60"/>
+      <c r="G970" s="60"/>
+      <c r="H970" s="60">
+        <v>3</v>
+      </c>
+      <c r="I970" s="60" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="971" spans="1:9">
+      <c r="A971" s="60">
+        <v>10540034</v>
+      </c>
+      <c r="B971" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C971" s="60">
+        <v>34</v>
+      </c>
+      <c r="D971" s="60"/>
+      <c r="E971" s="60"/>
+      <c r="F971" s="60"/>
+      <c r="G971" s="60"/>
+      <c r="H971" s="60">
+        <v>3</v>
+      </c>
+      <c r="I971" s="60" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="972" spans="1:9">
+      <c r="A972" s="60">
+        <v>10540035</v>
+      </c>
+      <c r="B972" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C972" s="60">
+        <v>35</v>
+      </c>
+      <c r="D972" s="60"/>
+      <c r="E972" s="60"/>
+      <c r="F972" s="60"/>
+      <c r="G972" s="60"/>
+      <c r="H972" s="60">
+        <v>3</v>
+      </c>
+      <c r="I972" s="60" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="973" spans="1:9">
+      <c r="A973" s="60">
+        <v>10540036</v>
+      </c>
+      <c r="B973" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C973" s="60">
+        <v>36</v>
+      </c>
+      <c r="D973" s="60"/>
+      <c r="E973" s="60"/>
+      <c r="F973" s="60"/>
+      <c r="G973" s="60"/>
+      <c r="H973" s="60">
+        <v>3</v>
+      </c>
+      <c r="I973" s="60" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="974" spans="1:9">
+      <c r="A974" s="60">
+        <v>10540037</v>
+      </c>
+      <c r="B974" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C974" s="60">
+        <v>37</v>
+      </c>
+      <c r="D974" s="60"/>
+      <c r="E974" s="60"/>
+      <c r="F974" s="60"/>
+      <c r="G974" s="60"/>
+      <c r="H974" s="60">
+        <v>3</v>
+      </c>
+      <c r="I974" s="60" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="975" spans="1:9">
+      <c r="A975" s="60">
+        <v>10540038</v>
+      </c>
+      <c r="B975" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C975" s="60">
+        <v>38</v>
+      </c>
+      <c r="D975" s="60"/>
+      <c r="E975" s="60"/>
+      <c r="F975" s="60"/>
+      <c r="G975" s="60"/>
+      <c r="H975" s="60">
+        <v>3</v>
+      </c>
+      <c r="I975" s="60" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="976" spans="1:9">
+      <c r="A976" s="60">
+        <v>10540039</v>
+      </c>
+      <c r="B976" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C976" s="60">
+        <v>39</v>
+      </c>
+      <c r="D976" s="60"/>
+      <c r="E976" s="60"/>
+      <c r="F976" s="60"/>
+      <c r="G976" s="60"/>
+      <c r="H976" s="60">
+        <v>4</v>
+      </c>
+      <c r="I976" s="61" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="977" spans="1:9">
+      <c r="A977" s="60">
+        <v>10540040</v>
+      </c>
+      <c r="B977" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C977" s="60">
+        <v>40</v>
+      </c>
+      <c r="D977" s="60"/>
+      <c r="E977" s="60"/>
+      <c r="F977" s="60"/>
+      <c r="G977" s="60"/>
+      <c r="H977" s="60">
+        <v>4</v>
+      </c>
+      <c r="I977" s="60" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="978" spans="1:9">
+      <c r="A978" s="60">
+        <v>10540041</v>
+      </c>
+      <c r="B978" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C978" s="60">
+        <v>41</v>
+      </c>
+      <c r="D978" s="60"/>
+      <c r="E978" s="60"/>
+      <c r="F978" s="60"/>
+      <c r="G978" s="60"/>
+      <c r="H978" s="60">
+        <v>4</v>
+      </c>
+      <c r="I978" s="60" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="979" spans="1:9">
+      <c r="A979" s="60">
+        <v>10540042</v>
+      </c>
+      <c r="B979" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C979" s="60">
+        <v>42</v>
+      </c>
+      <c r="D979" s="60"/>
+      <c r="E979" s="60"/>
+      <c r="F979" s="60"/>
+      <c r="G979" s="60"/>
+      <c r="H979" s="60">
+        <v>4</v>
+      </c>
+      <c r="I979" s="60" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="980" spans="1:9">
+      <c r="A980" s="60">
+        <v>10540043</v>
+      </c>
+      <c r="B980" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C980" s="60">
+        <v>43</v>
+      </c>
+      <c r="D980" s="60"/>
+      <c r="E980" s="60"/>
+      <c r="F980" s="60"/>
+      <c r="G980" s="60"/>
+      <c r="H980" s="60">
+        <v>4</v>
+      </c>
+      <c r="I980" s="60" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="981" spans="1:9">
+      <c r="A981" s="60">
+        <v>10540044</v>
+      </c>
+      <c r="B981" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C981" s="60">
+        <v>44</v>
+      </c>
+      <c r="D981" s="60"/>
+      <c r="E981" s="60"/>
+      <c r="F981" s="60"/>
+      <c r="G981" s="60"/>
+      <c r="H981" s="60">
+        <v>4</v>
+      </c>
+      <c r="I981" s="60" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="982" spans="1:9">
+      <c r="A982" s="60">
+        <v>10540045</v>
+      </c>
+      <c r="B982" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C982" s="60">
+        <v>45</v>
+      </c>
+      <c r="D982" s="60"/>
+      <c r="E982" s="60"/>
+      <c r="F982" s="60"/>
+      <c r="G982" s="60"/>
+      <c r="H982" s="60">
+        <v>4</v>
+      </c>
+      <c r="I982" s="60" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="983" spans="1:9">
+      <c r="A983" s="60">
+        <v>10540046</v>
+      </c>
+      <c r="B983" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C983" s="60">
+        <v>46</v>
+      </c>
+      <c r="D983" s="60"/>
+      <c r="E983" s="60"/>
+      <c r="F983" s="60"/>
+      <c r="G983" s="60"/>
+      <c r="H983" s="60">
+        <v>4</v>
+      </c>
+      <c r="I983" s="60" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="984" spans="1:9">
+      <c r="A984" s="60">
+        <v>10540047</v>
+      </c>
+      <c r="B984" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C984" s="60">
+        <v>47</v>
+      </c>
+      <c r="D984" s="60"/>
+      <c r="E984" s="60"/>
+      <c r="F984" s="60"/>
+      <c r="G984" s="60"/>
+      <c r="H984" s="60">
+        <v>4</v>
+      </c>
+      <c r="I984" s="60" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="985" spans="1:9">
+      <c r="A985" s="60">
+        <v>10540048</v>
+      </c>
+      <c r="B985" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C985" s="60">
+        <v>48</v>
+      </c>
+      <c r="D985" s="60"/>
+      <c r="E985" s="60"/>
+      <c r="F985" s="60"/>
+      <c r="G985" s="60"/>
+      <c r="H985" s="60">
+        <v>4</v>
+      </c>
+      <c r="I985" s="60" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="986" spans="1:9">
+      <c r="A986" s="60">
+        <v>10540049</v>
+      </c>
+      <c r="B986" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C986" s="60">
+        <v>49</v>
+      </c>
+      <c r="D986" s="60"/>
+      <c r="E986" s="60"/>
+      <c r="F986" s="60"/>
+      <c r="G986" s="60"/>
+      <c r="H986" s="60">
+        <v>4</v>
+      </c>
+      <c r="I986" s="60" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="987" spans="1:9">
+      <c r="A987" s="60">
+        <v>10540050</v>
+      </c>
+      <c r="B987" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C987" s="60">
+        <v>50</v>
+      </c>
+      <c r="D987" s="60"/>
+      <c r="E987" s="60"/>
+      <c r="F987" s="60" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G987" s="60"/>
+      <c r="H987" s="60"/>
+      <c r="I987" s="60" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="988" spans="1:9">
+      <c r="A988" s="60">
+        <v>10540051</v>
+      </c>
+      <c r="B988" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C988" s="60">
+        <v>51</v>
+      </c>
+      <c r="D988" s="60"/>
+      <c r="E988" s="60"/>
+      <c r="F988" s="60" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G988" s="60"/>
+      <c r="H988" s="60"/>
+      <c r="I988" s="60" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="989" spans="1:9">
+      <c r="A989" s="60">
+        <v>10540052</v>
+      </c>
+      <c r="B989" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C989" s="60">
+        <v>52</v>
+      </c>
+      <c r="D989" s="60"/>
+      <c r="E989" s="60"/>
+      <c r="F989" s="60" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G989" s="60"/>
+      <c r="H989" s="60"/>
+      <c r="I989" s="60" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="990" spans="1:9">
+      <c r="A990" s="60">
+        <v>10540053</v>
+      </c>
+      <c r="B990" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C990" s="60">
+        <v>53</v>
+      </c>
+      <c r="D990" s="60"/>
+      <c r="E990" s="60"/>
+      <c r="F990" s="60" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G990" s="60"/>
+      <c r="H990" s="60"/>
+      <c r="I990" s="60" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="991" spans="1:9">
+      <c r="A991" s="60">
+        <v>10540054</v>
+      </c>
+      <c r="B991" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C991" s="60">
+        <v>54</v>
+      </c>
+      <c r="D991" s="60"/>
+      <c r="E991" s="60"/>
+      <c r="F991" s="60" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G991" s="60"/>
+      <c r="H991" s="60"/>
+      <c r="I991" s="60" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="992" spans="1:9">
+      <c r="A992" s="60">
+        <v>10540055</v>
+      </c>
+      <c r="B992" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C992" s="60">
+        <v>55</v>
+      </c>
+      <c r="D992" s="60"/>
+      <c r="E992" s="60"/>
+      <c r="F992" s="60" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G992" s="60"/>
+      <c r="H992" s="60"/>
+      <c r="I992" s="60" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="993" spans="1:9">
+      <c r="A993" s="60">
+        <v>10540056</v>
+      </c>
+      <c r="B993" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C993" s="60">
+        <v>56</v>
+      </c>
+      <c r="D993" s="60"/>
+      <c r="E993" s="60"/>
+      <c r="F993" s="60" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G993" s="60"/>
+      <c r="H993" s="60"/>
+      <c r="I993" s="60" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="994" spans="1:9">
+      <c r="A994" s="60">
+        <v>10540057</v>
+      </c>
+      <c r="B994" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C994" s="60">
+        <v>57</v>
+      </c>
+      <c r="D994" s="60"/>
+      <c r="E994" s="60"/>
+      <c r="F994" s="60" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G994" s="60"/>
+      <c r="H994" s="60"/>
+      <c r="I994" s="60" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="995" spans="1:9">
+      <c r="A995" s="60">
+        <v>10540058</v>
+      </c>
+      <c r="B995" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C995" s="60">
+        <v>58</v>
+      </c>
+      <c r="D995" s="60"/>
+      <c r="E995" s="60"/>
+      <c r="F995" s="60" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G995" s="60"/>
+      <c r="H995" s="60"/>
+      <c r="I995" s="60" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="996" spans="1:9">
+      <c r="A996" s="60">
+        <v>10540059</v>
+      </c>
+      <c r="B996" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C996" s="60">
+        <v>59</v>
+      </c>
+      <c r="D996" s="60"/>
+      <c r="E996" s="60"/>
+      <c r="F996" s="60" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G996" s="60"/>
+      <c r="H996" s="60"/>
+      <c r="I996" s="60" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="997" spans="1:9">
+      <c r="A997" s="60">
+        <v>10540060</v>
+      </c>
+      <c r="B997" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C997" s="60">
+        <v>60</v>
+      </c>
+      <c r="D997" s="60"/>
+      <c r="E997" s="60"/>
+      <c r="F997" s="60" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G997" s="60"/>
+      <c r="H997" s="60">
+        <v>2</v>
+      </c>
+      <c r="I997" s="60" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="998" spans="1:9">
+      <c r="A998" s="60">
+        <v>10540061</v>
+      </c>
+      <c r="B998" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C998" s="60">
+        <v>61</v>
+      </c>
+      <c r="D998" s="60"/>
+      <c r="E998" s="60"/>
+      <c r="F998" s="60" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G998" s="60"/>
+      <c r="H998" s="60">
+        <v>2</v>
+      </c>
+      <c r="I998" s="60" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="999" spans="1:9">
+      <c r="A999" s="60">
+        <v>10540062</v>
+      </c>
+      <c r="B999" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C999" s="60">
+        <v>62</v>
+      </c>
+      <c r="D999" s="60"/>
+      <c r="E999" s="60"/>
+      <c r="F999" s="60" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G999" s="60"/>
+      <c r="H999" s="60">
+        <v>2</v>
+      </c>
+      <c r="I999" s="60" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:9">
+      <c r="A1000" s="60">
+        <v>10540063</v>
+      </c>
+      <c r="B1000" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1000" s="60">
+        <v>63</v>
+      </c>
+      <c r="D1000" s="60"/>
+      <c r="E1000" s="60"/>
+      <c r="F1000" s="60" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G1000" s="60"/>
+      <c r="H1000" s="60">
+        <v>2</v>
+      </c>
+      <c r="I1000" s="60" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:9">
+      <c r="A1001" s="60">
+        <v>10540064</v>
+      </c>
+      <c r="B1001" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1001" s="60">
+        <v>64</v>
+      </c>
+      <c r="D1001" s="60"/>
+      <c r="E1001" s="60"/>
+      <c r="F1001" s="60" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G1001" s="60"/>
+      <c r="H1001" s="60">
+        <v>2</v>
+      </c>
+      <c r="I1001" s="60" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:9">
+      <c r="A1002" s="60">
+        <v>10540065</v>
+      </c>
+      <c r="B1002" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1002" s="60">
+        <v>65</v>
+      </c>
+      <c r="D1002" s="60"/>
+      <c r="E1002" s="60"/>
+      <c r="F1002" s="60" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G1002" s="60"/>
+      <c r="H1002" s="60">
+        <v>2</v>
+      </c>
+      <c r="I1002" s="60" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:9">
+      <c r="A1003" s="60">
+        <v>10540066</v>
+      </c>
+      <c r="B1003" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1003" s="60">
+        <v>66</v>
+      </c>
+      <c r="D1003" s="60"/>
+      <c r="E1003" s="60"/>
+      <c r="F1003" s="60" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G1003" s="60"/>
+      <c r="H1003" s="60">
+        <v>2</v>
+      </c>
+      <c r="I1003" s="60" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:9">
+      <c r="A1004" s="60">
+        <v>10540067</v>
+      </c>
+      <c r="B1004" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1004" s="60">
+        <v>67</v>
+      </c>
+      <c r="D1004" s="60"/>
+      <c r="E1004" s="60"/>
+      <c r="F1004" s="60" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G1004" s="60"/>
+      <c r="H1004" s="60">
+        <v>2</v>
+      </c>
+      <c r="I1004" s="60" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:9">
+      <c r="A1005" s="60">
+        <v>10540068</v>
+      </c>
+      <c r="B1005" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1005" s="60">
+        <v>68</v>
+      </c>
+      <c r="D1005" s="60"/>
+      <c r="E1005" s="60"/>
+      <c r="F1005" s="60" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G1005" s="60"/>
+      <c r="H1005" s="60">
+        <v>2</v>
+      </c>
+      <c r="I1005" s="60" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:9">
+      <c r="A1006" s="60">
+        <v>10540069</v>
+      </c>
+      <c r="B1006" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1006" s="60">
+        <v>69</v>
+      </c>
+      <c r="D1006" s="60"/>
+      <c r="E1006" s="60"/>
+      <c r="F1006" s="60" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G1006" s="60"/>
+      <c r="H1006" s="60">
+        <v>2</v>
+      </c>
+      <c r="I1006" s="60" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:9">
+      <c r="A1007" s="60">
+        <v>10540070</v>
+      </c>
+      <c r="B1007" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1007" s="60">
+        <v>70</v>
+      </c>
+      <c r="D1007" s="60"/>
+      <c r="E1007" s="60"/>
+      <c r="F1007" s="60" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G1007" s="60"/>
+      <c r="H1007" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1007" s="60" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:9">
+      <c r="A1008" s="60">
+        <v>10540071</v>
+      </c>
+      <c r="B1008" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1008" s="60">
+        <v>71</v>
+      </c>
+      <c r="D1008" s="60"/>
+      <c r="E1008" s="60"/>
+      <c r="F1008" s="60" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G1008" s="60"/>
+      <c r="H1008" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1008" s="60" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:9">
+      <c r="A1009" s="60">
+        <v>10540072</v>
+      </c>
+      <c r="B1009" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1009" s="60">
+        <v>72</v>
+      </c>
+      <c r="D1009" s="60"/>
+      <c r="E1009" s="60"/>
+      <c r="F1009" s="60" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G1009" s="60"/>
+      <c r="H1009" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1009" s="60" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:9">
+      <c r="A1010" s="60">
+        <v>10540073</v>
+      </c>
+      <c r="B1010" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1010" s="60">
+        <v>73</v>
+      </c>
+      <c r="D1010" s="60"/>
+      <c r="E1010" s="60"/>
+      <c r="F1010" s="60" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G1010" s="60"/>
+      <c r="H1010" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1010" s="60" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:9">
+      <c r="A1011" s="60">
+        <v>10540074</v>
+      </c>
+      <c r="B1011" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1011" s="60">
+        <v>74</v>
+      </c>
+      <c r="D1011" s="60"/>
+      <c r="E1011" s="60"/>
+      <c r="F1011" s="60" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G1011" s="60"/>
+      <c r="H1011" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1011" s="60" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:9">
+      <c r="A1012" s="60">
+        <v>10540075</v>
+      </c>
+      <c r="B1012" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1012" s="60">
+        <v>75</v>
+      </c>
+      <c r="D1012" s="60"/>
+      <c r="E1012" s="60"/>
+      <c r="F1012" s="60" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G1012" s="60"/>
+      <c r="H1012" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1012" s="60" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:9">
+      <c r="A1013" s="60">
+        <v>10540076</v>
+      </c>
+      <c r="B1013" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1013" s="60">
+        <v>76</v>
+      </c>
+      <c r="D1013" s="60"/>
+      <c r="E1013" s="60"/>
+      <c r="F1013" s="60" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G1013" s="60"/>
+      <c r="H1013" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1013" s="60" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:9">
+      <c r="A1014" s="60">
+        <v>10540077</v>
+      </c>
+      <c r="B1014" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1014" s="60">
+        <v>77</v>
+      </c>
+      <c r="D1014" s="60"/>
+      <c r="E1014" s="60"/>
+      <c r="F1014" s="60" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G1014" s="60"/>
+      <c r="H1014" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1014" s="60" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:9">
+      <c r="A1015" s="60">
+        <v>10540078</v>
+      </c>
+      <c r="B1015" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1015" s="60">
+        <v>78</v>
+      </c>
+      <c r="D1015" s="60"/>
+      <c r="E1015" s="60"/>
+      <c r="F1015" s="60" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G1015" s="60"/>
+      <c r="H1015" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1015" s="60" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:9">
+      <c r="A1016" s="60">
+        <v>10540079</v>
+      </c>
+      <c r="B1016" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1016" s="60">
+        <v>79</v>
+      </c>
+      <c r="D1016" s="60"/>
+      <c r="E1016" s="60"/>
+      <c r="F1016" s="60" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G1016" s="60"/>
+      <c r="H1016" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1016" s="60" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:9">
+      <c r="A1017" s="60">
+        <v>10540080</v>
+      </c>
+      <c r="B1017" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1017" s="60">
+        <v>80</v>
+      </c>
+      <c r="D1017" s="60"/>
+      <c r="E1017" s="60"/>
+      <c r="F1017" s="60" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G1017" s="60"/>
+      <c r="H1017" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1017" s="60" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:9">
+      <c r="A1018" s="60">
+        <v>10540081</v>
+      </c>
+      <c r="B1018" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1018" s="60">
+        <v>81</v>
+      </c>
+      <c r="D1018" s="60"/>
+      <c r="E1018" s="60"/>
+      <c r="F1018" s="60" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G1018" s="60"/>
+      <c r="H1018" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1018" s="60" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:9">
+      <c r="A1019" s="60">
+        <v>10540082</v>
+      </c>
+      <c r="B1019" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1019" s="60">
+        <v>82</v>
+      </c>
+      <c r="D1019" s="60"/>
+      <c r="E1019" s="60"/>
+      <c r="F1019" s="60" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G1019" s="60"/>
+      <c r="H1019" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1019" s="60" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:9">
+      <c r="A1020" s="60">
+        <v>10540083</v>
+      </c>
+      <c r="B1020" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1020" s="60">
+        <v>83</v>
+      </c>
+      <c r="D1020" s="60"/>
+      <c r="E1020" s="60"/>
+      <c r="F1020" s="60" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G1020" s="60"/>
+      <c r="H1020" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1020" s="60" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:9">
+      <c r="A1021" s="60">
+        <v>10540084</v>
+      </c>
+      <c r="B1021" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1021" s="60">
+        <v>84</v>
+      </c>
+      <c r="D1021" s="60"/>
+      <c r="E1021" s="60"/>
+      <c r="F1021" s="60" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G1021" s="60"/>
+      <c r="H1021" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1021" s="60" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:9">
+      <c r="A1022" s="60">
+        <v>10540085</v>
+      </c>
+      <c r="B1022" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1022" s="60">
+        <v>85</v>
+      </c>
+      <c r="D1022" s="60"/>
+      <c r="E1022" s="60"/>
+      <c r="F1022" s="60" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G1022" s="60"/>
+      <c r="H1022" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1022" s="60" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:9">
+      <c r="A1023" s="60">
+        <v>10540086</v>
+      </c>
+      <c r="B1023" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1023" s="60">
+        <v>86</v>
+      </c>
+      <c r="D1023" s="60"/>
+      <c r="E1023" s="60"/>
+      <c r="F1023" s="60" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G1023" s="60"/>
+      <c r="H1023" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1023" s="60" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:9">
+      <c r="A1024" s="60">
+        <v>10540087</v>
+      </c>
+      <c r="B1024" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1024" s="60">
+        <v>87</v>
+      </c>
+      <c r="D1024" s="60"/>
+      <c r="E1024" s="60"/>
+      <c r="F1024" s="60" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G1024" s="60"/>
+      <c r="H1024" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1024" s="60" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:9">
+      <c r="A1025" s="60">
+        <v>10540088</v>
+      </c>
+      <c r="B1025" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1025" s="60">
+        <v>88</v>
+      </c>
+      <c r="D1025" s="60"/>
+      <c r="E1025" s="60"/>
+      <c r="F1025" s="60" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G1025" s="60"/>
+      <c r="H1025" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1025" s="60" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:9">
+      <c r="A1026" s="60">
+        <v>10540089</v>
+      </c>
+      <c r="B1026" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1026" s="60">
+        <v>89</v>
+      </c>
+      <c r="D1026" s="60"/>
+      <c r="E1026" s="60"/>
+      <c r="F1026" s="60" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G1026" s="60"/>
+      <c r="H1026" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1026" s="60" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:9">
+      <c r="A1027" s="28">
+        <v>10080001</v>
+      </c>
+      <c r="B1027" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1027" s="28">
+        <v>1</v>
+      </c>
+      <c r="D1027" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1027" s="28"/>
+      <c r="F1027" s="28"/>
+      <c r="G1027" s="28"/>
+      <c r="H1027" s="28"/>
+      <c r="I1027" s="62">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:9">
+      <c r="A1028" s="28">
+        <v>10080002</v>
+      </c>
+      <c r="B1028" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1028" s="28">
+        <v>2</v>
+      </c>
+      <c r="D1028" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1028" s="28"/>
+      <c r="F1028" s="28"/>
+      <c r="G1028" s="28"/>
+      <c r="H1028" s="28"/>
+      <c r="I1028" s="28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:9">
+      <c r="A1029" s="28">
+        <v>10080003</v>
+      </c>
+      <c r="B1029" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1029" s="28">
+        <v>3</v>
+      </c>
+      <c r="D1029" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1029" s="28"/>
+      <c r="F1029" s="28"/>
+      <c r="G1029" s="28"/>
+      <c r="H1029" s="28"/>
+      <c r="I1029" s="28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:9">
+      <c r="A1030" s="28">
+        <v>10080004</v>
+      </c>
+      <c r="B1030" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1030" s="28">
+        <v>4</v>
+      </c>
+      <c r="D1030" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1030" s="28"/>
+      <c r="F1030" s="28"/>
+      <c r="G1030" s="28"/>
+      <c r="H1030" s="28"/>
+      <c r="I1030" s="28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:9">
+      <c r="A1031" s="28">
+        <v>10080005</v>
+      </c>
+      <c r="B1031" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1031" s="28">
+        <v>5</v>
+      </c>
+      <c r="D1031" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1031" s="28"/>
+      <c r="F1031" s="28"/>
+      <c r="G1031" s="28"/>
+      <c r="H1031" s="28"/>
+      <c r="I1031" s="28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:9">
+      <c r="A1032" s="28">
+        <v>10080006</v>
+      </c>
+      <c r="B1032" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1032" s="28">
+        <v>6</v>
+      </c>
+      <c r="D1032" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1032" s="28"/>
+      <c r="F1032" s="28"/>
+      <c r="G1032" s="28"/>
+      <c r="H1032" s="28"/>
+      <c r="I1032" s="28" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:9">
+      <c r="A1033" s="28">
+        <v>10080007</v>
+      </c>
+      <c r="B1033" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1033" s="28">
+        <v>7</v>
+      </c>
+      <c r="D1033" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1033" s="28"/>
+      <c r="F1033" s="28"/>
+      <c r="G1033" s="28"/>
+      <c r="H1033" s="28"/>
+      <c r="I1033" s="28" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:9">
+      <c r="A1034" s="28">
+        <v>10080008</v>
+      </c>
+      <c r="B1034" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1034" s="28">
+        <v>8</v>
+      </c>
+      <c r="D1034" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1034" s="28"/>
+      <c r="F1034" s="28"/>
+      <c r="G1034" s="28"/>
+      <c r="H1034" s="28"/>
+      <c r="I1034" s="28" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:9">
+      <c r="A1035" s="28">
+        <v>10080009</v>
+      </c>
+      <c r="B1035" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1035" s="28">
+        <v>9</v>
+      </c>
+      <c r="D1035" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1035" s="28"/>
+      <c r="F1035" s="28"/>
+      <c r="G1035" s="28"/>
+      <c r="H1035" s="28"/>
+      <c r="I1035" s="28" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:9">
+      <c r="A1036" s="28">
+        <v>10080010</v>
+      </c>
+      <c r="B1036" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1036" s="28">
+        <v>10</v>
+      </c>
+      <c r="D1036" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1036" s="28"/>
+      <c r="F1036" s="28"/>
+      <c r="G1036" s="28"/>
+      <c r="H1036" s="28"/>
+      <c r="I1036" s="28" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:9">
+      <c r="A1037" s="28">
+        <v>10080011</v>
+      </c>
+      <c r="B1037" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1037" s="28">
+        <v>11</v>
+      </c>
+      <c r="D1037" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1037" s="28"/>
+      <c r="F1037" s="28"/>
+      <c r="G1037" s="28"/>
+      <c r="H1037" s="28"/>
+      <c r="I1037" s="28" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:9">
+      <c r="A1038" s="28">
+        <v>10080012</v>
+      </c>
+      <c r="B1038" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1038" s="28">
+        <v>12</v>
+      </c>
+      <c r="D1038" s="28">
+        <v>1</v>
+      </c>
+      <c r="E1038" s="28"/>
+      <c r="F1038" s="28"/>
+      <c r="G1038" s="28"/>
+      <c r="H1038" s="28"/>
+      <c r="I1038" s="28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:9">
+      <c r="A1039" s="28">
+        <v>10080013</v>
+      </c>
+      <c r="B1039" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1039" s="28">
+        <v>13</v>
+      </c>
+      <c r="D1039" s="28">
+        <v>2</v>
+      </c>
+      <c r="E1039" s="28"/>
+      <c r="F1039" s="28"/>
+      <c r="G1039" s="28"/>
+      <c r="H1039" s="28"/>
+      <c r="I1039" s="28" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:9">
+      <c r="A1040" s="28">
+        <v>10080014</v>
+      </c>
+      <c r="B1040" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1040" s="28">
+        <v>14</v>
+      </c>
+      <c r="D1040" s="28">
+        <v>2</v>
+      </c>
+      <c r="E1040" s="28"/>
+      <c r="F1040" s="28"/>
+      <c r="G1040" s="28"/>
+      <c r="H1040" s="28"/>
+      <c r="I1040" s="63" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:9">
+      <c r="A1041" s="28">
+        <v>10080015</v>
+      </c>
+      <c r="B1041" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1041" s="28">
+        <v>15</v>
+      </c>
+      <c r="D1041" s="28">
+        <v>2</v>
+      </c>
+      <c r="E1041" s="28"/>
+      <c r="F1041" s="28"/>
+      <c r="G1041" s="28"/>
+      <c r="H1041" s="28"/>
+      <c r="I1041" s="63" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:9">
+      <c r="A1042" s="28">
+        <v>10080016</v>
+      </c>
+      <c r="B1042" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1042" s="28">
+        <v>16</v>
+      </c>
+      <c r="D1042" s="28">
+        <v>2</v>
+      </c>
+      <c r="E1042" s="28"/>
+      <c r="F1042" s="28"/>
+      <c r="G1042" s="28"/>
+      <c r="H1042" s="28"/>
+      <c r="I1042" s="63" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:9">
+      <c r="A1043" s="28">
+        <v>10080017</v>
+      </c>
+      <c r="B1043" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1043" s="28">
+        <v>17</v>
+      </c>
+      <c r="D1043" s="28">
+        <v>2</v>
+      </c>
+      <c r="E1043" s="28"/>
+      <c r="F1043" s="28"/>
+      <c r="G1043" s="28"/>
+      <c r="H1043" s="28"/>
+      <c r="I1043" s="63" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:9">
+      <c r="A1044" s="28">
+        <v>10080018</v>
+      </c>
+      <c r="B1044" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1044" s="28">
+        <v>18</v>
+      </c>
+      <c r="D1044" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1044" s="28"/>
+      <c r="F1044" s="28"/>
+      <c r="G1044" s="28"/>
+      <c r="H1044" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1044" s="45" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:9">
+      <c r="A1045" s="28">
+        <v>10080019</v>
+      </c>
+      <c r="B1045" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1045" s="28">
+        <v>19</v>
+      </c>
+      <c r="D1045" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1045" s="28"/>
+      <c r="F1045" s="28"/>
+      <c r="G1045" s="28"/>
+      <c r="H1045" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1045" s="45" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:9">
+      <c r="A1046" s="28">
+        <v>10080020</v>
+      </c>
+      <c r="B1046" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1046" s="28">
+        <v>20</v>
+      </c>
+      <c r="D1046" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1046" s="28"/>
+      <c r="F1046" s="28"/>
+      <c r="G1046" s="28"/>
+      <c r="H1046" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1046" s="45" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:9">
+      <c r="A1047" s="28">
+        <v>10080021</v>
+      </c>
+      <c r="B1047" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1047" s="28">
+        <v>21</v>
+      </c>
+      <c r="D1047" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1047" s="28"/>
+      <c r="F1047" s="28"/>
+      <c r="G1047" s="28"/>
+      <c r="H1047" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1047" s="45" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:9">
+      <c r="A1048" s="28">
+        <v>10080022</v>
+      </c>
+      <c r="B1048" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1048" s="28">
+        <v>22</v>
+      </c>
+      <c r="D1048" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1048" s="28"/>
+      <c r="F1048" s="28"/>
+      <c r="G1048" s="28"/>
+      <c r="H1048" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1048" s="45" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:9">
+      <c r="A1049" s="28">
+        <v>10080023</v>
+      </c>
+      <c r="B1049" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1049" s="28">
+        <v>23</v>
+      </c>
+      <c r="D1049" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1049" s="28"/>
+      <c r="F1049" s="28"/>
+      <c r="G1049" s="28"/>
+      <c r="H1049" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1049" s="45" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:9">
+      <c r="A1050" s="28">
+        <v>10080024</v>
+      </c>
+      <c r="B1050" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1050" s="28">
+        <v>24</v>
+      </c>
+      <c r="D1050" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1050" s="28"/>
+      <c r="F1050" s="28"/>
+      <c r="G1050" s="28"/>
+      <c r="H1050" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1050" s="45" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:9">
+      <c r="A1051" s="28">
+        <v>10080025</v>
+      </c>
+      <c r="B1051" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1051" s="28">
+        <v>25</v>
+      </c>
+      <c r="D1051" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1051" s="28"/>
+      <c r="F1051" s="28"/>
+      <c r="G1051" s="28"/>
+      <c r="H1051" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1051" s="45" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:9">
+      <c r="A1052" s="28">
+        <v>10080026</v>
+      </c>
+      <c r="B1052" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1052" s="28">
+        <v>26</v>
+      </c>
+      <c r="D1052" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1052" s="28"/>
+      <c r="F1052" s="28"/>
+      <c r="G1052" s="28"/>
+      <c r="H1052" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1052" s="45" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:9">
+      <c r="A1053" s="28">
+        <v>10080027</v>
+      </c>
+      <c r="B1053" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1053" s="28">
+        <v>27</v>
+      </c>
+      <c r="D1053" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1053" s="28"/>
+      <c r="F1053" s="28"/>
+      <c r="G1053" s="28"/>
+      <c r="H1053" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1053" s="45" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:9">
+      <c r="A1054" s="28">
+        <v>10080028</v>
+      </c>
+      <c r="B1054" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1054" s="28">
+        <v>28</v>
+      </c>
+      <c r="D1054" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1054" s="28"/>
+      <c r="F1054" s="28"/>
+      <c r="G1054" s="28"/>
+      <c r="H1054" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1054" s="45" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:9">
+      <c r="A1055" s="28">
+        <v>10080029</v>
+      </c>
+      <c r="B1055" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1055" s="28">
+        <v>29</v>
+      </c>
+      <c r="D1055" s="28">
+        <v>1</v>
+      </c>
+      <c r="E1055" s="28"/>
+      <c r="F1055" s="28"/>
+      <c r="G1055" s="28"/>
+      <c r="H1055" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1055" s="45" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:9">
+      <c r="A1056" s="28">
+        <v>10080030</v>
+      </c>
+      <c r="B1056" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1056" s="28">
+        <v>30</v>
+      </c>
+      <c r="D1056" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1056" s="28"/>
+      <c r="F1056" s="28"/>
+      <c r="G1056" s="28"/>
+      <c r="H1056" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1056" s="45" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:9">
+      <c r="A1057" s="28">
+        <v>10080031</v>
+      </c>
+      <c r="B1057" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1057" s="28">
+        <v>31</v>
+      </c>
+      <c r="D1057" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1057" s="28"/>
+      <c r="F1057" s="28"/>
+      <c r="G1057" s="28"/>
+      <c r="H1057" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1057" s="45" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:9">
+      <c r="A1058" s="28">
+        <v>10080032</v>
+      </c>
+      <c r="B1058" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1058" s="28">
+        <v>32</v>
+      </c>
+      <c r="D1058" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1058" s="28"/>
+      <c r="F1058" s="28"/>
+      <c r="G1058" s="28"/>
+      <c r="H1058" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1058" s="45" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:9">
+      <c r="A1059" s="28">
+        <v>10080033</v>
+      </c>
+      <c r="B1059" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1059" s="28">
+        <v>33</v>
+      </c>
+      <c r="D1059" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1059" s="28"/>
+      <c r="F1059" s="28"/>
+      <c r="G1059" s="28"/>
+      <c r="H1059" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1059" s="45" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:9">
+      <c r="A1060" s="28">
+        <v>10080034</v>
+      </c>
+      <c r="B1060" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1060" s="28">
+        <v>34</v>
+      </c>
+      <c r="D1060" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1060" s="28"/>
+      <c r="F1060" s="28"/>
+      <c r="G1060" s="28"/>
+      <c r="H1060" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1060" s="45" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:9">
+      <c r="A1061" s="28">
+        <v>10080035</v>
+      </c>
+      <c r="B1061" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1061" s="28">
+        <v>35</v>
+      </c>
+      <c r="D1061" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1061" s="28"/>
+      <c r="F1061" s="28"/>
+      <c r="G1061" s="28"/>
+      <c r="H1061" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1061" s="45" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:9">
+      <c r="A1062" s="28">
+        <v>10080036</v>
+      </c>
+      <c r="B1062" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1062" s="28">
+        <v>36</v>
+      </c>
+      <c r="D1062" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1062" s="28"/>
+      <c r="F1062" s="28"/>
+      <c r="G1062" s="28"/>
+      <c r="H1062" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1062" s="45" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:9">
+      <c r="A1063" s="28">
+        <v>10080037</v>
+      </c>
+      <c r="B1063" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1063" s="28">
+        <v>37</v>
+      </c>
+      <c r="D1063" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1063" s="28"/>
+      <c r="F1063" s="28"/>
+      <c r="G1063" s="28"/>
+      <c r="H1063" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1063" s="45" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:9">
+      <c r="A1064" s="28">
+        <v>10080038</v>
+      </c>
+      <c r="B1064" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1064" s="28">
+        <v>38</v>
+      </c>
+      <c r="D1064" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1064" s="28"/>
+      <c r="F1064" s="28"/>
+      <c r="G1064" s="28"/>
+      <c r="H1064" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1064" s="45" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:9">
+      <c r="A1065" s="28">
+        <v>10080039</v>
+      </c>
+      <c r="B1065" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1065" s="28">
+        <v>39</v>
+      </c>
+      <c r="D1065" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1065" s="28"/>
+      <c r="F1065" s="28"/>
+      <c r="G1065" s="28"/>
+      <c r="H1065" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1065" s="45" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:9">
+      <c r="A1066" s="28">
+        <v>10080040</v>
+      </c>
+      <c r="B1066" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1066" s="28">
+        <v>40</v>
+      </c>
+      <c r="D1066" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1066" s="28"/>
+      <c r="F1066" s="28"/>
+      <c r="G1066" s="28"/>
+      <c r="H1066" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1066" s="45" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:9">
+      <c r="A1067" s="28">
+        <v>10080041</v>
+      </c>
+      <c r="B1067" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1067" s="28">
+        <v>41</v>
+      </c>
+      <c r="D1067" s="28">
+        <v>1</v>
+      </c>
+      <c r="E1067" s="28"/>
+      <c r="F1067" s="28"/>
+      <c r="G1067" s="28"/>
+      <c r="H1067" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1067" s="45" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:9">
+      <c r="A1068" s="28">
+        <v>10080042</v>
+      </c>
+      <c r="B1068" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1068" s="28">
+        <v>42</v>
+      </c>
+      <c r="D1068" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1068" s="28"/>
+      <c r="F1068" s="28"/>
+      <c r="G1068" s="28"/>
+      <c r="H1068" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1068" s="45" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:9">
+      <c r="A1069" s="28">
+        <v>10080043</v>
+      </c>
+      <c r="B1069" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1069" s="28">
+        <v>43</v>
+      </c>
+      <c r="D1069" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1069" s="28"/>
+      <c r="F1069" s="28"/>
+      <c r="G1069" s="28"/>
+      <c r="H1069" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1069" s="45" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:9">
+      <c r="A1070" s="28">
+        <v>10080044</v>
+      </c>
+      <c r="B1070" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1070" s="28">
+        <v>44</v>
+      </c>
+      <c r="D1070" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1070" s="28"/>
+      <c r="F1070" s="28"/>
+      <c r="G1070" s="28"/>
+      <c r="H1070" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1070" s="45" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:9">
+      <c r="A1071" s="28">
+        <v>10080045</v>
+      </c>
+      <c r="B1071" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1071" s="28">
+        <v>45</v>
+      </c>
+      <c r="D1071" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1071" s="28"/>
+      <c r="F1071" s="28"/>
+      <c r="G1071" s="28"/>
+      <c r="H1071" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1071" s="45" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:9">
+      <c r="A1072" s="28">
+        <v>10080046</v>
+      </c>
+      <c r="B1072" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1072" s="28">
+        <v>46</v>
+      </c>
+      <c r="D1072" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1072" s="28"/>
+      <c r="F1072" s="28"/>
+      <c r="G1072" s="28"/>
+      <c r="H1072" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1072" s="45" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:9">
+      <c r="A1073" s="28">
+        <v>10080047</v>
+      </c>
+      <c r="B1073" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1073" s="28">
+        <v>47</v>
+      </c>
+      <c r="D1073" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1073" s="28"/>
+      <c r="F1073" s="28"/>
+      <c r="G1073" s="28"/>
+      <c r="H1073" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1073" s="45" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:9">
+      <c r="A1074" s="28">
+        <v>10080048</v>
+      </c>
+      <c r="B1074" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1074" s="28">
+        <v>48</v>
+      </c>
+      <c r="D1074" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1074" s="28"/>
+      <c r="F1074" s="28"/>
+      <c r="G1074" s="28"/>
+      <c r="H1074" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1074" s="45" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:9">
+      <c r="A1075" s="28">
+        <v>10080049</v>
+      </c>
+      <c r="B1075" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1075" s="28">
+        <v>49</v>
+      </c>
+      <c r="D1075" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1075" s="28"/>
+      <c r="F1075" s="28"/>
+      <c r="G1075" s="28"/>
+      <c r="H1075" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1075" s="45" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:9">
+      <c r="A1076" s="28">
+        <v>10080050</v>
+      </c>
+      <c r="B1076" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1076" s="28">
+        <v>50</v>
+      </c>
+      <c r="D1076" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1076" s="28"/>
+      <c r="F1076" s="28"/>
+      <c r="G1076" s="28"/>
+      <c r="H1076" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1076" s="45" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:9">
+      <c r="A1077" s="28">
+        <v>10080051</v>
+      </c>
+      <c r="B1077" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1077" s="28">
+        <v>51</v>
+      </c>
+      <c r="D1077" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1077" s="28"/>
+      <c r="F1077" s="28"/>
+      <c r="G1077" s="28"/>
+      <c r="H1077" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1077" s="45" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:9">
+      <c r="A1078" s="28">
+        <v>10080052</v>
+      </c>
+      <c r="B1078" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1078" s="28">
+        <v>52</v>
+      </c>
+      <c r="D1078" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1078" s="28"/>
+      <c r="F1078" s="28"/>
+      <c r="G1078" s="28"/>
+      <c r="H1078" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1078" s="45" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:9">
+      <c r="A1079" s="28">
+        <v>10080053</v>
+      </c>
+      <c r="B1079" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1079" s="28">
+        <v>53</v>
+      </c>
+      <c r="D1079" s="28">
+        <v>1</v>
+      </c>
+      <c r="E1079" s="28"/>
+      <c r="F1079" s="28"/>
+      <c r="G1079" s="28"/>
+      <c r="H1079" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1079" s="45" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:9">
+      <c r="A1080" s="28">
+        <v>10080054</v>
+      </c>
+      <c r="B1080" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1080" s="28">
+        <v>54</v>
+      </c>
+      <c r="D1080" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1080" s="28"/>
+      <c r="F1080" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1080" s="28"/>
+      <c r="H1080" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1080" s="45" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:9">
+      <c r="A1081" s="28">
+        <v>10080055</v>
+      </c>
+      <c r="B1081" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1081" s="28">
+        <v>55</v>
+      </c>
+      <c r="D1081" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1081" s="28"/>
+      <c r="F1081" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1081" s="28"/>
+      <c r="H1081" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1081" s="45" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:9">
+      <c r="A1082" s="28">
+        <v>10080056</v>
+      </c>
+      <c r="B1082" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1082" s="28">
+        <v>56</v>
+      </c>
+      <c r="D1082" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1082" s="28"/>
+      <c r="F1082" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1082" s="28"/>
+      <c r="H1082" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1082" s="45" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:9">
+      <c r="A1083" s="28">
+        <v>10080057</v>
+      </c>
+      <c r="B1083" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1083" s="28">
+        <v>57</v>
+      </c>
+      <c r="D1083" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1083" s="28"/>
+      <c r="F1083" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1083" s="28"/>
+      <c r="H1083" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1083" s="45" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:9">
+      <c r="A1084" s="28">
+        <v>10080058</v>
+      </c>
+      <c r="B1084" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1084" s="28">
+        <v>58</v>
+      </c>
+      <c r="D1084" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1084" s="28"/>
+      <c r="F1084" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1084" s="28"/>
+      <c r="H1084" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1084" s="45" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:9">
+      <c r="A1085" s="28">
+        <v>10080059</v>
+      </c>
+      <c r="B1085" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1085" s="28">
+        <v>59</v>
+      </c>
+      <c r="D1085" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1085" s="28"/>
+      <c r="F1085" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1085" s="28"/>
+      <c r="H1085" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1085" s="45" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:9">
+      <c r="A1086" s="28">
+        <v>10080060</v>
+      </c>
+      <c r="B1086" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1086" s="28">
+        <v>60</v>
+      </c>
+      <c r="D1086" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1086" s="28"/>
+      <c r="F1086" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1086" s="28"/>
+      <c r="H1086" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1086" s="45" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:9">
+      <c r="A1087" s="28">
+        <v>10080061</v>
+      </c>
+      <c r="B1087" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1087" s="28">
+        <v>61</v>
+      </c>
+      <c r="D1087" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1087" s="28"/>
+      <c r="F1087" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1087" s="28"/>
+      <c r="H1087" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1087" s="45" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:9">
+      <c r="A1088" s="28">
+        <v>10080062</v>
+      </c>
+      <c r="B1088" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1088" s="28">
+        <v>62</v>
+      </c>
+      <c r="D1088" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1088" s="28"/>
+      <c r="F1088" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1088" s="28"/>
+      <c r="H1088" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1088" s="45" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:9">
+      <c r="A1089" s="28">
+        <v>10080063</v>
+      </c>
+      <c r="B1089" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1089" s="28">
+        <v>63</v>
+      </c>
+      <c r="D1089" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1089" s="28"/>
+      <c r="F1089" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1089" s="28"/>
+      <c r="H1089" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1089" s="45" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:9">
+      <c r="A1090" s="28">
+        <v>10080064</v>
+      </c>
+      <c r="B1090" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1090" s="28">
+        <v>64</v>
+      </c>
+      <c r="D1090" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1090" s="28"/>
+      <c r="F1090" s="28" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G1090" s="28"/>
+      <c r="H1090" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1090" s="45" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:9">
+      <c r="A1091" s="28">
+        <v>10080065</v>
+      </c>
+      <c r="B1091" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1091" s="28">
+        <v>65</v>
+      </c>
+      <c r="D1091" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1091" s="28"/>
+      <c r="F1091" s="28" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G1091" s="28"/>
+      <c r="H1091" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1091" s="45" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:9">
+      <c r="A1092" s="28">
+        <v>10080066</v>
+      </c>
+      <c r="B1092" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1092" s="28">
+        <v>66</v>
+      </c>
+      <c r="D1092" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1092" s="28"/>
+      <c r="F1092" s="28" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G1092" s="28"/>
+      <c r="H1092" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1092" s="45" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:9">
+      <c r="A1093" s="28">
+        <v>10080067</v>
+      </c>
+      <c r="B1093" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1093" s="28">
+        <v>67</v>
+      </c>
+      <c r="D1093" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1093" s="28"/>
+      <c r="F1093" s="28" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G1093" s="28"/>
+      <c r="H1093" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1093" s="45" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:9">
+      <c r="A1094" s="28">
+        <v>10080068</v>
+      </c>
+      <c r="B1094" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1094" s="28">
+        <v>68</v>
+      </c>
+      <c r="D1094" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1094" s="28"/>
+      <c r="F1094" s="28" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G1094" s="28"/>
+      <c r="H1094" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1094" s="45" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:9">
+      <c r="A1095" s="28">
+        <v>10080069</v>
+      </c>
+      <c r="B1095" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1095" s="28">
+        <v>69</v>
+      </c>
+      <c r="D1095" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1095" s="28"/>
+      <c r="F1095" s="28" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G1095" s="28"/>
+      <c r="H1095" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1095" s="45" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:9">
+      <c r="A1096" s="28">
+        <v>10080070</v>
+      </c>
+      <c r="B1096" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1096" s="28">
+        <v>70</v>
+      </c>
+      <c r="D1096" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1096" s="28"/>
+      <c r="F1096" s="28" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G1096" s="28"/>
+      <c r="H1096" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1096" s="45" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:9">
+      <c r="A1097" s="28">
+        <v>10080071</v>
+      </c>
+      <c r="B1097" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1097" s="28">
+        <v>71</v>
+      </c>
+      <c r="D1097" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1097" s="28"/>
+      <c r="F1097" s="28" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G1097" s="28"/>
+      <c r="H1097" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1097" s="45" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:9">
+      <c r="A1098" s="28">
+        <v>10080072</v>
+      </c>
+      <c r="B1098" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1098" s="28">
+        <v>72</v>
+      </c>
+      <c r="D1098" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1098" s="28"/>
+      <c r="F1098" s="28" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G1098" s="28"/>
+      <c r="H1098" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1098" s="45" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:9">
+      <c r="A1099" s="28">
+        <v>10080073</v>
+      </c>
+      <c r="B1099" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1099" s="28">
+        <v>73</v>
+      </c>
+      <c r="D1099" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1099" s="28"/>
+      <c r="F1099" s="28" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G1099" s="28"/>
+      <c r="H1099" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1099" s="45" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:9">
+      <c r="A1100" s="28">
+        <v>10080074</v>
+      </c>
+      <c r="B1100" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1100" s="28">
+        <v>74</v>
+      </c>
+      <c r="D1100" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1100" s="28"/>
+      <c r="F1100" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1100" s="28"/>
+      <c r="H1100" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1100" s="45" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:9">
+      <c r="A1101" s="28">
+        <v>10080075</v>
+      </c>
+      <c r="B1101" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1101" s="28">
+        <v>75</v>
+      </c>
+      <c r="D1101" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1101" s="28"/>
+      <c r="F1101" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1101" s="28"/>
+      <c r="H1101" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1101" s="45" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:9">
+      <c r="A1102" s="28">
+        <v>10080076</v>
+      </c>
+      <c r="B1102" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1102" s="28">
+        <v>76</v>
+      </c>
+      <c r="D1102" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1102" s="28"/>
+      <c r="F1102" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1102" s="28"/>
+      <c r="H1102" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1102" s="45" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:9">
+      <c r="A1103" s="28">
+        <v>10080077</v>
+      </c>
+      <c r="B1103" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1103" s="28">
+        <v>77</v>
+      </c>
+      <c r="D1103" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1103" s="28"/>
+      <c r="F1103" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1103" s="28"/>
+      <c r="H1103" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1103" s="45" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:9">
+      <c r="A1104" s="28">
+        <v>10080078</v>
+      </c>
+      <c r="B1104" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1104" s="28">
+        <v>78</v>
+      </c>
+      <c r="D1104" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1104" s="28"/>
+      <c r="F1104" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1104" s="28"/>
+      <c r="H1104" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1104" s="45" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:9">
+      <c r="A1105" s="28">
+        <v>10080079</v>
+      </c>
+      <c r="B1105" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1105" s="28">
+        <v>79</v>
+      </c>
+      <c r="D1105" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1105" s="28"/>
+      <c r="F1105" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1105" s="28"/>
+      <c r="H1105" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1105" s="45" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:9">
+      <c r="A1106" s="28">
+        <v>10080080</v>
+      </c>
+      <c r="B1106" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1106" s="28">
+        <v>80</v>
+      </c>
+      <c r="D1106" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1106" s="28"/>
+      <c r="F1106" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1106" s="28"/>
+      <c r="H1106" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1106" s="45" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:9">
+      <c r="A1107" s="28">
+        <v>10080081</v>
+      </c>
+      <c r="B1107" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1107" s="28">
+        <v>81</v>
+      </c>
+      <c r="D1107" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1107" s="28"/>
+      <c r="F1107" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1107" s="28"/>
+      <c r="H1107" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1107" s="45" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:9">
+      <c r="A1108" s="28">
+        <v>10080082</v>
+      </c>
+      <c r="B1108" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1108" s="28">
+        <v>82</v>
+      </c>
+      <c r="D1108" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1108" s="28"/>
+      <c r="F1108" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1108" s="28"/>
+      <c r="H1108" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1108" s="45" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:9">
+      <c r="A1109" s="28">
+        <v>10080083</v>
+      </c>
+      <c r="B1109" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1109" s="28">
+        <v>83</v>
+      </c>
+      <c r="D1109" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1109" s="28"/>
+      <c r="F1109" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1109" s="28"/>
+      <c r="H1109" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1109" s="45" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:9">
+      <c r="A1110" s="28">
+        <v>10080084</v>
+      </c>
+      <c r="B1110" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1110" s="28">
+        <v>84</v>
+      </c>
+      <c r="D1110" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1110" s="28"/>
+      <c r="F1110" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1110" s="28"/>
+      <c r="H1110" s="64">
+        <v>2</v>
+      </c>
+      <c r="I1110" s="45" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:9">
+      <c r="A1111" s="28">
+        <v>10080085</v>
+      </c>
+      <c r="B1111" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1111" s="28">
+        <v>85</v>
+      </c>
+      <c r="D1111" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1111" s="28"/>
+      <c r="F1111" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1111" s="28"/>
+      <c r="H1111" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1111" s="45" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:9">
+      <c r="A1112" s="28">
+        <v>10080086</v>
+      </c>
+      <c r="B1112" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1112" s="28">
+        <v>86</v>
+      </c>
+      <c r="D1112" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1112" s="28"/>
+      <c r="F1112" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1112" s="28"/>
+      <c r="H1112" s="64">
+        <v>2</v>
+      </c>
+      <c r="I1112" s="45" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:9">
+      <c r="A1113" s="28">
+        <v>10080087</v>
+      </c>
+      <c r="B1113" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1113" s="28">
+        <v>87</v>
+      </c>
+      <c r="D1113" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1113" s="28"/>
+      <c r="F1113" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1113" s="28"/>
+      <c r="H1113" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1113" s="45" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:9">
+      <c r="A1114" s="28">
+        <v>10080088</v>
+      </c>
+      <c r="B1114" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1114" s="28">
+        <v>88</v>
+      </c>
+      <c r="D1114" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1114" s="28"/>
+      <c r="F1114" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1114" s="28"/>
+      <c r="H1114" s="64">
+        <v>2</v>
+      </c>
+      <c r="I1114" s="45" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:9">
+      <c r="A1115" s="28">
+        <v>10080089</v>
+      </c>
+      <c r="B1115" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1115" s="28">
+        <v>89</v>
+      </c>
+      <c r="D1115" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1115" s="28"/>
+      <c r="F1115" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1115" s="28"/>
+      <c r="H1115" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1115" s="45" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:9">
+      <c r="A1116" s="28">
+        <v>10080090</v>
+      </c>
+      <c r="B1116" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1116" s="28">
+        <v>90</v>
+      </c>
+      <c r="D1116" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1116" s="28"/>
+      <c r="F1116" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1116" s="28"/>
+      <c r="H1116" s="64">
+        <v>2</v>
+      </c>
+      <c r="I1116" s="45" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:9">
+      <c r="A1117" s="28">
+        <v>10080091</v>
+      </c>
+      <c r="B1117" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1117" s="28">
+        <v>91</v>
+      </c>
+      <c r="D1117" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1117" s="28"/>
+      <c r="F1117" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1117" s="28"/>
+      <c r="H1117" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1117" s="45" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:9">
+      <c r="A1118" s="28">
+        <v>10080092</v>
+      </c>
+      <c r="B1118" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1118" s="28">
+        <v>92</v>
+      </c>
+      <c r="D1118" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1118" s="28"/>
+      <c r="F1118" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1118" s="28"/>
+      <c r="H1118" s="64">
+        <v>2</v>
+      </c>
+      <c r="I1118" s="45" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:9">
+      <c r="A1119" s="28">
+        <v>10080093</v>
+      </c>
+      <c r="B1119" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1119" s="28">
+        <v>93</v>
+      </c>
+      <c r="D1119" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1119" s="28"/>
+      <c r="F1119" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1119" s="28"/>
+      <c r="H1119" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1119" s="45" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:9">
+      <c r="A1120" s="28">
+        <v>10080094</v>
+      </c>
+      <c r="B1120" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1120" s="28">
+        <v>94</v>
+      </c>
+      <c r="D1120" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1120" s="28"/>
+      <c r="F1120" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1120" s="28"/>
+      <c r="H1120" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1120" s="45" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:9">
+      <c r="A1121" s="28">
+        <v>10080095</v>
+      </c>
+      <c r="B1121" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1121" s="28">
+        <v>95</v>
+      </c>
+      <c r="D1121" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1121" s="28"/>
+      <c r="F1121" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1121" s="28"/>
+      <c r="H1121" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1121" s="45" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:9">
+      <c r="A1122" s="28">
+        <v>10080096</v>
+      </c>
+      <c r="B1122" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1122" s="28">
+        <v>96</v>
+      </c>
+      <c r="D1122" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1122" s="28"/>
+      <c r="F1122" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1122" s="28"/>
+      <c r="H1122" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1122" s="45" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:9">
+      <c r="A1123" s="28">
+        <v>10080097</v>
+      </c>
+      <c r="B1123" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1123" s="28">
+        <v>97</v>
+      </c>
+      <c r="D1123" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1123" s="28"/>
+      <c r="F1123" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1123" s="28"/>
+      <c r="H1123" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1123" s="45" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:9">
+      <c r="A1124" s="28">
+        <v>10080098</v>
+      </c>
+      <c r="B1124" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1124" s="28">
+        <v>98</v>
+      </c>
+      <c r="D1124" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1124" s="28"/>
+      <c r="F1124" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1124" s="28"/>
+      <c r="H1124" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1124" s="45" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:9">
+      <c r="A1125" s="28">
+        <v>10080099</v>
+      </c>
+      <c r="B1125" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1125" s="28">
+        <v>99</v>
+      </c>
+      <c r="D1125" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1125" s="28"/>
+      <c r="F1125" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1125" s="28"/>
+      <c r="H1125" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1125" s="45" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:9">
+      <c r="A1126" s="28">
+        <v>10080100</v>
+      </c>
+      <c r="B1126" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1126" s="28">
+        <v>100</v>
+      </c>
+      <c r="D1126" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1126" s="28"/>
+      <c r="F1126" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1126" s="28"/>
+      <c r="H1126" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1126" s="45" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:9">
+      <c r="A1127" s="28">
+        <v>10080101</v>
+      </c>
+      <c r="B1127" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1127" s="28">
+        <v>101</v>
+      </c>
+      <c r="D1127" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1127" s="28"/>
+      <c r="F1127" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1127" s="28"/>
+      <c r="H1127" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1127" s="45" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:9">
+      <c r="A1128" s="28">
+        <v>10080102</v>
+      </c>
+      <c r="B1128" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1128" s="28">
+        <v>102</v>
+      </c>
+      <c r="D1128" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1128" s="28"/>
+      <c r="F1128" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1128" s="28"/>
+      <c r="H1128" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1128" s="45" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:9">
+      <c r="A1129" s="28">
+        <v>10080103</v>
+      </c>
+      <c r="B1129" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1129" s="28">
+        <v>103</v>
+      </c>
+      <c r="D1129" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1129" s="28"/>
+      <c r="F1129" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1129" s="28"/>
+      <c r="H1129" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1129" s="45" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:9">
+      <c r="A1130" s="28">
+        <v>10080104</v>
+      </c>
+      <c r="B1130" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1130" s="28">
+        <v>104</v>
+      </c>
+      <c r="D1130" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1130" s="28"/>
+      <c r="F1130" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1130" s="28"/>
+      <c r="H1130" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1130" s="45" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:9">
+      <c r="A1131" s="28">
+        <v>10080105</v>
+      </c>
+      <c r="B1131" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1131" s="28">
+        <v>105</v>
+      </c>
+      <c r="D1131" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1131" s="28"/>
+      <c r="F1131" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1131" s="28"/>
+      <c r="H1131" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1131" s="45" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:9">
+      <c r="A1132" s="28">
+        <v>10080106</v>
+      </c>
+      <c r="B1132" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1132" s="28">
+        <v>106</v>
+      </c>
+      <c r="D1132" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1132" s="28"/>
+      <c r="F1132" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1132" s="28"/>
+      <c r="H1132" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1132" s="45" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:9">
+      <c r="A1133" s="28">
+        <v>10080107</v>
+      </c>
+      <c r="B1133" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1133" s="28">
+        <v>107</v>
+      </c>
+      <c r="D1133" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1133" s="28"/>
+      <c r="F1133" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1133" s="28"/>
+      <c r="H1133" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1133" s="45" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:9">
+      <c r="A1134" s="28">
+        <v>10080108</v>
+      </c>
+      <c r="B1134" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1134" s="28">
+        <v>108</v>
+      </c>
+      <c r="D1134" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1134" s="28"/>
+      <c r="F1134" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1134" s="28"/>
+      <c r="H1134" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1134" s="45" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:9">
+      <c r="A1135" s="28">
+        <v>10080109</v>
+      </c>
+      <c r="B1135" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1135" s="28">
+        <v>109</v>
+      </c>
+      <c r="D1135" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1135" s="28"/>
+      <c r="F1135" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1135" s="28"/>
+      <c r="H1135" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1135" s="45" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:9">
+      <c r="A1136" s="28">
+        <v>10080110</v>
+      </c>
+      <c r="B1136" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1136" s="28">
+        <v>110</v>
+      </c>
+      <c r="D1136" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1136" s="28"/>
+      <c r="F1136" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1136" s="28"/>
+      <c r="H1136" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1136" s="45" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:9">
+      <c r="A1137" s="28">
+        <v>10080111</v>
+      </c>
+      <c r="B1137" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1137" s="28">
+        <v>111</v>
+      </c>
+      <c r="D1137" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1137" s="28"/>
+      <c r="F1137" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1137" s="28"/>
+      <c r="H1137" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1137" s="45" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:9">
+      <c r="A1138" s="28">
+        <v>10080112</v>
+      </c>
+      <c r="B1138" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1138" s="28">
+        <v>112</v>
+      </c>
+      <c r="D1138" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1138" s="28"/>
+      <c r="F1138" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1138" s="28"/>
+      <c r="H1138" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1138" s="45" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:9">
+      <c r="A1139" s="28">
+        <v>10080113</v>
+      </c>
+      <c r="B1139" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1139" s="28">
+        <v>113</v>
+      </c>
+      <c r="D1139" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1139" s="28"/>
+      <c r="F1139" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1139" s="28"/>
+      <c r="H1139" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1139" s="45" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:9">
+      <c r="A1140" s="65">
+        <v>10530001</v>
+      </c>
+      <c r="B1140" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1140" s="65">
+        <v>1</v>
+      </c>
+      <c r="D1140" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1140" s="65"/>
+      <c r="F1140" s="65"/>
+      <c r="G1140" s="65"/>
+      <c r="H1140" s="65"/>
+      <c r="I1140" s="65" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:9">
+      <c r="A1141" s="65">
+        <v>10530002</v>
+      </c>
+      <c r="B1141" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1141" s="65">
+        <v>2</v>
+      </c>
+      <c r="D1141" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1141" s="65"/>
+      <c r="F1141" s="65"/>
+      <c r="G1141" s="65"/>
+      <c r="H1141" s="65"/>
+      <c r="I1141" s="65" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:9">
+      <c r="A1142" s="65">
+        <v>10530003</v>
+      </c>
+      <c r="B1142" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1142" s="65">
+        <v>3</v>
+      </c>
+      <c r="D1142" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1142" s="65"/>
+      <c r="F1142" s="65"/>
+      <c r="G1142" s="65"/>
+      <c r="H1142" s="65"/>
+      <c r="I1142" s="65" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:9">
+      <c r="A1143" s="65">
+        <v>10530004</v>
+      </c>
+      <c r="B1143" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1143" s="65">
+        <v>4</v>
+      </c>
+      <c r="D1143" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1143" s="65"/>
+      <c r="F1143" s="65"/>
+      <c r="G1143" s="65"/>
+      <c r="H1143" s="65"/>
+      <c r="I1143" s="65" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:9">
+      <c r="A1144" s="65">
+        <v>10530005</v>
+      </c>
+      <c r="B1144" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1144" s="65">
+        <v>5</v>
+      </c>
+      <c r="D1144" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1144" s="65"/>
+      <c r="F1144" s="65"/>
+      <c r="G1144" s="65"/>
+      <c r="H1144" s="65"/>
+      <c r="I1144" s="65" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:9">
+      <c r="A1145" s="65">
+        <v>10530006</v>
+      </c>
+      <c r="B1145" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1145" s="65">
+        <v>6</v>
+      </c>
+      <c r="D1145" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1145" s="65"/>
+      <c r="F1145" s="65"/>
+      <c r="G1145" s="65"/>
+      <c r="H1145" s="65"/>
+      <c r="I1145" s="65" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:9">
+      <c r="A1146" s="65">
+        <v>10530007</v>
+      </c>
+      <c r="B1146" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1146" s="65">
+        <v>7</v>
+      </c>
+      <c r="D1146" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1146" s="65"/>
+      <c r="F1146" s="65"/>
+      <c r="G1146" s="65"/>
+      <c r="H1146" s="65"/>
+      <c r="I1146" s="65" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:9">
+      <c r="A1147" s="65">
+        <v>10530008</v>
+      </c>
+      <c r="B1147" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1147" s="65">
+        <v>8</v>
+      </c>
+      <c r="D1147" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1147" s="65"/>
+      <c r="F1147" s="65"/>
+      <c r="G1147" s="65"/>
+      <c r="H1147" s="65"/>
+      <c r="I1147" s="65" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:9">
+      <c r="A1148" s="65">
+        <v>10530009</v>
+      </c>
+      <c r="B1148" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1148" s="65">
+        <v>9</v>
+      </c>
+      <c r="D1148" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1148" s="65"/>
+      <c r="F1148" s="65"/>
+      <c r="G1148" s="65"/>
+      <c r="H1148" s="65"/>
+      <c r="I1148" s="65" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:9">
+      <c r="A1149" s="65">
+        <v>10530010</v>
+      </c>
+      <c r="B1149" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1149" s="65">
+        <v>10</v>
+      </c>
+      <c r="D1149" s="65">
+        <v>1</v>
+      </c>
+      <c r="E1149" s="65"/>
+      <c r="F1149" s="65"/>
+      <c r="G1149" s="65"/>
+      <c r="H1149" s="65"/>
+      <c r="I1149" s="65" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:9">
+      <c r="A1150" s="65">
+        <v>10530011</v>
+      </c>
+      <c r="B1150" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1150" s="65">
+        <v>11</v>
+      </c>
+      <c r="D1150" s="65">
+        <v>2</v>
+      </c>
+      <c r="E1150" s="65"/>
+      <c r="F1150" s="65"/>
+      <c r="G1150" s="65"/>
+      <c r="H1150" s="65"/>
+      <c r="I1150" s="65" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:9">
+      <c r="A1151" s="65">
+        <v>10530012</v>
+      </c>
+      <c r="B1151" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1151" s="65">
+        <v>12</v>
+      </c>
+      <c r="D1151" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1151" s="65"/>
+      <c r="F1151" s="65" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G1151" s="65"/>
+      <c r="H1151" s="65"/>
+      <c r="I1151" s="65" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:9">
+      <c r="A1152" s="65">
+        <v>10530013</v>
+      </c>
+      <c r="B1152" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1152" s="65">
+        <v>13</v>
+      </c>
+      <c r="D1152" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1152" s="65"/>
+      <c r="F1152" s="65" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G1152" s="65"/>
+      <c r="H1152" s="65"/>
+      <c r="I1152" s="65" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:9">
+      <c r="A1153" s="65">
+        <v>10530014</v>
+      </c>
+      <c r="B1153" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1153" s="65">
+        <v>14</v>
+      </c>
+      <c r="D1153" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1153" s="65"/>
+      <c r="F1153" s="65" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G1153" s="65"/>
+      <c r="H1153" s="65"/>
+      <c r="I1153" s="65" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:9">
+      <c r="A1154" s="65">
+        <v>10530015</v>
+      </c>
+      <c r="B1154" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1154" s="65">
+        <v>15</v>
+      </c>
+      <c r="D1154" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1154" s="65"/>
+      <c r="F1154" s="65" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G1154" s="65"/>
+      <c r="H1154" s="65"/>
+      <c r="I1154" s="65" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:9">
+      <c r="A1155" s="65">
+        <v>10530016</v>
+      </c>
+      <c r="B1155" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1155" s="65">
+        <v>16</v>
+      </c>
+      <c r="D1155" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1155" s="65"/>
+      <c r="F1155" s="65" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G1155" s="65"/>
+      <c r="H1155" s="65"/>
+      <c r="I1155" s="65" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:9">
+      <c r="A1156" s="65">
+        <v>10530017</v>
+      </c>
+      <c r="B1156" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1156" s="65">
+        <v>17</v>
+      </c>
+      <c r="D1156" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1156" s="65"/>
+      <c r="F1156" s="65" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G1156" s="65"/>
+      <c r="H1156" s="65"/>
+      <c r="I1156" s="65" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:9">
+      <c r="A1157" s="65">
+        <v>10530018</v>
+      </c>
+      <c r="B1157" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1157" s="65">
+        <v>18</v>
+      </c>
+      <c r="D1157" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1157" s="65"/>
+      <c r="F1157" s="65" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G1157" s="65"/>
+      <c r="H1157" s="65"/>
+      <c r="I1157" s="65" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:9">
+      <c r="A1158" s="65">
+        <v>10530019</v>
+      </c>
+      <c r="B1158" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1158" s="65">
+        <v>19</v>
+      </c>
+      <c r="D1158" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1158" s="65"/>
+      <c r="F1158" s="65" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G1158" s="65"/>
+      <c r="H1158" s="65"/>
+      <c r="I1158" s="65" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:9">
+      <c r="A1159" s="65">
+        <v>10530020</v>
+      </c>
+      <c r="B1159" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1159" s="65">
+        <v>20</v>
+      </c>
+      <c r="D1159" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1159" s="65"/>
+      <c r="F1159" s="65" t="s">
+        <v>1503</v>
+      </c>
+      <c r="G1159" s="65"/>
+      <c r="H1159" s="65"/>
+      <c r="I1159" s="65" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:9">
+      <c r="A1160" s="23">
+        <v>10570001</v>
+      </c>
+      <c r="B1160" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1160" s="23">
+        <v>1</v>
+      </c>
+      <c r="D1160" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1160" s="23"/>
+      <c r="F1160" s="23"/>
+      <c r="G1160" s="23"/>
+      <c r="H1160" s="23"/>
+      <c r="I1160" s="23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:9">
+      <c r="A1161" s="23">
+        <v>10570002</v>
+      </c>
+      <c r="B1161" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1161" s="23">
+        <v>2</v>
+      </c>
+      <c r="D1161" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1161" s="23"/>
+      <c r="F1161" s="23"/>
+      <c r="G1161" s="23"/>
+      <c r="H1161" s="23"/>
+      <c r="I1161" s="23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:9">
+      <c r="A1162" s="23">
+        <v>10570003</v>
+      </c>
+      <c r="B1162" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1162" s="23">
+        <v>3</v>
+      </c>
+      <c r="D1162" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1162" s="23"/>
+      <c r="F1162" s="23"/>
+      <c r="G1162" s="23"/>
+      <c r="H1162" s="23"/>
+      <c r="I1162" s="23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:9">
+      <c r="A1163" s="23">
+        <v>10570004</v>
+      </c>
+      <c r="B1163" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1163" s="23">
+        <v>4</v>
+      </c>
+      <c r="D1163" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1163" s="23"/>
+      <c r="F1163" s="23"/>
+      <c r="G1163" s="23"/>
+      <c r="H1163" s="23"/>
+      <c r="I1163" s="23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:9">
+      <c r="A1164" s="23">
+        <v>10570005</v>
+      </c>
+      <c r="B1164" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1164" s="23">
+        <v>5</v>
+      </c>
+      <c r="D1164" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1164" s="23"/>
+      <c r="F1164" s="23"/>
+      <c r="G1164" s="23"/>
+      <c r="H1164" s="23"/>
+      <c r="I1164" s="23" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:9">
+      <c r="A1165" s="23">
+        <v>10570006</v>
+      </c>
+      <c r="B1165" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1165" s="23">
+        <v>6</v>
+      </c>
+      <c r="D1165" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1165" s="23"/>
+      <c r="F1165" s="23"/>
+      <c r="G1165" s="23"/>
+      <c r="H1165" s="23"/>
+      <c r="I1165" s="23" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:9">
+      <c r="A1166" s="23">
+        <v>10570007</v>
+      </c>
+      <c r="B1166" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1166" s="23">
+        <v>7</v>
+      </c>
+      <c r="D1166" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1166" s="23"/>
+      <c r="F1166" s="23"/>
+      <c r="G1166" s="23"/>
+      <c r="H1166" s="23"/>
+      <c r="I1166" s="23" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:9">
+      <c r="A1167" s="23">
+        <v>10570008</v>
+      </c>
+      <c r="B1167" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1167" s="23">
+        <v>8</v>
+      </c>
+      <c r="D1167" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1167" s="23"/>
+      <c r="F1167" s="23"/>
+      <c r="G1167" s="23"/>
+      <c r="H1167" s="23"/>
+      <c r="I1167" s="23" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:9">
+      <c r="A1168" s="23">
+        <v>10570009</v>
+      </c>
+      <c r="B1168" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1168" s="23">
+        <v>9</v>
+      </c>
+      <c r="D1168" s="23">
+        <v>1</v>
+      </c>
+      <c r="E1168" s="23"/>
+      <c r="F1168" s="23"/>
+      <c r="G1168" s="23"/>
+      <c r="H1168" s="23"/>
+      <c r="I1168" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:9">
+      <c r="A1169" s="23">
+        <v>10570010</v>
+      </c>
+      <c r="B1169" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1169" s="23">
+        <v>10</v>
+      </c>
+      <c r="D1169" s="23">
+        <v>2</v>
+      </c>
+      <c r="E1169" s="23"/>
+      <c r="F1169" s="23"/>
+      <c r="G1169" s="23"/>
+      <c r="H1169" s="23"/>
+      <c r="I1169" s="23" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:9">
+      <c r="A1170" s="23">
+        <v>10570011</v>
+      </c>
+      <c r="B1170" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1170" s="23">
+        <v>11</v>
+      </c>
+      <c r="D1170" s="23">
+        <v>2</v>
+      </c>
+      <c r="E1170" s="23"/>
+      <c r="F1170" s="23"/>
+      <c r="G1170" s="23"/>
+      <c r="H1170" s="23"/>
+      <c r="I1170" s="23" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:9">
+      <c r="A1171" s="23">
+        <v>10570012</v>
+      </c>
+      <c r="B1171" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1171" s="23">
+        <v>12</v>
+      </c>
+      <c r="D1171" s="23">
+        <v>2</v>
+      </c>
+      <c r="E1171" s="23"/>
+      <c r="F1171" s="23"/>
+      <c r="G1171" s="23"/>
+      <c r="H1171" s="23"/>
+      <c r="I1171" s="23" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:9">
+      <c r="A1172" s="23">
+        <v>10570013</v>
+      </c>
+      <c r="B1172" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1172" s="23">
+        <v>13</v>
+      </c>
+      <c r="D1172" s="23">
+        <v>2</v>
+      </c>
+      <c r="E1172" s="23"/>
+      <c r="F1172" s="23"/>
+      <c r="G1172" s="23"/>
+      <c r="H1172" s="23"/>
+      <c r="I1172" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:9">
+      <c r="A1173" s="23">
+        <v>10570014</v>
+      </c>
+      <c r="B1173" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1173" s="23">
+        <v>14</v>
+      </c>
+      <c r="D1173" s="23">
+        <v>2</v>
+      </c>
+      <c r="E1173" s="23"/>
+      <c r="F1173" s="23"/>
+      <c r="G1173" s="23"/>
+      <c r="H1173" s="23"/>
+      <c r="I1173" s="23" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:9">
+      <c r="A1174" s="23">
+        <v>10570015</v>
+      </c>
+      <c r="B1174" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1174" s="23">
+        <v>15</v>
+      </c>
+      <c r="D1174" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1174" s="23"/>
+      <c r="F1174" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1174" s="23"/>
+      <c r="H1174" s="23"/>
+      <c r="I1174" s="23" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:9">
+      <c r="A1175" s="23">
+        <v>10570016</v>
+      </c>
+      <c r="B1175" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1175" s="23">
+        <v>16</v>
+      </c>
+      <c r="D1175" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1175" s="23"/>
+      <c r="F1175" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1175" s="23"/>
+      <c r="H1175" s="23"/>
+      <c r="I1175" s="23" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:9">
+      <c r="A1176" s="23">
+        <v>10570017</v>
+      </c>
+      <c r="B1176" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1176" s="23">
+        <v>17</v>
+      </c>
+      <c r="D1176" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1176" s="23"/>
+      <c r="F1176" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1176" s="23"/>
+      <c r="H1176" s="23"/>
+      <c r="I1176" s="23" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:9">
+      <c r="A1177" s="23">
+        <v>10570018</v>
+      </c>
+      <c r="B1177" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1177" s="23">
+        <v>18</v>
+      </c>
+      <c r="D1177" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1177" s="23"/>
+      <c r="F1177" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1177" s="23"/>
+      <c r="H1177" s="23"/>
+      <c r="I1177" s="23" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:9">
+      <c r="A1178" s="23">
+        <v>10570019</v>
+      </c>
+      <c r="B1178" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1178" s="23">
+        <v>19</v>
+      </c>
+      <c r="D1178" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1178" s="23"/>
+      <c r="F1178" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1178" s="23"/>
+      <c r="H1178" s="23"/>
+      <c r="I1178" s="23" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:9">
+      <c r="A1179" s="23">
+        <v>10570020</v>
+      </c>
+      <c r="B1179" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1179" s="23">
+        <v>20</v>
+      </c>
+      <c r="D1179" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1179" s="23"/>
+      <c r="F1179" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1179" s="23"/>
+      <c r="H1179" s="23"/>
+      <c r="I1179" s="23" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:9">
+      <c r="A1180" s="23">
+        <v>10570021</v>
+      </c>
+      <c r="B1180" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1180" s="23">
+        <v>21</v>
+      </c>
+      <c r="D1180" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1180" s="23"/>
+      <c r="F1180" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1180" s="23"/>
+      <c r="H1180" s="23"/>
+      <c r="I1180" s="23" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:9">
+      <c r="A1181" s="23">
+        <v>10570022</v>
+      </c>
+      <c r="B1181" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1181" s="23">
+        <v>22</v>
+      </c>
+      <c r="D1181" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1181" s="23"/>
+      <c r="F1181" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1181" s="23"/>
+      <c r="H1181" s="23"/>
+      <c r="I1181" s="23" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:9">
+      <c r="A1182" s="43">
+        <v>10580001</v>
+      </c>
+      <c r="B1182" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1182" s="43">
+        <v>1</v>
+      </c>
+      <c r="D1182" s="43">
+        <v>0</v>
+      </c>
+      <c r="E1182" s="43"/>
+      <c r="F1182" s="43"/>
+      <c r="G1182" s="43"/>
+      <c r="H1182" s="43"/>
+      <c r="I1182" s="43" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:9">
+      <c r="A1183" s="43">
+        <v>10580002</v>
+      </c>
+      <c r="B1183" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1183" s="43">
+        <v>2</v>
+      </c>
+      <c r="D1183" s="43">
+        <v>0</v>
+      </c>
+      <c r="E1183" s="43"/>
+      <c r="F1183" s="43"/>
+      <c r="G1183" s="43"/>
+      <c r="H1183" s="43"/>
+      <c r="I1183" s="43" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:9">
+      <c r="A1184" s="43">
+        <v>10580003</v>
+      </c>
+      <c r="B1184" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1184" s="43">
+        <v>3</v>
+      </c>
+      <c r="D1184" s="43">
+        <v>0</v>
+      </c>
+      <c r="E1184" s="43"/>
+      <c r="F1184" s="43"/>
+      <c r="G1184" s="43"/>
+      <c r="H1184" s="43"/>
+      <c r="I1184" s="43" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:9">
+      <c r="A1185" s="43">
+        <v>10580004</v>
+      </c>
+      <c r="B1185" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1185" s="43">
+        <v>4</v>
+      </c>
+      <c r="D1185" s="43">
+        <v>0</v>
+      </c>
+      <c r="E1185" s="43"/>
+      <c r="F1185" s="43"/>
+      <c r="G1185" s="43"/>
+      <c r="H1185" s="43"/>
+      <c r="I1185" s="43" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:9">
+      <c r="A1186" s="43">
+        <v>10580005</v>
+      </c>
+      <c r="B1186" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1186" s="43">
+        <v>5</v>
+      </c>
+      <c r="D1186" s="43">
+        <v>0</v>
+      </c>
+      <c r="E1186" s="43"/>
+      <c r="F1186" s="43"/>
+      <c r="G1186" s="43"/>
+      <c r="H1186" s="43"/>
+      <c r="I1186" s="43" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:9">
+      <c r="A1187" s="43">
+        <v>10580006</v>
+      </c>
+      <c r="B1187" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1187" s="43">
+        <v>6</v>
+      </c>
+      <c r="D1187" s="43">
+        <v>0</v>
+      </c>
+      <c r="E1187" s="43"/>
+      <c r="F1187" s="43"/>
+      <c r="G1187" s="43"/>
+      <c r="H1187" s="43"/>
+      <c r="I1187" s="43" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:9">
+      <c r="A1188" s="43">
+        <v>10580007</v>
+      </c>
+      <c r="B1188" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1188" s="43">
+        <v>7</v>
+      </c>
+      <c r="D1188" s="43">
+        <v>0</v>
+      </c>
+      <c r="E1188" s="43"/>
+      <c r="F1188" s="43"/>
+      <c r="G1188" s="43"/>
+      <c r="H1188" s="43"/>
+      <c r="I1188" s="43" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:9">
+      <c r="A1189" s="43">
+        <v>10580008</v>
+      </c>
+      <c r="B1189" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1189" s="43">
+        <v>8</v>
+      </c>
+      <c r="D1189" s="43">
+        <v>2</v>
+      </c>
+      <c r="E1189" s="43"/>
+      <c r="F1189" s="43"/>
+      <c r="G1189" s="43"/>
+      <c r="H1189" s="43"/>
+      <c r="I1189" s="43" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1190" ht="17.25" spans="1:9">
+      <c r="A1190" s="43">
+        <v>10580009</v>
+      </c>
+      <c r="B1190" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1190" s="43">
+        <v>9</v>
+      </c>
+      <c r="D1190" s="43">
+        <v>2</v>
+      </c>
+      <c r="E1190" s="43"/>
+      <c r="F1190" s="43"/>
+      <c r="G1190" s="43"/>
+      <c r="H1190" s="43"/>
+      <c r="I1190" s="66" t="s">
+        <v>1524</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="9855" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2368" uniqueCount="1536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2490" uniqueCount="1604">
   <si>
     <t>图标</t>
   </si>
@@ -4723,6 +4723,210 @@
   </si>
   <si>
     <t>15x</t>
+  </si>
+  <si>
+    <t>图标10</t>
+  </si>
+  <si>
+    <t>图标J</t>
+  </si>
+  <si>
+    <t>图标Q</t>
+  </si>
+  <si>
+    <t>图标K</t>
+  </si>
+  <si>
+    <t>图标A</t>
+  </si>
+  <si>
+    <t>图标6</t>
+  </si>
+  <si>
+    <t>百搭符号</t>
+  </si>
+  <si>
+    <t>夺宝符号</t>
+  </si>
+  <si>
+    <t>神秘符号</t>
+  </si>
+  <si>
+    <t>图标10x2</t>
+  </si>
+  <si>
+    <t>图标Jx2</t>
+  </si>
+  <si>
+    <t>图标Qx2</t>
+  </si>
+  <si>
+    <t>图标Kx2</t>
+  </si>
+  <si>
+    <t>图标Ax2</t>
+  </si>
+  <si>
+    <t>图标1x2</t>
+  </si>
+  <si>
+    <t>图标2x2</t>
+  </si>
+  <si>
+    <t>图标3x2</t>
+  </si>
+  <si>
+    <t>图标4x2</t>
+  </si>
+  <si>
+    <t>图标5x2</t>
+  </si>
+  <si>
+    <t>图标6x2</t>
+  </si>
+  <si>
+    <t>图标10x3</t>
+  </si>
+  <si>
+    <t>图标Jx3</t>
+  </si>
+  <si>
+    <t>图标Qx3</t>
+  </si>
+  <si>
+    <t>图标Kx3</t>
+  </si>
+  <si>
+    <t>图标Ax3</t>
+  </si>
+  <si>
+    <t>图标1x3</t>
+  </si>
+  <si>
+    <t>图标2x3</t>
+  </si>
+  <si>
+    <t>图标3x3</t>
+  </si>
+  <si>
+    <t>图标4x3</t>
+  </si>
+  <si>
+    <t>图标5x3</t>
+  </si>
+  <si>
+    <t>图标6x3</t>
+  </si>
+  <si>
+    <t>1_100|2_80|3_60|4_40|5_20|6_10|7_8|8_6|9_4|10_2|11_1</t>
+  </si>
+  <si>
+    <t>方框图标10消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标J消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标Q消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标K消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标A消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标1消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标2消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标3消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标4消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标5消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标6消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>19_100|20_80|21_60|22_40|23_20|24_10|25_8|26_6|27_4|28_2|29_1</t>
+  </si>
+  <si>
+    <t>方框图标10x2消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标Jx2消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标Qx2消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标Kx2消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标Ax2消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标1x2消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标2x2消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标3x2消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标4x2消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标5x2消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标6x2消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>30_100|31_80|32_60|33_40|34_20|35_10|36_8|37_6|38_4|39_2|40_1</t>
+  </si>
+  <si>
+    <t>方框图标10x3消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标Jx3消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标Qx3消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标Kx3消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标Ax3消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标1x3消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标2x3消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标3x3消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标4x3消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标5x3消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>方框图标6x3消除后随机变成普通符号</t>
+  </si>
+  <si>
+    <t>wheel</t>
   </si>
 </sst>
 </file>
@@ -4942,17 +5146,17 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -5254,7 +5458,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -5304,6 +5508,32 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5431,7 +5661,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5443,34 +5673,34 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5556,7 +5786,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5756,6 +5986,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
@@ -6082,7 +6318,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N1206"/>
+  <dimension ref="A1:N1295"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -11680,7 +11916,7 @@
       <c r="F211" s="31"/>
       <c r="G211" s="32"/>
       <c r="H211" s="34"/>
-      <c r="I211" s="67" t="s">
+      <c r="I211" s="69" t="s">
         <v>302</v>
       </c>
     </row>
@@ -35605,6 +35841,2029 @@
       <c r="H1206" s="66"/>
       <c r="I1206" s="66" t="s">
         <v>1535</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:9">
+      <c r="A1207" s="50">
+        <v>10480001</v>
+      </c>
+      <c r="B1207" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1207" s="50">
+        <v>1</v>
+      </c>
+      <c r="D1207" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1207" s="50"/>
+      <c r="F1207" s="50"/>
+      <c r="G1207" s="50"/>
+      <c r="H1207" s="50"/>
+      <c r="I1207" s="50" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:9">
+      <c r="A1208" s="50">
+        <v>10480002</v>
+      </c>
+      <c r="B1208" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1208" s="50">
+        <v>2</v>
+      </c>
+      <c r="D1208" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1208" s="50"/>
+      <c r="F1208" s="50"/>
+      <c r="G1208" s="50"/>
+      <c r="H1208" s="50"/>
+      <c r="I1208" s="50" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:9">
+      <c r="A1209" s="50">
+        <v>10480003</v>
+      </c>
+      <c r="B1209" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1209" s="50">
+        <v>3</v>
+      </c>
+      <c r="D1209" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1209" s="50"/>
+      <c r="F1209" s="50"/>
+      <c r="G1209" s="50"/>
+      <c r="H1209" s="50"/>
+      <c r="I1209" s="50" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:9">
+      <c r="A1210" s="50">
+        <v>10480004</v>
+      </c>
+      <c r="B1210" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1210" s="50">
+        <v>4</v>
+      </c>
+      <c r="D1210" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1210" s="50"/>
+      <c r="F1210" s="50"/>
+      <c r="G1210" s="50"/>
+      <c r="H1210" s="50"/>
+      <c r="I1210" s="50" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:9">
+      <c r="A1211" s="50">
+        <v>10480005</v>
+      </c>
+      <c r="B1211" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1211" s="50">
+        <v>5</v>
+      </c>
+      <c r="D1211" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1211" s="50"/>
+      <c r="F1211" s="50"/>
+      <c r="G1211" s="50"/>
+      <c r="H1211" s="50"/>
+      <c r="I1211" s="50" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:9">
+      <c r="A1212" s="50">
+        <v>10480006</v>
+      </c>
+      <c r="B1212" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1212" s="50">
+        <v>6</v>
+      </c>
+      <c r="D1212" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1212" s="50"/>
+      <c r="F1212" s="50"/>
+      <c r="G1212" s="50"/>
+      <c r="H1212" s="50"/>
+      <c r="I1212" s="50" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:9">
+      <c r="A1213" s="50">
+        <v>10480007</v>
+      </c>
+      <c r="B1213" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1213" s="50">
+        <v>7</v>
+      </c>
+      <c r="D1213" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1213" s="50"/>
+      <c r="F1213" s="50"/>
+      <c r="G1213" s="50"/>
+      <c r="H1213" s="50"/>
+      <c r="I1213" s="50" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:9">
+      <c r="A1214" s="50">
+        <v>10480008</v>
+      </c>
+      <c r="B1214" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1214" s="50">
+        <v>8</v>
+      </c>
+      <c r="D1214" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1214" s="50"/>
+      <c r="F1214" s="50"/>
+      <c r="G1214" s="50"/>
+      <c r="H1214" s="50"/>
+      <c r="I1214" s="50" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:9">
+      <c r="A1215" s="50">
+        <v>10480009</v>
+      </c>
+      <c r="B1215" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1215" s="50">
+        <v>9</v>
+      </c>
+      <c r="D1215" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1215" s="50"/>
+      <c r="F1215" s="50"/>
+      <c r="G1215" s="50"/>
+      <c r="H1215" s="50"/>
+      <c r="I1215" s="50" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:9">
+      <c r="A1216" s="50">
+        <v>10480010</v>
+      </c>
+      <c r="B1216" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1216" s="50">
+        <v>10</v>
+      </c>
+      <c r="D1216" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1216" s="50"/>
+      <c r="F1216" s="50"/>
+      <c r="G1216" s="50"/>
+      <c r="H1216" s="50"/>
+      <c r="I1216" s="50" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:9">
+      <c r="A1217" s="50">
+        <v>10480011</v>
+      </c>
+      <c r="B1217" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1217" s="50">
+        <v>11</v>
+      </c>
+      <c r="D1217" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1217" s="50"/>
+      <c r="F1217" s="50"/>
+      <c r="G1217" s="50"/>
+      <c r="H1217" s="50"/>
+      <c r="I1217" s="50" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:9">
+      <c r="A1218" s="50">
+        <v>10480012</v>
+      </c>
+      <c r="B1218" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1218" s="50">
+        <v>12</v>
+      </c>
+      <c r="D1218" s="50">
+        <v>1</v>
+      </c>
+      <c r="E1218" s="50"/>
+      <c r="F1218" s="50"/>
+      <c r="G1218" s="50"/>
+      <c r="H1218" s="50"/>
+      <c r="I1218" s="50" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:9">
+      <c r="A1219" s="50">
+        <v>10480013</v>
+      </c>
+      <c r="B1219" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1219" s="50">
+        <v>13</v>
+      </c>
+      <c r="D1219" s="50">
+        <v>2</v>
+      </c>
+      <c r="E1219" s="50"/>
+      <c r="F1219" s="50"/>
+      <c r="G1219" s="50"/>
+      <c r="H1219" s="50"/>
+      <c r="I1219" s="50" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:9">
+      <c r="A1220" s="50">
+        <v>10480014</v>
+      </c>
+      <c r="B1220" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1220" s="50">
+        <v>14</v>
+      </c>
+      <c r="D1220" s="50">
+        <v>2</v>
+      </c>
+      <c r="E1220" s="50"/>
+      <c r="F1220" s="50"/>
+      <c r="G1220" s="50"/>
+      <c r="H1220" s="50"/>
+      <c r="I1220" s="50" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:9">
+      <c r="A1221" s="50">
+        <v>10480015</v>
+      </c>
+      <c r="B1221" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1221" s="50">
+        <v>15</v>
+      </c>
+      <c r="D1221" s="50">
+        <v>2</v>
+      </c>
+      <c r="E1221" s="50"/>
+      <c r="F1221" s="50"/>
+      <c r="G1221" s="50"/>
+      <c r="H1221" s="50"/>
+      <c r="I1221" s="50" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:9">
+      <c r="A1222" s="50">
+        <v>10480016</v>
+      </c>
+      <c r="B1222" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1222" s="50">
+        <v>16</v>
+      </c>
+      <c r="D1222" s="50">
+        <v>2</v>
+      </c>
+      <c r="E1222" s="50"/>
+      <c r="F1222" s="50"/>
+      <c r="G1222" s="50"/>
+      <c r="H1222" s="50"/>
+      <c r="I1222" s="50" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:9">
+      <c r="A1223" s="50">
+        <v>10480017</v>
+      </c>
+      <c r="B1223" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1223" s="50">
+        <v>17</v>
+      </c>
+      <c r="D1223" s="50">
+        <v>2</v>
+      </c>
+      <c r="E1223" s="50"/>
+      <c r="F1223" s="50"/>
+      <c r="G1223" s="50"/>
+      <c r="H1223" s="50"/>
+      <c r="I1223" s="50" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:9">
+      <c r="A1224" s="50">
+        <v>10480018</v>
+      </c>
+      <c r="B1224" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1224" s="50">
+        <v>18</v>
+      </c>
+      <c r="D1224" s="50">
+        <v>2</v>
+      </c>
+      <c r="E1224" s="50"/>
+      <c r="F1224" s="50"/>
+      <c r="G1224" s="50"/>
+      <c r="H1224" s="50"/>
+      <c r="I1224" s="50" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:9">
+      <c r="A1225" s="50">
+        <v>10480019</v>
+      </c>
+      <c r="B1225" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1225" s="50">
+        <v>19</v>
+      </c>
+      <c r="D1225" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1225" s="50"/>
+      <c r="F1225" s="50"/>
+      <c r="G1225" s="50"/>
+      <c r="H1225" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1225" s="50" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:9">
+      <c r="A1226" s="50">
+        <v>10480020</v>
+      </c>
+      <c r="B1226" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1226" s="50">
+        <v>20</v>
+      </c>
+      <c r="D1226" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1226" s="50"/>
+      <c r="F1226" s="50"/>
+      <c r="G1226" s="50"/>
+      <c r="H1226" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1226" s="50" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:9">
+      <c r="A1227" s="50">
+        <v>10480021</v>
+      </c>
+      <c r="B1227" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1227" s="50">
+        <v>21</v>
+      </c>
+      <c r="D1227" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1227" s="50"/>
+      <c r="F1227" s="50"/>
+      <c r="G1227" s="50"/>
+      <c r="H1227" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1227" s="67" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:9">
+      <c r="A1228" s="50">
+        <v>10480022</v>
+      </c>
+      <c r="B1228" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1228" s="50">
+        <v>22</v>
+      </c>
+      <c r="D1228" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1228" s="50"/>
+      <c r="F1228" s="50"/>
+      <c r="G1228" s="50"/>
+      <c r="H1228" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1228" s="67" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:9">
+      <c r="A1229" s="50">
+        <v>10480023</v>
+      </c>
+      <c r="B1229" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1229" s="50">
+        <v>23</v>
+      </c>
+      <c r="D1229" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1229" s="50"/>
+      <c r="F1229" s="50"/>
+      <c r="G1229" s="50"/>
+      <c r="H1229" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1229" s="67" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:9">
+      <c r="A1230" s="50">
+        <v>10480024</v>
+      </c>
+      <c r="B1230" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1230" s="50">
+        <v>24</v>
+      </c>
+      <c r="D1230" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1230" s="50"/>
+      <c r="F1230" s="50"/>
+      <c r="G1230" s="50"/>
+      <c r="H1230" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1230" s="67" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:9">
+      <c r="A1231" s="50">
+        <v>10480025</v>
+      </c>
+      <c r="B1231" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1231" s="50">
+        <v>25</v>
+      </c>
+      <c r="D1231" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1231" s="50"/>
+      <c r="F1231" s="50"/>
+      <c r="G1231" s="50"/>
+      <c r="H1231" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1231" s="67" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:9">
+      <c r="A1232" s="50">
+        <v>10480026</v>
+      </c>
+      <c r="B1232" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1232" s="50">
+        <v>26</v>
+      </c>
+      <c r="D1232" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1232" s="50"/>
+      <c r="F1232" s="50"/>
+      <c r="G1232" s="50"/>
+      <c r="H1232" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1232" s="67" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:9">
+      <c r="A1233" s="50">
+        <v>10480027</v>
+      </c>
+      <c r="B1233" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1233" s="50">
+        <v>27</v>
+      </c>
+      <c r="D1233" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1233" s="50"/>
+      <c r="F1233" s="50"/>
+      <c r="G1233" s="50"/>
+      <c r="H1233" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1233" s="67" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:9">
+      <c r="A1234" s="50">
+        <v>10480028</v>
+      </c>
+      <c r="B1234" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1234" s="50">
+        <v>28</v>
+      </c>
+      <c r="D1234" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1234" s="50"/>
+      <c r="F1234" s="50"/>
+      <c r="G1234" s="50"/>
+      <c r="H1234" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1234" s="67" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:9">
+      <c r="A1235" s="50">
+        <v>10480029</v>
+      </c>
+      <c r="B1235" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1235" s="50">
+        <v>29</v>
+      </c>
+      <c r="D1235" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1235" s="50"/>
+      <c r="F1235" s="50"/>
+      <c r="G1235" s="50"/>
+      <c r="H1235" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1235" s="67" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:9">
+      <c r="A1236" s="50">
+        <v>10480030</v>
+      </c>
+      <c r="B1236" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1236" s="50">
+        <v>30</v>
+      </c>
+      <c r="D1236" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1236" s="50"/>
+      <c r="F1236" s="50"/>
+      <c r="G1236" s="50"/>
+      <c r="H1236" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1236" s="67" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:9">
+      <c r="A1237" s="50">
+        <v>10480031</v>
+      </c>
+      <c r="B1237" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1237" s="50">
+        <v>31</v>
+      </c>
+      <c r="D1237" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1237" s="50"/>
+      <c r="F1237" s="50"/>
+      <c r="G1237" s="50"/>
+      <c r="H1237" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1237" s="67" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:9">
+      <c r="A1238" s="50">
+        <v>10480032</v>
+      </c>
+      <c r="B1238" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1238" s="50">
+        <v>32</v>
+      </c>
+      <c r="D1238" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1238" s="50"/>
+      <c r="F1238" s="50"/>
+      <c r="G1238" s="50"/>
+      <c r="H1238" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1238" s="67" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:9">
+      <c r="A1239" s="50">
+        <v>10480033</v>
+      </c>
+      <c r="B1239" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1239" s="50">
+        <v>33</v>
+      </c>
+      <c r="D1239" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1239" s="50"/>
+      <c r="F1239" s="50"/>
+      <c r="G1239" s="50"/>
+      <c r="H1239" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1239" s="67" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:9">
+      <c r="A1240" s="50">
+        <v>10480034</v>
+      </c>
+      <c r="B1240" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1240" s="50">
+        <v>34</v>
+      </c>
+      <c r="D1240" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1240" s="50"/>
+      <c r="F1240" s="50"/>
+      <c r="G1240" s="50"/>
+      <c r="H1240" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1240" s="67" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:9">
+      <c r="A1241" s="50">
+        <v>10480035</v>
+      </c>
+      <c r="B1241" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1241" s="50">
+        <v>35</v>
+      </c>
+      <c r="D1241" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1241" s="50"/>
+      <c r="F1241" s="50"/>
+      <c r="G1241" s="50"/>
+      <c r="H1241" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1241" s="67" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:9">
+      <c r="A1242" s="50">
+        <v>10480036</v>
+      </c>
+      <c r="B1242" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1242" s="50">
+        <v>36</v>
+      </c>
+      <c r="D1242" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1242" s="50"/>
+      <c r="F1242" s="50"/>
+      <c r="G1242" s="50"/>
+      <c r="H1242" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1242" s="67" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:9">
+      <c r="A1243" s="50">
+        <v>10480037</v>
+      </c>
+      <c r="B1243" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1243" s="50">
+        <v>37</v>
+      </c>
+      <c r="D1243" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1243" s="50"/>
+      <c r="F1243" s="50"/>
+      <c r="G1243" s="50"/>
+      <c r="H1243" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1243" s="67" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:9">
+      <c r="A1244" s="50">
+        <v>10480038</v>
+      </c>
+      <c r="B1244" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1244" s="50">
+        <v>38</v>
+      </c>
+      <c r="D1244" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1244" s="50"/>
+      <c r="F1244" s="50"/>
+      <c r="G1244" s="50"/>
+      <c r="H1244" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1244" s="67" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:9">
+      <c r="A1245" s="50">
+        <v>10480039</v>
+      </c>
+      <c r="B1245" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1245" s="50">
+        <v>39</v>
+      </c>
+      <c r="D1245" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1245" s="50"/>
+      <c r="F1245" s="50"/>
+      <c r="G1245" s="50"/>
+      <c r="H1245" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1245" s="67" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:9">
+      <c r="A1246" s="50">
+        <v>10480040</v>
+      </c>
+      <c r="B1246" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1246" s="50">
+        <v>40</v>
+      </c>
+      <c r="D1246" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1246" s="50"/>
+      <c r="F1246" s="50"/>
+      <c r="G1246" s="50"/>
+      <c r="H1246" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1246" s="67" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:9">
+      <c r="A1247" s="50">
+        <v>10480041</v>
+      </c>
+      <c r="B1247" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1247" s="50">
+        <v>41</v>
+      </c>
+      <c r="D1247" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1247" s="50"/>
+      <c r="F1247" s="50" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G1247" s="50"/>
+      <c r="H1247" s="50"/>
+      <c r="I1247" s="67" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:9">
+      <c r="A1248" s="50">
+        <v>10480042</v>
+      </c>
+      <c r="B1248" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1248" s="50">
+        <v>42</v>
+      </c>
+      <c r="D1248" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1248" s="50"/>
+      <c r="F1248" s="50" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G1248" s="50"/>
+      <c r="H1248" s="50"/>
+      <c r="I1248" s="67" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:9">
+      <c r="A1249" s="50">
+        <v>10480043</v>
+      </c>
+      <c r="B1249" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1249" s="50">
+        <v>43</v>
+      </c>
+      <c r="D1249" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1249" s="50"/>
+      <c r="F1249" s="50" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G1249" s="50"/>
+      <c r="H1249" s="50"/>
+      <c r="I1249" s="67" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:9">
+      <c r="A1250" s="50">
+        <v>10480044</v>
+      </c>
+      <c r="B1250" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1250" s="50">
+        <v>44</v>
+      </c>
+      <c r="D1250" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1250" s="50"/>
+      <c r="F1250" s="50" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G1250" s="50"/>
+      <c r="H1250" s="50"/>
+      <c r="I1250" s="67" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:9">
+      <c r="A1251" s="50">
+        <v>10480045</v>
+      </c>
+      <c r="B1251" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1251" s="50">
+        <v>45</v>
+      </c>
+      <c r="D1251" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1251" s="50"/>
+      <c r="F1251" s="50" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G1251" s="50"/>
+      <c r="H1251" s="50"/>
+      <c r="I1251" s="67" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:9">
+      <c r="A1252" s="50">
+        <v>10480046</v>
+      </c>
+      <c r="B1252" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1252" s="50">
+        <v>46</v>
+      </c>
+      <c r="D1252" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1252" s="50"/>
+      <c r="F1252" s="50" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G1252" s="50"/>
+      <c r="H1252" s="50"/>
+      <c r="I1252" s="67" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:9">
+      <c r="A1253" s="50">
+        <v>10480047</v>
+      </c>
+      <c r="B1253" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1253" s="50">
+        <v>47</v>
+      </c>
+      <c r="D1253" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1253" s="50"/>
+      <c r="F1253" s="50" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G1253" s="50"/>
+      <c r="H1253" s="50"/>
+      <c r="I1253" s="67" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:9">
+      <c r="A1254" s="50">
+        <v>10480048</v>
+      </c>
+      <c r="B1254" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1254" s="50">
+        <v>48</v>
+      </c>
+      <c r="D1254" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1254" s="50"/>
+      <c r="F1254" s="50" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G1254" s="50"/>
+      <c r="H1254" s="50"/>
+      <c r="I1254" s="67" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:9">
+      <c r="A1255" s="50">
+        <v>10480049</v>
+      </c>
+      <c r="B1255" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1255" s="50">
+        <v>49</v>
+      </c>
+      <c r="D1255" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1255" s="50"/>
+      <c r="F1255" s="50" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G1255" s="50"/>
+      <c r="H1255" s="50"/>
+      <c r="I1255" s="67" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:9">
+      <c r="A1256" s="50">
+        <v>10480050</v>
+      </c>
+      <c r="B1256" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1256" s="50">
+        <v>50</v>
+      </c>
+      <c r="D1256" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1256" s="50"/>
+      <c r="F1256" s="50" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G1256" s="50"/>
+      <c r="H1256" s="50"/>
+      <c r="I1256" s="67" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:9">
+      <c r="A1257" s="50">
+        <v>10480051</v>
+      </c>
+      <c r="B1257" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1257" s="50">
+        <v>51</v>
+      </c>
+      <c r="D1257" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1257" s="50"/>
+      <c r="F1257" s="50" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G1257" s="50"/>
+      <c r="H1257" s="50"/>
+      <c r="I1257" s="67" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:9">
+      <c r="A1258" s="50">
+        <v>10480052</v>
+      </c>
+      <c r="B1258" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1258" s="50">
+        <v>52</v>
+      </c>
+      <c r="D1258" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1258" s="50"/>
+      <c r="F1258" s="50" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G1258" s="50"/>
+      <c r="H1258" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1258" s="68" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:9">
+      <c r="A1259" s="50">
+        <v>10480053</v>
+      </c>
+      <c r="B1259" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1259" s="50">
+        <v>53</v>
+      </c>
+      <c r="D1259" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1259" s="50"/>
+      <c r="F1259" s="50" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G1259" s="50"/>
+      <c r="H1259" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1259" s="68" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:9">
+      <c r="A1260" s="50">
+        <v>10480054</v>
+      </c>
+      <c r="B1260" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1260" s="50">
+        <v>54</v>
+      </c>
+      <c r="D1260" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1260" s="50"/>
+      <c r="F1260" s="50" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G1260" s="50"/>
+      <c r="H1260" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1260" s="68" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:9">
+      <c r="A1261" s="50">
+        <v>10480055</v>
+      </c>
+      <c r="B1261" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1261" s="50">
+        <v>55</v>
+      </c>
+      <c r="D1261" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1261" s="50"/>
+      <c r="F1261" s="50" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G1261" s="50"/>
+      <c r="H1261" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1261" s="68" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:9">
+      <c r="A1262" s="50">
+        <v>10480056</v>
+      </c>
+      <c r="B1262" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1262" s="50">
+        <v>56</v>
+      </c>
+      <c r="D1262" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1262" s="50"/>
+      <c r="F1262" s="50" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G1262" s="50"/>
+      <c r="H1262" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1262" s="68" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:9">
+      <c r="A1263" s="50">
+        <v>10480057</v>
+      </c>
+      <c r="B1263" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1263" s="50">
+        <v>57</v>
+      </c>
+      <c r="D1263" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1263" s="50"/>
+      <c r="F1263" s="50" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G1263" s="50"/>
+      <c r="H1263" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1263" s="68" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:9">
+      <c r="A1264" s="50">
+        <v>10480058</v>
+      </c>
+      <c r="B1264" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1264" s="50">
+        <v>58</v>
+      </c>
+      <c r="D1264" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1264" s="50"/>
+      <c r="F1264" s="50" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G1264" s="50"/>
+      <c r="H1264" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1264" s="68" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:9">
+      <c r="A1265" s="50">
+        <v>10480059</v>
+      </c>
+      <c r="B1265" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1265" s="50">
+        <v>59</v>
+      </c>
+      <c r="D1265" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1265" s="50"/>
+      <c r="F1265" s="50" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G1265" s="50"/>
+      <c r="H1265" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1265" s="68" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:9">
+      <c r="A1266" s="50">
+        <v>10480060</v>
+      </c>
+      <c r="B1266" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1266" s="50">
+        <v>60</v>
+      </c>
+      <c r="D1266" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1266" s="50"/>
+      <c r="F1266" s="50" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G1266" s="50"/>
+      <c r="H1266" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1266" s="68" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:9">
+      <c r="A1267" s="50">
+        <v>10480061</v>
+      </c>
+      <c r="B1267" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1267" s="50">
+        <v>61</v>
+      </c>
+      <c r="D1267" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1267" s="50"/>
+      <c r="F1267" s="50" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G1267" s="50"/>
+      <c r="H1267" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1267" s="68" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:9">
+      <c r="A1268" s="50">
+        <v>10480062</v>
+      </c>
+      <c r="B1268" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1268" s="50">
+        <v>62</v>
+      </c>
+      <c r="D1268" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1268" s="50"/>
+      <c r="F1268" s="50" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G1268" s="50"/>
+      <c r="H1268" s="50">
+        <v>2</v>
+      </c>
+      <c r="I1268" s="68" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:9">
+      <c r="A1269" s="50">
+        <v>10480063</v>
+      </c>
+      <c r="B1269" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1269" s="50">
+        <v>63</v>
+      </c>
+      <c r="D1269" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1269" s="50"/>
+      <c r="F1269" s="50" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G1269" s="50"/>
+      <c r="H1269" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1269" s="67" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:9">
+      <c r="A1270" s="50">
+        <v>10480064</v>
+      </c>
+      <c r="B1270" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1270" s="50">
+        <v>64</v>
+      </c>
+      <c r="D1270" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1270" s="50"/>
+      <c r="F1270" s="50" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G1270" s="50"/>
+      <c r="H1270" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1270" s="67" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:9">
+      <c r="A1271" s="50">
+        <v>10480065</v>
+      </c>
+      <c r="B1271" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1271" s="50">
+        <v>65</v>
+      </c>
+      <c r="D1271" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1271" s="50"/>
+      <c r="F1271" s="50" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G1271" s="50"/>
+      <c r="H1271" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1271" s="67" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:9">
+      <c r="A1272" s="50">
+        <v>10480066</v>
+      </c>
+      <c r="B1272" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1272" s="50">
+        <v>66</v>
+      </c>
+      <c r="D1272" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1272" s="50"/>
+      <c r="F1272" s="50" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G1272" s="50"/>
+      <c r="H1272" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1272" s="67" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:9">
+      <c r="A1273" s="50">
+        <v>10480067</v>
+      </c>
+      <c r="B1273" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1273" s="50">
+        <v>67</v>
+      </c>
+      <c r="D1273" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1273" s="50"/>
+      <c r="F1273" s="50" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G1273" s="50"/>
+      <c r="H1273" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1273" s="67" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:9">
+      <c r="A1274" s="50">
+        <v>10480068</v>
+      </c>
+      <c r="B1274" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1274" s="50">
+        <v>68</v>
+      </c>
+      <c r="D1274" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1274" s="50"/>
+      <c r="F1274" s="50" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G1274" s="50"/>
+      <c r="H1274" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1274" s="67" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:9">
+      <c r="A1275" s="50">
+        <v>10480069</v>
+      </c>
+      <c r="B1275" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1275" s="50">
+        <v>69</v>
+      </c>
+      <c r="D1275" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1275" s="50"/>
+      <c r="F1275" s="50" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G1275" s="50"/>
+      <c r="H1275" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1275" s="67" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:9">
+      <c r="A1276" s="50">
+        <v>10480070</v>
+      </c>
+      <c r="B1276" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1276" s="50">
+        <v>70</v>
+      </c>
+      <c r="D1276" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1276" s="50"/>
+      <c r="F1276" s="50" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G1276" s="50"/>
+      <c r="H1276" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1276" s="67" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:9">
+      <c r="A1277" s="50">
+        <v>10480071</v>
+      </c>
+      <c r="B1277" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1277" s="50">
+        <v>71</v>
+      </c>
+      <c r="D1277" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1277" s="50"/>
+      <c r="F1277" s="50" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G1277" s="50"/>
+      <c r="H1277" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1277" s="67" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:9">
+      <c r="A1278" s="50">
+        <v>10480072</v>
+      </c>
+      <c r="B1278" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1278" s="50">
+        <v>72</v>
+      </c>
+      <c r="D1278" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1278" s="50"/>
+      <c r="F1278" s="50" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G1278" s="50"/>
+      <c r="H1278" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1278" s="67" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:9">
+      <c r="A1279" s="50">
+        <v>10480073</v>
+      </c>
+      <c r="B1279" s="50">
+        <v>104800</v>
+      </c>
+      <c r="C1279" s="50">
+        <v>73</v>
+      </c>
+      <c r="D1279" s="50">
+        <v>0</v>
+      </c>
+      <c r="E1279" s="50"/>
+      <c r="F1279" s="50" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G1279" s="50"/>
+      <c r="H1279" s="50">
+        <v>3</v>
+      </c>
+      <c r="I1279" s="67" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="1280" customFormat="1" spans="1:9">
+      <c r="A1280" s="31">
+        <v>10550101</v>
+      </c>
+      <c r="B1280" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1280" s="31">
+        <v>1</v>
+      </c>
+      <c r="D1280" s="31">
+        <v>0</v>
+      </c>
+      <c r="E1280" s="31"/>
+      <c r="F1280" s="31"/>
+      <c r="G1280" s="31"/>
+      <c r="H1280" s="31"/>
+      <c r="I1280" s="31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1281" customFormat="1" spans="1:9">
+      <c r="A1281" s="31">
+        <v>10550102</v>
+      </c>
+      <c r="B1281" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1281" s="31">
+        <v>2</v>
+      </c>
+      <c r="D1281" s="31">
+        <v>0</v>
+      </c>
+      <c r="E1281" s="31"/>
+      <c r="F1281" s="31"/>
+      <c r="G1281" s="31"/>
+      <c r="H1281" s="31"/>
+      <c r="I1281" s="31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1282" customFormat="1" spans="1:9">
+      <c r="A1282" s="31">
+        <v>10550103</v>
+      </c>
+      <c r="B1282" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1282" s="31">
+        <v>3</v>
+      </c>
+      <c r="D1282" s="31">
+        <v>0</v>
+      </c>
+      <c r="E1282" s="31"/>
+      <c r="F1282" s="31"/>
+      <c r="G1282" s="31"/>
+      <c r="H1282" s="31"/>
+      <c r="I1282" s="31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1283" customFormat="1" spans="1:9">
+      <c r="A1283" s="31">
+        <v>10550104</v>
+      </c>
+      <c r="B1283" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1283" s="31">
+        <v>4</v>
+      </c>
+      <c r="D1283" s="31">
+        <v>0</v>
+      </c>
+      <c r="E1283" s="31"/>
+      <c r="F1283" s="31"/>
+      <c r="G1283" s="31"/>
+      <c r="H1283" s="31"/>
+      <c r="I1283" s="31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1284" customFormat="1" spans="1:9">
+      <c r="A1284" s="31">
+        <v>10550105</v>
+      </c>
+      <c r="B1284" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1284" s="31">
+        <v>5</v>
+      </c>
+      <c r="D1284" s="31">
+        <v>0</v>
+      </c>
+      <c r="E1284" s="31"/>
+      <c r="F1284" s="31"/>
+      <c r="G1284" s="31"/>
+      <c r="H1284" s="31"/>
+      <c r="I1284" s="31" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="1285" customFormat="1" spans="1:9">
+      <c r="A1285" s="31">
+        <v>10550106</v>
+      </c>
+      <c r="B1285" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1285" s="31">
+        <v>6</v>
+      </c>
+      <c r="D1285" s="31">
+        <v>0</v>
+      </c>
+      <c r="E1285" s="31"/>
+      <c r="F1285" s="31"/>
+      <c r="G1285" s="31"/>
+      <c r="H1285" s="31"/>
+      <c r="I1285" s="31" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="1286" customFormat="1" spans="1:9">
+      <c r="A1286" s="31">
+        <v>10550107</v>
+      </c>
+      <c r="B1286" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1286" s="31">
+        <v>7</v>
+      </c>
+      <c r="D1286" s="31">
+        <v>0</v>
+      </c>
+      <c r="E1286" s="31"/>
+      <c r="F1286" s="31"/>
+      <c r="G1286" s="31"/>
+      <c r="H1286" s="31"/>
+      <c r="I1286" s="31" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="1287" customFormat="1" spans="1:9">
+      <c r="A1287" s="31">
+        <v>10550108</v>
+      </c>
+      <c r="B1287" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1287" s="31">
+        <v>8</v>
+      </c>
+      <c r="D1287" s="31">
+        <v>1</v>
+      </c>
+      <c r="E1287" s="31"/>
+      <c r="F1287" s="31"/>
+      <c r="G1287" s="31"/>
+      <c r="H1287" s="31"/>
+      <c r="I1287" s="31" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="1288" customFormat="1" spans="1:9">
+      <c r="A1288" s="31">
+        <v>10550109</v>
+      </c>
+      <c r="B1288" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1288" s="31">
+        <v>9</v>
+      </c>
+      <c r="D1288" s="31">
+        <v>2</v>
+      </c>
+      <c r="E1288" s="31"/>
+      <c r="F1288" s="31"/>
+      <c r="G1288" s="31"/>
+      <c r="H1288" s="31"/>
+      <c r="I1288" s="31" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="1289" customFormat="1" spans="1:9">
+      <c r="A1289" s="31">
+        <v>10550110</v>
+      </c>
+      <c r="B1289" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1289" s="31">
+        <v>10</v>
+      </c>
+      <c r="D1289" s="31">
+        <v>2</v>
+      </c>
+      <c r="E1289" s="31"/>
+      <c r="F1289" s="31"/>
+      <c r="G1289" s="31"/>
+      <c r="H1289" s="31"/>
+      <c r="I1289" s="31" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="1290" customFormat="1" spans="1:9">
+      <c r="A1290" s="31">
+        <v>10550111</v>
+      </c>
+      <c r="B1290" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1290" s="31">
+        <v>11</v>
+      </c>
+      <c r="D1290" s="31">
+        <v>2</v>
+      </c>
+      <c r="E1290" s="31"/>
+      <c r="F1290" s="31"/>
+      <c r="G1290" s="31"/>
+      <c r="H1290" s="31"/>
+      <c r="I1290" s="31" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="1291" customFormat="1" spans="1:9">
+      <c r="A1291" s="31">
+        <v>10550112</v>
+      </c>
+      <c r="B1291" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1291" s="31">
+        <v>12</v>
+      </c>
+      <c r="D1291" s="31">
+        <v>2</v>
+      </c>
+      <c r="E1291" s="31"/>
+      <c r="F1291" s="31"/>
+      <c r="G1291" s="31"/>
+      <c r="H1291" s="31"/>
+      <c r="I1291" s="31" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="1292" customFormat="1" spans="1:9">
+      <c r="A1292" s="31">
+        <v>10550113</v>
+      </c>
+      <c r="B1292" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1292" s="31">
+        <v>13</v>
+      </c>
+      <c r="D1292" s="31">
+        <v>2</v>
+      </c>
+      <c r="E1292" s="31"/>
+      <c r="F1292" s="31"/>
+      <c r="G1292" s="31"/>
+      <c r="H1292" s="31"/>
+      <c r="I1292" s="31" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="1293" customFormat="1" spans="1:9">
+      <c r="A1293" s="31">
+        <v>10550114</v>
+      </c>
+      <c r="B1293" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1293" s="31">
+        <v>14</v>
+      </c>
+      <c r="D1293" s="31">
+        <v>2</v>
+      </c>
+      <c r="E1293" s="31"/>
+      <c r="F1293" s="31"/>
+      <c r="G1293" s="31"/>
+      <c r="H1293" s="31"/>
+      <c r="I1293" s="31" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="1294" customFormat="1" spans="1:9">
+      <c r="A1294" s="31">
+        <v>10550115</v>
+      </c>
+      <c r="B1294" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1294" s="31">
+        <v>15</v>
+      </c>
+      <c r="D1294" s="31">
+        <v>2</v>
+      </c>
+      <c r="E1294" s="31"/>
+      <c r="F1294" s="31"/>
+      <c r="G1294" s="31"/>
+      <c r="H1294" s="31"/>
+      <c r="I1294" s="31" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="1295" customFormat="1" spans="1:9">
+      <c r="A1295" s="31">
+        <v>10550116</v>
+      </c>
+      <c r="B1295" s="31">
+        <v>105501</v>
+      </c>
+      <c r="C1295" s="31">
+        <v>16</v>
+      </c>
+      <c r="D1295" s="31">
+        <v>2</v>
+      </c>
+      <c r="E1295" s="31"/>
+      <c r="F1295" s="31"/>
+      <c r="G1295" s="31"/>
+      <c r="H1295" s="31"/>
+      <c r="I1295" s="31" t="s">
+        <v>1603</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2522" uniqueCount="1621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2551" uniqueCount="1626">
   <si>
     <t>图标</t>
   </si>
@@ -4978,6 +4978,21 @@
   </si>
   <si>
     <t>隐藏符号，触发多格模式</t>
+  </si>
+  <si>
+    <t>冰淇淋</t>
+  </si>
+  <si>
+    <t>水枪男孩</t>
+  </si>
+  <si>
+    <t>墨镜男孩</t>
+  </si>
+  <si>
+    <t>蓝发女孩</t>
+  </si>
+  <si>
+    <t>泳圈女孩</t>
   </si>
 </sst>
 </file>
@@ -4990,7 +5005,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5195,13 +5210,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -5215,18 +5223,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="50">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5337,6 +5345,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -5385,61 +5399,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5457,31 +5417,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5500,18 +5436,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5725,7 +5649,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5749,16 +5673,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -5767,22 +5691,46 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5791,7 +5739,19 @@
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5803,54 +5763,18 @@
     <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6042,6 +5966,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -6367,7 +6297,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J1327"/>
+  <dimension ref="A1:J1358"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -11482,7 +11412,7 @@
       <c r="F211" s="29"/>
       <c r="G211" s="30"/>
       <c r="H211" s="32"/>
-      <c r="I211" s="64" t="s">
+      <c r="I211" s="66" t="s">
         <v>302</v>
       </c>
     </row>
@@ -38102,6 +38032,657 @@
       <c r="H1327" s="49"/>
       <c r="I1327" s="49" t="s">
         <v>1620</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:9">
+      <c r="A1328" s="21">
+        <v>10410001</v>
+      </c>
+      <c r="B1328" s="21">
+        <v>104100</v>
+      </c>
+      <c r="C1328" s="21">
+        <v>1</v>
+      </c>
+      <c r="D1328" s="21">
+        <v>0</v>
+      </c>
+      <c r="E1328" s="21"/>
+      <c r="F1328" s="21"/>
+      <c r="G1328" s="21"/>
+      <c r="H1328" s="21"/>
+      <c r="I1328" s="21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:9">
+      <c r="A1329" s="21">
+        <v>10410002</v>
+      </c>
+      <c r="B1329" s="21">
+        <v>104100</v>
+      </c>
+      <c r="C1329" s="21">
+        <v>2</v>
+      </c>
+      <c r="D1329" s="21">
+        <v>0</v>
+      </c>
+      <c r="E1329" s="21"/>
+      <c r="F1329" s="21"/>
+      <c r="G1329" s="21"/>
+      <c r="H1329" s="21"/>
+      <c r="I1329" s="21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:9">
+      <c r="A1330" s="21">
+        <v>10410003</v>
+      </c>
+      <c r="B1330" s="21">
+        <v>104100</v>
+      </c>
+      <c r="C1330" s="21">
+        <v>3</v>
+      </c>
+      <c r="D1330" s="21">
+        <v>0</v>
+      </c>
+      <c r="E1330" s="21"/>
+      <c r="F1330" s="21"/>
+      <c r="G1330" s="21"/>
+      <c r="H1330" s="21"/>
+      <c r="I1330" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:9">
+      <c r="A1331" s="21">
+        <v>10410004</v>
+      </c>
+      <c r="B1331" s="21">
+        <v>104100</v>
+      </c>
+      <c r="C1331" s="21">
+        <v>4</v>
+      </c>
+      <c r="D1331" s="21">
+        <v>0</v>
+      </c>
+      <c r="E1331" s="21"/>
+      <c r="F1331" s="21"/>
+      <c r="G1331" s="21"/>
+      <c r="H1331" s="21"/>
+      <c r="I1331" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:9">
+      <c r="A1332" s="21">
+        <v>10410005</v>
+      </c>
+      <c r="B1332" s="21">
+        <v>104100</v>
+      </c>
+      <c r="C1332" s="21">
+        <v>5</v>
+      </c>
+      <c r="D1332" s="21">
+        <v>0</v>
+      </c>
+      <c r="E1332" s="21"/>
+      <c r="F1332" s="21"/>
+      <c r="G1332" s="21"/>
+      <c r="H1332" s="21"/>
+      <c r="I1332" s="21" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:9">
+      <c r="A1333" s="21">
+        <v>10410006</v>
+      </c>
+      <c r="B1333" s="21">
+        <v>104100</v>
+      </c>
+      <c r="C1333" s="21">
+        <v>6</v>
+      </c>
+      <c r="D1333" s="21">
+        <v>0</v>
+      </c>
+      <c r="E1333" s="21"/>
+      <c r="F1333" s="21"/>
+      <c r="G1333" s="21"/>
+      <c r="H1333" s="21"/>
+      <c r="I1333" s="21" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:9">
+      <c r="A1334" s="21">
+        <v>10410007</v>
+      </c>
+      <c r="B1334" s="21">
+        <v>104100</v>
+      </c>
+      <c r="C1334" s="21">
+        <v>7</v>
+      </c>
+      <c r="D1334" s="21">
+        <v>0</v>
+      </c>
+      <c r="E1334" s="21"/>
+      <c r="F1334" s="21"/>
+      <c r="G1334" s="21"/>
+      <c r="H1334" s="21"/>
+      <c r="I1334" s="21" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:9">
+      <c r="A1335" s="21">
+        <v>10410008</v>
+      </c>
+      <c r="B1335" s="21">
+        <v>104100</v>
+      </c>
+      <c r="C1335" s="21">
+        <v>8</v>
+      </c>
+      <c r="D1335" s="21">
+        <v>0</v>
+      </c>
+      <c r="E1335" s="21"/>
+      <c r="F1335" s="21"/>
+      <c r="G1335" s="21"/>
+      <c r="H1335" s="21"/>
+      <c r="I1335" s="21" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:9">
+      <c r="A1336" s="21">
+        <v>10410009</v>
+      </c>
+      <c r="B1336" s="21">
+        <v>104100</v>
+      </c>
+      <c r="C1336" s="21">
+        <v>9</v>
+      </c>
+      <c r="D1336" s="21">
+        <v>1</v>
+      </c>
+      <c r="E1336" s="21"/>
+      <c r="F1336" s="21"/>
+      <c r="G1336" s="21"/>
+      <c r="H1336" s="21"/>
+      <c r="I1336" s="21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:9">
+      <c r="A1337" s="21">
+        <v>10410010</v>
+      </c>
+      <c r="B1337" s="21">
+        <v>104100</v>
+      </c>
+      <c r="C1337" s="21">
+        <v>10</v>
+      </c>
+      <c r="D1337" s="21">
+        <v>2</v>
+      </c>
+      <c r="E1337" s="21"/>
+      <c r="F1337" s="21"/>
+      <c r="G1337" s="21"/>
+      <c r="H1337" s="21"/>
+      <c r="I1337" s="21" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:9">
+      <c r="A1338" s="21">
+        <v>10410011</v>
+      </c>
+      <c r="B1338" s="21">
+        <v>104100</v>
+      </c>
+      <c r="C1338" s="21">
+        <v>11</v>
+      </c>
+      <c r="D1338" s="21">
+        <v>2</v>
+      </c>
+      <c r="E1338" s="21"/>
+      <c r="F1338" s="21"/>
+      <c r="G1338" s="21"/>
+      <c r="H1338" s="21"/>
+      <c r="I1338" s="21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:9">
+      <c r="A1339" s="21">
+        <v>10410012</v>
+      </c>
+      <c r="B1339" s="21">
+        <v>104100</v>
+      </c>
+      <c r="C1339" s="21">
+        <v>12</v>
+      </c>
+      <c r="D1339" s="21">
+        <v>2</v>
+      </c>
+      <c r="E1339" s="21"/>
+      <c r="F1339" s="21"/>
+      <c r="G1339" s="21"/>
+      <c r="H1339" s="21"/>
+      <c r="I1339" s="21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:9">
+      <c r="A1340" s="21">
+        <v>10410013</v>
+      </c>
+      <c r="B1340" s="21">
+        <v>104100</v>
+      </c>
+      <c r="C1340" s="21">
+        <v>13</v>
+      </c>
+      <c r="D1340" s="21">
+        <v>2</v>
+      </c>
+      <c r="E1340" s="21"/>
+      <c r="F1340" s="21"/>
+      <c r="G1340" s="21"/>
+      <c r="H1340" s="21"/>
+      <c r="I1340" s="21" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:9">
+      <c r="A1341" s="21">
+        <v>10410014</v>
+      </c>
+      <c r="B1341" s="21">
+        <v>104100</v>
+      </c>
+      <c r="C1341" s="21">
+        <v>14</v>
+      </c>
+      <c r="D1341" s="21">
+        <v>2</v>
+      </c>
+      <c r="E1341" s="21"/>
+      <c r="F1341" s="21"/>
+      <c r="G1341" s="21"/>
+      <c r="H1341" s="21"/>
+      <c r="I1341" s="21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:9">
+      <c r="A1342" s="64">
+        <v>10420001</v>
+      </c>
+      <c r="B1342" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1342" s="64">
+        <v>1</v>
+      </c>
+      <c r="D1342" s="64">
+        <v>0</v>
+      </c>
+      <c r="E1342" s="64"/>
+      <c r="F1342" s="64"/>
+      <c r="G1342" s="64"/>
+      <c r="H1342" s="64"/>
+      <c r="I1342" s="65">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:9">
+      <c r="A1343" s="64">
+        <v>10420002</v>
+      </c>
+      <c r="B1343" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1343" s="64">
+        <v>2</v>
+      </c>
+      <c r="D1343" s="64">
+        <v>0</v>
+      </c>
+      <c r="E1343" s="64"/>
+      <c r="F1343" s="64"/>
+      <c r="G1343" s="64"/>
+      <c r="H1343" s="64"/>
+      <c r="I1343" s="65">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:9">
+      <c r="A1344" s="64">
+        <v>10420003</v>
+      </c>
+      <c r="B1344" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1344" s="64">
+        <v>3</v>
+      </c>
+      <c r="D1344" s="64">
+        <v>0</v>
+      </c>
+      <c r="E1344" s="64"/>
+      <c r="F1344" s="64"/>
+      <c r="G1344" s="64"/>
+      <c r="H1344" s="64"/>
+      <c r="I1344" s="65" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:9">
+      <c r="A1345" s="64">
+        <v>10420004</v>
+      </c>
+      <c r="B1345" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1345" s="64">
+        <v>4</v>
+      </c>
+      <c r="D1345" s="64">
+        <v>0</v>
+      </c>
+      <c r="E1345" s="64"/>
+      <c r="F1345" s="64"/>
+      <c r="G1345" s="64"/>
+      <c r="H1345" s="64"/>
+      <c r="I1345" s="64" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:9">
+      <c r="A1346" s="64">
+        <v>10420005</v>
+      </c>
+      <c r="B1346" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1346" s="64">
+        <v>5</v>
+      </c>
+      <c r="D1346" s="64">
+        <v>0</v>
+      </c>
+      <c r="E1346" s="64"/>
+      <c r="F1346" s="64"/>
+      <c r="G1346" s="64"/>
+      <c r="H1346" s="64"/>
+      <c r="I1346" s="64" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:9">
+      <c r="A1347" s="64">
+        <v>10420006</v>
+      </c>
+      <c r="B1347" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1347" s="64">
+        <v>6</v>
+      </c>
+      <c r="D1347" s="64">
+        <v>0</v>
+      </c>
+      <c r="E1347" s="64"/>
+      <c r="F1347" s="64"/>
+      <c r="G1347" s="64"/>
+      <c r="H1347" s="64"/>
+      <c r="I1347" s="64" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:9">
+      <c r="A1348" s="64">
+        <v>10420007</v>
+      </c>
+      <c r="B1348" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1348" s="64">
+        <v>7</v>
+      </c>
+      <c r="D1348" s="64">
+        <v>0</v>
+      </c>
+      <c r="E1348" s="64"/>
+      <c r="F1348" s="64"/>
+      <c r="G1348" s="64"/>
+      <c r="H1348" s="64"/>
+      <c r="I1348" s="64" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:9">
+      <c r="A1349" s="64">
+        <v>10420008</v>
+      </c>
+      <c r="B1349" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1349" s="64">
+        <v>8</v>
+      </c>
+      <c r="D1349" s="64">
+        <v>0</v>
+      </c>
+      <c r="E1349" s="64"/>
+      <c r="F1349" s="64"/>
+      <c r="G1349" s="64"/>
+      <c r="H1349" s="64"/>
+      <c r="I1349" s="64" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:9">
+      <c r="A1350" s="64">
+        <v>10420009</v>
+      </c>
+      <c r="B1350" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1350" s="64">
+        <v>9</v>
+      </c>
+      <c r="D1350" s="64">
+        <v>0</v>
+      </c>
+      <c r="E1350" s="64"/>
+      <c r="F1350" s="64"/>
+      <c r="G1350" s="64"/>
+      <c r="H1350" s="64"/>
+      <c r="I1350" s="64" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:9">
+      <c r="A1351" s="64">
+        <v>10420010</v>
+      </c>
+      <c r="B1351" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1351" s="64">
+        <v>10</v>
+      </c>
+      <c r="D1351" s="64">
+        <v>0</v>
+      </c>
+      <c r="E1351" s="64"/>
+      <c r="F1351" s="64"/>
+      <c r="G1351" s="64"/>
+      <c r="H1351" s="64"/>
+      <c r="I1351" s="64" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:9">
+      <c r="A1352" s="64">
+        <v>10420011</v>
+      </c>
+      <c r="B1352" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1352" s="64">
+        <v>11</v>
+      </c>
+      <c r="D1352" s="64">
+        <v>0</v>
+      </c>
+      <c r="E1352" s="64"/>
+      <c r="F1352" s="64"/>
+      <c r="G1352" s="64"/>
+      <c r="H1352" s="64"/>
+      <c r="I1352" s="64" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:9">
+      <c r="A1353" s="64">
+        <v>10420012</v>
+      </c>
+      <c r="B1353" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1353" s="64">
+        <v>12</v>
+      </c>
+      <c r="D1353" s="64">
+        <v>1</v>
+      </c>
+      <c r="E1353" s="64"/>
+      <c r="F1353" s="64"/>
+      <c r="G1353" s="64"/>
+      <c r="H1353" s="64"/>
+      <c r="I1353" s="64" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:9">
+      <c r="A1354" s="64">
+        <v>10420013</v>
+      </c>
+      <c r="B1354" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1354" s="64">
+        <v>13</v>
+      </c>
+      <c r="D1354" s="64">
+        <v>2</v>
+      </c>
+      <c r="E1354" s="64"/>
+      <c r="F1354" s="64"/>
+      <c r="G1354" s="64"/>
+      <c r="H1354" s="64"/>
+      <c r="I1354" s="64" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:9">
+      <c r="A1355" s="64">
+        <v>10420014</v>
+      </c>
+      <c r="B1355" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1355" s="64">
+        <v>14</v>
+      </c>
+      <c r="D1355" s="64">
+        <v>2</v>
+      </c>
+      <c r="E1355" s="64"/>
+      <c r="F1355" s="64"/>
+      <c r="G1355" s="64"/>
+      <c r="H1355" s="64"/>
+      <c r="I1355" s="64" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:9">
+      <c r="A1356" s="64">
+        <v>10420015</v>
+      </c>
+      <c r="B1356" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1356" s="64">
+        <v>15</v>
+      </c>
+      <c r="D1356" s="64">
+        <v>2</v>
+      </c>
+      <c r="E1356" s="64"/>
+      <c r="F1356" s="64"/>
+      <c r="G1356" s="64"/>
+      <c r="H1356" s="64"/>
+      <c r="I1356" s="64" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:9">
+      <c r="A1357" s="64">
+        <v>10420016</v>
+      </c>
+      <c r="B1357" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1357" s="64">
+        <v>16</v>
+      </c>
+      <c r="D1357" s="64">
+        <v>2</v>
+      </c>
+      <c r="E1357" s="64"/>
+      <c r="F1357" s="64"/>
+      <c r="G1357" s="64"/>
+      <c r="H1357" s="64"/>
+      <c r="I1357" s="64" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:9">
+      <c r="A1358" s="64">
+        <v>10420017</v>
+      </c>
+      <c r="B1358" s="64">
+        <v>104200</v>
+      </c>
+      <c r="C1358" s="64">
+        <v>17</v>
+      </c>
+      <c r="D1358" s="64">
+        <v>2</v>
+      </c>
+      <c r="E1358" s="64"/>
+      <c r="F1358" s="64"/>
+      <c r="G1358" s="64"/>
+      <c r="H1358" s="64"/>
+      <c r="I1358" s="64" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2551" uniqueCount="1626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2553" uniqueCount="1639">
   <si>
     <t>图标</t>
   </si>
@@ -3261,85 +3261,124 @@
     <t>黄金梅西消除后变成wild</t>
   </si>
   <si>
-    <t>ly__icon_1.png</t>
-  </si>
-  <si>
-    <t>ly__icon_2.png</t>
-  </si>
-  <si>
-    <t>ly__icon_3.png</t>
-  </si>
-  <si>
-    <t>ly__icon_4.png</t>
-  </si>
-  <si>
-    <t>ly__icon_5.png</t>
-  </si>
-  <si>
-    <t>ly__icon_6.png</t>
-  </si>
-  <si>
-    <t>ly__icon_7.png</t>
-  </si>
-  <si>
-    <t>匕首</t>
-  </si>
-  <si>
-    <t>ly__icon_8.png</t>
-  </si>
-  <si>
-    <t>ly__icon_9.png</t>
-  </si>
-  <si>
-    <t>狼爪</t>
-  </si>
-  <si>
-    <t>ly__icon_10.png</t>
-  </si>
-  <si>
-    <t>ly__icon_11.png</t>
-  </si>
-  <si>
-    <t>十字架</t>
-  </si>
-  <si>
-    <t>ly__icon_12.png</t>
-  </si>
-  <si>
-    <t>手枪</t>
-  </si>
-  <si>
-    <t>ly__icon_13.png</t>
-  </si>
-  <si>
-    <t>ly__icon_14.png</t>
-  </si>
-  <si>
-    <t>ly__icon_15.png</t>
-  </si>
-  <si>
-    <t>ly__icon_16.png</t>
-  </si>
-  <si>
-    <t>ly__icon_17.png</t>
-  </si>
-  <si>
-    <t>ly__icon_18.png</t>
-  </si>
-  <si>
-    <t>ly__icon_19.png</t>
-  </si>
-  <si>
-    <t>ly__icon_20.png</t>
+    <t>15.png</t>
+  </si>
+  <si>
+    <t>9（101）</t>
+  </si>
+  <si>
+    <t>14.png</t>
+  </si>
+  <si>
+    <t>10（102）</t>
+  </si>
+  <si>
+    <t>13.png</t>
+  </si>
+  <si>
+    <t>J（103）</t>
+  </si>
+  <si>
+    <t>12.png</t>
+  </si>
+  <si>
+    <t>Q（104）</t>
+  </si>
+  <si>
+    <t>11.png</t>
+  </si>
+  <si>
+    <t>K（105）</t>
+  </si>
+  <si>
+    <t>10.png</t>
+  </si>
+  <si>
+    <t>A（106）</t>
+  </si>
+  <si>
+    <t>4.png</t>
+  </si>
+  <si>
+    <t>匕首（107）</t>
+  </si>
+  <si>
+    <t>3.png</t>
+  </si>
+  <si>
+    <t>帽子（108）</t>
+  </si>
+  <si>
+    <t>7.png</t>
+  </si>
+  <si>
+    <t>狼爪（109）</t>
+  </si>
+  <si>
+    <t>2.png</t>
+  </si>
+  <si>
+    <t>药瓶（110）</t>
+  </si>
+  <si>
+    <t>6.png</t>
+  </si>
+  <si>
+    <t>十字架（111）</t>
+  </si>
+  <si>
+    <t>5.png</t>
+  </si>
+  <si>
+    <t>手枪（112）</t>
+  </si>
+  <si>
+    <t>9.png</t>
+  </si>
+  <si>
+    <t>wild（201）</t>
+  </si>
+  <si>
+    <t>8.png</t>
+  </si>
+  <si>
+    <t>scatter（401）</t>
+  </si>
+  <si>
+    <t>17.png</t>
+  </si>
+  <si>
+    <t>免费+1（113）</t>
+  </si>
+  <si>
+    <t>18.png</t>
+  </si>
+  <si>
+    <t>mini（501）</t>
+  </si>
+  <si>
+    <t>19.png</t>
+  </si>
+  <si>
+    <t>minor（502）</t>
+  </si>
+  <si>
+    <t>20.png</t>
+  </si>
+  <si>
+    <t>major（503）</t>
+  </si>
+  <si>
+    <t>21.png</t>
+  </si>
+  <si>
+    <t>grand（504）</t>
+  </si>
+  <si>
+    <t>1.png</t>
   </si>
   <si>
     <t>隐藏符号，用于触发免费游戏</t>
-  </si>
-  <si>
-    <t>ly__icon_21.png</t>
-  </si>
-  <si>
-    <t>ly__icon_22.png</t>
   </si>
   <si>
     <t>dbhjc__icon_1.png</t>
@@ -5223,12 +5262,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -22307,8 +22346,8 @@
       <c r="F650" s="42"/>
       <c r="G650" s="42"/>
       <c r="H650" s="42"/>
-      <c r="I650" s="42">
-        <v>9</v>
+      <c r="I650" s="42" t="s">
+        <v>1049</v>
       </c>
     </row>
     <row r="651" s="1" customFormat="1" spans="1:9">
@@ -22325,13 +22364,13 @@
         <v>0</v>
       </c>
       <c r="E651" s="42" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F651" s="42"/>
       <c r="G651" s="42"/>
       <c r="H651" s="42"/>
-      <c r="I651" s="42">
-        <v>10</v>
+      <c r="I651" s="42" t="s">
+        <v>1051</v>
       </c>
     </row>
     <row r="652" s="1" customFormat="1" spans="1:9">
@@ -22348,13 +22387,13 @@
         <v>0</v>
       </c>
       <c r="E652" s="42" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F652" s="42"/>
       <c r="G652" s="42"/>
       <c r="H652" s="42"/>
       <c r="I652" s="42" t="s">
-        <v>21</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="653" s="1" customFormat="1" spans="1:9">
@@ -22371,13 +22410,13 @@
         <v>0</v>
       </c>
       <c r="E653" s="42" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="F653" s="42"/>
       <c r="G653" s="42"/>
       <c r="H653" s="42"/>
       <c r="I653" s="42" t="s">
-        <v>23</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="654" s="1" customFormat="1" spans="1:9">
@@ -22394,13 +22433,13 @@
         <v>0</v>
       </c>
       <c r="E654" s="42" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="F654" s="42"/>
       <c r="G654" s="42"/>
       <c r="H654" s="42"/>
       <c r="I654" s="42" t="s">
-        <v>25</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="655" s="1" customFormat="1" spans="1:9">
@@ -22417,13 +22456,13 @@
         <v>0</v>
       </c>
       <c r="E655" s="42" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="F655" s="42"/>
       <c r="G655" s="42"/>
       <c r="H655" s="42"/>
       <c r="I655" s="42" t="s">
-        <v>27</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="656" s="1" customFormat="1" spans="1:9">
@@ -22440,13 +22479,13 @@
         <v>0</v>
       </c>
       <c r="E656" s="42" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="F656" s="42"/>
       <c r="G656" s="42"/>
       <c r="H656" s="42"/>
       <c r="I656" s="42" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="657" s="1" customFormat="1" spans="1:9">
@@ -22463,13 +22502,13 @@
         <v>0</v>
       </c>
       <c r="E657" s="42" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="F657" s="42"/>
       <c r="G657" s="42"/>
       <c r="H657" s="42"/>
       <c r="I657" s="42" t="s">
-        <v>29</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="658" s="1" customFormat="1" spans="1:9">
@@ -22486,13 +22525,13 @@
         <v>0</v>
       </c>
       <c r="E658" s="42" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="F658" s="42"/>
       <c r="G658" s="42"/>
       <c r="H658" s="42"/>
       <c r="I658" s="42" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="659" s="1" customFormat="1" spans="1:9">
@@ -22509,13 +22548,13 @@
         <v>0</v>
       </c>
       <c r="E659" s="42" t="s">
-        <v>1059</v>
+        <v>1066</v>
       </c>
       <c r="F659" s="42"/>
       <c r="G659" s="42"/>
       <c r="H659" s="42"/>
       <c r="I659" s="42" t="s">
-        <v>261</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="660" s="1" customFormat="1" spans="1:9">
@@ -22532,13 +22571,13 @@
         <v>0</v>
       </c>
       <c r="E660" s="42" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="F660" s="42"/>
       <c r="G660" s="42"/>
       <c r="H660" s="42"/>
       <c r="I660" s="42" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="661" s="1" customFormat="1" spans="1:9">
@@ -22555,13 +22594,13 @@
         <v>0</v>
       </c>
       <c r="E661" s="42" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="F661" s="42"/>
       <c r="G661" s="42"/>
       <c r="H661" s="42"/>
       <c r="I661" s="42" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="662" s="1" customFormat="1" spans="1:9">
@@ -22578,13 +22617,13 @@
         <v>1</v>
       </c>
       <c r="E662" s="42" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="F662" s="42"/>
       <c r="G662" s="42"/>
       <c r="H662" s="42"/>
       <c r="I662" s="42" t="s">
-        <v>249</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="663" s="1" customFormat="1" spans="1:9">
@@ -22601,13 +22640,13 @@
         <v>2</v>
       </c>
       <c r="E663" s="42" t="s">
-        <v>1065</v>
+        <v>1074</v>
       </c>
       <c r="F663" s="42"/>
       <c r="G663" s="42"/>
       <c r="H663" s="42"/>
       <c r="I663" s="42" t="s">
-        <v>431</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="664" s="1" customFormat="1" spans="1:9">
@@ -22624,13 +22663,13 @@
         <v>2</v>
       </c>
       <c r="E664" s="42" t="s">
-        <v>1066</v>
+        <v>1076</v>
       </c>
       <c r="F664" s="42"/>
       <c r="G664" s="42"/>
       <c r="H664" s="42"/>
       <c r="I664" s="42" t="s">
-        <v>342</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="665" s="1" customFormat="1" spans="1:9">
@@ -22647,13 +22686,13 @@
         <v>2</v>
       </c>
       <c r="E665" s="42" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
       <c r="F665" s="42"/>
       <c r="G665" s="42"/>
       <c r="H665" s="42"/>
       <c r="I665" s="42" t="s">
-        <v>433</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="666" s="1" customFormat="1" spans="1:9">
@@ -22670,13 +22709,13 @@
         <v>2</v>
       </c>
       <c r="E666" s="42" t="s">
-        <v>1068</v>
+        <v>1080</v>
       </c>
       <c r="F666" s="42"/>
       <c r="G666" s="42"/>
       <c r="H666" s="42"/>
       <c r="I666" s="42" t="s">
-        <v>435</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="667" s="1" customFormat="1" spans="1:9">
@@ -22693,13 +22732,13 @@
         <v>2</v>
       </c>
       <c r="E667" s="42" t="s">
-        <v>1069</v>
+        <v>1082</v>
       </c>
       <c r="F667" s="42"/>
       <c r="G667" s="42"/>
       <c r="H667" s="42"/>
       <c r="I667" s="42" t="s">
-        <v>437</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="668" s="1" customFormat="1" spans="1:9">
@@ -22716,13 +22755,13 @@
         <v>2</v>
       </c>
       <c r="E668" s="42" t="s">
-        <v>1070</v>
+        <v>1084</v>
       </c>
       <c r="F668" s="42"/>
       <c r="G668" s="42"/>
       <c r="H668" s="42"/>
       <c r="I668" s="42" t="s">
-        <v>439</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="669" s="1" customFormat="1" spans="1:9">
@@ -22739,13 +22778,13 @@
         <v>2</v>
       </c>
       <c r="E669" s="42" t="s">
-        <v>1071</v>
+        <v>1086</v>
       </c>
       <c r="F669" s="42"/>
       <c r="G669" s="42"/>
       <c r="H669" s="42"/>
       <c r="I669" s="42" t="s">
-        <v>1072</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="670" s="1" customFormat="1" spans="1:9">
@@ -22762,13 +22801,13 @@
         <v>2</v>
       </c>
       <c r="E670" s="42" t="s">
-        <v>1073</v>
+        <v>1086</v>
       </c>
       <c r="F670" s="42"/>
       <c r="G670" s="42"/>
       <c r="H670" s="42"/>
       <c r="I670" s="42" t="s">
-        <v>1072</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="671" s="1" customFormat="1" spans="1:9">
@@ -22785,13 +22824,13 @@
         <v>2</v>
       </c>
       <c r="E671" s="42" t="s">
-        <v>1074</v>
+        <v>1086</v>
       </c>
       <c r="F671" s="42"/>
       <c r="G671" s="42"/>
       <c r="H671" s="42"/>
       <c r="I671" s="42" t="s">
-        <v>1072</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="672" s="1" customFormat="1" spans="1:9">
@@ -22808,7 +22847,7 @@
         <v>0</v>
       </c>
       <c r="E672" s="50" t="s">
-        <v>1075</v>
+        <v>1088</v>
       </c>
       <c r="F672" s="50"/>
       <c r="G672" s="50"/>
@@ -22831,7 +22870,7 @@
         <v>0</v>
       </c>
       <c r="E673" s="50" t="s">
-        <v>1076</v>
+        <v>1089</v>
       </c>
       <c r="F673" s="50"/>
       <c r="G673" s="50"/>
@@ -22854,7 +22893,7 @@
         <v>0</v>
       </c>
       <c r="E674" s="50" t="s">
-        <v>1077</v>
+        <v>1090</v>
       </c>
       <c r="F674" s="50"/>
       <c r="G674" s="50"/>
@@ -22877,7 +22916,7 @@
         <v>0</v>
       </c>
       <c r="E675" s="50" t="s">
-        <v>1078</v>
+        <v>1091</v>
       </c>
       <c r="F675" s="50"/>
       <c r="G675" s="50"/>
@@ -22900,7 +22939,7 @@
         <v>0</v>
       </c>
       <c r="E676" s="50" t="s">
-        <v>1079</v>
+        <v>1092</v>
       </c>
       <c r="F676" s="50"/>
       <c r="G676" s="50"/>
@@ -22923,13 +22962,13 @@
         <v>0</v>
       </c>
       <c r="E677" s="50" t="s">
-        <v>1080</v>
+        <v>1093</v>
       </c>
       <c r="F677" s="50"/>
       <c r="G677" s="50"/>
       <c r="H677" s="50"/>
       <c r="I677" s="50" t="s">
-        <v>1081</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="678" s="1" customFormat="1" spans="1:9">
@@ -22946,13 +22985,13 @@
         <v>0</v>
       </c>
       <c r="E678" s="50" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="F678" s="50"/>
       <c r="G678" s="50"/>
       <c r="H678" s="50"/>
       <c r="I678" s="50" t="s">
-        <v>1083</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="679" s="1" customFormat="1" spans="1:9">
@@ -22969,13 +23008,13 @@
         <v>0</v>
       </c>
       <c r="E679" s="50" t="s">
-        <v>1084</v>
+        <v>1097</v>
       </c>
       <c r="F679" s="50"/>
       <c r="G679" s="50"/>
       <c r="H679" s="50"/>
       <c r="I679" s="50" t="s">
-        <v>1085</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="680" s="1" customFormat="1" spans="1:9">
@@ -22992,13 +23031,13 @@
         <v>0</v>
       </c>
       <c r="E680" s="50" t="s">
-        <v>1086</v>
+        <v>1099</v>
       </c>
       <c r="F680" s="50"/>
       <c r="G680" s="50"/>
       <c r="H680" s="50"/>
       <c r="I680" s="50" t="s">
-        <v>1087</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="681" s="1" customFormat="1" spans="1:9">
@@ -23015,13 +23054,13 @@
         <v>0</v>
       </c>
       <c r="E681" s="50" t="s">
-        <v>1088</v>
+        <v>1101</v>
       </c>
       <c r="F681" s="50"/>
       <c r="G681" s="50"/>
       <c r="H681" s="50"/>
       <c r="I681" s="50" t="s">
-        <v>1089</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="682" s="1" customFormat="1" spans="1:9">
@@ -23038,13 +23077,13 @@
         <v>0</v>
       </c>
       <c r="E682" s="50" t="s">
-        <v>1090</v>
+        <v>1103</v>
       </c>
       <c r="F682" s="50"/>
       <c r="G682" s="50"/>
       <c r="H682" s="50"/>
       <c r="I682" s="50" t="s">
-        <v>1091</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="683" s="1" customFormat="1" spans="1:9">
@@ -23061,7 +23100,7 @@
         <v>1</v>
       </c>
       <c r="E683" s="50" t="s">
-        <v>1092</v>
+        <v>1105</v>
       </c>
       <c r="F683" s="50"/>
       <c r="G683" s="50"/>
@@ -23084,7 +23123,7 @@
         <v>2</v>
       </c>
       <c r="E684" s="50" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="F684" s="50"/>
       <c r="G684" s="50"/>
@@ -23107,7 +23146,7 @@
         <v>2</v>
       </c>
       <c r="E685" s="50" t="s">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="F685" s="50"/>
       <c r="G685" s="50"/>
@@ -23130,7 +23169,7 @@
         <v>2</v>
       </c>
       <c r="E686" s="50" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="F686" s="50"/>
       <c r="G686" s="50"/>
@@ -23153,7 +23192,7 @@
         <v>2</v>
       </c>
       <c r="E687" s="50" t="s">
-        <v>1096</v>
+        <v>1109</v>
       </c>
       <c r="F687" s="50"/>
       <c r="G687" s="50"/>
@@ -23176,7 +23215,7 @@
         <v>2</v>
       </c>
       <c r="E688" s="50" t="s">
-        <v>1097</v>
+        <v>1110</v>
       </c>
       <c r="F688" s="50"/>
       <c r="G688" s="50"/>
@@ -23199,7 +23238,7 @@
         <v>0</v>
       </c>
       <c r="E689" s="50" t="s">
-        <v>1098</v>
+        <v>1111</v>
       </c>
       <c r="F689" s="50"/>
       <c r="G689" s="50"/>
@@ -23224,7 +23263,7 @@
         <v>0</v>
       </c>
       <c r="E690" s="50" t="s">
-        <v>1099</v>
+        <v>1112</v>
       </c>
       <c r="F690" s="50"/>
       <c r="G690" s="50"/>
@@ -23249,7 +23288,7 @@
         <v>0</v>
       </c>
       <c r="E691" s="50" t="s">
-        <v>1100</v>
+        <v>1113</v>
       </c>
       <c r="F691" s="50"/>
       <c r="G691" s="50"/>
@@ -23274,7 +23313,7 @@
         <v>0</v>
       </c>
       <c r="E692" s="50" t="s">
-        <v>1101</v>
+        <v>1114</v>
       </c>
       <c r="F692" s="50"/>
       <c r="G692" s="50"/>
@@ -23299,7 +23338,7 @@
         <v>0</v>
       </c>
       <c r="E693" s="50" t="s">
-        <v>1102</v>
+        <v>1115</v>
       </c>
       <c r="F693" s="50"/>
       <c r="G693" s="50"/>
@@ -23324,7 +23363,7 @@
         <v>0</v>
       </c>
       <c r="E694" s="50" t="s">
-        <v>1103</v>
+        <v>1116</v>
       </c>
       <c r="F694" s="50"/>
       <c r="G694" s="50"/>
@@ -23332,7 +23371,7 @@
         <v>2</v>
       </c>
       <c r="I694" s="50" t="s">
-        <v>1104</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="695" spans="1:9">
@@ -23349,7 +23388,7 @@
         <v>0</v>
       </c>
       <c r="E695" s="50" t="s">
-        <v>1105</v>
+        <v>1118</v>
       </c>
       <c r="F695" s="50"/>
       <c r="G695" s="51"/>
@@ -23357,7 +23396,7 @@
         <v>2</v>
       </c>
       <c r="I695" s="50" t="s">
-        <v>1106</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="696" spans="1:9">
@@ -23374,7 +23413,7 @@
         <v>0</v>
       </c>
       <c r="E696" s="50" t="s">
-        <v>1107</v>
+        <v>1120</v>
       </c>
       <c r="F696" s="50"/>
       <c r="G696" s="51"/>
@@ -23382,7 +23421,7 @@
         <v>2</v>
       </c>
       <c r="I696" s="50" t="s">
-        <v>1108</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="697" spans="1:9">
@@ -23399,7 +23438,7 @@
         <v>0</v>
       </c>
       <c r="E697" s="50" t="s">
-        <v>1109</v>
+        <v>1122</v>
       </c>
       <c r="F697" s="50"/>
       <c r="G697" s="51"/>
@@ -23407,7 +23446,7 @@
         <v>2</v>
       </c>
       <c r="I697" s="50" t="s">
-        <v>1110</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="698" spans="1:9">
@@ -23424,7 +23463,7 @@
         <v>0</v>
       </c>
       <c r="E698" s="50" t="s">
-        <v>1111</v>
+        <v>1124</v>
       </c>
       <c r="F698" s="50"/>
       <c r="G698" s="51"/>
@@ -23432,7 +23471,7 @@
         <v>2</v>
       </c>
       <c r="I698" s="50" t="s">
-        <v>1112</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="699" spans="1:9">
@@ -23449,7 +23488,7 @@
         <v>0</v>
       </c>
       <c r="E699" s="50" t="s">
-        <v>1113</v>
+        <v>1126</v>
       </c>
       <c r="F699" s="50"/>
       <c r="G699" s="51"/>
@@ -23457,7 +23496,7 @@
         <v>2</v>
       </c>
       <c r="I699" s="50" t="s">
-        <v>1114</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="700" spans="1:9">
@@ -23474,7 +23513,7 @@
         <v>1</v>
       </c>
       <c r="E700" s="50" t="s">
-        <v>1115</v>
+        <v>1128</v>
       </c>
       <c r="F700" s="50"/>
       <c r="G700" s="51"/>
@@ -23499,7 +23538,7 @@
         <v>0</v>
       </c>
       <c r="E701" s="50" t="s">
-        <v>1116</v>
+        <v>1129</v>
       </c>
       <c r="F701" s="50"/>
       <c r="G701" s="51"/>
@@ -23524,7 +23563,7 @@
         <v>0</v>
       </c>
       <c r="E702" s="50" t="s">
-        <v>1117</v>
+        <v>1130</v>
       </c>
       <c r="F702" s="50"/>
       <c r="G702" s="51"/>
@@ -23549,7 +23588,7 @@
         <v>0</v>
       </c>
       <c r="E703" s="50" t="s">
-        <v>1118</v>
+        <v>1131</v>
       </c>
       <c r="F703" s="50"/>
       <c r="G703" s="51"/>
@@ -23574,7 +23613,7 @@
         <v>0</v>
       </c>
       <c r="E704" s="50" t="s">
-        <v>1119</v>
+        <v>1132</v>
       </c>
       <c r="F704" s="50"/>
       <c r="G704" s="51"/>
@@ -23599,7 +23638,7 @@
         <v>0</v>
       </c>
       <c r="E705" s="50" t="s">
-        <v>1120</v>
+        <v>1133</v>
       </c>
       <c r="F705" s="50"/>
       <c r="G705" s="51"/>
@@ -23624,7 +23663,7 @@
         <v>0</v>
       </c>
       <c r="E706" s="50" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="F706" s="50"/>
       <c r="G706" s="51"/>
@@ -23632,7 +23671,7 @@
         <v>3</v>
       </c>
       <c r="I706" s="50" t="s">
-        <v>1122</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="707" spans="1:9">
@@ -23649,7 +23688,7 @@
         <v>0</v>
       </c>
       <c r="E707" s="50" t="s">
-        <v>1123</v>
+        <v>1136</v>
       </c>
       <c r="F707" s="50"/>
       <c r="G707" s="51"/>
@@ -23657,7 +23696,7 @@
         <v>3</v>
       </c>
       <c r="I707" s="50" t="s">
-        <v>1124</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="708" spans="1:9">
@@ -23674,7 +23713,7 @@
         <v>0</v>
       </c>
       <c r="E708" s="50" t="s">
-        <v>1125</v>
+        <v>1138</v>
       </c>
       <c r="F708" s="50"/>
       <c r="G708" s="51"/>
@@ -23682,7 +23721,7 @@
         <v>3</v>
       </c>
       <c r="I708" s="50" t="s">
-        <v>1126</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="709" spans="1:9">
@@ -23699,7 +23738,7 @@
         <v>0</v>
       </c>
       <c r="E709" s="50" t="s">
-        <v>1127</v>
+        <v>1140</v>
       </c>
       <c r="F709" s="50"/>
       <c r="G709" s="51"/>
@@ -23707,7 +23746,7 @@
         <v>3</v>
       </c>
       <c r="I709" s="50" t="s">
-        <v>1128</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="710" spans="1:9">
@@ -23724,7 +23763,7 @@
         <v>0</v>
       </c>
       <c r="E710" s="50" t="s">
-        <v>1129</v>
+        <v>1142</v>
       </c>
       <c r="F710" s="50"/>
       <c r="G710" s="51"/>
@@ -23732,7 +23771,7 @@
         <v>3</v>
       </c>
       <c r="I710" s="50" t="s">
-        <v>1130</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="711" spans="1:9">
@@ -23749,7 +23788,7 @@
         <v>0</v>
       </c>
       <c r="E711" s="50" t="s">
-        <v>1131</v>
+        <v>1144</v>
       </c>
       <c r="F711" s="50"/>
       <c r="G711" s="51"/>
@@ -23757,7 +23796,7 @@
         <v>3</v>
       </c>
       <c r="I711" s="50" t="s">
-        <v>1132</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="712" spans="1:9">
@@ -23774,7 +23813,7 @@
         <v>1</v>
       </c>
       <c r="E712" s="50" t="s">
-        <v>1133</v>
+        <v>1146</v>
       </c>
       <c r="F712" s="50"/>
       <c r="G712" s="51"/>
@@ -23799,7 +23838,7 @@
         <v>0</v>
       </c>
       <c r="E713" s="50" t="s">
-        <v>1134</v>
+        <v>1147</v>
       </c>
       <c r="F713" s="50"/>
       <c r="G713" s="51"/>
@@ -23824,7 +23863,7 @@
         <v>0</v>
       </c>
       <c r="E714" s="50" t="s">
-        <v>1135</v>
+        <v>1148</v>
       </c>
       <c r="F714" s="50"/>
       <c r="G714" s="51"/>
@@ -23849,7 +23888,7 @@
         <v>0</v>
       </c>
       <c r="E715" s="50" t="s">
-        <v>1136</v>
+        <v>1149</v>
       </c>
       <c r="F715" s="50"/>
       <c r="G715" s="51"/>
@@ -23874,7 +23913,7 @@
         <v>0</v>
       </c>
       <c r="E716" s="50" t="s">
-        <v>1137</v>
+        <v>1150</v>
       </c>
       <c r="F716" s="50"/>
       <c r="G716" s="51"/>
@@ -23899,7 +23938,7 @@
         <v>0</v>
       </c>
       <c r="E717" s="50" t="s">
-        <v>1138</v>
+        <v>1151</v>
       </c>
       <c r="F717" s="50"/>
       <c r="G717" s="51"/>
@@ -23924,7 +23963,7 @@
         <v>0</v>
       </c>
       <c r="E718" s="50" t="s">
-        <v>1139</v>
+        <v>1152</v>
       </c>
       <c r="F718" s="50"/>
       <c r="G718" s="51"/>
@@ -23932,7 +23971,7 @@
         <v>4</v>
       </c>
       <c r="I718" s="50" t="s">
-        <v>1140</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="719" spans="1:9">
@@ -23949,7 +23988,7 @@
         <v>0</v>
       </c>
       <c r="E719" s="50" t="s">
-        <v>1141</v>
+        <v>1154</v>
       </c>
       <c r="F719" s="50"/>
       <c r="G719" s="51"/>
@@ -23957,7 +23996,7 @@
         <v>4</v>
       </c>
       <c r="I719" s="50" t="s">
-        <v>1142</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="720" spans="1:9">
@@ -23974,7 +24013,7 @@
         <v>0</v>
       </c>
       <c r="E720" s="50" t="s">
-        <v>1143</v>
+        <v>1156</v>
       </c>
       <c r="F720" s="50"/>
       <c r="G720" s="51"/>
@@ -23982,7 +24021,7 @@
         <v>4</v>
       </c>
       <c r="I720" s="50" t="s">
-        <v>1144</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="721" spans="1:9">
@@ -23999,7 +24038,7 @@
         <v>0</v>
       </c>
       <c r="E721" s="50" t="s">
-        <v>1145</v>
+        <v>1158</v>
       </c>
       <c r="F721" s="50"/>
       <c r="G721" s="51"/>
@@ -24007,7 +24046,7 @@
         <v>4</v>
       </c>
       <c r="I721" s="50" t="s">
-        <v>1146</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="722" spans="1:9">
@@ -24024,7 +24063,7 @@
         <v>0</v>
       </c>
       <c r="E722" s="50" t="s">
-        <v>1147</v>
+        <v>1160</v>
       </c>
       <c r="F722" s="50"/>
       <c r="G722" s="51"/>
@@ -24032,7 +24071,7 @@
         <v>4</v>
       </c>
       <c r="I722" s="50" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="723" spans="1:9">
@@ -24049,7 +24088,7 @@
         <v>0</v>
       </c>
       <c r="E723" s="50" t="s">
-        <v>1149</v>
+        <v>1162</v>
       </c>
       <c r="F723" s="50"/>
       <c r="G723" s="51"/>
@@ -24057,7 +24096,7 @@
         <v>4</v>
       </c>
       <c r="I723" s="50" t="s">
-        <v>1150</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="724" spans="1:9">
@@ -24074,7 +24113,7 @@
         <v>1</v>
       </c>
       <c r="E724" s="50" t="s">
-        <v>1151</v>
+        <v>1164</v>
       </c>
       <c r="F724" s="50"/>
       <c r="G724" s="51"/>
@@ -24099,7 +24138,7 @@
         <v>0</v>
       </c>
       <c r="E725" s="50" t="s">
-        <v>1152</v>
+        <v>1165</v>
       </c>
       <c r="F725" s="50" t="s">
         <v>888</v>
@@ -24126,10 +24165,10 @@
         <v>0</v>
       </c>
       <c r="E726" s="50" t="s">
-        <v>1153</v>
+        <v>1166</v>
       </c>
       <c r="F726" s="50" t="s">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="G726" s="51"/>
       <c r="H726" s="50">
@@ -24153,10 +24192,10 @@
         <v>0</v>
       </c>
       <c r="E727" s="50" t="s">
-        <v>1155</v>
+        <v>1168</v>
       </c>
       <c r="F727" s="50" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="G727" s="51"/>
       <c r="H727" s="50">
@@ -24180,10 +24219,10 @@
         <v>0</v>
       </c>
       <c r="E728" s="50" t="s">
-        <v>1157</v>
+        <v>1170</v>
       </c>
       <c r="F728" s="50" t="s">
-        <v>1158</v>
+        <v>1171</v>
       </c>
       <c r="G728" s="51"/>
       <c r="H728" s="50">
@@ -24207,10 +24246,10 @@
         <v>0</v>
       </c>
       <c r="E729" s="50" t="s">
-        <v>1159</v>
+        <v>1172</v>
       </c>
       <c r="F729" s="50" t="s">
-        <v>1160</v>
+        <v>1173</v>
       </c>
       <c r="G729" s="51"/>
       <c r="H729" s="50">
@@ -24234,17 +24273,17 @@
         <v>0</v>
       </c>
       <c r="E730" s="50" t="s">
-        <v>1161</v>
+        <v>1174</v>
       </c>
       <c r="F730" s="50" t="s">
-        <v>1162</v>
+        <v>1175</v>
       </c>
       <c r="G730" s="51"/>
       <c r="H730" s="50">
         <v>2</v>
       </c>
       <c r="I730" s="50" t="s">
-        <v>1163</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="731" spans="1:9">
@@ -24261,17 +24300,17 @@
         <v>0</v>
       </c>
       <c r="E731" s="50" t="s">
-        <v>1164</v>
+        <v>1177</v>
       </c>
       <c r="F731" s="50" t="s">
-        <v>1165</v>
+        <v>1178</v>
       </c>
       <c r="G731" s="51"/>
       <c r="H731" s="50">
         <v>2</v>
       </c>
       <c r="I731" s="50" t="s">
-        <v>1166</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="732" spans="1:9">
@@ -24288,17 +24327,17 @@
         <v>0</v>
       </c>
       <c r="E732" s="50" t="s">
-        <v>1167</v>
+        <v>1180</v>
       </c>
       <c r="F732" s="50" t="s">
-        <v>1168</v>
+        <v>1181</v>
       </c>
       <c r="G732" s="51"/>
       <c r="H732" s="50">
         <v>2</v>
       </c>
       <c r="I732" s="50" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="733" spans="1:9">
@@ -24315,17 +24354,17 @@
         <v>0</v>
       </c>
       <c r="E733" s="50" t="s">
-        <v>1170</v>
+        <v>1183</v>
       </c>
       <c r="F733" s="50" t="s">
-        <v>1171</v>
+        <v>1184</v>
       </c>
       <c r="G733" s="51"/>
       <c r="H733" s="50">
         <v>2</v>
       </c>
       <c r="I733" s="50" t="s">
-        <v>1172</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="734" spans="1:9">
@@ -24342,17 +24381,17 @@
         <v>0</v>
       </c>
       <c r="E734" s="50" t="s">
-        <v>1173</v>
+        <v>1186</v>
       </c>
       <c r="F734" s="50" t="s">
-        <v>1174</v>
+        <v>1187</v>
       </c>
       <c r="G734" s="51"/>
       <c r="H734" s="50">
         <v>2</v>
       </c>
       <c r="I734" s="50" t="s">
-        <v>1175</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="735" spans="1:9">
@@ -24369,17 +24408,17 @@
         <v>0</v>
       </c>
       <c r="E735" s="50" t="s">
-        <v>1176</v>
+        <v>1189</v>
       </c>
       <c r="F735" s="50" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="G735" s="51"/>
       <c r="H735" s="50">
         <v>2</v>
       </c>
       <c r="I735" s="50" t="s">
-        <v>1178</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="736" spans="1:9">
@@ -24396,7 +24435,7 @@
         <v>0</v>
       </c>
       <c r="E736" s="50" t="s">
-        <v>1179</v>
+        <v>1192</v>
       </c>
       <c r="F736" s="50" t="s">
         <v>921</v>
@@ -24423,10 +24462,10 @@
         <v>0</v>
       </c>
       <c r="E737" s="50" t="s">
-        <v>1180</v>
+        <v>1193</v>
       </c>
       <c r="F737" s="50" t="s">
-        <v>1181</v>
+        <v>1194</v>
       </c>
       <c r="G737" s="51"/>
       <c r="H737" s="50">
@@ -24450,10 +24489,10 @@
         <v>0</v>
       </c>
       <c r="E738" s="50" t="s">
-        <v>1182</v>
+        <v>1195</v>
       </c>
       <c r="F738" s="50" t="s">
-        <v>1183</v>
+        <v>1196</v>
       </c>
       <c r="G738" s="51"/>
       <c r="H738" s="50">
@@ -24477,10 +24516,10 @@
         <v>0</v>
       </c>
       <c r="E739" s="50" t="s">
-        <v>1184</v>
+        <v>1197</v>
       </c>
       <c r="F739" s="50" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="G739" s="51"/>
       <c r="H739" s="50">
@@ -24504,10 +24543,10 @@
         <v>0</v>
       </c>
       <c r="E740" s="50" t="s">
-        <v>1186</v>
+        <v>1199</v>
       </c>
       <c r="F740" s="50" t="s">
-        <v>1187</v>
+        <v>1200</v>
       </c>
       <c r="G740" s="51"/>
       <c r="H740" s="50">
@@ -24531,17 +24570,17 @@
         <v>0</v>
       </c>
       <c r="E741" s="50" t="s">
-        <v>1188</v>
+        <v>1201</v>
       </c>
       <c r="F741" s="50" t="s">
-        <v>1189</v>
+        <v>1202</v>
       </c>
       <c r="G741" s="51"/>
       <c r="H741" s="50">
         <v>3</v>
       </c>
       <c r="I741" s="50" t="s">
-        <v>1190</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="742" spans="1:9">
@@ -24558,17 +24597,17 @@
         <v>0</v>
       </c>
       <c r="E742" s="50" t="s">
-        <v>1191</v>
+        <v>1204</v>
       </c>
       <c r="F742" s="50" t="s">
-        <v>1192</v>
+        <v>1205</v>
       </c>
       <c r="G742" s="51"/>
       <c r="H742" s="50">
         <v>3</v>
       </c>
       <c r="I742" s="50" t="s">
-        <v>1193</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="743" spans="1:9">
@@ -24585,17 +24624,17 @@
         <v>0</v>
       </c>
       <c r="E743" s="50" t="s">
-        <v>1194</v>
+        <v>1207</v>
       </c>
       <c r="F743" s="50" t="s">
-        <v>1195</v>
+        <v>1208</v>
       </c>
       <c r="G743" s="51"/>
       <c r="H743" s="50">
         <v>3</v>
       </c>
       <c r="I743" s="50" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="744" spans="1:9">
@@ -24612,17 +24651,17 @@
         <v>0</v>
       </c>
       <c r="E744" s="50" t="s">
-        <v>1197</v>
+        <v>1210</v>
       </c>
       <c r="F744" s="50" t="s">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="G744" s="51"/>
       <c r="H744" s="50">
         <v>3</v>
       </c>
       <c r="I744" s="50" t="s">
-        <v>1199</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="745" spans="1:9">
@@ -24639,17 +24678,17 @@
         <v>0</v>
       </c>
       <c r="E745" s="50" t="s">
-        <v>1200</v>
+        <v>1213</v>
       </c>
       <c r="F745" s="50" t="s">
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="G745" s="51"/>
       <c r="H745" s="50">
         <v>3</v>
       </c>
       <c r="I745" s="50" t="s">
-        <v>1202</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="746" spans="1:9">
@@ -24666,17 +24705,17 @@
         <v>0</v>
       </c>
       <c r="E746" s="50" t="s">
-        <v>1203</v>
+        <v>1216</v>
       </c>
       <c r="F746" s="50" t="s">
-        <v>1204</v>
+        <v>1217</v>
       </c>
       <c r="G746" s="51"/>
       <c r="H746" s="50">
         <v>3</v>
       </c>
       <c r="I746" s="50" t="s">
-        <v>1205</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="747" spans="1:9">
@@ -24693,7 +24732,7 @@
         <v>0</v>
       </c>
       <c r="E747" s="50" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="F747" s="50" t="s">
         <v>954</v>
@@ -24720,10 +24759,10 @@
         <v>0</v>
       </c>
       <c r="E748" s="50" t="s">
-        <v>1207</v>
+        <v>1220</v>
       </c>
       <c r="F748" s="50" t="s">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="G748" s="51"/>
       <c r="H748" s="50">
@@ -24747,10 +24786,10 @@
         <v>0</v>
       </c>
       <c r="E749" s="50" t="s">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="F749" s="50" t="s">
-        <v>1210</v>
+        <v>1223</v>
       </c>
       <c r="G749" s="51"/>
       <c r="H749" s="50">
@@ -24774,10 +24813,10 @@
         <v>0</v>
       </c>
       <c r="E750" s="50" t="s">
-        <v>1211</v>
+        <v>1224</v>
       </c>
       <c r="F750" s="50" t="s">
-        <v>1212</v>
+        <v>1225</v>
       </c>
       <c r="G750" s="51"/>
       <c r="H750" s="50">
@@ -24801,10 +24840,10 @@
         <v>0</v>
       </c>
       <c r="E751" s="50" t="s">
-        <v>1213</v>
+        <v>1226</v>
       </c>
       <c r="F751" s="50" t="s">
-        <v>1214</v>
+        <v>1227</v>
       </c>
       <c r="G751" s="51"/>
       <c r="H751" s="50">
@@ -24828,17 +24867,17 @@
         <v>0</v>
       </c>
       <c r="E752" s="50" t="s">
-        <v>1215</v>
+        <v>1228</v>
       </c>
       <c r="F752" s="50" t="s">
-        <v>1216</v>
+        <v>1229</v>
       </c>
       <c r="G752" s="51"/>
       <c r="H752" s="50">
         <v>4</v>
       </c>
       <c r="I752" s="50" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="753" spans="1:9">
@@ -24855,17 +24894,17 @@
         <v>0</v>
       </c>
       <c r="E753" s="50" t="s">
-        <v>1218</v>
+        <v>1231</v>
       </c>
       <c r="F753" s="50" t="s">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="G753" s="51"/>
       <c r="H753" s="50">
         <v>4</v>
       </c>
       <c r="I753" s="50" t="s">
-        <v>1220</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="754" spans="1:9">
@@ -24882,17 +24921,17 @@
         <v>0</v>
       </c>
       <c r="E754" s="50" t="s">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="F754" s="50" t="s">
-        <v>1222</v>
+        <v>1235</v>
       </c>
       <c r="G754" s="51"/>
       <c r="H754" s="50">
         <v>4</v>
       </c>
       <c r="I754" s="50" t="s">
-        <v>1223</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="755" spans="1:9">
@@ -24909,17 +24948,17 @@
         <v>0</v>
       </c>
       <c r="E755" s="50" t="s">
-        <v>1224</v>
+        <v>1237</v>
       </c>
       <c r="F755" s="50" t="s">
-        <v>1225</v>
+        <v>1238</v>
       </c>
       <c r="G755" s="51"/>
       <c r="H755" s="50">
         <v>4</v>
       </c>
       <c r="I755" s="50" t="s">
-        <v>1226</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="756" spans="1:9">
@@ -24936,17 +24975,17 @@
         <v>0</v>
       </c>
       <c r="E756" s="50" t="s">
-        <v>1227</v>
+        <v>1240</v>
       </c>
       <c r="F756" s="50" t="s">
-        <v>1228</v>
+        <v>1241</v>
       </c>
       <c r="G756" s="51"/>
       <c r="H756" s="50">
         <v>4</v>
       </c>
       <c r="I756" s="50" t="s">
-        <v>1229</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="757" spans="1:9">
@@ -24963,17 +25002,17 @@
         <v>0</v>
       </c>
       <c r="E757" s="50" t="s">
-        <v>1230</v>
+        <v>1243</v>
       </c>
       <c r="F757" s="50" t="s">
-        <v>1231</v>
+        <v>1244</v>
       </c>
       <c r="G757" s="51"/>
       <c r="H757" s="50">
         <v>4</v>
       </c>
       <c r="I757" s="50" t="s">
-        <v>1232</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="758" spans="1:9">
@@ -24990,7 +25029,7 @@
         <v>0</v>
       </c>
       <c r="E758" s="50" t="s">
-        <v>1233</v>
+        <v>1246</v>
       </c>
       <c r="F758" s="50" t="s">
         <v>513</v>
@@ -25017,7 +25056,7 @@
         <v>0</v>
       </c>
       <c r="E759" s="50" t="s">
-        <v>1234</v>
+        <v>1247</v>
       </c>
       <c r="F759" s="50" t="s">
         <v>513</v>
@@ -25044,7 +25083,7 @@
         <v>0</v>
       </c>
       <c r="E760" s="50" t="s">
-        <v>1235</v>
+        <v>1248</v>
       </c>
       <c r="F760" s="50" t="s">
         <v>513</v>
@@ -25071,7 +25110,7 @@
         <v>0</v>
       </c>
       <c r="E761" s="50" t="s">
-        <v>1236</v>
+        <v>1249</v>
       </c>
       <c r="F761" s="50" t="s">
         <v>513</v>
@@ -25098,7 +25137,7 @@
         <v>0</v>
       </c>
       <c r="E762" s="50" t="s">
-        <v>1237</v>
+        <v>1250</v>
       </c>
       <c r="F762" s="50" t="s">
         <v>513</v>
@@ -25125,7 +25164,7 @@
         <v>0</v>
       </c>
       <c r="E763" s="50" t="s">
-        <v>1238</v>
+        <v>1251</v>
       </c>
       <c r="F763" s="50" t="s">
         <v>513</v>
@@ -25135,7 +25174,7 @@
         <v>2</v>
       </c>
       <c r="I763" s="50" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="764" spans="1:9">
@@ -25152,7 +25191,7 @@
         <v>0</v>
       </c>
       <c r="E764" s="50" t="s">
-        <v>1240</v>
+        <v>1253</v>
       </c>
       <c r="F764" s="50" t="s">
         <v>513</v>
@@ -25162,7 +25201,7 @@
         <v>2</v>
       </c>
       <c r="I764" s="50" t="s">
-        <v>1241</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="765" spans="1:9">
@@ -25179,7 +25218,7 @@
         <v>0</v>
       </c>
       <c r="E765" s="50" t="s">
-        <v>1242</v>
+        <v>1255</v>
       </c>
       <c r="F765" s="50" t="s">
         <v>513</v>
@@ -25189,7 +25228,7 @@
         <v>2</v>
       </c>
       <c r="I765" s="50" t="s">
-        <v>1243</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="766" spans="1:9">
@@ -25206,7 +25245,7 @@
         <v>0</v>
       </c>
       <c r="E766" s="50" t="s">
-        <v>1244</v>
+        <v>1257</v>
       </c>
       <c r="F766" s="50" t="s">
         <v>513</v>
@@ -25216,7 +25255,7 @@
         <v>2</v>
       </c>
       <c r="I766" s="50" t="s">
-        <v>1245</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="767" spans="1:9">
@@ -25233,7 +25272,7 @@
         <v>0</v>
       </c>
       <c r="E767" s="50" t="s">
-        <v>1246</v>
+        <v>1259</v>
       </c>
       <c r="F767" s="50" t="s">
         <v>513</v>
@@ -25243,7 +25282,7 @@
         <v>2</v>
       </c>
       <c r="I767" s="50" t="s">
-        <v>1247</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="768" spans="1:9">
@@ -25260,7 +25299,7 @@
         <v>0</v>
       </c>
       <c r="E768" s="50" t="s">
-        <v>1248</v>
+        <v>1261</v>
       </c>
       <c r="F768" s="50" t="s">
         <v>513</v>
@@ -25270,7 +25309,7 @@
         <v>2</v>
       </c>
       <c r="I768" s="50" t="s">
-        <v>1249</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="769" spans="1:9">
@@ -25287,7 +25326,7 @@
         <v>0</v>
       </c>
       <c r="E769" s="50" t="s">
-        <v>1250</v>
+        <v>1263</v>
       </c>
       <c r="F769" s="50" t="s">
         <v>536</v>
@@ -25314,7 +25353,7 @@
         <v>0</v>
       </c>
       <c r="E770" s="50" t="s">
-        <v>1251</v>
+        <v>1264</v>
       </c>
       <c r="F770" s="50" t="s">
         <v>536</v>
@@ -25341,7 +25380,7 @@
         <v>0</v>
       </c>
       <c r="E771" s="50" t="s">
-        <v>1252</v>
+        <v>1265</v>
       </c>
       <c r="F771" s="50" t="s">
         <v>536</v>
@@ -25368,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="E772" s="50" t="s">
-        <v>1253</v>
+        <v>1266</v>
       </c>
       <c r="F772" s="50" t="s">
         <v>536</v>
@@ -25395,7 +25434,7 @@
         <v>0</v>
       </c>
       <c r="E773" s="50" t="s">
-        <v>1254</v>
+        <v>1267</v>
       </c>
       <c r="F773" s="50" t="s">
         <v>536</v>
@@ -25422,7 +25461,7 @@
         <v>0</v>
       </c>
       <c r="E774" s="50" t="s">
-        <v>1255</v>
+        <v>1268</v>
       </c>
       <c r="F774" s="50" t="s">
         <v>536</v>
@@ -25432,7 +25471,7 @@
         <v>3</v>
       </c>
       <c r="I774" s="50" t="s">
-        <v>1256</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="775" spans="1:9">
@@ -25449,7 +25488,7 @@
         <v>0</v>
       </c>
       <c r="E775" s="50" t="s">
-        <v>1257</v>
+        <v>1270</v>
       </c>
       <c r="F775" s="50" t="s">
         <v>536</v>
@@ -25459,7 +25498,7 @@
         <v>3</v>
       </c>
       <c r="I775" s="50" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="776" spans="1:9">
@@ -25476,7 +25515,7 @@
         <v>0</v>
       </c>
       <c r="E776" s="50" t="s">
-        <v>1259</v>
+        <v>1272</v>
       </c>
       <c r="F776" s="50" t="s">
         <v>536</v>
@@ -25486,7 +25525,7 @@
         <v>3</v>
       </c>
       <c r="I776" s="50" t="s">
-        <v>1260</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="777" spans="1:9">
@@ -25503,7 +25542,7 @@
         <v>0</v>
       </c>
       <c r="E777" s="50" t="s">
-        <v>1261</v>
+        <v>1274</v>
       </c>
       <c r="F777" s="50" t="s">
         <v>536</v>
@@ -25513,7 +25552,7 @@
         <v>3</v>
       </c>
       <c r="I777" s="50" t="s">
-        <v>1262</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="778" spans="1:9">
@@ -25530,7 +25569,7 @@
         <v>0</v>
       </c>
       <c r="E778" s="50" t="s">
-        <v>1263</v>
+        <v>1276</v>
       </c>
       <c r="F778" s="50" t="s">
         <v>536</v>
@@ -25540,7 +25579,7 @@
         <v>3</v>
       </c>
       <c r="I778" s="50" t="s">
-        <v>1264</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="779" spans="1:9">
@@ -25557,7 +25596,7 @@
         <v>0</v>
       </c>
       <c r="E779" s="50" t="s">
-        <v>1265</v>
+        <v>1278</v>
       </c>
       <c r="F779" s="50" t="s">
         <v>536</v>
@@ -25567,7 +25606,7 @@
         <v>3</v>
       </c>
       <c r="I779" s="50" t="s">
-        <v>1266</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="780" spans="1:9">
@@ -25584,7 +25623,7 @@
         <v>0</v>
       </c>
       <c r="E780" s="50" t="s">
-        <v>1267</v>
+        <v>1280</v>
       </c>
       <c r="F780" s="50" t="s">
         <v>559</v>
@@ -25611,7 +25650,7 @@
         <v>0</v>
       </c>
       <c r="E781" s="50" t="s">
-        <v>1268</v>
+        <v>1281</v>
       </c>
       <c r="F781" s="50" t="s">
         <v>559</v>
@@ -25638,7 +25677,7 @@
         <v>0</v>
       </c>
       <c r="E782" s="50" t="s">
-        <v>1269</v>
+        <v>1282</v>
       </c>
       <c r="F782" s="50" t="s">
         <v>559</v>
@@ -25665,7 +25704,7 @@
         <v>0</v>
       </c>
       <c r="E783" s="50" t="s">
-        <v>1270</v>
+        <v>1283</v>
       </c>
       <c r="F783" s="50" t="s">
         <v>559</v>
@@ -25692,7 +25731,7 @@
         <v>0</v>
       </c>
       <c r="E784" s="50" t="s">
-        <v>1271</v>
+        <v>1284</v>
       </c>
       <c r="F784" s="50" t="s">
         <v>559</v>
@@ -25719,7 +25758,7 @@
         <v>0</v>
       </c>
       <c r="E785" s="50" t="s">
-        <v>1272</v>
+        <v>1285</v>
       </c>
       <c r="F785" s="50" t="s">
         <v>559</v>
@@ -25729,7 +25768,7 @@
         <v>4</v>
       </c>
       <c r="I785" s="50" t="s">
-        <v>1273</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="786" spans="1:9">
@@ -25746,7 +25785,7 @@
         <v>0</v>
       </c>
       <c r="E786" s="50" t="s">
-        <v>1274</v>
+        <v>1287</v>
       </c>
       <c r="F786" s="50" t="s">
         <v>559</v>
@@ -25756,7 +25795,7 @@
         <v>4</v>
       </c>
       <c r="I786" s="50" t="s">
-        <v>1275</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="787" spans="1:9">
@@ -25773,7 +25812,7 @@
         <v>0</v>
       </c>
       <c r="E787" s="50" t="s">
-        <v>1276</v>
+        <v>1289</v>
       </c>
       <c r="F787" s="50" t="s">
         <v>559</v>
@@ -25783,7 +25822,7 @@
         <v>4</v>
       </c>
       <c r="I787" s="50" t="s">
-        <v>1277</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="788" spans="1:9">
@@ -25800,7 +25839,7 @@
         <v>0</v>
       </c>
       <c r="E788" s="50" t="s">
-        <v>1278</v>
+        <v>1291</v>
       </c>
       <c r="F788" s="50" t="s">
         <v>559</v>
@@ -25810,7 +25849,7 @@
         <v>4</v>
       </c>
       <c r="I788" s="50" t="s">
-        <v>1279</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="789" spans="1:9">
@@ -25827,7 +25866,7 @@
         <v>0</v>
       </c>
       <c r="E789" s="50" t="s">
-        <v>1280</v>
+        <v>1293</v>
       </c>
       <c r="F789" s="50" t="s">
         <v>559</v>
@@ -25837,7 +25876,7 @@
         <v>4</v>
       </c>
       <c r="I789" s="50" t="s">
-        <v>1281</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="790" spans="1:9">
@@ -25854,7 +25893,7 @@
         <v>0</v>
       </c>
       <c r="E790" s="50" t="s">
-        <v>1282</v>
+        <v>1295</v>
       </c>
       <c r="F790" s="50" t="s">
         <v>559</v>
@@ -25864,7 +25903,7 @@
         <v>4</v>
       </c>
       <c r="I790" s="50" t="s">
-        <v>1283</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="791" spans="1:9">
@@ -25990,7 +26029,7 @@
       <c r="G796" s="52"/>
       <c r="H796" s="42"/>
       <c r="I796" s="42" t="s">
-        <v>1284</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="797" spans="1:9">
@@ -26011,7 +26050,7 @@
       <c r="G797" s="52"/>
       <c r="H797" s="42"/>
       <c r="I797" s="42" t="s">
-        <v>1285</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="798" spans="1:9">
@@ -26032,7 +26071,7 @@
       <c r="G798" s="52"/>
       <c r="H798" s="42"/>
       <c r="I798" s="42" t="s">
-        <v>1286</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="799" spans="1:9">
@@ -26053,7 +26092,7 @@
       <c r="G799" s="52"/>
       <c r="H799" s="42"/>
       <c r="I799" s="42" t="s">
-        <v>1287</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="800" spans="1:9">
@@ -26074,7 +26113,7 @@
       <c r="G800" s="52"/>
       <c r="H800" s="42"/>
       <c r="I800" s="42" t="s">
-        <v>1288</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="801" spans="1:9">
@@ -26095,7 +26134,7 @@
       <c r="G801" s="52"/>
       <c r="H801" s="42"/>
       <c r="I801" s="42" t="s">
-        <v>1289</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="802" spans="1:9">
@@ -26116,7 +26155,7 @@
       <c r="G802" s="52"/>
       <c r="H802" s="42"/>
       <c r="I802" s="42" t="s">
-        <v>1290</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="803" spans="1:9">
@@ -26137,7 +26176,7 @@
       <c r="G803" s="52"/>
       <c r="H803" s="42"/>
       <c r="I803" s="42" t="s">
-        <v>1291</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="804" spans="1:9">
@@ -26244,7 +26283,7 @@
         <v>2</v>
       </c>
       <c r="I808" s="53" t="s">
-        <v>1292</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="809" spans="1:9">
@@ -26267,7 +26306,7 @@
         <v>2</v>
       </c>
       <c r="I809" s="42" t="s">
-        <v>1293</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="810" spans="1:9">
@@ -26290,7 +26329,7 @@
         <v>2</v>
       </c>
       <c r="I810" s="42" t="s">
-        <v>1294</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="811" spans="1:9">
@@ -26313,7 +26352,7 @@
         <v>2</v>
       </c>
       <c r="I811" s="42" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="812" spans="1:9">
@@ -26336,7 +26375,7 @@
         <v>2</v>
       </c>
       <c r="I812" s="42" t="s">
-        <v>1296</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="813" spans="1:9">
@@ -26359,7 +26398,7 @@
         <v>2</v>
       </c>
       <c r="I813" s="42" t="s">
-        <v>1297</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="814" spans="1:9">
@@ -26382,7 +26421,7 @@
         <v>2</v>
       </c>
       <c r="I814" s="42" t="s">
-        <v>1298</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="815" spans="1:9">
@@ -26405,7 +26444,7 @@
         <v>2</v>
       </c>
       <c r="I815" s="42" t="s">
-        <v>1299</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="816" spans="1:9">
@@ -26428,7 +26467,7 @@
         <v>2</v>
       </c>
       <c r="I816" s="42" t="s">
-        <v>1300</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="817" spans="1:9">
@@ -26451,7 +26490,7 @@
         <v>2</v>
       </c>
       <c r="I817" s="42" t="s">
-        <v>1301</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="818" spans="1:9">
@@ -26474,7 +26513,7 @@
         <v>2</v>
       </c>
       <c r="I818" s="42" t="s">
-        <v>1302</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="819" spans="1:9">
@@ -26497,7 +26536,7 @@
         <v>2</v>
       </c>
       <c r="I819" s="42" t="s">
-        <v>1303</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="820" spans="1:9">
@@ -26520,7 +26559,7 @@
         <v>2</v>
       </c>
       <c r="I820" s="42" t="s">
-        <v>1304</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="821" spans="1:9">
@@ -26543,7 +26582,7 @@
         <v>2</v>
       </c>
       <c r="I821" s="42" t="s">
-        <v>1305</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="822" spans="1:9">
@@ -26566,7 +26605,7 @@
         <v>3</v>
       </c>
       <c r="I822" s="53" t="s">
-        <v>1306</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="823" spans="1:9">
@@ -26589,7 +26628,7 @@
         <v>3</v>
       </c>
       <c r="I823" s="42" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="824" spans="1:9">
@@ -26612,7 +26651,7 @@
         <v>3</v>
       </c>
       <c r="I824" s="42" t="s">
-        <v>1308</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="825" spans="1:9">
@@ -26635,7 +26674,7 @@
         <v>3</v>
       </c>
       <c r="I825" s="42" t="s">
-        <v>1309</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="826" spans="1:9">
@@ -26658,7 +26697,7 @@
         <v>3</v>
       </c>
       <c r="I826" s="42" t="s">
-        <v>1310</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="827" spans="1:9">
@@ -26681,7 +26720,7 @@
         <v>3</v>
       </c>
       <c r="I827" s="42" t="s">
-        <v>1311</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="828" spans="1:9">
@@ -26704,7 +26743,7 @@
         <v>3</v>
       </c>
       <c r="I828" s="42" t="s">
-        <v>1312</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="829" spans="1:9">
@@ -26727,7 +26766,7 @@
         <v>3</v>
       </c>
       <c r="I829" s="42" t="s">
-        <v>1313</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="830" spans="1:9">
@@ -26750,7 +26789,7 @@
         <v>3</v>
       </c>
       <c r="I830" s="42" t="s">
-        <v>1314</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="831" spans="1:9">
@@ -26773,7 +26812,7 @@
         <v>3</v>
       </c>
       <c r="I831" s="42" t="s">
-        <v>1315</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="832" spans="1:9">
@@ -26796,7 +26835,7 @@
         <v>3</v>
       </c>
       <c r="I832" s="42" t="s">
-        <v>1316</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="833" spans="1:9">
@@ -26819,7 +26858,7 @@
         <v>3</v>
       </c>
       <c r="I833" s="42" t="s">
-        <v>1317</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="834" spans="1:9">
@@ -26842,7 +26881,7 @@
         <v>3</v>
       </c>
       <c r="I834" s="42" t="s">
-        <v>1318</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="835" spans="1:9">
@@ -26865,7 +26904,7 @@
         <v>3</v>
       </c>
       <c r="I835" s="42" t="s">
-        <v>1319</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="836" spans="1:9">
@@ -26888,7 +26927,7 @@
         <v>4</v>
       </c>
       <c r="I836" s="53" t="s">
-        <v>1320</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="837" spans="1:9">
@@ -26911,7 +26950,7 @@
         <v>4</v>
       </c>
       <c r="I837" s="42" t="s">
-        <v>1321</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="838" spans="1:9">
@@ -26934,7 +26973,7 @@
         <v>4</v>
       </c>
       <c r="I838" s="42" t="s">
-        <v>1322</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="839" spans="1:9">
@@ -26957,7 +26996,7 @@
         <v>4</v>
       </c>
       <c r="I839" s="42" t="s">
-        <v>1323</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="840" spans="1:9">
@@ -26980,7 +27019,7 @@
         <v>4</v>
       </c>
       <c r="I840" s="42" t="s">
-        <v>1324</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="841" spans="1:9">
@@ -27003,7 +27042,7 @@
         <v>4</v>
       </c>
       <c r="I841" s="42" t="s">
-        <v>1325</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="842" spans="1:9">
@@ -27026,7 +27065,7 @@
         <v>4</v>
       </c>
       <c r="I842" s="42" t="s">
-        <v>1326</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="843" spans="1:9">
@@ -27049,7 +27088,7 @@
         <v>4</v>
       </c>
       <c r="I843" s="42" t="s">
-        <v>1327</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="844" spans="1:9">
@@ -27072,7 +27111,7 @@
         <v>4</v>
       </c>
       <c r="I844" s="42" t="s">
-        <v>1328</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="845" spans="1:9">
@@ -27095,7 +27134,7 @@
         <v>4</v>
       </c>
       <c r="I845" s="42" t="s">
-        <v>1329</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="846" spans="1:9">
@@ -27118,7 +27157,7 @@
         <v>4</v>
       </c>
       <c r="I846" s="42" t="s">
-        <v>1330</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="847" spans="1:9">
@@ -27141,7 +27180,7 @@
         <v>4</v>
       </c>
       <c r="I847" s="42" t="s">
-        <v>1331</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="848" spans="1:9">
@@ -27164,7 +27203,7 @@
         <v>4</v>
       </c>
       <c r="I848" s="42" t="s">
-        <v>1332</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="849" spans="1:9">
@@ -27187,7 +27226,7 @@
         <v>4</v>
       </c>
       <c r="I849" s="42" t="s">
-        <v>1333</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="850" spans="1:9">
@@ -27205,14 +27244,14 @@
       </c>
       <c r="E850" s="42"/>
       <c r="F850" s="42" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="G850" s="52"/>
       <c r="H850" s="42">
         <v>2</v>
       </c>
       <c r="I850" s="42" t="s">
-        <v>1335</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="851" spans="1:9">
@@ -27230,14 +27269,14 @@
       </c>
       <c r="E851" s="42"/>
       <c r="F851" s="42" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="G851" s="52"/>
       <c r="H851" s="42">
         <v>2</v>
       </c>
       <c r="I851" s="42" t="s">
-        <v>1336</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="852" spans="1:9">
@@ -27255,14 +27294,14 @@
       </c>
       <c r="E852" s="42"/>
       <c r="F852" s="42" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="G852" s="52"/>
       <c r="H852" s="42">
         <v>2</v>
       </c>
       <c r="I852" s="42" t="s">
-        <v>1337</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="853" spans="1:9">
@@ -27280,14 +27319,14 @@
       </c>
       <c r="E853" s="42"/>
       <c r="F853" s="42" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="G853" s="52"/>
       <c r="H853" s="42">
         <v>2</v>
       </c>
       <c r="I853" s="42" t="s">
-        <v>1338</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="854" spans="1:9">
@@ -27305,14 +27344,14 @@
       </c>
       <c r="E854" s="42"/>
       <c r="F854" s="42" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="G854" s="52"/>
       <c r="H854" s="42">
         <v>2</v>
       </c>
       <c r="I854" s="42" t="s">
-        <v>1339</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="855" spans="1:9">
@@ -27330,14 +27369,14 @@
       </c>
       <c r="E855" s="42"/>
       <c r="F855" s="42" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="G855" s="52"/>
       <c r="H855" s="42">
         <v>2</v>
       </c>
       <c r="I855" s="42" t="s">
-        <v>1340</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="856" spans="1:9">
@@ -27355,14 +27394,14 @@
       </c>
       <c r="E856" s="42"/>
       <c r="F856" s="42" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="G856" s="52"/>
       <c r="H856" s="42">
         <v>2</v>
       </c>
       <c r="I856" s="42" t="s">
-        <v>1341</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="857" spans="1:9">
@@ -27380,14 +27419,14 @@
       </c>
       <c r="E857" s="42"/>
       <c r="F857" s="42" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="G857" s="52"/>
       <c r="H857" s="42">
         <v>2</v>
       </c>
       <c r="I857" s="42" t="s">
-        <v>1342</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="858" spans="1:9">
@@ -27405,14 +27444,14 @@
       </c>
       <c r="E858" s="42"/>
       <c r="F858" s="42" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="G858" s="52"/>
       <c r="H858" s="42">
         <v>2</v>
       </c>
       <c r="I858" s="42" t="s">
-        <v>1343</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="859" spans="1:9">
@@ -27430,14 +27469,14 @@
       </c>
       <c r="E859" s="42"/>
       <c r="F859" s="42" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="G859" s="52"/>
       <c r="H859" s="42">
         <v>2</v>
       </c>
       <c r="I859" s="42" t="s">
-        <v>1344</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="860" spans="1:9">
@@ -27455,14 +27494,14 @@
       </c>
       <c r="E860" s="42"/>
       <c r="F860" s="42" t="s">
-        <v>1334</v>
+        <v>1347</v>
       </c>
       <c r="G860" s="52"/>
       <c r="H860" s="42">
         <v>2</v>
       </c>
       <c r="I860" s="42" t="s">
-        <v>1345</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="861" spans="1:9">
@@ -27480,14 +27519,14 @@
       </c>
       <c r="E861" s="42"/>
       <c r="F861" s="42" t="s">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="G861" s="52"/>
       <c r="H861" s="42">
         <v>3</v>
       </c>
       <c r="I861" s="42" t="s">
-        <v>1347</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="862" spans="1:9">
@@ -27505,14 +27544,14 @@
       </c>
       <c r="E862" s="42"/>
       <c r="F862" s="42" t="s">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="G862" s="52"/>
       <c r="H862" s="42">
         <v>3</v>
       </c>
       <c r="I862" s="42" t="s">
-        <v>1348</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="863" spans="1:9">
@@ -27530,14 +27569,14 @@
       </c>
       <c r="E863" s="42"/>
       <c r="F863" s="42" t="s">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="G863" s="52"/>
       <c r="H863" s="42">
         <v>3</v>
       </c>
       <c r="I863" s="42" t="s">
-        <v>1349</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="864" spans="1:9">
@@ -27555,14 +27594,14 @@
       </c>
       <c r="E864" s="42"/>
       <c r="F864" s="42" t="s">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="G864" s="52"/>
       <c r="H864" s="42">
         <v>3</v>
       </c>
       <c r="I864" s="42" t="s">
-        <v>1350</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="865" spans="1:9">
@@ -27580,14 +27619,14 @@
       </c>
       <c r="E865" s="42"/>
       <c r="F865" s="42" t="s">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="G865" s="52"/>
       <c r="H865" s="42">
         <v>3</v>
       </c>
       <c r="I865" s="42" t="s">
-        <v>1351</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="866" spans="1:9">
@@ -27605,14 +27644,14 @@
       </c>
       <c r="E866" s="42"/>
       <c r="F866" s="42" t="s">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="G866" s="52"/>
       <c r="H866" s="42">
         <v>3</v>
       </c>
       <c r="I866" s="42" t="s">
-        <v>1352</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="867" spans="1:9">
@@ -27630,14 +27669,14 @@
       </c>
       <c r="E867" s="42"/>
       <c r="F867" s="42" t="s">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="G867" s="52"/>
       <c r="H867" s="42">
         <v>3</v>
       </c>
       <c r="I867" s="42" t="s">
-        <v>1353</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="868" spans="1:9">
@@ -27655,14 +27694,14 @@
       </c>
       <c r="E868" s="42"/>
       <c r="F868" s="42" t="s">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="G868" s="52"/>
       <c r="H868" s="42">
         <v>3</v>
       </c>
       <c r="I868" s="42" t="s">
-        <v>1354</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="869" spans="1:9">
@@ -27680,14 +27719,14 @@
       </c>
       <c r="E869" s="42"/>
       <c r="F869" s="42" t="s">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="G869" s="52"/>
       <c r="H869" s="42">
         <v>3</v>
       </c>
       <c r="I869" s="42" t="s">
-        <v>1355</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="870" spans="1:9">
@@ -27705,14 +27744,14 @@
       </c>
       <c r="E870" s="42"/>
       <c r="F870" s="42" t="s">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="G870" s="52"/>
       <c r="H870" s="42">
         <v>3</v>
       </c>
       <c r="I870" s="42" t="s">
-        <v>1356</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="871" spans="1:9">
@@ -27730,14 +27769,14 @@
       </c>
       <c r="E871" s="42"/>
       <c r="F871" s="42" t="s">
-        <v>1346</v>
+        <v>1359</v>
       </c>
       <c r="G871" s="52"/>
       <c r="H871" s="42">
         <v>3</v>
       </c>
       <c r="I871" s="42" t="s">
-        <v>1357</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="872" spans="1:9">
@@ -27755,14 +27794,14 @@
       </c>
       <c r="E872" s="42"/>
       <c r="F872" s="42" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="G872" s="52"/>
       <c r="H872" s="42">
         <v>4</v>
       </c>
       <c r="I872" s="42" t="s">
-        <v>1359</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="873" spans="1:9">
@@ -27780,14 +27819,14 @@
       </c>
       <c r="E873" s="42"/>
       <c r="F873" s="42" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="G873" s="52"/>
       <c r="H873" s="42">
         <v>4</v>
       </c>
       <c r="I873" s="42" t="s">
-        <v>1360</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="874" spans="1:9">
@@ -27805,14 +27844,14 @@
       </c>
       <c r="E874" s="42"/>
       <c r="F874" s="42" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="G874" s="52"/>
       <c r="H874" s="42">
         <v>4</v>
       </c>
       <c r="I874" s="42" t="s">
-        <v>1361</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="875" spans="1:9">
@@ -27830,14 +27869,14 @@
       </c>
       <c r="E875" s="42"/>
       <c r="F875" s="42" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="G875" s="52"/>
       <c r="H875" s="42">
         <v>4</v>
       </c>
       <c r="I875" s="42" t="s">
-        <v>1362</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="876" spans="1:9">
@@ -27855,14 +27894,14 @@
       </c>
       <c r="E876" s="42"/>
       <c r="F876" s="42" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="G876" s="52"/>
       <c r="H876" s="42">
         <v>4</v>
       </c>
       <c r="I876" s="42" t="s">
-        <v>1363</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="877" spans="1:9">
@@ -27880,14 +27919,14 @@
       </c>
       <c r="E877" s="42"/>
       <c r="F877" s="42" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="G877" s="52"/>
       <c r="H877" s="42">
         <v>4</v>
       </c>
       <c r="I877" s="42" t="s">
-        <v>1364</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="878" spans="1:9">
@@ -27905,14 +27944,14 @@
       </c>
       <c r="E878" s="42"/>
       <c r="F878" s="42" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="G878" s="52"/>
       <c r="H878" s="42">
         <v>4</v>
       </c>
       <c r="I878" s="42" t="s">
-        <v>1365</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="879" spans="1:9">
@@ -27930,14 +27969,14 @@
       </c>
       <c r="E879" s="42"/>
       <c r="F879" s="42" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="G879" s="52"/>
       <c r="H879" s="42">
         <v>4</v>
       </c>
       <c r="I879" s="42" t="s">
-        <v>1366</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="880" spans="1:9">
@@ -27955,14 +27994,14 @@
       </c>
       <c r="E880" s="42"/>
       <c r="F880" s="42" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="G880" s="52"/>
       <c r="H880" s="42">
         <v>4</v>
       </c>
       <c r="I880" s="42" t="s">
-        <v>1367</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="881" spans="1:9">
@@ -27980,14 +28019,14 @@
       </c>
       <c r="E881" s="42"/>
       <c r="F881" s="42" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="G881" s="52"/>
       <c r="H881" s="42">
         <v>4</v>
       </c>
       <c r="I881" s="42" t="s">
-        <v>1368</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="882" spans="1:9">
@@ -28005,14 +28044,14 @@
       </c>
       <c r="E882" s="42"/>
       <c r="F882" s="42" t="s">
-        <v>1358</v>
+        <v>1371</v>
       </c>
       <c r="G882" s="52"/>
       <c r="H882" s="42">
         <v>4</v>
       </c>
       <c r="I882" s="42" t="s">
-        <v>1369</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="883" spans="1:9">
@@ -28030,14 +28069,14 @@
       </c>
       <c r="E883" s="42"/>
       <c r="F883" s="42" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="G883" s="52"/>
       <c r="H883" s="42">
         <v>2</v>
       </c>
       <c r="I883" s="42" t="s">
-        <v>1371</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="884" spans="1:9">
@@ -28055,14 +28094,14 @@
       </c>
       <c r="E884" s="42"/>
       <c r="F884" s="42" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="G884" s="52"/>
       <c r="H884" s="42">
         <v>2</v>
       </c>
       <c r="I884" s="42" t="s">
-        <v>1372</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="885" spans="1:9">
@@ -28080,14 +28119,14 @@
       </c>
       <c r="E885" s="42"/>
       <c r="F885" s="42" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="G885" s="52"/>
       <c r="H885" s="42">
         <v>2</v>
       </c>
       <c r="I885" s="42" t="s">
-        <v>1373</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="886" spans="1:9">
@@ -28105,14 +28144,14 @@
       </c>
       <c r="E886" s="42"/>
       <c r="F886" s="42" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="G886" s="52"/>
       <c r="H886" s="42">
         <v>2</v>
       </c>
       <c r="I886" s="42" t="s">
-        <v>1374</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="887" spans="1:9">
@@ -28130,14 +28169,14 @@
       </c>
       <c r="E887" s="42"/>
       <c r="F887" s="42" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="G887" s="52"/>
       <c r="H887" s="42">
         <v>2</v>
       </c>
       <c r="I887" s="42" t="s">
-        <v>1375</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="888" spans="1:9">
@@ -28155,14 +28194,14 @@
       </c>
       <c r="E888" s="42"/>
       <c r="F888" s="42" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="G888" s="52"/>
       <c r="H888" s="42">
         <v>2</v>
       </c>
       <c r="I888" s="42" t="s">
-        <v>1376</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="889" spans="1:9">
@@ -28180,14 +28219,14 @@
       </c>
       <c r="E889" s="42"/>
       <c r="F889" s="42" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="G889" s="52"/>
       <c r="H889" s="42">
         <v>2</v>
       </c>
       <c r="I889" s="42" t="s">
-        <v>1377</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="890" spans="1:9">
@@ -28205,14 +28244,14 @@
       </c>
       <c r="E890" s="42"/>
       <c r="F890" s="42" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="G890" s="52"/>
       <c r="H890" s="42">
         <v>2</v>
       </c>
       <c r="I890" s="42" t="s">
-        <v>1378</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="891" spans="1:9">
@@ -28230,14 +28269,14 @@
       </c>
       <c r="E891" s="42"/>
       <c r="F891" s="42" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="G891" s="52"/>
       <c r="H891" s="42">
         <v>2</v>
       </c>
       <c r="I891" s="42" t="s">
-        <v>1379</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="892" spans="1:9">
@@ -28255,14 +28294,14 @@
       </c>
       <c r="E892" s="42"/>
       <c r="F892" s="42" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="G892" s="52"/>
       <c r="H892" s="42">
         <v>2</v>
       </c>
       <c r="I892" s="42" t="s">
-        <v>1380</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="893" spans="1:9">
@@ -28280,14 +28319,14 @@
       </c>
       <c r="E893" s="42"/>
       <c r="F893" s="42" t="s">
-        <v>1370</v>
+        <v>1383</v>
       </c>
       <c r="G893" s="52"/>
       <c r="H893" s="42">
         <v>2</v>
       </c>
       <c r="I893" s="42" t="s">
-        <v>1381</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="894" spans="1:9">
@@ -28305,14 +28344,14 @@
       </c>
       <c r="E894" s="42"/>
       <c r="F894" s="42" t="s">
-        <v>1382</v>
+        <v>1395</v>
       </c>
       <c r="G894" s="52"/>
       <c r="H894" s="42">
         <v>3</v>
       </c>
       <c r="I894" s="42" t="s">
-        <v>1383</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="895" spans="1:9">
@@ -28330,14 +28369,14 @@
       </c>
       <c r="E895" s="42"/>
       <c r="F895" s="42" t="s">
-        <v>1382</v>
+        <v>1395</v>
       </c>
       <c r="G895" s="52"/>
       <c r="H895" s="42">
         <v>3</v>
       </c>
       <c r="I895" s="42" t="s">
-        <v>1384</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="896" spans="1:9">
@@ -28355,14 +28394,14 @@
       </c>
       <c r="E896" s="42"/>
       <c r="F896" s="42" t="s">
-        <v>1382</v>
+        <v>1395</v>
       </c>
       <c r="G896" s="52"/>
       <c r="H896" s="42">
         <v>3</v>
       </c>
       <c r="I896" s="42" t="s">
-        <v>1385</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="897" spans="1:9">
@@ -28380,14 +28419,14 @@
       </c>
       <c r="E897" s="42"/>
       <c r="F897" s="42" t="s">
-        <v>1382</v>
+        <v>1395</v>
       </c>
       <c r="G897" s="52"/>
       <c r="H897" s="42">
         <v>3</v>
       </c>
       <c r="I897" s="42" t="s">
-        <v>1386</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="898" spans="1:9">
@@ -28405,14 +28444,14 @@
       </c>
       <c r="E898" s="42"/>
       <c r="F898" s="42" t="s">
-        <v>1382</v>
+        <v>1395</v>
       </c>
       <c r="G898" s="52"/>
       <c r="H898" s="42">
         <v>3</v>
       </c>
       <c r="I898" s="42" t="s">
-        <v>1387</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="899" spans="1:9">
@@ -28430,14 +28469,14 @@
       </c>
       <c r="E899" s="42"/>
       <c r="F899" s="42" t="s">
-        <v>1382</v>
+        <v>1395</v>
       </c>
       <c r="G899" s="52"/>
       <c r="H899" s="42">
         <v>3</v>
       </c>
       <c r="I899" s="42" t="s">
-        <v>1388</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="900" spans="1:9">
@@ -28455,14 +28494,14 @@
       </c>
       <c r="E900" s="42"/>
       <c r="F900" s="42" t="s">
-        <v>1382</v>
+        <v>1395</v>
       </c>
       <c r="G900" s="52"/>
       <c r="H900" s="42">
         <v>3</v>
       </c>
       <c r="I900" s="42" t="s">
-        <v>1389</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="901" spans="1:9">
@@ -28480,14 +28519,14 @@
       </c>
       <c r="E901" s="42"/>
       <c r="F901" s="42" t="s">
-        <v>1382</v>
+        <v>1395</v>
       </c>
       <c r="G901" s="52"/>
       <c r="H901" s="42">
         <v>3</v>
       </c>
       <c r="I901" s="42" t="s">
-        <v>1390</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="902" spans="1:9">
@@ -28505,14 +28544,14 @@
       </c>
       <c r="E902" s="42"/>
       <c r="F902" s="42" t="s">
-        <v>1382</v>
+        <v>1395</v>
       </c>
       <c r="G902" s="52"/>
       <c r="H902" s="42">
         <v>3</v>
       </c>
       <c r="I902" s="42" t="s">
-        <v>1391</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="903" spans="1:9">
@@ -28530,14 +28569,14 @@
       </c>
       <c r="E903" s="42"/>
       <c r="F903" s="42" t="s">
-        <v>1382</v>
+        <v>1395</v>
       </c>
       <c r="G903" s="52"/>
       <c r="H903" s="42">
         <v>3</v>
       </c>
       <c r="I903" s="42" t="s">
-        <v>1392</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="904" spans="1:9">
@@ -28555,14 +28594,14 @@
       </c>
       <c r="E904" s="42"/>
       <c r="F904" s="42" t="s">
-        <v>1382</v>
+        <v>1395</v>
       </c>
       <c r="G904" s="52"/>
       <c r="H904" s="42">
         <v>3</v>
       </c>
       <c r="I904" s="42" t="s">
-        <v>1393</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="905" spans="1:9">
@@ -28580,14 +28619,14 @@
       </c>
       <c r="E905" s="42"/>
       <c r="F905" s="42" t="s">
-        <v>1394</v>
+        <v>1407</v>
       </c>
       <c r="G905" s="52"/>
       <c r="H905" s="42">
         <v>4</v>
       </c>
       <c r="I905" s="42" t="s">
-        <v>1395</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="906" spans="1:9">
@@ -28605,14 +28644,14 @@
       </c>
       <c r="E906" s="42"/>
       <c r="F906" s="42" t="s">
-        <v>1394</v>
+        <v>1407</v>
       </c>
       <c r="G906" s="52"/>
       <c r="H906" s="42">
         <v>4</v>
       </c>
       <c r="I906" s="42" t="s">
-        <v>1396</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="907" spans="1:9">
@@ -28630,14 +28669,14 @@
       </c>
       <c r="E907" s="42"/>
       <c r="F907" s="42" t="s">
-        <v>1394</v>
+        <v>1407</v>
       </c>
       <c r="G907" s="52"/>
       <c r="H907" s="42">
         <v>4</v>
       </c>
       <c r="I907" s="42" t="s">
-        <v>1397</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="908" spans="1:9">
@@ -28655,14 +28694,14 @@
       </c>
       <c r="E908" s="42"/>
       <c r="F908" s="42" t="s">
-        <v>1394</v>
+        <v>1407</v>
       </c>
       <c r="G908" s="52"/>
       <c r="H908" s="42">
         <v>4</v>
       </c>
       <c r="I908" s="42" t="s">
-        <v>1398</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="909" spans="1:9">
@@ -28680,14 +28719,14 @@
       </c>
       <c r="E909" s="42"/>
       <c r="F909" s="42" t="s">
-        <v>1394</v>
+        <v>1407</v>
       </c>
       <c r="G909" s="52"/>
       <c r="H909" s="42">
         <v>4</v>
       </c>
       <c r="I909" s="42" t="s">
-        <v>1399</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="910" spans="1:9">
@@ -28705,14 +28744,14 @@
       </c>
       <c r="E910" s="42"/>
       <c r="F910" s="42" t="s">
-        <v>1394</v>
+        <v>1407</v>
       </c>
       <c r="G910" s="52"/>
       <c r="H910" s="42">
         <v>4</v>
       </c>
       <c r="I910" s="42" t="s">
-        <v>1400</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="911" spans="1:9">
@@ -28730,14 +28769,14 @@
       </c>
       <c r="E911" s="42"/>
       <c r="F911" s="42" t="s">
-        <v>1394</v>
+        <v>1407</v>
       </c>
       <c r="G911" s="52"/>
       <c r="H911" s="42">
         <v>4</v>
       </c>
       <c r="I911" s="42" t="s">
-        <v>1401</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="912" spans="1:9">
@@ -28755,14 +28794,14 @@
       </c>
       <c r="E912" s="42"/>
       <c r="F912" s="42" t="s">
-        <v>1394</v>
+        <v>1407</v>
       </c>
       <c r="G912" s="52"/>
       <c r="H912" s="42">
         <v>4</v>
       </c>
       <c r="I912" s="42" t="s">
-        <v>1402</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="913" spans="1:9">
@@ -28780,14 +28819,14 @@
       </c>
       <c r="E913" s="42"/>
       <c r="F913" s="42" t="s">
-        <v>1394</v>
+        <v>1407</v>
       </c>
       <c r="G913" s="52"/>
       <c r="H913" s="42">
         <v>4</v>
       </c>
       <c r="I913" s="42" t="s">
-        <v>1403</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="914" spans="1:9">
@@ -28805,14 +28844,14 @@
       </c>
       <c r="E914" s="42"/>
       <c r="F914" s="42" t="s">
-        <v>1394</v>
+        <v>1407</v>
       </c>
       <c r="G914" s="52"/>
       <c r="H914" s="42">
         <v>4</v>
       </c>
       <c r="I914" s="42" t="s">
-        <v>1404</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="915" spans="1:9">
@@ -28830,14 +28869,14 @@
       </c>
       <c r="E915" s="42"/>
       <c r="F915" s="42" t="s">
-        <v>1394</v>
+        <v>1407</v>
       </c>
       <c r="G915" s="52"/>
       <c r="H915" s="42">
         <v>4</v>
       </c>
       <c r="I915" s="42" t="s">
-        <v>1405</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="916" spans="1:9">
@@ -28858,7 +28897,7 @@
       <c r="G916" s="54"/>
       <c r="H916" s="54"/>
       <c r="I916" s="55" t="s">
-        <v>1406</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="917" spans="1:9">
@@ -28879,7 +28918,7 @@
       <c r="G917" s="54"/>
       <c r="H917" s="54"/>
       <c r="I917" s="55" t="s">
-        <v>1407</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="918" spans="1:9">
@@ -28900,7 +28939,7 @@
       <c r="G918" s="54"/>
       <c r="H918" s="54"/>
       <c r="I918" s="55" t="s">
-        <v>1408</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="919" spans="1:9">
@@ -28921,7 +28960,7 @@
       <c r="G919" s="54"/>
       <c r="H919" s="54"/>
       <c r="I919" s="55" t="s">
-        <v>1409</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="920" spans="1:9">
@@ -28942,7 +28981,7 @@
       <c r="G920" s="54"/>
       <c r="H920" s="54"/>
       <c r="I920" s="55" t="s">
-        <v>1410</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="921" spans="1:9">
@@ -28963,7 +29002,7 @@
       <c r="G921" s="54"/>
       <c r="H921" s="54"/>
       <c r="I921" s="55" t="s">
-        <v>1411</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="922" spans="1:9">
@@ -28984,7 +29023,7 @@
       <c r="G922" s="54"/>
       <c r="H922" s="54"/>
       <c r="I922" s="55" t="s">
-        <v>1412</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="923" spans="1:9">
@@ -29005,7 +29044,7 @@
       <c r="G923" s="54"/>
       <c r="H923" s="54"/>
       <c r="I923" s="55" t="s">
-        <v>1413</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="924" spans="1:9">
@@ -29026,7 +29065,7 @@
       <c r="G924" s="54"/>
       <c r="H924" s="54"/>
       <c r="I924" s="55" t="s">
-        <v>1414</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="925" spans="1:9">
@@ -29047,7 +29086,7 @@
       <c r="G925" s="54"/>
       <c r="H925" s="54"/>
       <c r="I925" s="55" t="s">
-        <v>1415</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="926" spans="1:9">
@@ -29068,7 +29107,7 @@
       <c r="G926" s="54"/>
       <c r="H926" s="54"/>
       <c r="I926" s="55" t="s">
-        <v>1416</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="927" spans="1:9">
@@ -29089,7 +29128,7 @@
       <c r="G927" s="54"/>
       <c r="H927" s="54"/>
       <c r="I927" s="55" t="s">
-        <v>1417</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="928" spans="1:9">
@@ -29110,7 +29149,7 @@
       <c r="G928" s="54"/>
       <c r="H928" s="54"/>
       <c r="I928" s="55" t="s">
-        <v>1418</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="929" spans="1:10">
@@ -29131,7 +29170,7 @@
       <c r="G929" s="54"/>
       <c r="H929" s="54"/>
       <c r="I929" s="55" t="s">
-        <v>1419</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="930" spans="1:10">
@@ -29152,7 +29191,7 @@
       <c r="G930" s="54"/>
       <c r="H930" s="54"/>
       <c r="I930" s="55" t="s">
-        <v>1420</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="931" spans="1:10">
@@ -29173,7 +29212,7 @@
       <c r="G931" s="54"/>
       <c r="H931" s="54"/>
       <c r="I931" s="55" t="s">
-        <v>1421</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="932" spans="1:10">
@@ -29194,7 +29233,7 @@
       <c r="G932" s="54"/>
       <c r="H932" s="54"/>
       <c r="I932" s="55" t="s">
-        <v>1422</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="933" spans="1:10">
@@ -29215,7 +29254,7 @@
       <c r="G933" s="54"/>
       <c r="H933" s="54"/>
       <c r="I933" s="55" t="s">
-        <v>1423</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="934" spans="1:10">
@@ -29236,7 +29275,7 @@
       <c r="G934" s="54"/>
       <c r="H934" s="54"/>
       <c r="I934" s="55" t="s">
-        <v>1424</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="935" spans="1:10">
@@ -29257,7 +29296,7 @@
       <c r="G935" s="54"/>
       <c r="H935" s="54"/>
       <c r="I935" s="55" t="s">
-        <v>1425</v>
+        <v>1438</v>
       </c>
       <c r="J935" t="s">
         <v>226</v>
@@ -29281,7 +29320,7 @@
       <c r="G936" s="54"/>
       <c r="H936" s="54"/>
       <c r="I936" s="55" t="s">
-        <v>1426</v>
+        <v>1439</v>
       </c>
       <c r="J936" t="s">
         <v>228</v>
@@ -29305,7 +29344,7 @@
       <c r="G937" s="54"/>
       <c r="H937" s="54"/>
       <c r="I937" s="55" t="s">
-        <v>1427</v>
+        <v>1440</v>
       </c>
       <c r="J937" t="s">
         <v>230</v>
@@ -29329,7 +29368,7 @@
       <c r="G938" s="54"/>
       <c r="H938" s="54"/>
       <c r="I938" s="55" t="s">
-        <v>1428</v>
+        <v>1441</v>
       </c>
       <c r="J938" t="s">
         <v>232</v>
@@ -29448,7 +29487,7 @@
       <c r="G944" s="49"/>
       <c r="H944" s="49"/>
       <c r="I944" s="49" t="s">
-        <v>1429</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="945" spans="1:9">
@@ -29467,7 +29506,7 @@
       <c r="G945" s="49"/>
       <c r="H945" s="49"/>
       <c r="I945" s="49" t="s">
-        <v>1430</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="946" spans="1:9">
@@ -29486,7 +29525,7 @@
       <c r="G946" s="49"/>
       <c r="H946" s="49"/>
       <c r="I946" s="49" t="s">
-        <v>1431</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="947" spans="1:9">
@@ -29505,7 +29544,7 @@
       <c r="G947" s="49"/>
       <c r="H947" s="49"/>
       <c r="I947" s="49" t="s">
-        <v>1432</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="948" spans="1:9">
@@ -29524,7 +29563,7 @@
       <c r="G948" s="49"/>
       <c r="H948" s="49"/>
       <c r="I948" s="49" t="s">
-        <v>1433</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="949" spans="1:9">
@@ -29581,7 +29620,7 @@
       <c r="G951" s="49"/>
       <c r="H951" s="49"/>
       <c r="I951" s="49" t="s">
-        <v>1425</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="952" spans="1:9">
@@ -29600,7 +29639,7 @@
       <c r="G952" s="49"/>
       <c r="H952" s="49"/>
       <c r="I952" s="49" t="s">
-        <v>1426</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="953" spans="1:9">
@@ -29619,7 +29658,7 @@
       <c r="G953" s="49"/>
       <c r="H953" s="49"/>
       <c r="I953" s="49" t="s">
-        <v>1427</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="954" spans="1:9">
@@ -29638,7 +29677,7 @@
       <c r="G954" s="49"/>
       <c r="H954" s="49"/>
       <c r="I954" s="49" t="s">
-        <v>1428</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="955" spans="1:9">
@@ -29659,7 +29698,7 @@
         <v>2</v>
       </c>
       <c r="I955" s="56" t="s">
-        <v>1292</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="956" spans="1:9">
@@ -29680,7 +29719,7 @@
         <v>2</v>
       </c>
       <c r="I956" s="49" t="s">
-        <v>1293</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="957" spans="1:9">
@@ -29701,7 +29740,7 @@
         <v>2</v>
       </c>
       <c r="I957" s="49" t="s">
-        <v>1294</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="958" spans="1:9">
@@ -29722,7 +29761,7 @@
         <v>2</v>
       </c>
       <c r="I958" s="49" t="s">
-        <v>1295</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="959" spans="1:9">
@@ -29743,7 +29782,7 @@
         <v>2</v>
       </c>
       <c r="I959" s="49" t="s">
-        <v>1296</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="960" spans="1:9">
@@ -29764,7 +29803,7 @@
         <v>2</v>
       </c>
       <c r="I960" s="49" t="s">
-        <v>1434</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="961" spans="1:9">
@@ -29785,7 +29824,7 @@
         <v>2</v>
       </c>
       <c r="I961" s="49" t="s">
-        <v>1435</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="962" spans="1:9">
@@ -29806,7 +29845,7 @@
         <v>2</v>
       </c>
       <c r="I962" s="49" t="s">
-        <v>1436</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="963" spans="1:9">
@@ -29827,7 +29866,7 @@
         <v>2</v>
       </c>
       <c r="I963" s="49" t="s">
-        <v>1437</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="964" spans="1:9">
@@ -29848,7 +29887,7 @@
         <v>2</v>
       </c>
       <c r="I964" s="49" t="s">
-        <v>1438</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="965" spans="1:9">
@@ -29869,7 +29908,7 @@
         <v>2</v>
       </c>
       <c r="I965" s="49" t="s">
-        <v>1439</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="966" spans="1:9">
@@ -29890,7 +29929,7 @@
         <v>3</v>
       </c>
       <c r="I966" s="56" t="s">
-        <v>1306</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="967" spans="1:9">
@@ -29911,7 +29950,7 @@
         <v>3</v>
       </c>
       <c r="I967" s="49" t="s">
-        <v>1307</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="968" spans="1:9">
@@ -29932,7 +29971,7 @@
         <v>3</v>
       </c>
       <c r="I968" s="49" t="s">
-        <v>1308</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="969" spans="1:9">
@@ -29953,7 +29992,7 @@
         <v>3</v>
       </c>
       <c r="I969" s="49" t="s">
-        <v>1309</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="970" spans="1:9">
@@ -29974,7 +30013,7 @@
         <v>3</v>
       </c>
       <c r="I970" s="49" t="s">
-        <v>1310</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="971" spans="1:9">
@@ -29995,7 +30034,7 @@
         <v>3</v>
       </c>
       <c r="I971" s="49" t="s">
-        <v>1440</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="972" spans="1:9">
@@ -30016,7 +30055,7 @@
         <v>3</v>
       </c>
       <c r="I972" s="49" t="s">
-        <v>1441</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="973" spans="1:9">
@@ -30037,7 +30076,7 @@
         <v>3</v>
       </c>
       <c r="I973" s="49" t="s">
-        <v>1442</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="974" spans="1:9">
@@ -30058,7 +30097,7 @@
         <v>3</v>
       </c>
       <c r="I974" s="49" t="s">
-        <v>1443</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="975" spans="1:9">
@@ -30079,7 +30118,7 @@
         <v>3</v>
       </c>
       <c r="I975" s="49" t="s">
-        <v>1444</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="976" spans="1:9">
@@ -30100,7 +30139,7 @@
         <v>3</v>
       </c>
       <c r="I976" s="49" t="s">
-        <v>1445</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="977" spans="1:9">
@@ -30121,7 +30160,7 @@
         <v>4</v>
       </c>
       <c r="I977" s="56" t="s">
-        <v>1320</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="978" spans="1:9">
@@ -30142,7 +30181,7 @@
         <v>4</v>
       </c>
       <c r="I978" s="49" t="s">
-        <v>1321</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="979" spans="1:9">
@@ -30163,7 +30202,7 @@
         <v>4</v>
       </c>
       <c r="I979" s="49" t="s">
-        <v>1322</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="980" spans="1:9">
@@ -30184,7 +30223,7 @@
         <v>4</v>
       </c>
       <c r="I980" s="49" t="s">
-        <v>1323</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="981" spans="1:9">
@@ -30205,7 +30244,7 @@
         <v>4</v>
       </c>
       <c r="I981" s="49" t="s">
-        <v>1324</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="982" spans="1:9">
@@ -30226,7 +30265,7 @@
         <v>4</v>
       </c>
       <c r="I982" s="49" t="s">
-        <v>1446</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="983" spans="1:9">
@@ -30247,7 +30286,7 @@
         <v>4</v>
       </c>
       <c r="I983" s="49" t="s">
-        <v>1447</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="984" spans="1:9">
@@ -30268,7 +30307,7 @@
         <v>4</v>
       </c>
       <c r="I984" s="49" t="s">
-        <v>1448</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="985" spans="1:9">
@@ -30289,7 +30328,7 @@
         <v>4</v>
       </c>
       <c r="I985" s="49" t="s">
-        <v>1449</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="986" spans="1:9">
@@ -30310,7 +30349,7 @@
         <v>4</v>
       </c>
       <c r="I986" s="49" t="s">
-        <v>1450</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="987" spans="1:9">
@@ -30331,7 +30370,7 @@
         <v>4</v>
       </c>
       <c r="I987" s="49" t="s">
-        <v>1451</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="988" spans="1:9">
@@ -30347,12 +30386,12 @@
       <c r="D988" s="49"/>
       <c r="E988" s="49"/>
       <c r="F988" s="49" t="s">
-        <v>1452</v>
+        <v>1465</v>
       </c>
       <c r="G988" s="49"/>
       <c r="H988" s="49"/>
       <c r="I988" s="49" t="s">
-        <v>1453</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="989" spans="1:9">
@@ -30368,12 +30407,12 @@
       <c r="D989" s="49"/>
       <c r="E989" s="49"/>
       <c r="F989" s="49" t="s">
-        <v>1452</v>
+        <v>1465</v>
       </c>
       <c r="G989" s="49"/>
       <c r="H989" s="49"/>
       <c r="I989" s="49" t="s">
-        <v>1454</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="990" spans="1:9">
@@ -30389,12 +30428,12 @@
       <c r="D990" s="49"/>
       <c r="E990" s="49"/>
       <c r="F990" s="49" t="s">
-        <v>1452</v>
+        <v>1465</v>
       </c>
       <c r="G990" s="49"/>
       <c r="H990" s="49"/>
       <c r="I990" s="49" t="s">
-        <v>1455</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="991" spans="1:9">
@@ -30410,12 +30449,12 @@
       <c r="D991" s="49"/>
       <c r="E991" s="49"/>
       <c r="F991" s="49" t="s">
-        <v>1452</v>
+        <v>1465</v>
       </c>
       <c r="G991" s="49"/>
       <c r="H991" s="49"/>
       <c r="I991" s="49" t="s">
-        <v>1456</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="992" spans="1:9">
@@ -30431,12 +30470,12 @@
       <c r="D992" s="49"/>
       <c r="E992" s="49"/>
       <c r="F992" s="49" t="s">
-        <v>1452</v>
+        <v>1465</v>
       </c>
       <c r="G992" s="49"/>
       <c r="H992" s="49"/>
       <c r="I992" s="49" t="s">
-        <v>1457</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="993" spans="1:9">
@@ -30452,12 +30491,12 @@
       <c r="D993" s="49"/>
       <c r="E993" s="49"/>
       <c r="F993" s="49" t="s">
-        <v>1452</v>
+        <v>1465</v>
       </c>
       <c r="G993" s="49"/>
       <c r="H993" s="49"/>
       <c r="I993" s="49" t="s">
-        <v>1458</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="994" spans="1:9">
@@ -30473,12 +30512,12 @@
       <c r="D994" s="49"/>
       <c r="E994" s="49"/>
       <c r="F994" s="49" t="s">
-        <v>1452</v>
+        <v>1465</v>
       </c>
       <c r="G994" s="49"/>
       <c r="H994" s="49"/>
       <c r="I994" s="49" t="s">
-        <v>1459</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="995" spans="1:9">
@@ -30494,12 +30533,12 @@
       <c r="D995" s="49"/>
       <c r="E995" s="49"/>
       <c r="F995" s="49" t="s">
-        <v>1452</v>
+        <v>1465</v>
       </c>
       <c r="G995" s="49"/>
       <c r="H995" s="49"/>
       <c r="I995" s="49" t="s">
-        <v>1460</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="996" spans="1:9">
@@ -30515,12 +30554,12 @@
       <c r="D996" s="49"/>
       <c r="E996" s="49"/>
       <c r="F996" s="49" t="s">
-        <v>1452</v>
+        <v>1465</v>
       </c>
       <c r="G996" s="49"/>
       <c r="H996" s="49"/>
       <c r="I996" s="49" t="s">
-        <v>1461</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="997" spans="1:9">
@@ -30536,12 +30575,12 @@
       <c r="D997" s="49"/>
       <c r="E997" s="49"/>
       <c r="F997" s="49" t="s">
-        <v>1452</v>
+        <v>1465</v>
       </c>
       <c r="G997" s="49"/>
       <c r="H997" s="49"/>
       <c r="I997" s="49" t="s">
-        <v>1462</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="998" spans="1:9">
@@ -30557,14 +30596,14 @@
       <c r="D998" s="49"/>
       <c r="E998" s="49"/>
       <c r="F998" s="49" t="s">
-        <v>1463</v>
+        <v>1476</v>
       </c>
       <c r="G998" s="49"/>
       <c r="H998" s="49">
         <v>2</v>
       </c>
       <c r="I998" s="49" t="s">
-        <v>1464</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="999" spans="1:9">
@@ -30580,14 +30619,14 @@
       <c r="D999" s="49"/>
       <c r="E999" s="49"/>
       <c r="F999" s="49" t="s">
-        <v>1463</v>
+        <v>1476</v>
       </c>
       <c r="G999" s="49"/>
       <c r="H999" s="49">
         <v>2</v>
       </c>
       <c r="I999" s="49" t="s">
-        <v>1465</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="1000" spans="1:9">
@@ -30603,14 +30642,14 @@
       <c r="D1000" s="49"/>
       <c r="E1000" s="49"/>
       <c r="F1000" s="49" t="s">
-        <v>1463</v>
+        <v>1476</v>
       </c>
       <c r="G1000" s="49"/>
       <c r="H1000" s="49">
         <v>2</v>
       </c>
       <c r="I1000" s="49" t="s">
-        <v>1466</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="1001" spans="1:9">
@@ -30626,14 +30665,14 @@
       <c r="D1001" s="49"/>
       <c r="E1001" s="49"/>
       <c r="F1001" s="49" t="s">
-        <v>1463</v>
+        <v>1476</v>
       </c>
       <c r="G1001" s="49"/>
       <c r="H1001" s="49">
         <v>2</v>
       </c>
       <c r="I1001" s="49" t="s">
-        <v>1467</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1002" spans="1:9">
@@ -30649,14 +30688,14 @@
       <c r="D1002" s="49"/>
       <c r="E1002" s="49"/>
       <c r="F1002" s="49" t="s">
-        <v>1463</v>
+        <v>1476</v>
       </c>
       <c r="G1002" s="49"/>
       <c r="H1002" s="49">
         <v>2</v>
       </c>
       <c r="I1002" s="49" t="s">
-        <v>1468</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="1003" spans="1:9">
@@ -30672,14 +30711,14 @@
       <c r="D1003" s="49"/>
       <c r="E1003" s="49"/>
       <c r="F1003" s="49" t="s">
-        <v>1463</v>
+        <v>1476</v>
       </c>
       <c r="G1003" s="49"/>
       <c r="H1003" s="49">
         <v>2</v>
       </c>
       <c r="I1003" s="49" t="s">
-        <v>1469</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="1004" spans="1:9">
@@ -30695,14 +30734,14 @@
       <c r="D1004" s="49"/>
       <c r="E1004" s="49"/>
       <c r="F1004" s="49" t="s">
-        <v>1463</v>
+        <v>1476</v>
       </c>
       <c r="G1004" s="49"/>
       <c r="H1004" s="49">
         <v>2</v>
       </c>
       <c r="I1004" s="49" t="s">
-        <v>1470</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="1005" spans="1:9">
@@ -30718,14 +30757,14 @@
       <c r="D1005" s="49"/>
       <c r="E1005" s="49"/>
       <c r="F1005" s="49" t="s">
-        <v>1463</v>
+        <v>1476</v>
       </c>
       <c r="G1005" s="49"/>
       <c r="H1005" s="49">
         <v>2</v>
       </c>
       <c r="I1005" s="49" t="s">
-        <v>1471</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="1006" spans="1:9">
@@ -30741,14 +30780,14 @@
       <c r="D1006" s="49"/>
       <c r="E1006" s="49"/>
       <c r="F1006" s="49" t="s">
-        <v>1463</v>
+        <v>1476</v>
       </c>
       <c r="G1006" s="49"/>
       <c r="H1006" s="49">
         <v>2</v>
       </c>
       <c r="I1006" s="49" t="s">
-        <v>1472</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="1007" spans="1:9">
@@ -30764,14 +30803,14 @@
       <c r="D1007" s="49"/>
       <c r="E1007" s="49"/>
       <c r="F1007" s="49" t="s">
-        <v>1463</v>
+        <v>1476</v>
       </c>
       <c r="G1007" s="49"/>
       <c r="H1007" s="49">
         <v>2</v>
       </c>
       <c r="I1007" s="49" t="s">
-        <v>1473</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="1008" spans="1:9">
@@ -30787,14 +30826,14 @@
       <c r="D1008" s="49"/>
       <c r="E1008" s="49"/>
       <c r="F1008" s="49" t="s">
-        <v>1474</v>
+        <v>1487</v>
       </c>
       <c r="G1008" s="49"/>
       <c r="H1008" s="49">
         <v>3</v>
       </c>
       <c r="I1008" s="49" t="s">
-        <v>1475</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1009" spans="1:9">
@@ -30810,14 +30849,14 @@
       <c r="D1009" s="49"/>
       <c r="E1009" s="49"/>
       <c r="F1009" s="49" t="s">
-        <v>1474</v>
+        <v>1487</v>
       </c>
       <c r="G1009" s="49"/>
       <c r="H1009" s="49">
         <v>3</v>
       </c>
       <c r="I1009" s="49" t="s">
-        <v>1476</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="1010" spans="1:9">
@@ -30833,14 +30872,14 @@
       <c r="D1010" s="49"/>
       <c r="E1010" s="49"/>
       <c r="F1010" s="49" t="s">
-        <v>1474</v>
+        <v>1487</v>
       </c>
       <c r="G1010" s="49"/>
       <c r="H1010" s="49">
         <v>3</v>
       </c>
       <c r="I1010" s="49" t="s">
-        <v>1477</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="1011" spans="1:9">
@@ -30856,14 +30895,14 @@
       <c r="D1011" s="49"/>
       <c r="E1011" s="49"/>
       <c r="F1011" s="49" t="s">
-        <v>1474</v>
+        <v>1487</v>
       </c>
       <c r="G1011" s="49"/>
       <c r="H1011" s="49">
         <v>3</v>
       </c>
       <c r="I1011" s="49" t="s">
-        <v>1478</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="1012" spans="1:9">
@@ -30879,14 +30918,14 @@
       <c r="D1012" s="49"/>
       <c r="E1012" s="49"/>
       <c r="F1012" s="49" t="s">
-        <v>1474</v>
+        <v>1487</v>
       </c>
       <c r="G1012" s="49"/>
       <c r="H1012" s="49">
         <v>3</v>
       </c>
       <c r="I1012" s="49" t="s">
-        <v>1479</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1013" spans="1:9">
@@ -30902,14 +30941,14 @@
       <c r="D1013" s="49"/>
       <c r="E1013" s="49"/>
       <c r="F1013" s="49" t="s">
-        <v>1474</v>
+        <v>1487</v>
       </c>
       <c r="G1013" s="49"/>
       <c r="H1013" s="49">
         <v>3</v>
       </c>
       <c r="I1013" s="49" t="s">
-        <v>1480</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="1014" spans="1:9">
@@ -30925,14 +30964,14 @@
       <c r="D1014" s="49"/>
       <c r="E1014" s="49"/>
       <c r="F1014" s="49" t="s">
-        <v>1474</v>
+        <v>1487</v>
       </c>
       <c r="G1014" s="49"/>
       <c r="H1014" s="49">
         <v>3</v>
       </c>
       <c r="I1014" s="49" t="s">
-        <v>1481</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="1015" spans="1:9">
@@ -30948,14 +30987,14 @@
       <c r="D1015" s="49"/>
       <c r="E1015" s="49"/>
       <c r="F1015" s="49" t="s">
-        <v>1474</v>
+        <v>1487</v>
       </c>
       <c r="G1015" s="49"/>
       <c r="H1015" s="49">
         <v>3</v>
       </c>
       <c r="I1015" s="49" t="s">
-        <v>1482</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="1016" spans="1:9">
@@ -30971,14 +31010,14 @@
       <c r="D1016" s="49"/>
       <c r="E1016" s="49"/>
       <c r="F1016" s="49" t="s">
-        <v>1474</v>
+        <v>1487</v>
       </c>
       <c r="G1016" s="49"/>
       <c r="H1016" s="49">
         <v>3</v>
       </c>
       <c r="I1016" s="49" t="s">
-        <v>1483</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="1017" spans="1:9">
@@ -30994,14 +31033,14 @@
       <c r="D1017" s="49"/>
       <c r="E1017" s="49"/>
       <c r="F1017" s="49" t="s">
-        <v>1474</v>
+        <v>1487</v>
       </c>
       <c r="G1017" s="49"/>
       <c r="H1017" s="49">
         <v>3</v>
       </c>
       <c r="I1017" s="49" t="s">
-        <v>1484</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="1018" spans="1:9">
@@ -31017,14 +31056,14 @@
       <c r="D1018" s="49"/>
       <c r="E1018" s="49"/>
       <c r="F1018" s="49" t="s">
-        <v>1485</v>
+        <v>1498</v>
       </c>
       <c r="G1018" s="49"/>
       <c r="H1018" s="49">
         <v>4</v>
       </c>
       <c r="I1018" s="49" t="s">
-        <v>1486</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="1019" spans="1:9">
@@ -31040,14 +31079,14 @@
       <c r="D1019" s="49"/>
       <c r="E1019" s="49"/>
       <c r="F1019" s="49" t="s">
-        <v>1485</v>
+        <v>1498</v>
       </c>
       <c r="G1019" s="49"/>
       <c r="H1019" s="49">
         <v>4</v>
       </c>
       <c r="I1019" s="49" t="s">
-        <v>1487</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1020" spans="1:9">
@@ -31063,14 +31102,14 @@
       <c r="D1020" s="49"/>
       <c r="E1020" s="49"/>
       <c r="F1020" s="49" t="s">
-        <v>1485</v>
+        <v>1498</v>
       </c>
       <c r="G1020" s="49"/>
       <c r="H1020" s="49">
         <v>4</v>
       </c>
       <c r="I1020" s="49" t="s">
-        <v>1488</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="1021" spans="1:9">
@@ -31086,14 +31125,14 @@
       <c r="D1021" s="49"/>
       <c r="E1021" s="49"/>
       <c r="F1021" s="49" t="s">
-        <v>1485</v>
+        <v>1498</v>
       </c>
       <c r="G1021" s="49"/>
       <c r="H1021" s="49">
         <v>4</v>
       </c>
       <c r="I1021" s="49" t="s">
-        <v>1489</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="1022" spans="1:9">
@@ -31109,14 +31148,14 @@
       <c r="D1022" s="49"/>
       <c r="E1022" s="49"/>
       <c r="F1022" s="49" t="s">
-        <v>1485</v>
+        <v>1498</v>
       </c>
       <c r="G1022" s="49"/>
       <c r="H1022" s="49">
         <v>4</v>
       </c>
       <c r="I1022" s="49" t="s">
-        <v>1490</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="1023" spans="1:9">
@@ -31132,14 +31171,14 @@
       <c r="D1023" s="49"/>
       <c r="E1023" s="49"/>
       <c r="F1023" s="49" t="s">
-        <v>1485</v>
+        <v>1498</v>
       </c>
       <c r="G1023" s="49"/>
       <c r="H1023" s="49">
         <v>4</v>
       </c>
       <c r="I1023" s="49" t="s">
-        <v>1491</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="1024" spans="1:9">
@@ -31155,14 +31194,14 @@
       <c r="D1024" s="49"/>
       <c r="E1024" s="49"/>
       <c r="F1024" s="49" t="s">
-        <v>1485</v>
+        <v>1498</v>
       </c>
       <c r="G1024" s="49"/>
       <c r="H1024" s="49">
         <v>4</v>
       </c>
       <c r="I1024" s="49" t="s">
-        <v>1492</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="1025" spans="1:9">
@@ -31178,14 +31217,14 @@
       <c r="D1025" s="49"/>
       <c r="E1025" s="49"/>
       <c r="F1025" s="49" t="s">
-        <v>1485</v>
+        <v>1498</v>
       </c>
       <c r="G1025" s="49"/>
       <c r="H1025" s="49">
         <v>4</v>
       </c>
       <c r="I1025" s="49" t="s">
-        <v>1493</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="1026" spans="1:9">
@@ -31201,14 +31240,14 @@
       <c r="D1026" s="49"/>
       <c r="E1026" s="49"/>
       <c r="F1026" s="49" t="s">
-        <v>1485</v>
+        <v>1498</v>
       </c>
       <c r="G1026" s="49"/>
       <c r="H1026" s="49">
         <v>4</v>
       </c>
       <c r="I1026" s="49" t="s">
-        <v>1494</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="1027" spans="1:9">
@@ -31224,14 +31263,14 @@
       <c r="D1027" s="49"/>
       <c r="E1027" s="49"/>
       <c r="F1027" s="49" t="s">
-        <v>1485</v>
+        <v>1498</v>
       </c>
       <c r="G1027" s="49"/>
       <c r="H1027" s="49">
         <v>4</v>
       </c>
       <c r="I1027" s="49" t="s">
-        <v>1495</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="1028" spans="1:9">
@@ -31357,7 +31396,7 @@
       <c r="G1033" s="26"/>
       <c r="H1033" s="26"/>
       <c r="I1033" s="26" t="s">
-        <v>1081</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="1034" spans="1:9">
@@ -31378,7 +31417,7 @@
       <c r="G1034" s="26"/>
       <c r="H1034" s="26"/>
       <c r="I1034" s="26" t="s">
-        <v>1083</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="1035" spans="1:9">
@@ -31399,7 +31438,7 @@
       <c r="G1035" s="26"/>
       <c r="H1035" s="26"/>
       <c r="I1035" s="26" t="s">
-        <v>1085</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="1036" spans="1:9">
@@ -31420,7 +31459,7 @@
       <c r="G1036" s="26"/>
       <c r="H1036" s="26"/>
       <c r="I1036" s="26" t="s">
-        <v>1087</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="1037" spans="1:9">
@@ -31441,7 +31480,7 @@
       <c r="G1037" s="26"/>
       <c r="H1037" s="26"/>
       <c r="I1037" s="26" t="s">
-        <v>1089</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="1038" spans="1:9">
@@ -31462,7 +31501,7 @@
       <c r="G1038" s="26"/>
       <c r="H1038" s="26"/>
       <c r="I1038" s="26" t="s">
-        <v>1091</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="1039" spans="1:9">
@@ -31726,7 +31765,7 @@
         <v>2</v>
       </c>
       <c r="I1050" s="43" t="s">
-        <v>1104</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="1051" spans="1:9">
@@ -31749,7 +31788,7 @@
         <v>2</v>
       </c>
       <c r="I1051" s="43" t="s">
-        <v>1106</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="1052" spans="1:9">
@@ -31772,7 +31811,7 @@
         <v>2</v>
       </c>
       <c r="I1052" s="43" t="s">
-        <v>1108</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="1053" spans="1:9">
@@ -31795,7 +31834,7 @@
         <v>2</v>
       </c>
       <c r="I1053" s="43" t="s">
-        <v>1110</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="1054" spans="1:9">
@@ -31818,7 +31857,7 @@
         <v>2</v>
       </c>
       <c r="I1054" s="43" t="s">
-        <v>1112</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="1055" spans="1:9">
@@ -31841,7 +31880,7 @@
         <v>2</v>
       </c>
       <c r="I1055" s="43" t="s">
-        <v>1114</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="1056" spans="1:9">
@@ -32002,7 +32041,7 @@
         <v>3</v>
       </c>
       <c r="I1062" s="43" t="s">
-        <v>1122</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="1063" spans="1:9">
@@ -32025,7 +32064,7 @@
         <v>3</v>
       </c>
       <c r="I1063" s="43" t="s">
-        <v>1124</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="1064" spans="1:9">
@@ -32048,7 +32087,7 @@
         <v>3</v>
       </c>
       <c r="I1064" s="43" t="s">
-        <v>1126</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="1065" spans="1:9">
@@ -32071,7 +32110,7 @@
         <v>3</v>
       </c>
       <c r="I1065" s="43" t="s">
-        <v>1128</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="1066" spans="1:9">
@@ -32094,7 +32133,7 @@
         <v>3</v>
       </c>
       <c r="I1066" s="43" t="s">
-        <v>1130</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="1067" spans="1:9">
@@ -32117,7 +32156,7 @@
         <v>3</v>
       </c>
       <c r="I1067" s="43" t="s">
-        <v>1132</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="1068" spans="1:9">
@@ -32278,7 +32317,7 @@
         <v>4</v>
       </c>
       <c r="I1074" s="43" t="s">
-        <v>1140</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="1075" spans="1:9">
@@ -32301,7 +32340,7 @@
         <v>4</v>
       </c>
       <c r="I1075" s="43" t="s">
-        <v>1142</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="1076" spans="1:9">
@@ -32324,7 +32363,7 @@
         <v>4</v>
       </c>
       <c r="I1076" s="43" t="s">
-        <v>1144</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="1077" spans="1:9">
@@ -32347,7 +32386,7 @@
         <v>4</v>
       </c>
       <c r="I1077" s="43" t="s">
-        <v>1146</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="1078" spans="1:9">
@@ -32370,7 +32409,7 @@
         <v>4</v>
       </c>
       <c r="I1078" s="43" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="1079" spans="1:9">
@@ -32393,7 +32432,7 @@
         <v>4</v>
       </c>
       <c r="I1079" s="43" t="s">
-        <v>1150</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="1080" spans="1:9">
@@ -32434,7 +32473,7 @@
       </c>
       <c r="E1081" s="26"/>
       <c r="F1081" s="26" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="G1081" s="26"/>
       <c r="H1081" s="26">
@@ -32459,7 +32498,7 @@
       </c>
       <c r="E1082" s="26"/>
       <c r="F1082" s="26" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="G1082" s="26"/>
       <c r="H1082" s="26">
@@ -32484,7 +32523,7 @@
       </c>
       <c r="E1083" s="26"/>
       <c r="F1083" s="26" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="G1083" s="26"/>
       <c r="H1083" s="26">
@@ -32509,7 +32548,7 @@
       </c>
       <c r="E1084" s="26"/>
       <c r="F1084" s="26" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="G1084" s="26"/>
       <c r="H1084" s="26">
@@ -32534,7 +32573,7 @@
       </c>
       <c r="E1085" s="26"/>
       <c r="F1085" s="26" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="G1085" s="26"/>
       <c r="H1085" s="26">
@@ -32559,14 +32598,14 @@
       </c>
       <c r="E1086" s="26"/>
       <c r="F1086" s="26" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="G1086" s="26"/>
       <c r="H1086" s="26">
         <v>2</v>
       </c>
       <c r="I1086" s="43" t="s">
-        <v>1163</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="1087" spans="1:9">
@@ -32584,14 +32623,14 @@
       </c>
       <c r="E1087" s="26"/>
       <c r="F1087" s="26" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="G1087" s="26"/>
       <c r="H1087" s="26">
         <v>2</v>
       </c>
       <c r="I1087" s="43" t="s">
-        <v>1166</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="1088" spans="1:9">
@@ -32609,14 +32648,14 @@
       </c>
       <c r="E1088" s="26"/>
       <c r="F1088" s="26" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="G1088" s="26"/>
       <c r="H1088" s="26">
         <v>2</v>
       </c>
       <c r="I1088" s="43" t="s">
-        <v>1169</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="1089" spans="1:9">
@@ -32634,14 +32673,14 @@
       </c>
       <c r="E1089" s="26"/>
       <c r="F1089" s="26" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="G1089" s="26"/>
       <c r="H1089" s="26">
         <v>2</v>
       </c>
       <c r="I1089" s="43" t="s">
-        <v>1172</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="1090" spans="1:9">
@@ -32659,14 +32698,14 @@
       </c>
       <c r="E1090" s="26"/>
       <c r="F1090" s="26" t="s">
-        <v>1177</v>
+        <v>1190</v>
       </c>
       <c r="G1090" s="26"/>
       <c r="H1090" s="26">
         <v>2</v>
       </c>
       <c r="I1090" s="43" t="s">
-        <v>1175</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="1091" spans="1:9">
@@ -32684,7 +32723,7 @@
       </c>
       <c r="E1091" s="26"/>
       <c r="F1091" s="26" t="s">
-        <v>1496</v>
+        <v>1509</v>
       </c>
       <c r="G1091" s="26"/>
       <c r="H1091" s="26">
@@ -32709,7 +32748,7 @@
       </c>
       <c r="E1092" s="26"/>
       <c r="F1092" s="26" t="s">
-        <v>1496</v>
+        <v>1509</v>
       </c>
       <c r="G1092" s="26"/>
       <c r="H1092" s="26">
@@ -32734,7 +32773,7 @@
       </c>
       <c r="E1093" s="26"/>
       <c r="F1093" s="26" t="s">
-        <v>1496</v>
+        <v>1509</v>
       </c>
       <c r="G1093" s="26"/>
       <c r="H1093" s="26">
@@ -32759,7 +32798,7 @@
       </c>
       <c r="E1094" s="26"/>
       <c r="F1094" s="26" t="s">
-        <v>1496</v>
+        <v>1509</v>
       </c>
       <c r="G1094" s="26"/>
       <c r="H1094" s="26">
@@ -32784,7 +32823,7 @@
       </c>
       <c r="E1095" s="26"/>
       <c r="F1095" s="26" t="s">
-        <v>1496</v>
+        <v>1509</v>
       </c>
       <c r="G1095" s="26"/>
       <c r="H1095" s="26">
@@ -32809,14 +32848,14 @@
       </c>
       <c r="E1096" s="26"/>
       <c r="F1096" s="26" t="s">
-        <v>1496</v>
+        <v>1509</v>
       </c>
       <c r="G1096" s="26"/>
       <c r="H1096" s="26">
         <v>3</v>
       </c>
       <c r="I1096" s="43" t="s">
-        <v>1190</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="1097" spans="1:9">
@@ -32834,14 +32873,14 @@
       </c>
       <c r="E1097" s="26"/>
       <c r="F1097" s="26" t="s">
-        <v>1496</v>
+        <v>1509</v>
       </c>
       <c r="G1097" s="26"/>
       <c r="H1097" s="26">
         <v>3</v>
       </c>
       <c r="I1097" s="43" t="s">
-        <v>1193</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="1098" spans="1:9">
@@ -32859,14 +32898,14 @@
       </c>
       <c r="E1098" s="26"/>
       <c r="F1098" s="26" t="s">
-        <v>1496</v>
+        <v>1509</v>
       </c>
       <c r="G1098" s="26"/>
       <c r="H1098" s="26">
         <v>3</v>
       </c>
       <c r="I1098" s="43" t="s">
-        <v>1196</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="1099" spans="1:9">
@@ -32884,14 +32923,14 @@
       </c>
       <c r="E1099" s="26"/>
       <c r="F1099" s="26" t="s">
-        <v>1496</v>
+        <v>1509</v>
       </c>
       <c r="G1099" s="26"/>
       <c r="H1099" s="26">
         <v>3</v>
       </c>
       <c r="I1099" s="43" t="s">
-        <v>1199</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="1100" spans="1:9">
@@ -32909,14 +32948,14 @@
       </c>
       <c r="E1100" s="26"/>
       <c r="F1100" s="26" t="s">
-        <v>1496</v>
+        <v>1509</v>
       </c>
       <c r="G1100" s="26"/>
       <c r="H1100" s="26">
         <v>3</v>
       </c>
       <c r="I1100" s="43" t="s">
-        <v>1202</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="1101" spans="1:9">
@@ -32934,7 +32973,7 @@
       </c>
       <c r="E1101" s="26"/>
       <c r="F1101" s="26" t="s">
-        <v>1497</v>
+        <v>1510</v>
       </c>
       <c r="G1101" s="26"/>
       <c r="H1101" s="26">
@@ -32959,7 +32998,7 @@
       </c>
       <c r="E1102" s="26"/>
       <c r="F1102" s="26" t="s">
-        <v>1497</v>
+        <v>1510</v>
       </c>
       <c r="G1102" s="26"/>
       <c r="H1102" s="26">
@@ -32984,7 +33023,7 @@
       </c>
       <c r="E1103" s="26"/>
       <c r="F1103" s="26" t="s">
-        <v>1497</v>
+        <v>1510</v>
       </c>
       <c r="G1103" s="26"/>
       <c r="H1103" s="26">
@@ -33009,7 +33048,7 @@
       </c>
       <c r="E1104" s="26"/>
       <c r="F1104" s="26" t="s">
-        <v>1497</v>
+        <v>1510</v>
       </c>
       <c r="G1104" s="26"/>
       <c r="H1104" s="26">
@@ -33034,7 +33073,7 @@
       </c>
       <c r="E1105" s="26"/>
       <c r="F1105" s="26" t="s">
-        <v>1497</v>
+        <v>1510</v>
       </c>
       <c r="G1105" s="26"/>
       <c r="H1105" s="26">
@@ -33059,14 +33098,14 @@
       </c>
       <c r="E1106" s="26"/>
       <c r="F1106" s="26" t="s">
-        <v>1497</v>
+        <v>1510</v>
       </c>
       <c r="G1106" s="26"/>
       <c r="H1106" s="26">
         <v>4</v>
       </c>
       <c r="I1106" s="43" t="s">
-        <v>1217</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="1107" spans="1:9">
@@ -33084,14 +33123,14 @@
       </c>
       <c r="E1107" s="26"/>
       <c r="F1107" s="26" t="s">
-        <v>1497</v>
+        <v>1510</v>
       </c>
       <c r="G1107" s="26"/>
       <c r="H1107" s="26">
         <v>4</v>
       </c>
       <c r="I1107" s="43" t="s">
-        <v>1220</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="1108" spans="1:9">
@@ -33109,14 +33148,14 @@
       </c>
       <c r="E1108" s="26"/>
       <c r="F1108" s="26" t="s">
-        <v>1497</v>
+        <v>1510</v>
       </c>
       <c r="G1108" s="26"/>
       <c r="H1108" s="26">
         <v>4</v>
       </c>
       <c r="I1108" s="43" t="s">
-        <v>1223</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="1109" spans="1:9">
@@ -33134,14 +33173,14 @@
       </c>
       <c r="E1109" s="26"/>
       <c r="F1109" s="26" t="s">
-        <v>1497</v>
+        <v>1510</v>
       </c>
       <c r="G1109" s="26"/>
       <c r="H1109" s="26">
         <v>4</v>
       </c>
       <c r="I1109" s="43" t="s">
-        <v>1226</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="1110" spans="1:9">
@@ -33159,14 +33198,14 @@
       </c>
       <c r="E1110" s="26"/>
       <c r="F1110" s="26" t="s">
-        <v>1497</v>
+        <v>1510</v>
       </c>
       <c r="G1110" s="26"/>
       <c r="H1110" s="26">
         <v>4</v>
       </c>
       <c r="I1110" s="43" t="s">
-        <v>1229</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="1111" spans="1:9">
@@ -33316,7 +33355,7 @@
         <v>2</v>
       </c>
       <c r="I1116" s="43" t="s">
-        <v>1239</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="1117" spans="1:9">
@@ -33341,7 +33380,7 @@
         <v>2</v>
       </c>
       <c r="I1117" s="43" t="s">
-        <v>1241</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="1118" spans="1:9">
@@ -33366,7 +33405,7 @@
         <v>2</v>
       </c>
       <c r="I1118" s="43" t="s">
-        <v>1243</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="1119" spans="1:9">
@@ -33391,7 +33430,7 @@
         <v>2</v>
       </c>
       <c r="I1119" s="43" t="s">
-        <v>1245</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="1120" spans="1:9">
@@ -33416,7 +33455,7 @@
         <v>2</v>
       </c>
       <c r="I1120" s="43" t="s">
-        <v>1247</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="1121" spans="1:9">
@@ -33566,7 +33605,7 @@
         <v>3</v>
       </c>
       <c r="I1126" s="43" t="s">
-        <v>1256</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="1127" spans="1:9">
@@ -33591,7 +33630,7 @@
         <v>3</v>
       </c>
       <c r="I1127" s="43" t="s">
-        <v>1258</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="1128" spans="1:9">
@@ -33616,7 +33655,7 @@
         <v>3</v>
       </c>
       <c r="I1128" s="43" t="s">
-        <v>1260</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="1129" spans="1:9">
@@ -33641,7 +33680,7 @@
         <v>3</v>
       </c>
       <c r="I1129" s="43" t="s">
-        <v>1262</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="1130" spans="1:9">
@@ -33666,7 +33705,7 @@
         <v>3</v>
       </c>
       <c r="I1130" s="43" t="s">
-        <v>1264</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="1131" spans="1:9">
@@ -33684,7 +33723,7 @@
       </c>
       <c r="E1131" s="26"/>
       <c r="F1131" s="26" t="s">
-        <v>1498</v>
+        <v>1511</v>
       </c>
       <c r="G1131" s="26"/>
       <c r="H1131" s="26">
@@ -33709,7 +33748,7 @@
       </c>
       <c r="E1132" s="26"/>
       <c r="F1132" s="26" t="s">
-        <v>1498</v>
+        <v>1511</v>
       </c>
       <c r="G1132" s="26"/>
       <c r="H1132" s="26">
@@ -33734,7 +33773,7 @@
       </c>
       <c r="E1133" s="26"/>
       <c r="F1133" s="26" t="s">
-        <v>1498</v>
+        <v>1511</v>
       </c>
       <c r="G1133" s="26"/>
       <c r="H1133" s="26">
@@ -33759,7 +33798,7 @@
       </c>
       <c r="E1134" s="26"/>
       <c r="F1134" s="26" t="s">
-        <v>1498</v>
+        <v>1511</v>
       </c>
       <c r="G1134" s="26"/>
       <c r="H1134" s="26">
@@ -33784,7 +33823,7 @@
       </c>
       <c r="E1135" s="26"/>
       <c r="F1135" s="26" t="s">
-        <v>1498</v>
+        <v>1511</v>
       </c>
       <c r="G1135" s="26"/>
       <c r="H1135" s="26">
@@ -33809,14 +33848,14 @@
       </c>
       <c r="E1136" s="26"/>
       <c r="F1136" s="26" t="s">
-        <v>1498</v>
+        <v>1511</v>
       </c>
       <c r="G1136" s="26"/>
       <c r="H1136" s="26">
         <v>4</v>
       </c>
       <c r="I1136" s="43" t="s">
-        <v>1273</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="1137" spans="1:9">
@@ -33834,14 +33873,14 @@
       </c>
       <c r="E1137" s="26"/>
       <c r="F1137" s="26" t="s">
-        <v>1498</v>
+        <v>1511</v>
       </c>
       <c r="G1137" s="26"/>
       <c r="H1137" s="26">
         <v>4</v>
       </c>
       <c r="I1137" s="43" t="s">
-        <v>1275</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="1138" spans="1:9">
@@ -33859,14 +33898,14 @@
       </c>
       <c r="E1138" s="26"/>
       <c r="F1138" s="26" t="s">
-        <v>1498</v>
+        <v>1511</v>
       </c>
       <c r="G1138" s="26"/>
       <c r="H1138" s="26">
         <v>4</v>
       </c>
       <c r="I1138" s="43" t="s">
-        <v>1277</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="1139" spans="1:9">
@@ -33884,14 +33923,14 @@
       </c>
       <c r="E1139" s="26"/>
       <c r="F1139" s="26" t="s">
-        <v>1498</v>
+        <v>1511</v>
       </c>
       <c r="G1139" s="26"/>
       <c r="H1139" s="26">
         <v>4</v>
       </c>
       <c r="I1139" s="43" t="s">
-        <v>1279</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="1140" spans="1:9">
@@ -33909,14 +33948,14 @@
       </c>
       <c r="E1140" s="26"/>
       <c r="F1140" s="26" t="s">
-        <v>1498</v>
+        <v>1511</v>
       </c>
       <c r="G1140" s="26"/>
       <c r="H1140" s="26">
         <v>4</v>
       </c>
       <c r="I1140" s="43" t="s">
-        <v>1281</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="1141" spans="1:9">
@@ -33937,7 +33976,7 @@
       <c r="G1141" s="59"/>
       <c r="H1141" s="59"/>
       <c r="I1141" s="59" t="s">
-        <v>1499</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="1142" spans="1:9">
@@ -33958,7 +33997,7 @@
       <c r="G1142" s="59"/>
       <c r="H1142" s="59"/>
       <c r="I1142" s="59" t="s">
-        <v>1500</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="1143" spans="1:9">
@@ -33979,7 +34018,7 @@
       <c r="G1143" s="59"/>
       <c r="H1143" s="59"/>
       <c r="I1143" s="59" t="s">
-        <v>1501</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="1144" spans="1:9">
@@ -34000,7 +34039,7 @@
       <c r="G1144" s="59"/>
       <c r="H1144" s="59"/>
       <c r="I1144" s="59" t="s">
-        <v>1502</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="1145" spans="1:9">
@@ -34021,7 +34060,7 @@
       <c r="G1145" s="59"/>
       <c r="H1145" s="59"/>
       <c r="I1145" s="59" t="s">
-        <v>1503</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="1146" spans="1:9">
@@ -34165,12 +34204,12 @@
       </c>
       <c r="E1152" s="59"/>
       <c r="F1152" s="59" t="s">
-        <v>1504</v>
+        <v>1517</v>
       </c>
       <c r="G1152" s="59"/>
       <c r="H1152" s="59"/>
       <c r="I1152" s="59" t="s">
-        <v>1505</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="1153" spans="1:9">
@@ -34188,12 +34227,12 @@
       </c>
       <c r="E1153" s="59"/>
       <c r="F1153" s="59" t="s">
-        <v>1504</v>
+        <v>1517</v>
       </c>
       <c r="G1153" s="59"/>
       <c r="H1153" s="59"/>
       <c r="I1153" s="59" t="s">
-        <v>1506</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="1154" spans="1:9">
@@ -34211,12 +34250,12 @@
       </c>
       <c r="E1154" s="59"/>
       <c r="F1154" s="59" t="s">
-        <v>1504</v>
+        <v>1517</v>
       </c>
       <c r="G1154" s="59"/>
       <c r="H1154" s="59"/>
       <c r="I1154" s="59" t="s">
-        <v>1507</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="1155" spans="1:9">
@@ -34234,12 +34273,12 @@
       </c>
       <c r="E1155" s="59"/>
       <c r="F1155" s="59" t="s">
-        <v>1504</v>
+        <v>1517</v>
       </c>
       <c r="G1155" s="59"/>
       <c r="H1155" s="59"/>
       <c r="I1155" s="59" t="s">
-        <v>1508</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="1156" spans="1:9">
@@ -34257,12 +34296,12 @@
       </c>
       <c r="E1156" s="59"/>
       <c r="F1156" s="59" t="s">
-        <v>1504</v>
+        <v>1517</v>
       </c>
       <c r="G1156" s="59"/>
       <c r="H1156" s="59"/>
       <c r="I1156" s="59" t="s">
-        <v>1509</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="1157" spans="1:9">
@@ -34280,7 +34319,7 @@
       </c>
       <c r="E1157" s="59"/>
       <c r="F1157" s="59" t="s">
-        <v>1504</v>
+        <v>1517</v>
       </c>
       <c r="G1157" s="59"/>
       <c r="H1157" s="59"/>
@@ -34303,7 +34342,7 @@
       </c>
       <c r="E1158" s="59"/>
       <c r="F1158" s="59" t="s">
-        <v>1504</v>
+        <v>1517</v>
       </c>
       <c r="G1158" s="59"/>
       <c r="H1158" s="59"/>
@@ -34326,7 +34365,7 @@
       </c>
       <c r="E1159" s="59"/>
       <c r="F1159" s="59" t="s">
-        <v>1504</v>
+        <v>1517</v>
       </c>
       <c r="G1159" s="59"/>
       <c r="H1159" s="59"/>
@@ -34349,7 +34388,7 @@
       </c>
       <c r="E1160" s="59"/>
       <c r="F1160" s="59" t="s">
-        <v>1504</v>
+        <v>1517</v>
       </c>
       <c r="G1160" s="59"/>
       <c r="H1160" s="59"/>
@@ -34459,7 +34498,7 @@
       <c r="G1165" s="21"/>
       <c r="H1165" s="21"/>
       <c r="I1165" s="21" t="s">
-        <v>1081</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="1166" spans="1:9">
@@ -34480,7 +34519,7 @@
       <c r="G1166" s="21"/>
       <c r="H1166" s="21"/>
       <c r="I1166" s="21" t="s">
-        <v>1083</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="1167" spans="1:9">
@@ -34501,7 +34540,7 @@
       <c r="G1167" s="21"/>
       <c r="H1167" s="21"/>
       <c r="I1167" s="21" t="s">
-        <v>1085</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="1168" spans="1:9">
@@ -34522,7 +34561,7 @@
       <c r="G1168" s="21"/>
       <c r="H1168" s="21"/>
       <c r="I1168" s="21" t="s">
-        <v>1087</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="1169" spans="1:9">
@@ -34671,7 +34710,7 @@
       <c r="G1175" s="21"/>
       <c r="H1175" s="21"/>
       <c r="I1175" s="21" t="s">
-        <v>1510</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="1176" spans="1:9">
@@ -34694,7 +34733,7 @@
       <c r="G1176" s="21"/>
       <c r="H1176" s="21"/>
       <c r="I1176" s="21" t="s">
-        <v>1511</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="1177" spans="1:9">
@@ -34717,7 +34756,7 @@
       <c r="G1177" s="21"/>
       <c r="H1177" s="21"/>
       <c r="I1177" s="21" t="s">
-        <v>1512</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="1178" spans="1:9">
@@ -34740,7 +34779,7 @@
       <c r="G1178" s="21"/>
       <c r="H1178" s="21"/>
       <c r="I1178" s="21" t="s">
-        <v>1513</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="1179" spans="1:9">
@@ -34763,7 +34802,7 @@
       <c r="G1179" s="21"/>
       <c r="H1179" s="21"/>
       <c r="I1179" s="21" t="s">
-        <v>1514</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="1180" spans="1:9">
@@ -34786,7 +34825,7 @@
       <c r="G1180" s="21"/>
       <c r="H1180" s="21"/>
       <c r="I1180" s="21" t="s">
-        <v>1515</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="1181" spans="1:9">
@@ -34809,7 +34848,7 @@
       <c r="G1181" s="21"/>
       <c r="H1181" s="21"/>
       <c r="I1181" s="21" t="s">
-        <v>1516</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="1182" spans="1:9">
@@ -34832,7 +34871,7 @@
       <c r="G1182" s="21"/>
       <c r="H1182" s="21"/>
       <c r="I1182" s="21" t="s">
-        <v>1517</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="1183" spans="1:9">
@@ -34853,7 +34892,7 @@
       <c r="G1183" s="41"/>
       <c r="H1183" s="41"/>
       <c r="I1183" s="41" t="s">
-        <v>1518</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="1184" spans="1:9">
@@ -34874,7 +34913,7 @@
       <c r="G1184" s="41"/>
       <c r="H1184" s="41"/>
       <c r="I1184" s="41" t="s">
-        <v>1519</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="1185" spans="1:9">
@@ -34895,7 +34934,7 @@
       <c r="G1185" s="41"/>
       <c r="H1185" s="41"/>
       <c r="I1185" s="41" t="s">
-        <v>1520</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="1186" spans="1:9">
@@ -34916,7 +34955,7 @@
       <c r="G1186" s="41"/>
       <c r="H1186" s="41"/>
       <c r="I1186" s="41" t="s">
-        <v>1521</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="1187" spans="1:9">
@@ -34937,7 +34976,7 @@
       <c r="G1187" s="41"/>
       <c r="H1187" s="41"/>
       <c r="I1187" s="41" t="s">
-        <v>1522</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="1188" spans="1:9">
@@ -34958,7 +34997,7 @@
       <c r="G1188" s="41"/>
       <c r="H1188" s="41"/>
       <c r="I1188" s="41" t="s">
-        <v>1523</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="1189" spans="1:9">
@@ -34979,7 +35018,7 @@
       <c r="G1189" s="41"/>
       <c r="H1189" s="41"/>
       <c r="I1189" s="41" t="s">
-        <v>1524</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="1190" spans="1:9">
@@ -35021,7 +35060,7 @@
       <c r="G1191" s="41"/>
       <c r="H1191" s="41"/>
       <c r="I1191" s="60" t="s">
-        <v>1525</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="1192" spans="1:9">
@@ -35126,7 +35165,7 @@
       <c r="G1196" s="61"/>
       <c r="H1196" s="61"/>
       <c r="I1196" s="61" t="s">
-        <v>1526</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1197" spans="1:9">
@@ -35147,7 +35186,7 @@
       <c r="G1197" s="61"/>
       <c r="H1197" s="61"/>
       <c r="I1197" s="61" t="s">
-        <v>1527</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="1198" spans="1:9">
@@ -35168,7 +35207,7 @@
       <c r="G1198" s="61"/>
       <c r="H1198" s="61"/>
       <c r="I1198" s="61" t="s">
-        <v>1528</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="1199" spans="1:9">
@@ -35210,7 +35249,7 @@
       <c r="G1200" s="61"/>
       <c r="H1200" s="61"/>
       <c r="I1200" s="61" t="s">
-        <v>1529</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1201" spans="1:9">
@@ -35231,7 +35270,7 @@
       <c r="G1201" s="61"/>
       <c r="H1201" s="61"/>
       <c r="I1201" s="61" t="s">
-        <v>1530</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="1202" spans="1:9">
@@ -35252,7 +35291,7 @@
       <c r="G1202" s="61"/>
       <c r="H1202" s="61"/>
       <c r="I1202" s="61" t="s">
-        <v>1531</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="1203" spans="1:9">
@@ -35273,7 +35312,7 @@
       <c r="G1203" s="61"/>
       <c r="H1203" s="61"/>
       <c r="I1203" s="61" t="s">
-        <v>1532</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="1204" spans="1:9">
@@ -35294,7 +35333,7 @@
       <c r="G1204" s="61"/>
       <c r="H1204" s="61"/>
       <c r="I1204" s="61" t="s">
-        <v>1533</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="1205" spans="1:9">
@@ -35315,7 +35354,7 @@
       <c r="G1205" s="61"/>
       <c r="H1205" s="61"/>
       <c r="I1205" s="61" t="s">
-        <v>1534</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="1206" spans="1:9">
@@ -35336,7 +35375,7 @@
       <c r="G1206" s="61"/>
       <c r="H1206" s="61"/>
       <c r="I1206" s="61" t="s">
-        <v>1535</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="1207" spans="1:9">
@@ -35357,7 +35396,7 @@
       <c r="G1207" s="48"/>
       <c r="H1207" s="48"/>
       <c r="I1207" s="48" t="s">
-        <v>1536</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="1208" spans="1:9">
@@ -35378,7 +35417,7 @@
       <c r="G1208" s="48"/>
       <c r="H1208" s="48"/>
       <c r="I1208" s="48" t="s">
-        <v>1537</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="1209" spans="1:9">
@@ -35399,7 +35438,7 @@
       <c r="G1209" s="48"/>
       <c r="H1209" s="48"/>
       <c r="I1209" s="48" t="s">
-        <v>1538</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="1210" spans="1:9">
@@ -35420,7 +35459,7 @@
       <c r="G1210" s="48"/>
       <c r="H1210" s="48"/>
       <c r="I1210" s="48" t="s">
-        <v>1539</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="1211" spans="1:9">
@@ -35441,7 +35480,7 @@
       <c r="G1211" s="48"/>
       <c r="H1211" s="48"/>
       <c r="I1211" s="48" t="s">
-        <v>1540</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="1212" spans="1:9">
@@ -35462,7 +35501,7 @@
       <c r="G1212" s="48"/>
       <c r="H1212" s="48"/>
       <c r="I1212" s="48" t="s">
-        <v>1429</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1213" spans="1:9">
@@ -35483,7 +35522,7 @@
       <c r="G1213" s="48"/>
       <c r="H1213" s="48"/>
       <c r="I1213" s="48" t="s">
-        <v>1430</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="1214" spans="1:9">
@@ -35504,7 +35543,7 @@
       <c r="G1214" s="48"/>
       <c r="H1214" s="48"/>
       <c r="I1214" s="48" t="s">
-        <v>1431</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="1215" spans="1:9">
@@ -35525,7 +35564,7 @@
       <c r="G1215" s="48"/>
       <c r="H1215" s="48"/>
       <c r="I1215" s="48" t="s">
-        <v>1432</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="1216" spans="1:9">
@@ -35546,7 +35585,7 @@
       <c r="G1216" s="48"/>
       <c r="H1216" s="48"/>
       <c r="I1216" s="48" t="s">
-        <v>1433</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="1217" spans="1:9">
@@ -35567,7 +35606,7 @@
       <c r="G1217" s="48"/>
       <c r="H1217" s="48"/>
       <c r="I1217" s="48" t="s">
-        <v>1541</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="1218" spans="1:9">
@@ -35588,7 +35627,7 @@
       <c r="G1218" s="48"/>
       <c r="H1218" s="48"/>
       <c r="I1218" s="48" t="s">
-        <v>1542</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="1219" spans="1:9">
@@ -35609,7 +35648,7 @@
       <c r="G1219" s="48"/>
       <c r="H1219" s="48"/>
       <c r="I1219" s="48" t="s">
-        <v>1543</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1220" spans="1:9">
@@ -35630,7 +35669,7 @@
       <c r="G1220" s="48"/>
       <c r="H1220" s="48"/>
       <c r="I1220" s="48" t="s">
-        <v>1544</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="1221" spans="1:9">
@@ -35737,7 +35776,7 @@
         <v>2</v>
       </c>
       <c r="I1225" s="48" t="s">
-        <v>1545</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="1226" spans="1:9">
@@ -35760,7 +35799,7 @@
         <v>2</v>
       </c>
       <c r="I1226" s="48" t="s">
-        <v>1546</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="1227" spans="1:9">
@@ -35783,7 +35822,7 @@
         <v>2</v>
       </c>
       <c r="I1227" s="62" t="s">
-        <v>1547</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="1228" spans="1:9">
@@ -35806,7 +35845,7 @@
         <v>2</v>
       </c>
       <c r="I1228" s="62" t="s">
-        <v>1548</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="1229" spans="1:9">
@@ -35829,7 +35868,7 @@
         <v>2</v>
       </c>
       <c r="I1229" s="62" t="s">
-        <v>1549</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1230" spans="1:9">
@@ -35852,7 +35891,7 @@
         <v>2</v>
       </c>
       <c r="I1230" s="62" t="s">
-        <v>1550</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1231" spans="1:9">
@@ -35875,7 +35914,7 @@
         <v>2</v>
       </c>
       <c r="I1231" s="62" t="s">
-        <v>1551</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="1232" spans="1:9">
@@ -35898,7 +35937,7 @@
         <v>2</v>
       </c>
       <c r="I1232" s="62" t="s">
-        <v>1552</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1233" spans="1:9">
@@ -35921,7 +35960,7 @@
         <v>2</v>
       </c>
       <c r="I1233" s="62" t="s">
-        <v>1553</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="1234" spans="1:9">
@@ -35944,7 +35983,7 @@
         <v>2</v>
       </c>
       <c r="I1234" s="62" t="s">
-        <v>1554</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1235" spans="1:9">
@@ -35967,7 +36006,7 @@
         <v>2</v>
       </c>
       <c r="I1235" s="62" t="s">
-        <v>1555</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="1236" spans="1:9">
@@ -35990,7 +36029,7 @@
         <v>3</v>
       </c>
       <c r="I1236" s="62" t="s">
-        <v>1556</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="1237" spans="1:9">
@@ -36013,7 +36052,7 @@
         <v>3</v>
       </c>
       <c r="I1237" s="62" t="s">
-        <v>1557</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="1238" spans="1:9">
@@ -36036,7 +36075,7 @@
         <v>3</v>
       </c>
       <c r="I1238" s="62" t="s">
-        <v>1558</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="1239" spans="1:9">
@@ -36059,7 +36098,7 @@
         <v>3</v>
       </c>
       <c r="I1239" s="62" t="s">
-        <v>1559</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="1240" spans="1:9">
@@ -36082,7 +36121,7 @@
         <v>3</v>
       </c>
       <c r="I1240" s="62" t="s">
-        <v>1560</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="1241" spans="1:9">
@@ -36105,7 +36144,7 @@
         <v>3</v>
       </c>
       <c r="I1241" s="62" t="s">
-        <v>1561</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="1242" spans="1:9">
@@ -36128,7 +36167,7 @@
         <v>3</v>
       </c>
       <c r="I1242" s="62" t="s">
-        <v>1562</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1243" spans="1:9">
@@ -36151,7 +36190,7 @@
         <v>3</v>
       </c>
       <c r="I1243" s="62" t="s">
-        <v>1563</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="1244" spans="1:9">
@@ -36174,7 +36213,7 @@
         <v>3</v>
       </c>
       <c r="I1244" s="62" t="s">
-        <v>1564</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1245" spans="1:9">
@@ -36197,7 +36236,7 @@
         <v>3</v>
       </c>
       <c r="I1245" s="62" t="s">
-        <v>1565</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1246" spans="1:9">
@@ -36220,7 +36259,7 @@
         <v>3</v>
       </c>
       <c r="I1246" s="62" t="s">
-        <v>1566</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1247" spans="1:9">
@@ -36238,12 +36277,12 @@
       </c>
       <c r="E1247" s="48"/>
       <c r="F1247" s="48" t="s">
-        <v>1567</v>
+        <v>1580</v>
       </c>
       <c r="G1247" s="48"/>
       <c r="H1247" s="48"/>
       <c r="I1247" s="62" t="s">
-        <v>1568</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="1248" spans="1:9">
@@ -36261,12 +36300,12 @@
       </c>
       <c r="E1248" s="48"/>
       <c r="F1248" s="48" t="s">
-        <v>1567</v>
+        <v>1580</v>
       </c>
       <c r="G1248" s="48"/>
       <c r="H1248" s="48"/>
       <c r="I1248" s="62" t="s">
-        <v>1569</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1249" spans="1:9">
@@ -36284,12 +36323,12 @@
       </c>
       <c r="E1249" s="48"/>
       <c r="F1249" s="48" t="s">
-        <v>1567</v>
+        <v>1580</v>
       </c>
       <c r="G1249" s="48"/>
       <c r="H1249" s="48"/>
       <c r="I1249" s="62" t="s">
-        <v>1570</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1250" spans="1:9">
@@ -36307,12 +36346,12 @@
       </c>
       <c r="E1250" s="48"/>
       <c r="F1250" s="48" t="s">
-        <v>1567</v>
+        <v>1580</v>
       </c>
       <c r="G1250" s="48"/>
       <c r="H1250" s="48"/>
       <c r="I1250" s="62" t="s">
-        <v>1571</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="1251" spans="1:9">
@@ -36330,12 +36369,12 @@
       </c>
       <c r="E1251" s="48"/>
       <c r="F1251" s="48" t="s">
-        <v>1567</v>
+        <v>1580</v>
       </c>
       <c r="G1251" s="48"/>
       <c r="H1251" s="48"/>
       <c r="I1251" s="62" t="s">
-        <v>1572</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1252" spans="1:9">
@@ -36353,12 +36392,12 @@
       </c>
       <c r="E1252" s="48"/>
       <c r="F1252" s="48" t="s">
-        <v>1567</v>
+        <v>1580</v>
       </c>
       <c r="G1252" s="48"/>
       <c r="H1252" s="48"/>
       <c r="I1252" s="62" t="s">
-        <v>1573</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1253" spans="1:9">
@@ -36376,12 +36415,12 @@
       </c>
       <c r="E1253" s="48"/>
       <c r="F1253" s="48" t="s">
-        <v>1567</v>
+        <v>1580</v>
       </c>
       <c r="G1253" s="48"/>
       <c r="H1253" s="48"/>
       <c r="I1253" s="62" t="s">
-        <v>1574</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="1254" spans="1:9">
@@ -36399,12 +36438,12 @@
       </c>
       <c r="E1254" s="48"/>
       <c r="F1254" s="48" t="s">
-        <v>1567</v>
+        <v>1580</v>
       </c>
       <c r="G1254" s="48"/>
       <c r="H1254" s="48"/>
       <c r="I1254" s="62" t="s">
-        <v>1575</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="1255" spans="1:9">
@@ -36422,12 +36461,12 @@
       </c>
       <c r="E1255" s="48"/>
       <c r="F1255" s="48" t="s">
-        <v>1567</v>
+        <v>1580</v>
       </c>
       <c r="G1255" s="48"/>
       <c r="H1255" s="48"/>
       <c r="I1255" s="62" t="s">
-        <v>1576</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1256" spans="1:9">
@@ -36445,12 +36484,12 @@
       </c>
       <c r="E1256" s="48"/>
       <c r="F1256" s="48" t="s">
-        <v>1567</v>
+        <v>1580</v>
       </c>
       <c r="G1256" s="48"/>
       <c r="H1256" s="48"/>
       <c r="I1256" s="62" t="s">
-        <v>1577</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="1257" spans="1:9">
@@ -36468,12 +36507,12 @@
       </c>
       <c r="E1257" s="48"/>
       <c r="F1257" s="48" t="s">
-        <v>1567</v>
+        <v>1580</v>
       </c>
       <c r="G1257" s="48"/>
       <c r="H1257" s="48"/>
       <c r="I1257" s="62" t="s">
-        <v>1578</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="1258" spans="1:9">
@@ -36491,14 +36530,14 @@
       </c>
       <c r="E1258" s="48"/>
       <c r="F1258" s="48" t="s">
-        <v>1579</v>
+        <v>1592</v>
       </c>
       <c r="G1258" s="48"/>
       <c r="H1258" s="48">
         <v>2</v>
       </c>
       <c r="I1258" s="63" t="s">
-        <v>1580</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="1259" spans="1:9">
@@ -36516,14 +36555,14 @@
       </c>
       <c r="E1259" s="48"/>
       <c r="F1259" s="48" t="s">
-        <v>1579</v>
+        <v>1592</v>
       </c>
       <c r="G1259" s="48"/>
       <c r="H1259" s="48">
         <v>2</v>
       </c>
       <c r="I1259" s="63" t="s">
-        <v>1581</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="1260" spans="1:9">
@@ -36541,14 +36580,14 @@
       </c>
       <c r="E1260" s="48"/>
       <c r="F1260" s="48" t="s">
-        <v>1579</v>
+        <v>1592</v>
       </c>
       <c r="G1260" s="48"/>
       <c r="H1260" s="48">
         <v>2</v>
       </c>
       <c r="I1260" s="63" t="s">
-        <v>1582</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="1261" spans="1:9">
@@ -36566,14 +36605,14 @@
       </c>
       <c r="E1261" s="48"/>
       <c r="F1261" s="48" t="s">
-        <v>1579</v>
+        <v>1592</v>
       </c>
       <c r="G1261" s="48"/>
       <c r="H1261" s="48">
         <v>2</v>
       </c>
       <c r="I1261" s="63" t="s">
-        <v>1583</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="1262" spans="1:9">
@@ -36591,14 +36630,14 @@
       </c>
       <c r="E1262" s="48"/>
       <c r="F1262" s="48" t="s">
-        <v>1579</v>
+        <v>1592</v>
       </c>
       <c r="G1262" s="48"/>
       <c r="H1262" s="48">
         <v>2</v>
       </c>
       <c r="I1262" s="63" t="s">
-        <v>1584</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="1263" spans="1:9">
@@ -36616,14 +36655,14 @@
       </c>
       <c r="E1263" s="48"/>
       <c r="F1263" s="48" t="s">
-        <v>1579</v>
+        <v>1592</v>
       </c>
       <c r="G1263" s="48"/>
       <c r="H1263" s="48">
         <v>2</v>
       </c>
       <c r="I1263" s="63" t="s">
-        <v>1585</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="1264" spans="1:9">
@@ -36641,14 +36680,14 @@
       </c>
       <c r="E1264" s="48"/>
       <c r="F1264" s="48" t="s">
-        <v>1579</v>
+        <v>1592</v>
       </c>
       <c r="G1264" s="48"/>
       <c r="H1264" s="48">
         <v>2</v>
       </c>
       <c r="I1264" s="63" t="s">
-        <v>1586</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="1265" spans="1:9">
@@ -36666,14 +36705,14 @@
       </c>
       <c r="E1265" s="48"/>
       <c r="F1265" s="48" t="s">
-        <v>1579</v>
+        <v>1592</v>
       </c>
       <c r="G1265" s="48"/>
       <c r="H1265" s="48">
         <v>2</v>
       </c>
       <c r="I1265" s="63" t="s">
-        <v>1587</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1266" spans="1:9">
@@ -36691,14 +36730,14 @@
       </c>
       <c r="E1266" s="48"/>
       <c r="F1266" s="48" t="s">
-        <v>1579</v>
+        <v>1592</v>
       </c>
       <c r="G1266" s="48"/>
       <c r="H1266" s="48">
         <v>2</v>
       </c>
       <c r="I1266" s="63" t="s">
-        <v>1588</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="1267" spans="1:9">
@@ -36716,14 +36755,14 @@
       </c>
       <c r="E1267" s="48"/>
       <c r="F1267" s="48" t="s">
-        <v>1579</v>
+        <v>1592</v>
       </c>
       <c r="G1267" s="48"/>
       <c r="H1267" s="48">
         <v>2</v>
       </c>
       <c r="I1267" s="63" t="s">
-        <v>1589</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="1268" spans="1:9">
@@ -36741,14 +36780,14 @@
       </c>
       <c r="E1268" s="48"/>
       <c r="F1268" s="48" t="s">
-        <v>1579</v>
+        <v>1592</v>
       </c>
       <c r="G1268" s="48"/>
       <c r="H1268" s="48">
         <v>2</v>
       </c>
       <c r="I1268" s="63" t="s">
-        <v>1590</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="1269" spans="1:9">
@@ -36766,14 +36805,14 @@
       </c>
       <c r="E1269" s="48"/>
       <c r="F1269" s="48" t="s">
-        <v>1591</v>
+        <v>1604</v>
       </c>
       <c r="G1269" s="48"/>
       <c r="H1269" s="48">
         <v>3</v>
       </c>
       <c r="I1269" s="62" t="s">
-        <v>1592</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="1270" spans="1:9">
@@ -36791,14 +36830,14 @@
       </c>
       <c r="E1270" s="48"/>
       <c r="F1270" s="48" t="s">
-        <v>1591</v>
+        <v>1604</v>
       </c>
       <c r="G1270" s="48"/>
       <c r="H1270" s="48">
         <v>3</v>
       </c>
       <c r="I1270" s="62" t="s">
-        <v>1593</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="1271" spans="1:9">
@@ -36816,14 +36855,14 @@
       </c>
       <c r="E1271" s="48"/>
       <c r="F1271" s="48" t="s">
-        <v>1591</v>
+        <v>1604</v>
       </c>
       <c r="G1271" s="48"/>
       <c r="H1271" s="48">
         <v>3</v>
       </c>
       <c r="I1271" s="62" t="s">
-        <v>1594</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="1272" spans="1:9">
@@ -36841,14 +36880,14 @@
       </c>
       <c r="E1272" s="48"/>
       <c r="F1272" s="48" t="s">
-        <v>1591</v>
+        <v>1604</v>
       </c>
       <c r="G1272" s="48"/>
       <c r="H1272" s="48">
         <v>3</v>
       </c>
       <c r="I1272" s="62" t="s">
-        <v>1595</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="1273" spans="1:9">
@@ -36866,14 +36905,14 @@
       </c>
       <c r="E1273" s="48"/>
       <c r="F1273" s="48" t="s">
-        <v>1591</v>
+        <v>1604</v>
       </c>
       <c r="G1273" s="48"/>
       <c r="H1273" s="48">
         <v>3</v>
       </c>
       <c r="I1273" s="62" t="s">
-        <v>1596</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="1274" spans="1:9">
@@ -36891,14 +36930,14 @@
       </c>
       <c r="E1274" s="48"/>
       <c r="F1274" s="48" t="s">
-        <v>1591</v>
+        <v>1604</v>
       </c>
       <c r="G1274" s="48"/>
       <c r="H1274" s="48">
         <v>3</v>
       </c>
       <c r="I1274" s="62" t="s">
-        <v>1597</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="1275" spans="1:9">
@@ -36916,14 +36955,14 @@
       </c>
       <c r="E1275" s="48"/>
       <c r="F1275" s="48" t="s">
-        <v>1591</v>
+        <v>1604</v>
       </c>
       <c r="G1275" s="48"/>
       <c r="H1275" s="48">
         <v>3</v>
       </c>
       <c r="I1275" s="62" t="s">
-        <v>1598</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="1276" spans="1:9">
@@ -36941,14 +36980,14 @@
       </c>
       <c r="E1276" s="48"/>
       <c r="F1276" s="48" t="s">
-        <v>1591</v>
+        <v>1604</v>
       </c>
       <c r="G1276" s="48"/>
       <c r="H1276" s="48">
         <v>3</v>
       </c>
       <c r="I1276" s="62" t="s">
-        <v>1599</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="1277" spans="1:9">
@@ -36966,14 +37005,14 @@
       </c>
       <c r="E1277" s="48"/>
       <c r="F1277" s="48" t="s">
-        <v>1591</v>
+        <v>1604</v>
       </c>
       <c r="G1277" s="48"/>
       <c r="H1277" s="48">
         <v>3</v>
       </c>
       <c r="I1277" s="62" t="s">
-        <v>1600</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="1278" spans="1:9">
@@ -36991,14 +37030,14 @@
       </c>
       <c r="E1278" s="48"/>
       <c r="F1278" s="48" t="s">
-        <v>1591</v>
+        <v>1604</v>
       </c>
       <c r="G1278" s="48"/>
       <c r="H1278" s="48">
         <v>3</v>
       </c>
       <c r="I1278" s="62" t="s">
-        <v>1601</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1279" spans="1:9">
@@ -37016,14 +37055,14 @@
       </c>
       <c r="E1279" s="48"/>
       <c r="F1279" s="48" t="s">
-        <v>1591</v>
+        <v>1604</v>
       </c>
       <c r="G1279" s="48"/>
       <c r="H1279" s="48">
         <v>3</v>
       </c>
       <c r="I1279" s="62" t="s">
-        <v>1602</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="1280" spans="1:9">
@@ -37128,7 +37167,7 @@
       <c r="G1284" s="29"/>
       <c r="H1284" s="29"/>
       <c r="I1284" s="29" t="s">
-        <v>1526</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1285" spans="1:9">
@@ -37149,7 +37188,7 @@
       <c r="G1285" s="29"/>
       <c r="H1285" s="29"/>
       <c r="I1285" s="29" t="s">
-        <v>1527</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="1286" spans="1:9">
@@ -37170,7 +37209,7 @@
       <c r="G1286" s="29"/>
       <c r="H1286" s="29"/>
       <c r="I1286" s="29" t="s">
-        <v>1528</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="1287" spans="1:9">
@@ -37212,7 +37251,7 @@
       <c r="G1288" s="29"/>
       <c r="H1288" s="29"/>
       <c r="I1288" s="29" t="s">
-        <v>1529</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1289" spans="1:9">
@@ -37233,7 +37272,7 @@
       <c r="G1289" s="29"/>
       <c r="H1289" s="29"/>
       <c r="I1289" s="29" t="s">
-        <v>1530</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="1290" spans="1:9">
@@ -37254,7 +37293,7 @@
       <c r="G1290" s="29"/>
       <c r="H1290" s="29"/>
       <c r="I1290" s="29" t="s">
-        <v>1531</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="1291" spans="1:9">
@@ -37275,7 +37314,7 @@
       <c r="G1291" s="29"/>
       <c r="H1291" s="29"/>
       <c r="I1291" s="29" t="s">
-        <v>1532</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="1292" spans="1:9">
@@ -37296,7 +37335,7 @@
       <c r="G1292" s="29"/>
       <c r="H1292" s="29"/>
       <c r="I1292" s="29" t="s">
-        <v>1533</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="1293" spans="1:9">
@@ -37317,7 +37356,7 @@
       <c r="G1293" s="29"/>
       <c r="H1293" s="29"/>
       <c r="I1293" s="29" t="s">
-        <v>1534</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="1294" spans="1:9">
@@ -37338,7 +37377,7 @@
       <c r="G1294" s="29"/>
       <c r="H1294" s="29"/>
       <c r="I1294" s="29" t="s">
-        <v>1535</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="1295" spans="1:9">
@@ -37359,7 +37398,7 @@
       <c r="G1295" s="29"/>
       <c r="H1295" s="29"/>
       <c r="I1295" s="29" t="s">
-        <v>1603</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="1296" spans="1:9">
@@ -37464,7 +37503,7 @@
       <c r="G1300" s="49"/>
       <c r="H1300" s="49"/>
       <c r="I1300" s="49" t="s">
-        <v>1526</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1301" spans="1:9">
@@ -37485,7 +37524,7 @@
       <c r="G1301" s="49"/>
       <c r="H1301" s="49"/>
       <c r="I1301" s="49" t="s">
-        <v>1527</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="1302" spans="1:9">
@@ -37506,7 +37545,7 @@
       <c r="G1302" s="49"/>
       <c r="H1302" s="49"/>
       <c r="I1302" s="49" t="s">
-        <v>1528</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="1303" spans="1:9">
@@ -37548,7 +37587,7 @@
       <c r="G1304" s="49"/>
       <c r="H1304" s="49"/>
       <c r="I1304" s="49" t="s">
-        <v>1529</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1305" spans="1:9">
@@ -37569,7 +37608,7 @@
       <c r="G1305" s="49"/>
       <c r="H1305" s="49"/>
       <c r="I1305" s="49" t="s">
-        <v>1530</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="1306" spans="1:9">
@@ -37590,7 +37629,7 @@
       <c r="G1306" s="49"/>
       <c r="H1306" s="49"/>
       <c r="I1306" s="49" t="s">
-        <v>1531</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="1307" spans="1:9">
@@ -37611,7 +37650,7 @@
       <c r="G1307" s="49"/>
       <c r="H1307" s="49"/>
       <c r="I1307" s="49" t="s">
-        <v>1532</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="1308" spans="1:9">
@@ -37632,7 +37671,7 @@
       <c r="G1308" s="49"/>
       <c r="H1308" s="49"/>
       <c r="I1308" s="49" t="s">
-        <v>1533</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="1309" spans="1:9">
@@ -37653,7 +37692,7 @@
       <c r="G1309" s="49"/>
       <c r="H1309" s="49"/>
       <c r="I1309" s="49" t="s">
-        <v>1534</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="1310" spans="1:9">
@@ -37674,7 +37713,7 @@
       <c r="G1310" s="49"/>
       <c r="H1310" s="49"/>
       <c r="I1310" s="49" t="s">
-        <v>1535</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="1311" spans="1:9">
@@ -37695,7 +37734,7 @@
       <c r="G1311" s="49"/>
       <c r="H1311" s="49"/>
       <c r="I1311" s="49" t="s">
-        <v>1604</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="1312" spans="1:9">
@@ -37716,7 +37755,7 @@
       <c r="G1312" s="49"/>
       <c r="H1312" s="49"/>
       <c r="I1312" s="49" t="s">
-        <v>1605</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="1313" spans="1:9">
@@ -37737,7 +37776,7 @@
       <c r="G1313" s="49"/>
       <c r="H1313" s="49"/>
       <c r="I1313" s="49" t="s">
-        <v>1606</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="1314" spans="1:9">
@@ -37758,7 +37797,7 @@
       <c r="G1314" s="49"/>
       <c r="H1314" s="49"/>
       <c r="I1314" s="49" t="s">
-        <v>1607</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="1315" spans="1:9">
@@ -37779,7 +37818,7 @@
       <c r="G1315" s="49"/>
       <c r="H1315" s="49"/>
       <c r="I1315" s="49" t="s">
-        <v>1608</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="1316" spans="1:9">
@@ -37800,7 +37839,7 @@
       <c r="G1316" s="49"/>
       <c r="H1316" s="49"/>
       <c r="I1316" s="49" t="s">
-        <v>1609</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="1317" spans="1:9">
@@ -37821,7 +37860,7 @@
       <c r="G1317" s="49"/>
       <c r="H1317" s="49"/>
       <c r="I1317" s="49" t="s">
-        <v>1610</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="1318" spans="1:9">
@@ -37842,7 +37881,7 @@
       <c r="G1318" s="49"/>
       <c r="H1318" s="49"/>
       <c r="I1318" s="49" t="s">
-        <v>1611</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="1319" spans="1:9">
@@ -37863,7 +37902,7 @@
       <c r="G1319" s="49"/>
       <c r="H1319" s="49"/>
       <c r="I1319" s="49" t="s">
-        <v>1612</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="1320" spans="1:9">
@@ -37884,7 +37923,7 @@
       <c r="G1320" s="49"/>
       <c r="H1320" s="49"/>
       <c r="I1320" s="49" t="s">
-        <v>1613</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="1321" spans="1:9">
@@ -37905,7 +37944,7 @@
       <c r="G1321" s="49"/>
       <c r="H1321" s="49"/>
       <c r="I1321" s="49" t="s">
-        <v>1614</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="1322" spans="1:9">
@@ -37926,7 +37965,7 @@
       <c r="G1322" s="49"/>
       <c r="H1322" s="49"/>
       <c r="I1322" s="49" t="s">
-        <v>1615</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="1323" spans="1:9">
@@ -37947,7 +37986,7 @@
       <c r="G1323" s="49"/>
       <c r="H1323" s="49"/>
       <c r="I1323" s="49" t="s">
-        <v>1616</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="1324" spans="1:9">
@@ -37968,7 +38007,7 @@
       <c r="G1324" s="49"/>
       <c r="H1324" s="49"/>
       <c r="I1324" s="49" t="s">
-        <v>1617</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="1325" spans="1:9">
@@ -37989,7 +38028,7 @@
       <c r="G1325" s="49"/>
       <c r="H1325" s="49"/>
       <c r="I1325" s="49" t="s">
-        <v>1618</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="1326" spans="1:9">
@@ -38010,7 +38049,7 @@
       <c r="G1326" s="49"/>
       <c r="H1326" s="49"/>
       <c r="I1326" s="49" t="s">
-        <v>1619</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="1327" spans="1:9">
@@ -38031,7 +38070,7 @@
       <c r="G1327" s="49"/>
       <c r="H1327" s="49"/>
       <c r="I1327" s="49" t="s">
-        <v>1620</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="1328" spans="1:9">
@@ -38136,7 +38175,7 @@
       <c r="G1332" s="21"/>
       <c r="H1332" s="21"/>
       <c r="I1332" s="21" t="s">
-        <v>1429</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1333" spans="1:9">
@@ -38157,7 +38196,7 @@
       <c r="G1333" s="21"/>
       <c r="H1333" s="21"/>
       <c r="I1333" s="21" t="s">
-        <v>1430</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="1334" spans="1:9">
@@ -38178,7 +38217,7 @@
       <c r="G1334" s="21"/>
       <c r="H1334" s="21"/>
       <c r="I1334" s="21" t="s">
-        <v>1431</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="1335" spans="1:9">
@@ -38199,7 +38238,7 @@
       <c r="G1335" s="21"/>
       <c r="H1335" s="21"/>
       <c r="I1335" s="21" t="s">
-        <v>1432</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="1336" spans="1:9">
@@ -38472,7 +38511,7 @@
       <c r="G1348" s="64"/>
       <c r="H1348" s="64"/>
       <c r="I1348" s="64" t="s">
-        <v>1621</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="1349" spans="1:9">
@@ -38493,7 +38532,7 @@
       <c r="G1349" s="64"/>
       <c r="H1349" s="64"/>
       <c r="I1349" s="64" t="s">
-        <v>1622</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="1350" spans="1:9">
@@ -38514,7 +38553,7 @@
       <c r="G1350" s="64"/>
       <c r="H1350" s="64"/>
       <c r="I1350" s="64" t="s">
-        <v>1623</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="1351" spans="1:9">
@@ -38535,7 +38574,7 @@
       <c r="G1351" s="64"/>
       <c r="H1351" s="64"/>
       <c r="I1351" s="64" t="s">
-        <v>1624</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="1352" spans="1:9">
@@ -38556,7 +38595,7 @@
       <c r="G1352" s="64"/>
       <c r="H1352" s="64"/>
       <c r="I1352" s="64" t="s">
-        <v>1625</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="1353" spans="1:9">
